--- a/migration/list of immigrants.xlsx
+++ b/migration/list of immigrants.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
-  <workbookPr/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
+  <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\migration\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\082_083\ward1\migration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CA772FA-600D-4762-8C54-E5F47FEDB565}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20736" windowHeight="11040"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Reasons" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId2"/>
+    <sheet name="Reasons" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$I$112</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$L$113</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Sheet2!$A$1:$L$110</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="477" uniqueCount="247">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1151" uniqueCount="342">
   <si>
     <t>Vikash Karki</t>
   </si>
@@ -748,9 +749,6 @@
   </si>
   <si>
     <t>Lalitpur</t>
-  </si>
-  <si>
-    <t>Issue District</t>
   </si>
   <si>
     <r>
@@ -804,14 +802,302 @@
   <si>
     <t>Kathmandu, Shankharapur-9</t>
   </si>
+  <si>
+    <t>हालको ठेगाना</t>
+  </si>
+  <si>
+    <t>सूचक</t>
+  </si>
+  <si>
+    <t>Kageswori manohara-5</t>
+  </si>
+  <si>
+    <t>Kathmandu, Shankharapur-10</t>
+  </si>
+  <si>
+    <t>Sindhupalchowk, Jugal-7</t>
+  </si>
+  <si>
+    <t>अध्ययन/शिक्षा</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-7</t>
+  </si>
+  <si>
+    <t>Sankhuwasabha, Madi-1</t>
+  </si>
+  <si>
+    <t>Kathmandu, Shankharapur-8</t>
+  </si>
+  <si>
+    <t>Parsa, Thori-3</t>
+  </si>
+  <si>
+    <t>Kathmandu, Budanilkantha-8</t>
+  </si>
+  <si>
+    <t>Kathmandu, Shankharapur-6</t>
+  </si>
+  <si>
+    <t>Kathmandu, Ktm-7</t>
+  </si>
+  <si>
+    <t>Lalitpur, Godavari-3</t>
+  </si>
+  <si>
+    <t>Slukhumbu, Mahakulung-1</t>
+  </si>
+  <si>
+    <t>Bhojpur, Arun-2</t>
+  </si>
+  <si>
+    <t>Bardiya, Gulariya-6</t>
+  </si>
+  <si>
+    <t>Jhapa, Gauradah-7</t>
+  </si>
+  <si>
+    <t>Okhaldhunga, Molung-8</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kageswori manohara-6</t>
+  </si>
+  <si>
+    <t>Solukhumbu, Khumbu Pasanglamhu-1</t>
+  </si>
+  <si>
+    <t>Nawalparasi, Binaya Triveni-1</t>
+  </si>
+  <si>
+    <t>Udayapur, Katari-10</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-8</t>
+  </si>
+  <si>
+    <t>Lalitpur, Lalitpur-15</t>
+  </si>
+  <si>
+    <t>Lalitpur, Lalitpur-18</t>
+  </si>
+  <si>
+    <t>Makwanpur, Makwanpurgadhi-2</t>
+  </si>
+  <si>
+    <t>Dolakha, Melung-7</t>
+  </si>
+  <si>
+    <t>Sankhuwasabha, Madi-3</t>
+  </si>
+  <si>
+    <t>Okhaldhunga, Champadevi-7</t>
+  </si>
+  <si>
+    <t>Solukhumbu, Sotang-5</t>
+  </si>
+  <si>
+    <t>Udayapur, Katari-3</t>
+  </si>
+  <si>
+    <t>Makwanpur, Hetauda-9</t>
+  </si>
+  <si>
+    <t>Palpa, Rainadevi Chhahara-5</t>
+  </si>
+  <si>
+    <t>Kathmandu, Tokha-7</t>
+  </si>
+  <si>
+    <t>Solukhumbu, Thulung dudhkoshi-3</t>
+  </si>
+  <si>
+    <t>Mahottari, Bardibas-3</t>
+  </si>
+  <si>
+    <t>Ramechhap, Ramechap-3</t>
+  </si>
+  <si>
+    <t>Ramechhap, Ramechap-5</t>
+  </si>
+  <si>
+    <t>Rautahat, Chandrapur-8</t>
+  </si>
+  <si>
+    <t>Ramechhap, Khadadevi-7</t>
+  </si>
+  <si>
+    <t>Darchula, Malikarjun-2</t>
+  </si>
+  <si>
+    <t>Makwanpur, Makwanpurgadhi-6</t>
+  </si>
+  <si>
+    <t>Kathmandu, Gokarneshwor-5</t>
+  </si>
+  <si>
+    <t>Makwanpur, Indrasarowar-1</t>
+  </si>
+  <si>
+    <t>Darchula, Mahakali-8</t>
+  </si>
+  <si>
+    <t>Ramechap, Sunapati-2</t>
+  </si>
+  <si>
+    <t>Udayapur, Udayapurgadhi-4</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kageswori manohara-1</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-5</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-28</t>
+  </si>
+  <si>
+    <t>Khotang, Barahapokhari-1</t>
+  </si>
+  <si>
+    <t>Kathmandu, Shankharapur-7</t>
+  </si>
+  <si>
+    <t>Morang, Pathari Shanischare-1</t>
+  </si>
+  <si>
+    <t>Mahottari, Bardibas-5</t>
+  </si>
+  <si>
+    <t>Dhading, Dhunibesi-3</t>
+  </si>
+  <si>
+    <t>Dhading, Gajuri-1</t>
+  </si>
+  <si>
+    <t>Kavrepalanchok, Banepa-2</t>
+  </si>
+  <si>
+    <t>Sunsari, Duhabi-8</t>
+  </si>
+  <si>
+    <t>Dhading, Khaniyabas-4</t>
+  </si>
+  <si>
+    <t>Okhaldunga, Champadevi-8</t>
+  </si>
+  <si>
+    <t>Sunsari, Dharan-13</t>
+  </si>
+  <si>
+    <t>Sindhupalchowk, Lisankhu Pakhar-7</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-30</t>
+  </si>
+  <si>
+    <t>Bhaktapur, Changunarayan-5</t>
+  </si>
+  <si>
+    <t>Sindhuli, Phikkal-5</t>
+  </si>
+  <si>
+    <t>Tehrathum, Chhathar-2</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-15</t>
+  </si>
+  <si>
+    <t>Bhaktapur, Changunarayan-7</t>
+  </si>
+  <si>
+    <t>Morang, Kanepokhari-6</t>
+  </si>
+  <si>
+    <t>Jhapa, Gauradah-4</t>
+  </si>
+  <si>
+    <t>Okhaldhunga, Manebhanjyang-6</t>
+  </si>
+  <si>
+    <t>Syangja, Waling-6</t>
+  </si>
+  <si>
+    <t>Makwanpur, Hetauda-10</t>
+  </si>
+  <si>
+    <t>Gorkha, Sahid Lakhan-8</t>
+  </si>
+  <si>
+    <t>Kathmandu, Gokarneswor-4</t>
+  </si>
+  <si>
+    <t>Kathmandu, Budanilkantha-12</t>
+  </si>
+  <si>
+    <t>Khotang, Ainselukharka-7</t>
+  </si>
+  <si>
+    <t>Jhapa, Kamal-4</t>
+  </si>
+  <si>
+    <t>Achham, Sanfebagar-4</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-4</t>
+  </si>
+  <si>
+    <t>Kavrepalanchok, Mandandeupur-10</t>
+  </si>
+  <si>
+    <t>Makwanpur, Hetauda-6</t>
+  </si>
+  <si>
+    <t>Udayapur, Tiyuga-5</t>
+  </si>
+  <si>
+    <t>Banke, Kohalpur-10</t>
+  </si>
+  <si>
+    <t>Okhaldhunga, Champadevi-8</t>
+  </si>
+  <si>
+    <t>Sunsari, Inaruwa-1</t>
+  </si>
+  <si>
+    <t>Kathmandu, Budanilkantha-9</t>
+  </si>
+  <si>
+    <t>Kathmandu, Kathmandu-29</t>
+  </si>
+  <si>
+    <t>Okhaldhunga, Champadevi-9</t>
+  </si>
+  <si>
+    <t>Bhojpur, Hatuwagadhi-7</t>
+  </si>
+  <si>
+    <t>Kathmandu, Shankharapur-3</t>
+  </si>
+  <si>
+    <t>Sindhupalchowk, Melamchi-6</t>
+  </si>
+  <si>
+    <t>Bara, Jitpursimara-3</t>
+  </si>
+  <si>
+    <t>Ramechhap, DorambaSailung-4</t>
+  </si>
+  <si>
+    <t>Rautahat, FatuwaBijaypur-9</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="[$-4000439]0"/>
-    <numFmt numFmtId="167" formatCode="[$-4000000]yyyy\-mm\-dd"/>
+    <numFmt numFmtId="165" formatCode="[$-4000000]yyyy\-mm\-dd"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -844,7 +1130,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -876,11 +1162,59 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -892,7 +1226,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -900,12 +1234,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -915,6 +1243,37 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1195,23 +1554,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L112"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:M113"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="19.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="5.42578125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="5.5703125" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="5.109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25.6640625" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="22.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9" hidden="1" customWidth="1"/>
+    <col min="5" max="5" width="12.21875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="18" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="11.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.21875" customWidth="1"/>
+    <col min="11" max="11" width="25.21875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="7" t="s">
         <v>103</v>
       </c>
@@ -1230,22 +1590,25 @@
       <c r="F1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="G1" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-      <c r="J1" s="10" t="s">
+      <c r="H1" s="18"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="K1" s="11" t="s">
-        <v>237</v>
-      </c>
-      <c r="L1" s="14" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="K1" s="20" t="s">
+        <v>246</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>243</v>
+      </c>
+      <c r="M1" s="23" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="7"/>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1255,357 +1618,524 @@
       <c r="G2" s="8" t="s">
         <v>232</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="H2" s="9" t="s">
         <v>233</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="I2" s="9" t="s">
         <v>234</v>
       </c>
-      <c r="J2" s="10"/>
-      <c r="K2" s="11"/>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="6">
-        <v>1</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="J2" s="21"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="22"/>
+      <c r="M2" s="23"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="14"/>
+      <c r="G3" s="14"/>
+      <c r="H3" s="14"/>
+      <c r="I3" s="14"/>
+      <c r="J3" s="16"/>
+      <c r="K3" s="15"/>
+      <c r="L3" s="12"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C4" t="s">
         <v>231</v>
       </c>
-      <c r="D3" t="s">
-        <v>1</v>
-      </c>
-      <c r="E3" s="5">
+      <c r="D4" t="s">
+        <v>1</v>
+      </c>
+      <c r="E4" s="5">
         <v>66897</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3">
-        <v>4</v>
-      </c>
-      <c r="H3" s="3"/>
-      <c r="I3">
-        <v>0</v>
-      </c>
-      <c r="K3" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="6">
-        <v>2</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="F4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G4" s="3">
+        <v>4</v>
+      </c>
+      <c r="H4" s="3">
         <v>3</v>
       </c>
-      <c r="C4" t="s">
+      <c r="I4" s="3">
+        <v>1</v>
+      </c>
+      <c r="J4" t="s">
+        <v>242</v>
+      </c>
+      <c r="K4" t="s">
+        <v>339</v>
+      </c>
+      <c r="L4" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" t="s">
         <v>52</v>
       </c>
-      <c r="D4" t="s">
-        <v>4</v>
-      </c>
-      <c r="E4" s="5">
+      <c r="D5" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" s="5">
         <v>66890</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G4" s="2">
-        <v>4</v>
-      </c>
-      <c r="K4" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="6">
+      <c r="F5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2">
+        <v>2</v>
+      </c>
+      <c r="I5" s="2">
+        <v>2</v>
+      </c>
+      <c r="J5" t="s">
+        <v>242</v>
+      </c>
+      <c r="K5" t="s">
+        <v>332</v>
+      </c>
+      <c r="L5" t="s">
+        <v>245</v>
+      </c>
+      <c r="M5" t="str">
+        <f>C5</f>
+        <v>दिपक बहादुर भट्टराई</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
         <v>3</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B6" t="s">
         <v>5</v>
       </c>
-      <c r="C5" t="s">
+      <c r="C6" t="s">
         <v>53</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E6" s="5">
         <v>66876</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G5" s="2">
+      <c r="F6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="2">
         <v>5</v>
       </c>
-      <c r="K5" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
+      <c r="H6" s="2">
+        <v>3</v>
+      </c>
+      <c r="I6" s="2">
+        <v>2</v>
+      </c>
+      <c r="J6" t="s">
+        <v>242</v>
+      </c>
+      <c r="K6" t="s">
+        <v>338</v>
+      </c>
+      <c r="L6" t="s">
+        <v>245</v>
+      </c>
+      <c r="M6" t="str">
+        <f t="shared" ref="M6:M11" si="0">C6</f>
+        <v>कृष्ण प्रसाद प्याकुरेल</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
         <v>6</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C7" t="s">
         <v>54</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E7" s="5">
         <v>66828</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="2">
-        <v>2</v>
-      </c>
-      <c r="K6" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="6">
+      <c r="F7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>2</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>242</v>
+      </c>
+      <c r="K7" t="s">
+        <v>337</v>
+      </c>
+      <c r="L7" t="s">
+        <v>245</v>
+      </c>
+      <c r="M7" t="str">
+        <f t="shared" si="0"/>
+        <v>ठुलो कान्छो कामी</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
         <v>7</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C8" t="s">
         <v>55</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E8" s="5">
         <v>66809</v>
       </c>
-      <c r="F7" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G7" s="2">
-        <v>4</v>
-      </c>
-      <c r="K7" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="6">
+      <c r="F8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>4</v>
+      </c>
+      <c r="H8" s="2">
+        <v>3</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" t="s">
+        <v>238</v>
+      </c>
+      <c r="K8" t="s">
+        <v>336</v>
+      </c>
+      <c r="L8" t="s">
+        <v>245</v>
+      </c>
+      <c r="M8" t="str">
+        <f t="shared" si="0"/>
+        <v>मनिता रिसाल</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
         <v>6</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B9" t="s">
         <v>8</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E9" s="5">
         <v>66762</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G8" s="2">
-        <v>1</v>
-      </c>
-      <c r="K8" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="6">
+      <c r="F9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>1</v>
+      </c>
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" t="s">
+        <v>242</v>
+      </c>
+      <c r="K9" t="s">
+        <v>341</v>
+      </c>
+      <c r="L9" t="s">
+        <v>245</v>
+      </c>
+      <c r="M9" t="str">
+        <f t="shared" si="0"/>
+        <v>दुर्गा प्रसाद दाहाल</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
         <v>7</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E10" s="5">
         <v>66760</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G9" s="2">
-        <v>1</v>
-      </c>
-      <c r="K9" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="6">
+      <c r="F10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>1</v>
+      </c>
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" t="s">
+        <v>242</v>
+      </c>
+      <c r="K10" t="s">
+        <v>340</v>
+      </c>
+      <c r="L10" t="s">
+        <v>245</v>
+      </c>
+      <c r="M10" t="str">
+        <f t="shared" si="0"/>
+        <v>सन्दिप परियार</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
         <v>8</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B11" t="s">
         <v>10</v>
       </c>
-      <c r="C10" t="s">
+      <c r="C11" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E11" s="5">
         <v>66711</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="2">
-        <v>4</v>
-      </c>
-      <c r="K10" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="6">
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2">
+        <v>2</v>
+      </c>
+      <c r="I11" s="2">
+        <v>2</v>
+      </c>
+      <c r="J11" t="s">
+        <v>238</v>
+      </c>
+      <c r="K11" t="s">
+        <v>320</v>
+      </c>
+      <c r="L11" t="s">
+        <v>245</v>
+      </c>
+      <c r="M11" t="str">
+        <f t="shared" si="0"/>
+        <v>सिता अधिकारी</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
         <v>9</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B12" t="s">
         <v>11</v>
       </c>
-      <c r="C11" t="s">
+      <c r="C12" t="s">
         <v>59</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E12" s="5">
         <v>66689</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G11" s="2">
-        <v>4</v>
-      </c>
-      <c r="K11" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="6">
+      <c r="F12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G12" s="2">
+        <v>4</v>
+      </c>
+      <c r="H12" s="2">
+        <v>2</v>
+      </c>
+      <c r="I12" s="2">
+        <v>2</v>
+      </c>
+      <c r="J12" t="s">
+        <v>242</v>
+      </c>
+      <c r="K12" t="s">
+        <v>303</v>
+      </c>
+      <c r="L12" t="s">
+        <v>245</v>
+      </c>
+      <c r="M12" t="str">
+        <f t="shared" ref="M12" si="1">C12</f>
+        <v>पुण्य प्रसाद घिमिरे</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
         <v>10</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B13" t="s">
         <v>12</v>
       </c>
-      <c r="C12" t="s">
+      <c r="C13" t="s">
         <v>60</v>
       </c>
-      <c r="E12" s="5">
+      <c r="E13" s="5">
         <v>66687</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G12" s="2">
-        <v>4</v>
-      </c>
-      <c r="K12" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="6">
+      <c r="F13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G13" s="2">
+        <v>4</v>
+      </c>
+      <c r="J13" t="s">
+        <v>242</v>
+      </c>
+      <c r="M13" t="str">
+        <f t="shared" ref="M13" si="2">C13</f>
+        <v>राजेश कुमार विष्ट</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>13</v>
       </c>
-      <c r="C13" t="s">
+      <c r="C14" t="s">
         <v>61</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E14" s="5">
         <v>66674</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G13" s="2">
+      <c r="F14" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="2">
         <v>8</v>
       </c>
-      <c r="K13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="6">
+      <c r="H14" s="2">
+        <v>4</v>
+      </c>
+      <c r="I14" s="2">
+        <v>4</v>
+      </c>
+      <c r="J14" t="s">
+        <v>242</v>
+      </c>
+      <c r="K14" t="s">
+        <v>272</v>
+      </c>
+      <c r="L14" t="s">
+        <v>245</v>
+      </c>
+      <c r="M14" t="str">
+        <f t="shared" ref="M14:M15" si="3">C14</f>
+        <v>इन्दिरा परियार</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
         <v>12</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B15" t="s">
         <v>14</v>
       </c>
-      <c r="C14" t="s">
+      <c r="C15" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E15" s="5">
         <v>66668</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="2">
-        <v>1</v>
-      </c>
-      <c r="K14" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="6">
+      <c r="F15" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G15" s="2">
+        <v>1</v>
+      </c>
+      <c r="H15" s="2">
+        <v>1</v>
+      </c>
+      <c r="J15" t="s">
+        <v>242</v>
+      </c>
+      <c r="K15" t="s">
+        <v>319</v>
+      </c>
+      <c r="L15" t="s">
+        <v>245</v>
+      </c>
+      <c r="M15" t="str">
+        <f t="shared" si="3"/>
+        <v>श्याम खत्री</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B16" t="s">
         <v>15</v>
       </c>
-      <c r="C15" t="s">
+      <c r="C16" t="s">
         <v>63</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E16" s="5">
         <v>66618</v>
       </c>
-      <c r="F15" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G15" s="2">
-        <v>4</v>
-      </c>
-      <c r="K15" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="6">
+      <c r="F16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2">
+        <v>4</v>
+      </c>
+      <c r="H16" s="2">
+        <v>3</v>
+      </c>
+      <c r="I16" s="2">
+        <v>1</v>
+      </c>
+      <c r="J16" t="s">
+        <v>242</v>
+      </c>
+      <c r="K16" t="s">
+        <v>327</v>
+      </c>
+      <c r="L16" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
         <v>14</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B17" t="s">
         <v>16</v>
       </c>
-      <c r="C16" t="s">
+      <c r="C17" t="s">
         <v>64</v>
-      </c>
-      <c r="E16" s="5">
-        <v>66605</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G16" s="2">
-        <v>3</v>
-      </c>
-      <c r="K16" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A17" s="6">
-        <v>15</v>
-      </c>
-      <c r="B17" t="s">
-        <v>17</v>
-      </c>
-      <c r="C17" t="s">
-        <v>65</v>
       </c>
       <c r="E17" s="5">
         <v>66605</v>
@@ -1614,550 +2144,826 @@
         <v>2</v>
       </c>
       <c r="G17" s="2">
-        <v>4</v>
+        <v>3</v>
+      </c>
+      <c r="H17" s="2">
+        <v>2</v>
+      </c>
+      <c r="I17" s="2">
+        <v>1</v>
+      </c>
+      <c r="J17" t="s">
+        <v>242</v>
       </c>
       <c r="K17" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>312</v>
+      </c>
+      <c r="L17" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" s="6">
+        <v>15</v>
+      </c>
+      <c r="B18" t="s">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="5">
+        <v>66605</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>4</v>
+      </c>
+      <c r="H18" s="2">
+        <v>2</v>
+      </c>
+      <c r="I18" s="2">
+        <v>2</v>
+      </c>
+      <c r="J18" t="s">
+        <v>242</v>
+      </c>
+      <c r="K18" t="s">
+        <v>285</v>
+      </c>
+      <c r="L18" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
         <v>16</v>
       </c>
-      <c r="B18" t="s">
+      <c r="B19" t="s">
         <v>19</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>66</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E19" s="5">
         <v>66594</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="2">
+      <c r="F19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
         <v>3</v>
       </c>
-      <c r="K18" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A19" s="6">
+      <c r="H19" s="2">
+        <v>1</v>
+      </c>
+      <c r="I19" s="2">
+        <v>2</v>
+      </c>
+      <c r="J19" t="s">
+        <v>242</v>
+      </c>
+      <c r="K19" t="s">
+        <v>275</v>
+      </c>
+      <c r="L19" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
         <v>17</v>
       </c>
-      <c r="B19" t="s">
+      <c r="B20" t="s">
         <v>18</v>
       </c>
-      <c r="C19" t="s">
+      <c r="C20" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E20" s="5">
         <v>66589</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G19" s="2">
+      <c r="F20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2">
         <v>6</v>
       </c>
-      <c r="K19" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A20" s="6">
+      <c r="H20" s="2">
+        <v>2</v>
+      </c>
+      <c r="I20" s="2">
+        <v>4</v>
+      </c>
+      <c r="J20" t="s">
+        <v>242</v>
+      </c>
+      <c r="K20" t="s">
+        <v>333</v>
+      </c>
+      <c r="L20" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
         <v>18</v>
       </c>
-      <c r="B20" t="s">
+      <c r="B21" t="s">
         <v>20</v>
       </c>
-      <c r="C20" t="s">
+      <c r="C21" t="s">
         <v>68</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E21" s="5">
         <v>66587</v>
       </c>
-      <c r="F20" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G20" s="2">
-        <v>4</v>
-      </c>
-      <c r="K20" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A21" s="6">
+      <c r="F21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2">
+        <v>4</v>
+      </c>
+      <c r="H21" s="2">
+        <v>2</v>
+      </c>
+      <c r="I21" s="2">
+        <v>2</v>
+      </c>
+      <c r="J21" t="s">
+        <v>242</v>
+      </c>
+      <c r="K21" t="s">
+        <v>252</v>
+      </c>
+      <c r="L21" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
         <v>19</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>21</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>69</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E22" s="5">
         <v>66573</v>
       </c>
-      <c r="F21" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G21" s="2">
-        <v>4</v>
-      </c>
-      <c r="K21" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A22" s="6">
+      <c r="F22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>4</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2</v>
+      </c>
+      <c r="I22" s="2">
+        <v>2</v>
+      </c>
+      <c r="J22" t="s">
+        <v>242</v>
+      </c>
+      <c r="K22" t="s">
+        <v>256</v>
+      </c>
+      <c r="L22" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
         <v>20</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>22</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>70</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E23" s="5">
         <v>66559</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G22" s="2">
-        <v>1</v>
-      </c>
-      <c r="K22" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A23" s="6">
-        <v>21</v>
-      </c>
-      <c r="B23" t="s">
-        <v>23</v>
-      </c>
-      <c r="C23" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="5">
-        <v>66423</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>100</v>
       </c>
       <c r="G23" s="2">
-        <v>5</v>
+        <v>1</v>
+      </c>
+      <c r="I23" s="2">
+        <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>240</v>
       </c>
       <c r="K23" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="L23" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" s="6">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E24" s="5">
-        <v>66408</v>
+        <v>66423</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="G24" s="2">
         <v>5</v>
       </c>
+      <c r="H24" s="2">
+        <v>2</v>
+      </c>
+      <c r="I24" s="2">
+        <v>3</v>
+      </c>
+      <c r="J24" t="s">
+        <v>242</v>
+      </c>
       <c r="K24" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="L24" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" s="6">
+        <v>22</v>
+      </c>
+      <c r="B25" t="s">
+        <v>24</v>
+      </c>
+      <c r="C25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E25" s="5">
+        <v>66408</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G25" s="2">
+        <v>5</v>
+      </c>
+      <c r="H25" s="2">
+        <v>2</v>
+      </c>
+      <c r="I25" s="2">
+        <v>3</v>
+      </c>
+      <c r="J25" t="s">
+        <v>242</v>
+      </c>
+      <c r="K25" t="s">
+        <v>276</v>
+      </c>
+      <c r="L25" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
         <v>23</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>25</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>73</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E26" s="5">
         <v>66392</v>
       </c>
-      <c r="F25" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G25" s="2">
-        <v>4</v>
-      </c>
-      <c r="K25" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A26" s="6">
+      <c r="F26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2</v>
+      </c>
+      <c r="I26" s="2">
+        <v>2</v>
+      </c>
+      <c r="J26" t="s">
+        <v>238</v>
+      </c>
+      <c r="K26" t="s">
+        <v>253</v>
+      </c>
+      <c r="L26" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
         <v>24</v>
       </c>
-      <c r="B26" t="s">
+      <c r="B27" t="s">
         <v>26</v>
       </c>
-      <c r="C26" t="s">
+      <c r="C27" t="s">
         <v>74</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E27" s="5">
         <v>66262</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="2">
+      <c r="F27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2">
         <v>8</v>
       </c>
-      <c r="K26" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A27" s="6">
+      <c r="H27" s="2">
+        <v>5</v>
+      </c>
+      <c r="I27" s="2">
+        <v>3</v>
+      </c>
+      <c r="J27" t="s">
+        <v>242</v>
+      </c>
+      <c r="K27" t="s">
+        <v>330</v>
+      </c>
+      <c r="L27" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
         <v>25</v>
       </c>
-      <c r="B27" t="s">
+      <c r="B28" t="s">
         <v>3</v>
       </c>
-      <c r="C27" t="s">
+      <c r="C28" t="s">
         <v>52</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E28" s="5">
         <v>66242</v>
       </c>
-      <c r="F27" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G27" s="2">
+      <c r="G28" s="2">
         <v>3</v>
       </c>
-      <c r="K27" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A28" s="6">
+      <c r="H28" s="2">
+        <v>1</v>
+      </c>
+      <c r="I28" s="2">
+        <v>2</v>
+      </c>
+      <c r="J28" t="s">
+        <v>238</v>
+      </c>
+      <c r="K28" t="s">
+        <v>245</v>
+      </c>
+      <c r="L28" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
         <v>26</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B29" t="s">
         <v>27</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C29" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E29" s="5">
         <v>66240</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G28" s="2">
+      <c r="F29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2">
         <v>5</v>
       </c>
-      <c r="K28" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A29" s="6">
+      <c r="H29" s="2">
+        <v>3</v>
+      </c>
+      <c r="I29" s="2">
+        <v>2</v>
+      </c>
+      <c r="J29" t="s">
+        <v>242</v>
+      </c>
+      <c r="K29" t="s">
+        <v>329</v>
+      </c>
+      <c r="L29" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
         <v>27</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B30" t="s">
         <v>28</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C30" t="s">
         <v>76</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E30" s="5">
         <v>66231</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G29" s="2">
-        <v>1</v>
-      </c>
-      <c r="K29" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A30" s="6">
+      <c r="F30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>1</v>
+      </c>
+      <c r="J30" t="s">
+        <v>242</v>
+      </c>
+      <c r="K30" t="s">
+        <v>314</v>
+      </c>
+      <c r="L30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
         <v>28</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B31" t="s">
         <v>29</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C31" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E31" s="5">
         <v>66195</v>
       </c>
-      <c r="F30" s="2" t="s">
+      <c r="F31" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G30" s="2">
-        <v>1</v>
-      </c>
-      <c r="K30" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A31" s="6">
+      <c r="G31" s="2">
+        <v>1</v>
+      </c>
+      <c r="H31" s="2">
+        <v>1</v>
+      </c>
+      <c r="J31" t="s">
+        <v>242</v>
+      </c>
+      <c r="K31" t="s">
+        <v>245</v>
+      </c>
+      <c r="L31" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
         <v>29</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B32" t="s">
         <v>30</v>
       </c>
-      <c r="C31" t="s">
+      <c r="C32" t="s">
         <v>78</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E32" s="5">
         <v>66188</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G31" s="2">
+      <c r="F32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2">
         <v>7</v>
       </c>
-      <c r="K31" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" s="6">
+      <c r="H32" s="2">
+        <v>3</v>
+      </c>
+      <c r="I32" s="2">
+        <v>4</v>
+      </c>
+      <c r="J32" t="s">
+        <v>242</v>
+      </c>
+      <c r="K32" t="s">
+        <v>254</v>
+      </c>
+      <c r="L32" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
         <v>30</v>
       </c>
-      <c r="B32" t="s">
+      <c r="B33" t="s">
         <v>31</v>
       </c>
-      <c r="C32" t="s">
+      <c r="C33" t="s">
         <v>79</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E33" s="5">
         <v>66183</v>
       </c>
-      <c r="F32" s="2" t="s">
+      <c r="F33" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G32" s="2">
-        <v>1</v>
-      </c>
-      <c r="K32" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A33" s="6">
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
+        <v>1</v>
+      </c>
+      <c r="J33" t="s">
+        <v>242</v>
+      </c>
+      <c r="K33" t="s">
+        <v>245</v>
+      </c>
+      <c r="L33" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
         <v>31</v>
       </c>
-      <c r="B33" t="s">
+      <c r="B34" t="s">
         <v>32</v>
       </c>
-      <c r="C33" t="s">
+      <c r="C34" t="s">
         <v>80</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E34" s="5">
         <v>66182</v>
       </c>
-      <c r="F33" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G33" s="2">
+      <c r="F34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2">
         <v>9</v>
       </c>
-      <c r="K33" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A34" s="6">
+      <c r="H34" s="2">
+        <v>5</v>
+      </c>
+      <c r="I34" s="2">
+        <v>4</v>
+      </c>
+      <c r="J34" t="s">
+        <v>241</v>
+      </c>
+      <c r="K34" t="s">
+        <v>264</v>
+      </c>
+      <c r="L34" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
         <v>32</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B35" t="s">
         <v>33</v>
       </c>
-      <c r="C34" t="s">
+      <c r="C35" t="s">
         <v>81</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E35" s="5">
         <v>66169</v>
       </c>
-      <c r="F34" s="2" t="s">
+      <c r="F35" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G34" s="2">
+      <c r="G35" s="2">
         <v>6</v>
       </c>
-      <c r="K34" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A35" s="6">
+      <c r="H35" s="2">
+        <v>3</v>
+      </c>
+      <c r="I35" s="2">
+        <v>3</v>
+      </c>
+      <c r="J35" t="s">
+        <v>242</v>
+      </c>
+      <c r="K35" t="s">
+        <v>245</v>
+      </c>
+      <c r="L35" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
         <v>33</v>
       </c>
-      <c r="B35" t="s">
+      <c r="B36" t="s">
         <v>34</v>
       </c>
-      <c r="C35" t="s">
+      <c r="C36" t="s">
         <v>82</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E36" s="5">
         <v>66138</v>
       </c>
-      <c r="F35" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G35" s="2">
-        <v>4</v>
-      </c>
-      <c r="K35" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A36" s="6">
+      <c r="F36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2">
+        <v>4</v>
+      </c>
+      <c r="H36" s="2">
+        <v>2</v>
+      </c>
+      <c r="I36" s="2">
+        <v>2</v>
+      </c>
+      <c r="J36" t="s">
+        <v>242</v>
+      </c>
+      <c r="K36" t="s">
+        <v>266</v>
+      </c>
+      <c r="L36" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A37" s="6">
         <v>34</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>35</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>83</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E37" s="5">
         <v>66132</v>
       </c>
-      <c r="F36" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G36" s="2">
-        <v>4</v>
-      </c>
-      <c r="K36" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A37" s="6">
+      <c r="F37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2">
+        <v>4</v>
+      </c>
+      <c r="H37" s="2">
+        <v>2</v>
+      </c>
+      <c r="I37" s="2">
+        <v>2</v>
+      </c>
+      <c r="J37" t="s">
+        <v>242</v>
+      </c>
+      <c r="K37" t="s">
+        <v>287</v>
+      </c>
+      <c r="L37" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A38" s="6">
         <v>35</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B38" t="s">
         <v>36</v>
       </c>
-      <c r="C37" t="s">
+      <c r="C38" t="s">
         <v>84</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E38" s="5">
         <v>66127</v>
       </c>
-      <c r="F37" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G37" s="2">
-        <v>4</v>
-      </c>
-      <c r="K37" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" s="6">
+      <c r="F38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2">
+        <v>4</v>
+      </c>
+      <c r="H38" s="2">
+        <v>2</v>
+      </c>
+      <c r="I38" s="2">
+        <v>2</v>
+      </c>
+      <c r="J38" t="s">
+        <v>242</v>
+      </c>
+      <c r="K38" t="s">
+        <v>275</v>
+      </c>
+      <c r="L38" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A39" s="6">
         <v>36</v>
       </c>
-      <c r="B38" t="s">
+      <c r="B39" t="s">
         <v>37</v>
       </c>
-      <c r="C38" t="s">
+      <c r="C39" t="s">
         <v>85</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E39" s="5">
         <v>66121</v>
       </c>
-      <c r="F38" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="2">
-        <v>4</v>
-      </c>
-      <c r="K38" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A39" s="6">
+      <c r="F39" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G39" s="2">
+        <v>4</v>
+      </c>
+      <c r="H39" s="2">
+        <v>1</v>
+      </c>
+      <c r="I39" s="2">
+        <v>3</v>
+      </c>
+      <c r="J39" t="s">
+        <v>242</v>
+      </c>
+      <c r="K39" t="s">
+        <v>290</v>
+      </c>
+      <c r="L39" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A40" s="6">
         <v>37</v>
       </c>
-      <c r="B39" t="s">
+      <c r="B40" t="s">
         <v>38</v>
       </c>
-      <c r="C39" t="s">
+      <c r="C40" t="s">
         <v>86</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E40" s="5">
         <v>66058</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F40" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G39" s="2">
-        <v>4</v>
-      </c>
-      <c r="K39" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A40" s="6">
+      <c r="G40" s="2">
+        <v>4</v>
+      </c>
+      <c r="H40" s="2">
+        <v>3</v>
+      </c>
+      <c r="I40" s="2">
+        <v>1</v>
+      </c>
+      <c r="J40" t="s">
+        <v>242</v>
+      </c>
+      <c r="K40" t="s">
+        <v>245</v>
+      </c>
+      <c r="L40" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A41" s="6">
         <v>38</v>
       </c>
-      <c r="B40" t="s">
+      <c r="B41" t="s">
         <v>39</v>
       </c>
-      <c r="C40" t="s">
+      <c r="C41" t="s">
         <v>87</v>
-      </c>
-      <c r="E40" s="5">
-        <v>66029</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G40" s="2">
-        <v>3</v>
-      </c>
-      <c r="K40" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A41" s="6">
-        <v>39</v>
-      </c>
-      <c r="B41" t="s">
-        <v>40</v>
-      </c>
-      <c r="C41" t="s">
-        <v>88</v>
       </c>
       <c r="E41" s="5">
         <v>66029</v>
@@ -2166,402 +2972,582 @@
         <v>2</v>
       </c>
       <c r="G41" s="2">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="H41" s="2">
+        <v>1</v>
+      </c>
+      <c r="I41" s="2">
+        <v>2</v>
+      </c>
+      <c r="J41" t="s">
+        <v>242</v>
       </c>
       <c r="K41" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>255</v>
+      </c>
+      <c r="L41" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
+        <v>39</v>
+      </c>
+      <c r="B42" t="s">
         <v>40</v>
       </c>
-      <c r="B42" t="s">
+      <c r="C42" t="s">
+        <v>88</v>
+      </c>
+      <c r="E42" s="5">
+        <v>66029</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2">
+        <v>2</v>
+      </c>
+      <c r="I42" s="2">
+        <v>2</v>
+      </c>
+      <c r="J42" t="s">
+        <v>242</v>
+      </c>
+      <c r="K42" t="s">
+        <v>302</v>
+      </c>
+      <c r="L42" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A43" s="6">
+        <v>40</v>
+      </c>
+      <c r="B43" t="s">
         <v>41</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>89</v>
       </c>
-      <c r="E42" s="5">
+      <c r="E43" s="5">
         <v>66021</v>
       </c>
-      <c r="F42" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="2">
-        <v>4</v>
-      </c>
-      <c r="K42" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A43" s="6">
+      <c r="F43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>4</v>
+      </c>
+      <c r="H43" s="2">
+        <v>2</v>
+      </c>
+      <c r="I43" s="2">
+        <v>2</v>
+      </c>
+      <c r="J43" t="s">
+        <v>242</v>
+      </c>
+      <c r="K43" t="s">
+        <v>267</v>
+      </c>
+      <c r="L43" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A44" s="6">
         <v>41</v>
       </c>
-      <c r="B43" t="s">
+      <c r="B44" t="s">
         <v>42</v>
       </c>
-      <c r="C43" t="s">
+      <c r="C44" t="s">
         <v>90</v>
       </c>
-      <c r="E43" s="5">
+      <c r="E44" s="5">
         <v>65997</v>
       </c>
-      <c r="F43" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="G43" s="2">
-        <v>3</v>
-      </c>
-      <c r="K43" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A44" s="6">
-        <v>42</v>
-      </c>
-      <c r="B44" t="s">
-        <v>43</v>
-      </c>
-      <c r="C44" t="s">
-        <v>91</v>
-      </c>
-      <c r="E44" s="5">
-        <v>65972</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="G44" s="2">
         <v>3</v>
       </c>
+      <c r="H44" s="2">
+        <v>1</v>
+      </c>
+      <c r="I44" s="2">
+        <v>2</v>
+      </c>
+      <c r="J44" t="s">
+        <v>242</v>
+      </c>
       <c r="K44" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="L44" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A45" s="6">
+        <v>42</v>
+      </c>
+      <c r="B45" t="s">
         <v>43</v>
       </c>
-      <c r="B45" t="s">
+      <c r="C45" t="s">
+        <v>91</v>
+      </c>
+      <c r="E45" s="5">
+        <v>65972</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2">
+        <v>3</v>
+      </c>
+      <c r="H45" s="2">
+        <v>2</v>
+      </c>
+      <c r="I45" s="2">
+        <v>1</v>
+      </c>
+      <c r="J45" t="s">
+        <v>242</v>
+      </c>
+      <c r="K45" t="s">
+        <v>322</v>
+      </c>
+      <c r="L45" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="46" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A46" s="6">
+        <v>43</v>
+      </c>
+      <c r="B46" t="s">
         <v>44</v>
       </c>
-      <c r="C45" t="s">
+      <c r="C46" t="s">
         <v>92</v>
       </c>
-      <c r="D45" t="s">
+      <c r="D46" t="s">
         <v>115</v>
       </c>
-      <c r="E45" s="5">
+      <c r="E46" s="5">
         <v>65949</v>
       </c>
-      <c r="F45" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G45" s="2">
-        <v>4</v>
-      </c>
-      <c r="K45" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A46" s="6">
+      <c r="F46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2">
+        <v>4</v>
+      </c>
+      <c r="H46" s="2">
+        <v>2</v>
+      </c>
+      <c r="I46" s="2">
+        <v>2</v>
+      </c>
+      <c r="J46" t="s">
+        <v>242</v>
+      </c>
+      <c r="K46" t="s">
+        <v>313</v>
+      </c>
+      <c r="L46" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="47" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A47" s="6">
         <v>44</v>
       </c>
-      <c r="B46" t="s">
+      <c r="B47" t="s">
         <v>45</v>
       </c>
-      <c r="C46" t="s">
+      <c r="C47" t="s">
         <v>93</v>
       </c>
-      <c r="D46" t="s">
+      <c r="D47" t="s">
         <v>114</v>
       </c>
-      <c r="E46" s="5">
+      <c r="E47" s="5">
         <v>65877</v>
       </c>
-      <c r="F46" s="2" t="s">
+      <c r="F47" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G46" s="2">
-        <v>4</v>
-      </c>
-      <c r="K46" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A47" s="6">
+      <c r="G47" s="2">
+        <v>4</v>
+      </c>
+      <c r="H47" s="2">
+        <v>3</v>
+      </c>
+      <c r="I47" s="2">
+        <v>1</v>
+      </c>
+      <c r="J47" t="s">
+        <v>242</v>
+      </c>
+      <c r="K47" t="s">
+        <v>249</v>
+      </c>
+      <c r="L47" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="48" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
         <v>45</v>
       </c>
-      <c r="B47" t="s">
+      <c r="B48" t="s">
         <v>46</v>
       </c>
-      <c r="C47" t="s">
+      <c r="C48" t="s">
         <v>94</v>
       </c>
-      <c r="D47" t="s">
+      <c r="D48" t="s">
         <v>113</v>
       </c>
-      <c r="E47" s="5">
+      <c r="E48" s="5">
         <v>65858</v>
       </c>
-      <c r="F47" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G47" s="2">
+      <c r="F48" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G48" s="2">
         <v>5</v>
       </c>
-      <c r="K47" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A48" s="6">
+      <c r="H48" s="2">
+        <v>2</v>
+      </c>
+      <c r="I48" s="2">
+        <v>3</v>
+      </c>
+      <c r="J48" t="s">
+        <v>242</v>
+      </c>
+      <c r="K48" t="s">
+        <v>308</v>
+      </c>
+      <c r="L48" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
         <v>46</v>
       </c>
-      <c r="B48" t="s">
+      <c r="B49" t="s">
         <v>47</v>
       </c>
-      <c r="C48" t="s">
+      <c r="C49" t="s">
         <v>95</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>112</v>
       </c>
-      <c r="E48" s="5">
+      <c r="E49" s="5">
         <v>65840</v>
       </c>
-      <c r="F48" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G48" s="2">
-        <v>4</v>
-      </c>
-      <c r="K48" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A49" s="6">
+      <c r="F49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2">
+        <v>4</v>
+      </c>
+      <c r="H49" s="2">
+        <v>3</v>
+      </c>
+      <c r="I49" s="2">
+        <v>1</v>
+      </c>
+      <c r="J49" t="s">
+        <v>242</v>
+      </c>
+      <c r="K49" t="s">
+        <v>268</v>
+      </c>
+      <c r="L49" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
         <v>47</v>
       </c>
-      <c r="B49" t="s">
+      <c r="B50" t="s">
         <v>48</v>
       </c>
-      <c r="C49" t="s">
+      <c r="C50" t="s">
         <v>96</v>
       </c>
-      <c r="D49" t="s">
+      <c r="D50" t="s">
         <v>111</v>
       </c>
-      <c r="E49" s="5">
+      <c r="E50" s="5">
         <v>65826</v>
       </c>
-      <c r="F49" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G49" s="2">
+      <c r="G50" s="2">
         <v>3</v>
       </c>
-      <c r="K49" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A50" s="6">
+      <c r="H50" s="2">
+        <v>2</v>
+      </c>
+      <c r="I50" s="2">
+        <v>1</v>
+      </c>
+      <c r="J50" t="s">
+        <v>242</v>
+      </c>
+      <c r="K50" t="s">
+        <v>245</v>
+      </c>
+      <c r="L50" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="6">
         <v>48</v>
       </c>
-      <c r="B50" t="s">
+      <c r="B51" t="s">
         <v>49</v>
       </c>
-      <c r="C50" t="s">
+      <c r="C51" t="s">
         <v>97</v>
       </c>
-      <c r="D50" t="s">
+      <c r="D51" t="s">
         <v>110</v>
       </c>
-      <c r="E50" s="5">
+      <c r="E51" s="5">
         <v>65825</v>
       </c>
-      <c r="F50" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="2">
-        <v>4</v>
-      </c>
-      <c r="K50" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A51" s="6">
+      <c r="F51" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="2">
+        <v>4</v>
+      </c>
+      <c r="H51" s="2">
+        <v>3</v>
+      </c>
+      <c r="I51" s="2">
+        <v>1</v>
+      </c>
+      <c r="J51" t="s">
+        <v>242</v>
+      </c>
+      <c r="K51" t="s">
+        <v>317</v>
+      </c>
+      <c r="L51" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A52" s="6">
         <v>49</v>
       </c>
-      <c r="B51" t="s">
+      <c r="B52" t="s">
         <v>50</v>
       </c>
-      <c r="C51" t="s">
+      <c r="C52" t="s">
         <v>98</v>
       </c>
-      <c r="D51" t="s">
+      <c r="D52" t="s">
         <v>109</v>
       </c>
-      <c r="E51" s="5">
+      <c r="E52" s="5">
         <v>65800</v>
       </c>
-      <c r="F51" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G51" s="2">
+      <c r="G52" s="2">
         <v>3</v>
       </c>
-      <c r="H51" s="2">
-        <v>2</v>
-      </c>
-      <c r="I51">
-        <v>1</v>
-      </c>
-      <c r="K51" t="s">
-        <v>243</v>
-      </c>
-      <c r="L51" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A52" s="6">
+      <c r="H52" s="2">
+        <v>2</v>
+      </c>
+      <c r="I52" s="2">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
+        <v>242</v>
+      </c>
+      <c r="K52" t="s">
+        <v>245</v>
+      </c>
+      <c r="L52" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A53" s="6">
         <v>50</v>
       </c>
-      <c r="B52" t="s">
+      <c r="B53" t="s">
         <v>51</v>
       </c>
-      <c r="C52" t="s">
+      <c r="C53" t="s">
         <v>99</v>
       </c>
-      <c r="D52" t="s">
+      <c r="D53" t="s">
         <v>108</v>
       </c>
-      <c r="E52" s="5">
+      <c r="E53" s="5">
         <v>65762</v>
       </c>
-      <c r="F52" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G52" s="2">
-        <v>2</v>
-      </c>
-      <c r="K52" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A53" s="6">
+      <c r="F53" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="2">
+        <v>2</v>
+      </c>
+      <c r="H53" s="2">
+        <v>1</v>
+      </c>
+      <c r="I53" s="2">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
+        <v>242</v>
+      </c>
+      <c r="K53" t="s">
+        <v>321</v>
+      </c>
+      <c r="L53" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A54" s="6">
         <v>51</v>
       </c>
-      <c r="B53" t="s">
+      <c r="B54" t="s">
         <v>116</v>
       </c>
-      <c r="C53" t="s">
+      <c r="C54" t="s">
         <v>165</v>
       </c>
-      <c r="D53" t="s">
+      <c r="D54" t="s">
         <v>215</v>
       </c>
-      <c r="E53" s="5">
+      <c r="E54" s="5">
         <v>65736</v>
       </c>
-      <c r="F53" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G53" s="2">
+      <c r="F54" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="2">
         <v>3</v>
       </c>
-      <c r="K53" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A54" s="6">
+      <c r="H54" s="2">
+        <v>2</v>
+      </c>
+      <c r="I54" s="2">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
+        <v>242</v>
+      </c>
+      <c r="K54" t="s">
+        <v>305</v>
+      </c>
+      <c r="L54" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A55" s="6">
         <v>52</v>
       </c>
-      <c r="B54" t="s">
+      <c r="B55" t="s">
         <v>117</v>
       </c>
-      <c r="C54" s="1" t="s">
+      <c r="C55" s="1" t="s">
         <v>166</v>
       </c>
-      <c r="E54" s="5">
+      <c r="E55" s="5">
         <v>65695</v>
       </c>
-      <c r="F54" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G54" s="2">
-        <v>4</v>
-      </c>
-      <c r="K54" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A55" s="6">
+      <c r="F55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2">
+        <v>4</v>
+      </c>
+      <c r="H55" s="2">
+        <v>2</v>
+      </c>
+      <c r="I55" s="2">
+        <v>2</v>
+      </c>
+      <c r="J55" t="s">
+        <v>242</v>
+      </c>
+      <c r="K55" t="s">
+        <v>309</v>
+      </c>
+      <c r="L55" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A56" s="6">
         <v>53</v>
       </c>
-      <c r="B55" t="s">
+      <c r="B56" t="s">
         <v>118</v>
       </c>
-      <c r="C55" t="s">
+      <c r="C56" t="s">
         <v>167</v>
       </c>
-      <c r="E55" s="5">
+      <c r="E56" s="5">
         <v>65644</v>
       </c>
-      <c r="F55" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G55" s="2">
+      <c r="F56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2">
         <v>3</v>
       </c>
-      <c r="K55" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A56" s="6">
+      <c r="H56" s="2">
+        <v>1</v>
+      </c>
+      <c r="I56" s="2">
+        <v>2</v>
+      </c>
+      <c r="J56" t="s">
+        <v>242</v>
+      </c>
+      <c r="K56" t="s">
+        <v>310</v>
+      </c>
+      <c r="L56" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="6">
         <v>54</v>
       </c>
-      <c r="B56" t="s">
+      <c r="B57" t="s">
         <v>119</v>
       </c>
-      <c r="C56" t="s">
+      <c r="C57" t="s">
         <v>168</v>
-      </c>
-      <c r="E56" s="5">
-        <v>65631</v>
-      </c>
-      <c r="F56" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G56" s="2">
-        <v>4</v>
-      </c>
-      <c r="K56" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A57" s="6">
-        <v>55</v>
-      </c>
-      <c r="B57" t="s">
-        <v>120</v>
-      </c>
-      <c r="C57" t="s">
-        <v>169</v>
       </c>
       <c r="E57" s="5">
         <v>65631</v>
@@ -2570,70 +3556,106 @@
         <v>2</v>
       </c>
       <c r="G57" s="2">
+        <v>4</v>
+      </c>
+      <c r="H57" s="2">
+        <v>3</v>
+      </c>
+      <c r="I57" s="2">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
+        <v>242</v>
+      </c>
+      <c r="K57" t="s">
+        <v>324</v>
+      </c>
+      <c r="L57" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A58" s="6">
+        <v>55</v>
+      </c>
+      <c r="B58" t="s">
+        <v>120</v>
+      </c>
+      <c r="C58" t="s">
+        <v>169</v>
+      </c>
+      <c r="E58" s="5">
+        <v>65631</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="2">
         <v>7</v>
       </c>
-      <c r="K57" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A58" s="6">
+      <c r="H58" s="2">
+        <v>5</v>
+      </c>
+      <c r="I58" s="2">
+        <v>2</v>
+      </c>
+      <c r="J58" t="s">
+        <v>242</v>
+      </c>
+      <c r="K58" t="s">
+        <v>326</v>
+      </c>
+      <c r="L58" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A59" s="6">
         <v>56</v>
       </c>
-      <c r="B58" t="s">
+      <c r="B59" t="s">
         <v>121</v>
       </c>
-      <c r="C58" t="s">
+      <c r="C59" t="s">
         <v>170</v>
       </c>
-      <c r="E58" s="5">
+      <c r="E59" s="5">
         <v>65582</v>
       </c>
-      <c r="F58" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G58" s="2">
+      <c r="F59" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="2">
         <v>3</v>
       </c>
-      <c r="K58" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A59" s="6">
+      <c r="H59" s="2">
+        <v>1</v>
+      </c>
+      <c r="I59" s="2">
+        <v>2</v>
+      </c>
+      <c r="J59" t="s">
+        <v>242</v>
+      </c>
+      <c r="K59" t="s">
+        <v>293</v>
+      </c>
+      <c r="L59" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="6">
         <v>57</v>
       </c>
-      <c r="B59" t="s">
+      <c r="B60" t="s">
         <v>122</v>
       </c>
-      <c r="C59" t="s">
+      <c r="C60" t="s">
         <v>171</v>
       </c>
-      <c r="E59" s="5">
+      <c r="E60" s="5">
         <v>65533</v>
-      </c>
-      <c r="F59" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G59" s="2">
-        <v>5</v>
-      </c>
-      <c r="K59" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A60" s="6">
-        <v>58</v>
-      </c>
-      <c r="B60" t="s">
-        <v>123</v>
-      </c>
-      <c r="C60" t="s">
-        <v>172</v>
-      </c>
-      <c r="E60" s="5">
-        <v>65527</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>2</v>
@@ -2641,357 +3663,522 @@
       <c r="G60" s="2">
         <v>5</v>
       </c>
+      <c r="H60" s="2">
+        <v>2</v>
+      </c>
+      <c r="I60" s="2">
+        <v>3</v>
+      </c>
+      <c r="J60" t="s">
+        <v>242</v>
+      </c>
       <c r="K60" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.25">
+        <v>254</v>
+      </c>
+      <c r="L60" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A61" s="6">
+        <v>58</v>
+      </c>
+      <c r="B61" t="s">
+        <v>123</v>
+      </c>
+      <c r="C61" t="s">
+        <v>172</v>
+      </c>
+      <c r="E61" s="5">
+        <v>65527</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2">
+        <v>5</v>
+      </c>
+      <c r="H61" s="2">
+        <v>3</v>
+      </c>
+      <c r="I61" s="2">
+        <v>2</v>
+      </c>
+      <c r="J61" t="s">
+        <v>242</v>
+      </c>
+      <c r="K61" t="s">
+        <v>254</v>
+      </c>
+      <c r="L61" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A62" s="6">
         <v>59</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>124</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>173</v>
       </c>
-      <c r="E61" s="5">
+      <c r="E62" s="5">
         <v>65512</v>
       </c>
-      <c r="F61" s="2" t="s">
+      <c r="F62" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G61" s="2">
-        <v>2</v>
-      </c>
-      <c r="K61" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A62" s="6">
+      <c r="G62" s="2">
+        <v>2</v>
+      </c>
+      <c r="H62" s="2">
+        <v>1</v>
+      </c>
+      <c r="I62" s="2">
+        <v>1</v>
+      </c>
+      <c r="J62" t="s">
+        <v>242</v>
+      </c>
+      <c r="K62" t="s">
+        <v>245</v>
+      </c>
+      <c r="L62" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A63" s="6">
         <v>60</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>125</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>174</v>
       </c>
-      <c r="E62" s="5">
+      <c r="E63" s="5">
         <v>65490</v>
       </c>
-      <c r="F62" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G62" s="2">
-        <v>4</v>
-      </c>
-      <c r="K62" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A63" s="6">
+      <c r="F63" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2">
+        <v>4</v>
+      </c>
+      <c r="H63" s="2">
+        <v>3</v>
+      </c>
+      <c r="I63" s="2">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>242</v>
+      </c>
+      <c r="K63" t="s">
+        <v>296</v>
+      </c>
+      <c r="L63" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="64" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A64" s="6">
         <v>61</v>
       </c>
-      <c r="B63" t="s">
+      <c r="B64" t="s">
         <v>126</v>
       </c>
-      <c r="C63" t="s">
+      <c r="C64" t="s">
         <v>175</v>
       </c>
-      <c r="E63" s="5">
+      <c r="E64" s="5">
         <v>65479</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G63" s="2">
-        <v>4</v>
-      </c>
-      <c r="K63" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A64" s="6">
+      <c r="F64" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G64" s="2">
+        <v>4</v>
+      </c>
+      <c r="H64" s="2">
+        <v>3</v>
+      </c>
+      <c r="I64" s="2">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
+        <v>242</v>
+      </c>
+      <c r="K64" t="s">
+        <v>294</v>
+      </c>
+      <c r="L64" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A65" s="6">
         <v>62</v>
       </c>
-      <c r="B64" t="s">
+      <c r="B65" t="s">
         <v>127</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>176</v>
       </c>
-      <c r="E64" s="5">
+      <c r="E65" s="5">
         <v>65478</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G64" s="2">
-        <v>4</v>
-      </c>
-      <c r="K64" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A65" s="6">
+      <c r="F65" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2">
+        <v>4</v>
+      </c>
+      <c r="H65" s="2">
+        <v>3</v>
+      </c>
+      <c r="I65" s="2">
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
+        <v>242</v>
+      </c>
+      <c r="K65" t="s">
+        <v>294</v>
+      </c>
+      <c r="L65" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A66" s="6">
         <v>63</v>
       </c>
-      <c r="B65" t="s">
+      <c r="B66" t="s">
         <v>128</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>177</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E66" s="5">
         <v>65466</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G65" s="2">
-        <v>4</v>
-      </c>
-      <c r="K65" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A66" s="6">
+      <c r="F66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="2">
+        <v>4</v>
+      </c>
+      <c r="H66" s="2">
+        <v>1</v>
+      </c>
+      <c r="I66" s="2">
+        <v>3</v>
+      </c>
+      <c r="J66" t="s">
+        <v>242</v>
+      </c>
+      <c r="K66" t="s">
+        <v>311</v>
+      </c>
+      <c r="L66" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A67" s="6">
         <v>64</v>
       </c>
-      <c r="B66" t="s">
+      <c r="B67" t="s">
         <v>129</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>178</v>
       </c>
-      <c r="E66" s="5">
+      <c r="E67" s="5">
         <v>65447</v>
       </c>
-      <c r="F66" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G66" s="2">
+      <c r="F67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" s="2">
         <v>5</v>
       </c>
-      <c r="K66" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A67" s="6">
+      <c r="H67" s="2">
+        <v>3</v>
+      </c>
+      <c r="I67" s="2">
+        <v>2</v>
+      </c>
+      <c r="J67" t="s">
+        <v>239</v>
+      </c>
+      <c r="K67" t="s">
+        <v>300</v>
+      </c>
+      <c r="L67" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A68" s="6">
         <v>65</v>
       </c>
-      <c r="B67" t="s">
+      <c r="B68" t="s">
         <v>130</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>179</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E68" s="5">
         <v>65440</v>
       </c>
-      <c r="F67" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G67" s="2">
+      <c r="F68" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2">
         <v>6</v>
       </c>
-      <c r="K67" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="6">
+      <c r="H68" s="2">
+        <v>2</v>
+      </c>
+      <c r="I68" s="2">
+        <v>4</v>
+      </c>
+      <c r="J68" t="s">
+        <v>242</v>
+      </c>
+      <c r="K68" t="s">
+        <v>252</v>
+      </c>
+      <c r="L68" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A69" s="6">
         <v>66</v>
       </c>
-      <c r="B68" t="s">
+      <c r="B69" t="s">
         <v>131</v>
       </c>
-      <c r="C68" t="s">
+      <c r="C69" t="s">
         <v>180</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E69" s="5">
         <v>65369</v>
       </c>
-      <c r="F68" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G68" s="2">
-        <v>4</v>
-      </c>
-      <c r="K68" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="6">
+      <c r="F69" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G69" s="2">
+        <v>4</v>
+      </c>
+      <c r="H69" s="2">
+        <v>2</v>
+      </c>
+      <c r="I69" s="2">
+        <v>1</v>
+      </c>
+      <c r="J69" t="s">
+        <v>242</v>
+      </c>
+      <c r="K69" t="s">
+        <v>292</v>
+      </c>
+      <c r="L69" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A70" s="6">
         <v>67</v>
       </c>
-      <c r="B69" t="s">
+      <c r="B70" t="s">
         <v>132</v>
       </c>
-      <c r="C69" t="s">
+      <c r="C70" t="s">
         <v>181</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E70" s="5">
         <v>65366</v>
       </c>
-      <c r="F69" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G69" s="2">
-        <v>4</v>
-      </c>
-      <c r="H69" s="2">
-        <f>G69-I69</f>
-        <v>2</v>
-      </c>
-      <c r="I69">
-        <v>2</v>
-      </c>
-      <c r="J69" t="s">
+      <c r="F70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="2">
+        <v>4</v>
+      </c>
+      <c r="H70" s="2">
+        <f>G70-I70</f>
+        <v>2</v>
+      </c>
+      <c r="I70" s="2">
+        <v>2</v>
+      </c>
+      <c r="J70" t="s">
+        <v>242</v>
+      </c>
+      <c r="K70" t="s">
         <v>235</v>
       </c>
-      <c r="K69" t="s">
-        <v>243</v>
-      </c>
-      <c r="L69" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="6">
+      <c r="L70" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A71" s="6">
         <v>68</v>
       </c>
-      <c r="B70" t="s">
+      <c r="B71" t="s">
         <v>133</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" t="s">
         <v>182</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E71" s="5">
         <v>65365</v>
       </c>
-      <c r="F70" s="2" t="s">
+      <c r="F71" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G70" s="2">
-        <v>2</v>
-      </c>
-      <c r="K70" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="6">
+      <c r="G71" s="2">
+        <v>2</v>
+      </c>
+      <c r="H71" s="2">
+        <v>1</v>
+      </c>
+      <c r="J71" t="s">
+        <v>242</v>
+      </c>
+      <c r="K71" t="s">
+        <v>245</v>
+      </c>
+      <c r="L71" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A72" s="6">
         <v>69</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B72" t="s">
         <v>134</v>
       </c>
-      <c r="C71" t="s">
+      <c r="C72" t="s">
         <v>183</v>
-      </c>
-      <c r="E71" s="5">
-        <v>65356</v>
-      </c>
-      <c r="F71" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G71" s="2">
-        <v>6</v>
-      </c>
-      <c r="K71" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="6">
-        <v>70</v>
-      </c>
-      <c r="B72" t="s">
-        <v>135</v>
-      </c>
-      <c r="C72" s="1" t="s">
-        <v>184</v>
       </c>
       <c r="E72" s="5">
         <v>65356</v>
       </c>
       <c r="F72" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="2">
+        <v>6</v>
+      </c>
+      <c r="H72" s="2">
+        <v>2</v>
+      </c>
+      <c r="I72" s="2">
+        <v>3</v>
+      </c>
+      <c r="J72" t="s">
+        <v>242</v>
+      </c>
+      <c r="K72" t="s">
+        <v>283</v>
+      </c>
+      <c r="L72" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A73" s="6">
+        <v>70</v>
+      </c>
+      <c r="B73" t="s">
+        <v>135</v>
+      </c>
+      <c r="C73" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E73" s="5">
+        <v>65356</v>
+      </c>
+      <c r="F73" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G72" s="2">
+      <c r="G73" s="2">
         <v>5</v>
       </c>
-      <c r="K72" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A73" s="6">
+      <c r="H73" s="2">
+        <v>3</v>
+      </c>
+      <c r="I73" s="2">
+        <v>1</v>
+      </c>
+      <c r="J73" t="s">
+        <v>242</v>
+      </c>
+      <c r="K73" t="s">
+        <v>245</v>
+      </c>
+      <c r="L73" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A74" s="6">
         <v>71</v>
       </c>
-      <c r="B73" t="s">
+      <c r="B74" t="s">
         <v>136</v>
       </c>
-      <c r="C73" t="s">
+      <c r="C74" t="s">
         <v>185</v>
       </c>
-      <c r="E73" s="5">
+      <c r="E74" s="5">
         <v>65350</v>
       </c>
-      <c r="F73" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G73" s="2">
-        <v>3</v>
-      </c>
-      <c r="K73" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A74" s="6">
+      <c r="F74" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G74" s="2">
+        <v>2</v>
+      </c>
+      <c r="H74" s="2">
+        <v>1</v>
+      </c>
+      <c r="I74" s="2">
+        <v>1</v>
+      </c>
+      <c r="J74" t="s">
+        <v>242</v>
+      </c>
+      <c r="K74" t="s">
+        <v>254</v>
+      </c>
+      <c r="L74" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A75" s="6">
         <v>72</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B75" t="s">
         <v>137</v>
       </c>
-      <c r="C74" t="s">
+      <c r="C75" t="s">
         <v>186</v>
       </c>
-      <c r="E74" s="5">
+      <c r="E75" s="5">
         <v>65328</v>
-      </c>
-      <c r="F74" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G74" s="2">
-        <v>5</v>
-      </c>
-      <c r="K74" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="6">
-        <v>73</v>
-      </c>
-      <c r="B75" t="s">
-        <v>138</v>
-      </c>
-      <c r="C75" t="s">
-        <v>187</v>
-      </c>
-      <c r="E75" s="5">
-        <v>65306</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>2</v>
@@ -2999,160 +4186,241 @@
       <c r="G75" s="2">
         <v>5</v>
       </c>
+      <c r="H75" s="2">
+        <v>3</v>
+      </c>
+      <c r="I75" s="2">
+        <v>1</v>
+      </c>
+      <c r="J75" t="s">
+        <v>242</v>
+      </c>
       <c r="K75" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+        <v>270</v>
+      </c>
+      <c r="L75" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A76" s="6">
+        <v>73</v>
+      </c>
+      <c r="B76" t="s">
+        <v>138</v>
+      </c>
+      <c r="C76" t="s">
+        <v>187</v>
+      </c>
+      <c r="E76" s="5">
+        <v>65306</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="2">
+        <v>5</v>
+      </c>
+      <c r="H76" s="2">
+        <v>2</v>
+      </c>
+      <c r="I76" s="2">
+        <v>2</v>
+      </c>
+      <c r="J76" t="s">
+        <v>242</v>
+      </c>
+      <c r="K76" t="s">
+        <v>263</v>
+      </c>
+      <c r="L76" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A77" s="6">
         <v>74</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>139</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C77" t="s">
         <v>188</v>
       </c>
-      <c r="E76" s="5">
+      <c r="E77" s="5">
         <v>65304</v>
       </c>
-      <c r="F76" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G76" s="2">
-        <v>2</v>
-      </c>
-      <c r="K76" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A77" s="6">
+      <c r="F77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G77" s="2">
+        <v>2</v>
+      </c>
+      <c r="H77" s="2">
+        <v>1</v>
+      </c>
+      <c r="J77" t="s">
+        <v>242</v>
+      </c>
+      <c r="K77" t="s">
+        <v>334</v>
+      </c>
+      <c r="L77" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A78" s="6">
         <v>75</v>
       </c>
-      <c r="B77" t="s">
+      <c r="B78" t="s">
         <v>140</v>
       </c>
-      <c r="C77" t="s">
+      <c r="C78" t="s">
         <v>189</v>
       </c>
-      <c r="E77" s="5">
+      <c r="E78" s="5">
         <v>65302</v>
       </c>
-      <c r="F77" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G77" s="2">
+      <c r="F78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2">
         <v>3</v>
       </c>
-      <c r="K77" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="6">
+      <c r="H78" s="2">
+        <v>2</v>
+      </c>
+      <c r="I78" s="2">
+        <v>1</v>
+      </c>
+      <c r="J78" t="s">
+        <v>241</v>
+      </c>
+      <c r="K78" t="s">
+        <v>273</v>
+      </c>
+      <c r="L78" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="6">
         <v>76</v>
       </c>
-      <c r="B78" t="s">
+      <c r="B79" t="s">
         <v>141</v>
       </c>
-      <c r="C78" s="1" t="s">
+      <c r="C79" s="1" t="s">
         <v>190</v>
       </c>
-      <c r="E78" s="5">
+      <c r="E79" s="5">
         <v>65291</v>
       </c>
-      <c r="F78" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G78" s="2">
+      <c r="F79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="2">
         <v>5</v>
       </c>
-      <c r="K78" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="6">
+      <c r="H79" s="2">
+        <v>1</v>
+      </c>
+      <c r="I79" s="2">
+        <v>3</v>
+      </c>
+      <c r="J79" t="s">
+        <v>242</v>
+      </c>
+      <c r="K79" t="s">
+        <v>316</v>
+      </c>
+      <c r="L79" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="6">
         <v>77</v>
       </c>
-      <c r="B79" t="s">
+      <c r="B80" t="s">
         <v>142</v>
       </c>
-      <c r="C79" t="s">
+      <c r="C80" t="s">
         <v>191</v>
       </c>
-      <c r="E79" s="5">
+      <c r="E80" s="5">
         <v>65290</v>
       </c>
-      <c r="F79" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G79" s="2">
-        <v>4</v>
-      </c>
-      <c r="K79" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A80" s="6">
+      <c r="F80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="2">
+        <v>4</v>
+      </c>
+      <c r="H80" s="2">
+        <v>2</v>
+      </c>
+      <c r="I80" s="2">
+        <v>1</v>
+      </c>
+      <c r="J80" t="s">
+        <v>242</v>
+      </c>
+      <c r="K80" t="s">
+        <v>299</v>
+      </c>
+      <c r="L80" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="81" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A81" s="6">
         <v>78</v>
       </c>
-      <c r="B80" t="s">
+      <c r="B81" t="s">
         <v>143</v>
       </c>
-      <c r="C80" t="s">
+      <c r="C81" t="s">
         <v>192</v>
       </c>
-      <c r="E80" s="5">
+      <c r="E81" s="5">
         <v>65287</v>
       </c>
-      <c r="F80" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G80" s="2">
-        <v>4</v>
-      </c>
-      <c r="K80" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A81" s="6">
+      <c r="F81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G81" s="2">
+        <v>4</v>
+      </c>
+      <c r="H81" s="2">
+        <v>2</v>
+      </c>
+      <c r="I81" s="2">
+        <v>1</v>
+      </c>
+      <c r="J81" t="s">
+        <v>242</v>
+      </c>
+      <c r="K81" t="s">
+        <v>291</v>
+      </c>
+      <c r="L81" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="82" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A82" s="6">
         <v>79</v>
       </c>
-      <c r="B81" t="s">
+      <c r="B82" t="s">
         <v>145</v>
       </c>
-      <c r="C81" t="s">
+      <c r="C82" t="s">
         <v>193</v>
       </c>
-      <c r="E81" s="5">
+      <c r="E82" s="5">
         <v>65265</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="G81" s="2">
-        <v>5</v>
-      </c>
-      <c r="K81" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A82" s="6">
-        <v>80</v>
-      </c>
-      <c r="B82" t="s">
-        <v>144</v>
-      </c>
-      <c r="C82" t="s">
-        <v>194</v>
-      </c>
-      <c r="E82" s="5">
-        <v>65173</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>100</v>
@@ -3160,157 +4428,241 @@
       <c r="G82" s="2">
         <v>5</v>
       </c>
+      <c r="H82" s="2">
+        <v>2</v>
+      </c>
+      <c r="I82" s="2">
+        <v>2</v>
+      </c>
+      <c r="J82" t="s">
+        <v>242</v>
+      </c>
       <c r="K82" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="83" spans="1:11" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="L82" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="83" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A83" s="6">
+        <v>80</v>
+      </c>
+      <c r="B83" t="s">
+        <v>144</v>
+      </c>
+      <c r="C83" t="s">
+        <v>194</v>
+      </c>
+      <c r="E83" s="5">
+        <v>65173</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G83" s="2">
+        <v>4</v>
+      </c>
+      <c r="H83" s="2">
+        <v>2</v>
+      </c>
+      <c r="I83" s="2">
+        <v>2</v>
+      </c>
+      <c r="J83" t="s">
+        <v>241</v>
+      </c>
+      <c r="K83" t="s">
+        <v>245</v>
+      </c>
+      <c r="L83" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="84" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A84" s="6">
         <v>81</v>
       </c>
-      <c r="B83" t="s">
+      <c r="B84" t="s">
         <v>146</v>
       </c>
-      <c r="C83" t="s">
+      <c r="C84" t="s">
         <v>195</v>
       </c>
-      <c r="E83" s="5">
+      <c r="E84" s="5">
         <v>65146</v>
       </c>
-      <c r="F83" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G83" s="2">
+      <c r="F84" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="2">
         <v>5</v>
       </c>
-      <c r="K83" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="84" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A84" s="6">
+      <c r="H84" s="2">
+        <v>2</v>
+      </c>
+      <c r="I84" s="2">
+        <v>2</v>
+      </c>
+      <c r="J84" t="s">
+        <v>242</v>
+      </c>
+      <c r="K84" t="s">
+        <v>277</v>
+      </c>
+      <c r="L84" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="85" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A85" s="6">
         <v>82</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>147</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C85" t="s">
         <v>196</v>
       </c>
-      <c r="E84" s="5">
+      <c r="E85" s="5">
         <v>64977</v>
       </c>
-      <c r="F84" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G84" s="2">
-        <v>2</v>
-      </c>
-      <c r="K84" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="85" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A85" s="6">
+      <c r="F85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="2">
+        <v>2</v>
+      </c>
+      <c r="H85" s="2">
+        <v>1</v>
+      </c>
+      <c r="I85" s="2">
+        <v>1</v>
+      </c>
+      <c r="J85" t="s">
+        <v>240</v>
+      </c>
+      <c r="K85" t="s">
+        <v>315</v>
+      </c>
+      <c r="L85" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="86" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A86" s="6">
         <v>83</v>
       </c>
-      <c r="B85" t="s">
+      <c r="B86" t="s">
         <v>148</v>
       </c>
-      <c r="C85" t="s">
+      <c r="C86" t="s">
         <v>197</v>
       </c>
-      <c r="E85" s="5">
+      <c r="E86" s="5">
         <v>64935</v>
       </c>
-      <c r="F85" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G85" s="2">
-        <v>4</v>
-      </c>
-      <c r="K85" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="86" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A86" s="6">
+      <c r="G86" s="2">
+        <v>4</v>
+      </c>
+      <c r="H86" s="2">
+        <v>2</v>
+      </c>
+      <c r="I86" s="2">
+        <v>2</v>
+      </c>
+      <c r="J86" t="s">
+        <v>242</v>
+      </c>
+      <c r="K86" t="s">
+        <v>245</v>
+      </c>
+      <c r="L86" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="87" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A87" s="6">
         <v>84</v>
       </c>
-      <c r="B86" t="s">
+      <c r="B87" t="s">
         <v>149</v>
       </c>
-      <c r="C86" t="s">
+      <c r="C87" t="s">
         <v>198</v>
       </c>
-      <c r="E86" s="5">
+      <c r="E87" s="5">
         <v>64887</v>
       </c>
-      <c r="F86" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G86" s="2">
-        <v>4</v>
-      </c>
-      <c r="K86" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A87" s="6">
+      <c r="F87" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G87" s="2">
+        <v>4</v>
+      </c>
+      <c r="H87" s="2">
+        <v>2</v>
+      </c>
+      <c r="I87" s="2">
+        <v>2</v>
+      </c>
+      <c r="J87" t="s">
+        <v>242</v>
+      </c>
+      <c r="K87" t="s">
+        <v>286</v>
+      </c>
+      <c r="L87" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="88" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A88" s="6">
         <v>85</v>
       </c>
-      <c r="B87" t="s">
+      <c r="B88" t="s">
         <v>150</v>
       </c>
-      <c r="C87" t="s">
+      <c r="C88" t="s">
         <v>199</v>
       </c>
-      <c r="E87" s="5">
+      <c r="E88" s="5">
         <v>64813</v>
       </c>
-      <c r="F87" s="2" t="s">
+      <c r="F88" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G87" s="2">
-        <v>4</v>
-      </c>
-      <c r="K87" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="88" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A88" s="6">
+      <c r="G88" s="2">
+        <v>4</v>
+      </c>
+      <c r="H88" s="2">
+        <v>2</v>
+      </c>
+      <c r="I88" s="2">
+        <v>2</v>
+      </c>
+      <c r="J88" t="s">
+        <v>242</v>
+      </c>
+      <c r="K88" t="s">
+        <v>245</v>
+      </c>
+      <c r="L88" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="89" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A89" s="6">
         <v>86</v>
       </c>
-      <c r="B88" t="s">
+      <c r="B89" t="s">
         <v>45</v>
       </c>
-      <c r="C88" t="s">
+      <c r="C89" t="s">
         <v>93</v>
-      </c>
-      <c r="E88" s="5">
-        <v>64618</v>
-      </c>
-      <c r="F88" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G88" s="2">
-        <v>4</v>
-      </c>
-      <c r="K88" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="89" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A89" s="6">
-        <v>87</v>
-      </c>
-      <c r="B89" t="s">
-        <v>151</v>
-      </c>
-      <c r="C89" t="s">
-        <v>200</v>
       </c>
       <c r="E89" s="5">
         <v>64618</v>
@@ -3319,571 +4671,895 @@
         <v>2</v>
       </c>
       <c r="G89" s="2">
-        <v>1</v>
+        <v>4</v>
+      </c>
+      <c r="H89" s="2">
+        <v>3</v>
+      </c>
+      <c r="I89" s="2">
+        <v>1</v>
+      </c>
+      <c r="J89" t="s">
+        <v>241</v>
       </c>
       <c r="K89" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11" x14ac:dyDescent="0.25">
+        <v>250</v>
+      </c>
+      <c r="L89" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="90" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A90" s="6">
+        <v>87</v>
+      </c>
+      <c r="B90" t="s">
+        <v>151</v>
+      </c>
+      <c r="C90" t="s">
+        <v>200</v>
+      </c>
+      <c r="E90" s="5">
+        <v>64618</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G90" s="2">
+        <v>1</v>
+      </c>
+      <c r="I90" s="2">
+        <v>1</v>
+      </c>
+      <c r="J90" t="s">
+        <v>242</v>
+      </c>
+      <c r="K90" t="s">
+        <v>301</v>
+      </c>
+      <c r="L90" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="91" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A91" s="6">
         <v>88</v>
       </c>
-      <c r="B90" t="s">
+      <c r="B91" t="s">
         <v>152</v>
       </c>
-      <c r="C90" t="s">
+      <c r="C91" t="s">
         <v>201</v>
       </c>
-      <c r="E90" s="5">
+      <c r="E91" s="5">
         <v>64571</v>
       </c>
-      <c r="F90" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G90" s="2">
+      <c r="F91" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G91" s="2">
         <v>5</v>
       </c>
-      <c r="K90" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="91" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A91" s="6">
+      <c r="H91" s="2">
+        <v>3</v>
+      </c>
+      <c r="I91" s="2">
+        <v>2</v>
+      </c>
+      <c r="J91" t="s">
+        <v>242</v>
+      </c>
+      <c r="K91" t="s">
+        <v>281</v>
+      </c>
+      <c r="L91" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="92" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A92" s="6">
         <v>89</v>
       </c>
-      <c r="B91" t="s">
+      <c r="B92" t="s">
         <v>153</v>
       </c>
-      <c r="C91" t="s">
+      <c r="C92" t="s">
         <v>202</v>
       </c>
-      <c r="E91" s="5">
+      <c r="E92" s="5">
         <v>64532</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="F92" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="G91" s="2">
-        <v>4</v>
-      </c>
-      <c r="K91" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="92" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A92" s="6">
+      <c r="G92" s="2">
+        <v>4</v>
+      </c>
+      <c r="H92" s="2">
+        <v>2</v>
+      </c>
+      <c r="I92" s="2">
+        <v>2</v>
+      </c>
+      <c r="J92" t="s">
+        <v>242</v>
+      </c>
+      <c r="K92" t="s">
+        <v>245</v>
+      </c>
+      <c r="L92" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A93" s="6">
         <v>90</v>
       </c>
-      <c r="B92" t="s">
+      <c r="B93" t="s">
         <v>154</v>
       </c>
-      <c r="C92" t="s">
+      <c r="C93" t="s">
         <v>203</v>
       </c>
-      <c r="E92" s="5">
+      <c r="E93" s="5">
         <v>64446</v>
       </c>
-      <c r="F92" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G92" s="2">
-        <v>4</v>
-      </c>
-      <c r="K92" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="93" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A93" s="6">
+      <c r="F93" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G93" s="2">
+        <v>4</v>
+      </c>
+      <c r="H93" s="2">
+        <v>1</v>
+      </c>
+      <c r="I93" s="2">
+        <v>3</v>
+      </c>
+      <c r="J93" t="s">
+        <v>242</v>
+      </c>
+      <c r="K93" t="s">
+        <v>294</v>
+      </c>
+      <c r="L93" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="94" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A94" s="6">
         <v>91</v>
       </c>
-      <c r="B93" t="s">
+      <c r="B94" t="s">
         <v>155</v>
       </c>
-      <c r="C93" t="s">
+      <c r="C94" t="s">
         <v>204</v>
       </c>
-      <c r="E93" s="5">
+      <c r="E94" s="5">
         <v>64444</v>
       </c>
-      <c r="F93" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G93" s="2">
-        <v>4</v>
-      </c>
-      <c r="K93" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="94" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A94" s="6">
+      <c r="F94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G94" s="2">
+        <v>4</v>
+      </c>
+      <c r="H94" s="2">
+        <v>3</v>
+      </c>
+      <c r="I94" s="2">
+        <v>1</v>
+      </c>
+      <c r="J94" t="s">
+        <v>242</v>
+      </c>
+      <c r="K94" t="s">
+        <v>262</v>
+      </c>
+      <c r="L94" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A95" s="6">
         <v>92</v>
       </c>
-      <c r="B94" t="s">
+      <c r="B95" t="s">
         <v>156</v>
       </c>
-      <c r="C94" t="s">
+      <c r="C95" t="s">
         <v>205</v>
       </c>
-      <c r="E94" s="5">
+      <c r="E95" s="5">
         <v>64424</v>
       </c>
-      <c r="F94" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G94" s="2">
-        <v>4</v>
-      </c>
-      <c r="K94" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="95" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A95" s="6">
+      <c r="F95" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G95" s="2">
+        <v>4</v>
+      </c>
+      <c r="H95" s="2">
+        <v>2</v>
+      </c>
+      <c r="I95" s="2">
+        <v>2</v>
+      </c>
+      <c r="J95" t="s">
+        <v>242</v>
+      </c>
+      <c r="K95" t="s">
+        <v>265</v>
+      </c>
+      <c r="L95" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="96" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A96" s="6">
         <v>93</v>
       </c>
-      <c r="B95" t="s">
+      <c r="B96" t="s">
         <v>157</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C96" t="s">
         <v>206</v>
       </c>
-      <c r="E95" s="5">
+      <c r="E96" s="5">
         <v>64395</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G95" s="2">
-        <v>2</v>
-      </c>
-      <c r="K95" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A96" s="6">
+      <c r="F96" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G96" s="2">
+        <v>2</v>
+      </c>
+      <c r="H96" s="2">
+        <v>1</v>
+      </c>
+      <c r="I96" s="2">
+        <v>1</v>
+      </c>
+      <c r="J96" t="s">
+        <v>242</v>
+      </c>
+      <c r="K96" t="s">
+        <v>335</v>
+      </c>
+      <c r="L96" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A97" s="6">
         <v>94</v>
       </c>
-      <c r="B96" t="s">
+      <c r="B97" t="s">
         <v>158</v>
       </c>
-      <c r="C96" t="s">
+      <c r="C97" t="s">
         <v>207</v>
       </c>
-      <c r="E96" s="5">
+      <c r="E97" s="5">
         <v>64320</v>
       </c>
-      <c r="F96" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G96" s="2">
-        <v>4</v>
-      </c>
-      <c r="K96" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="97" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A97" s="6">
+      <c r="F97" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G97" s="2">
+        <v>4</v>
+      </c>
+      <c r="H97" s="2">
+        <v>1</v>
+      </c>
+      <c r="I97" s="2">
+        <v>3</v>
+      </c>
+      <c r="J97" t="s">
+        <v>241</v>
+      </c>
+      <c r="K97" t="s">
+        <v>323</v>
+      </c>
+      <c r="L97" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A98" s="6">
         <v>95</v>
       </c>
-      <c r="B97" t="s">
+      <c r="B98" t="s">
         <v>159</v>
       </c>
-      <c r="C97" t="s">
+      <c r="C98" t="s">
         <v>208</v>
       </c>
-      <c r="E97" s="5">
+      <c r="E98" s="5">
         <v>64167</v>
       </c>
-      <c r="F97" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G97" s="2">
-        <v>2</v>
-      </c>
-      <c r="K97" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="98" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
+      <c r="F98" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G98" s="2">
+        <v>2</v>
+      </c>
+      <c r="H98" s="2">
+        <v>1</v>
+      </c>
+      <c r="I98" s="2">
+        <v>1</v>
+      </c>
+      <c r="J98" t="s">
+        <v>242</v>
+      </c>
+      <c r="K98" t="s">
+        <v>306</v>
+      </c>
+      <c r="L98" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A99" s="6">
         <v>96</v>
       </c>
-      <c r="B98" t="s">
+      <c r="B99" t="s">
         <v>160</v>
       </c>
-      <c r="C98" t="s">
+      <c r="C99" t="s">
         <v>209</v>
       </c>
-      <c r="E98" s="5">
+      <c r="E99" s="5">
         <v>64166</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="G98" s="2">
-        <v>5</v>
-      </c>
-      <c r="K98" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="99" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
-        <v>97</v>
-      </c>
-      <c r="B99" t="s">
-        <v>161</v>
-      </c>
-      <c r="C99" t="s">
-        <v>210</v>
-      </c>
-      <c r="E99" s="5">
-        <v>64099</v>
-      </c>
-      <c r="F99" s="2" t="s">
-        <v>2</v>
       </c>
       <c r="G99" s="2">
         <v>5</v>
       </c>
+      <c r="H99" s="2">
+        <v>2</v>
+      </c>
+      <c r="I99" s="2">
+        <v>3</v>
+      </c>
+      <c r="J99" t="s">
+        <v>242</v>
+      </c>
       <c r="K99" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="100" spans="1:11" x14ac:dyDescent="0.25">
+        <v>245</v>
+      </c>
+      <c r="L99" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A100" s="6">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B100" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C100" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="E100" s="5">
-        <v>64032</v>
+        <v>64099</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="G100" s="2">
         <v>5</v>
       </c>
+      <c r="H100" s="2">
+        <v>3</v>
+      </c>
+      <c r="I100" s="2">
+        <v>2</v>
+      </c>
+      <c r="J100" t="s">
+        <v>242</v>
+      </c>
       <c r="K100" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="101" spans="1:11" x14ac:dyDescent="0.25">
+        <v>284</v>
+      </c>
+      <c r="L100" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="101" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A101" s="6">
+        <v>98</v>
+      </c>
+      <c r="B101" t="s">
+        <v>162</v>
+      </c>
+      <c r="C101" t="s">
+        <v>211</v>
+      </c>
+      <c r="E101" s="5">
+        <v>64032</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G101" s="2">
+        <v>5</v>
+      </c>
+      <c r="H101" s="2">
+        <v>3</v>
+      </c>
+      <c r="I101" s="2">
+        <v>2</v>
+      </c>
+      <c r="J101" t="s">
+        <v>242</v>
+      </c>
+      <c r="K101" t="s">
+        <v>245</v>
+      </c>
+      <c r="L101" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A102" s="6">
         <v>99</v>
       </c>
-      <c r="B101" t="s">
+      <c r="B102" t="s">
         <v>163</v>
       </c>
-      <c r="C101" t="s">
+      <c r="C102" t="s">
         <v>212</v>
       </c>
-      <c r="E101" s="5">
+      <c r="E102" s="5">
         <v>63997</v>
       </c>
-      <c r="F101" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G101" s="2">
-        <v>4</v>
-      </c>
-      <c r="K101" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="102" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A102" s="6">
+      <c r="F102" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G102" s="2">
+        <v>4</v>
+      </c>
+      <c r="H102" s="2">
+        <v>2</v>
+      </c>
+      <c r="I102" s="2">
+        <v>2</v>
+      </c>
+      <c r="J102" t="s">
+        <v>242</v>
+      </c>
+      <c r="K102" t="s">
+        <v>282</v>
+      </c>
+      <c r="L102" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="103" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A103" s="6">
         <v>100</v>
       </c>
-      <c r="B102" t="s">
+      <c r="B103" t="s">
         <v>164</v>
       </c>
-      <c r="C102" t="s">
+      <c r="C103" t="s">
         <v>213</v>
       </c>
-      <c r="D102" t="s">
+      <c r="D103" t="s">
         <v>214</v>
       </c>
-      <c r="E102" s="5">
+      <c r="E103" s="5">
         <v>63944</v>
       </c>
-      <c r="F102" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G102" s="2">
-        <v>2</v>
-      </c>
-      <c r="K102" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="103" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A103" s="6">
+      <c r="F103" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G103" s="2">
+        <v>2</v>
+      </c>
+      <c r="H103" s="2">
+        <v>1</v>
+      </c>
+      <c r="I103" s="2">
+        <v>1</v>
+      </c>
+      <c r="J103" t="s">
+        <v>242</v>
+      </c>
+      <c r="K103" t="s">
+        <v>269</v>
+      </c>
+      <c r="L103" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A104" s="6">
         <v>101</v>
       </c>
-      <c r="B103" t="s">
+      <c r="B104" t="s">
         <v>216</v>
       </c>
-      <c r="C103" t="s">
+      <c r="C104" t="s">
         <v>222</v>
       </c>
-      <c r="D103" t="s">
+      <c r="D104" t="s">
         <v>230</v>
       </c>
-      <c r="E103" s="5">
+      <c r="E104" s="5">
         <v>63928</v>
       </c>
-      <c r="F103" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G103" s="2">
-        <v>4</v>
-      </c>
-      <c r="K103" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="104" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A104" s="6">
+      <c r="F104" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G104" s="2">
+        <v>4</v>
+      </c>
+      <c r="H104" s="2">
+        <v>2</v>
+      </c>
+      <c r="I104" s="2">
+        <v>2</v>
+      </c>
+      <c r="J104" t="s">
+        <v>237</v>
+      </c>
+      <c r="K104" t="s">
+        <v>297</v>
+      </c>
+      <c r="L104" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A105" s="6">
         <v>102</v>
       </c>
-      <c r="B104" t="s">
+      <c r="B105" t="s">
         <v>145</v>
       </c>
-      <c r="C104" t="s">
+      <c r="C105" t="s">
         <v>193</v>
       </c>
-      <c r="E104" s="5">
+      <c r="E105" s="5">
         <v>63834</v>
       </c>
-      <c r="F104" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G104" s="2">
-        <v>4</v>
-      </c>
-      <c r="K104" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="105" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A105" s="6">
+      <c r="F105" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G105" s="2">
+        <v>4</v>
+      </c>
+      <c r="H105" s="2">
+        <v>2</v>
+      </c>
+      <c r="I105" s="2">
+        <v>2</v>
+      </c>
+      <c r="J105" t="s">
+        <v>241</v>
+      </c>
+      <c r="K105" t="s">
+        <v>288</v>
+      </c>
+      <c r="L105" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="106" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A106" s="6">
         <v>103</v>
       </c>
-      <c r="B105" t="s">
+      <c r="B106" t="s">
         <v>217</v>
       </c>
-      <c r="C105" t="s">
+      <c r="C106" t="s">
         <v>223</v>
       </c>
-      <c r="E105" s="5">
+      <c r="E106" s="5">
         <v>63817</v>
       </c>
-      <c r="F105" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G105" s="2">
+      <c r="F106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G106" s="2">
         <v>3</v>
       </c>
-      <c r="K105" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="106" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A106" s="6">
+      <c r="H106" s="2">
+        <v>1</v>
+      </c>
+      <c r="I106" s="2">
+        <v>2</v>
+      </c>
+      <c r="J106" t="s">
+        <v>242</v>
+      </c>
+      <c r="K106" t="s">
+        <v>295</v>
+      </c>
+      <c r="L106" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="107" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A107" s="6">
         <v>104</v>
       </c>
-      <c r="B106" t="s">
+      <c r="B107" t="s">
         <v>38</v>
       </c>
-      <c r="C106" t="s">
+      <c r="C107" t="s">
         <v>86</v>
       </c>
-      <c r="E106" s="5">
+      <c r="E107" s="5">
         <v>63725</v>
       </c>
-      <c r="F106" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G106" s="2">
+      <c r="F107" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G107" s="2">
         <v>5</v>
       </c>
-      <c r="K106" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="107" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
+      <c r="H107" s="2">
+        <v>3</v>
+      </c>
+      <c r="I107" s="2">
+        <v>2</v>
+      </c>
+      <c r="J107" t="s">
+        <v>239</v>
+      </c>
+      <c r="K107" t="s">
+        <v>279</v>
+      </c>
+      <c r="L107" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A108" s="6">
         <v>105</v>
       </c>
-      <c r="B107" t="s">
+      <c r="B108" t="s">
         <v>218</v>
       </c>
-      <c r="C107" t="s">
+      <c r="C108" t="s">
         <v>224</v>
       </c>
-      <c r="E107" s="5">
+      <c r="E108" s="5">
         <v>63683</v>
       </c>
-      <c r="F107" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G107" s="2">
+      <c r="F108" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G108" s="2">
         <v>3</v>
       </c>
-      <c r="K107" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="108" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
+      <c r="H108" s="2">
+        <v>2</v>
+      </c>
+      <c r="I108" s="2">
+        <v>1</v>
+      </c>
+      <c r="J108" t="s">
+        <v>242</v>
+      </c>
+      <c r="K108" t="s">
+        <v>269</v>
+      </c>
+      <c r="L108" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A109" s="6">
         <v>106</v>
       </c>
-      <c r="B108" t="s">
+      <c r="B109" t="s">
         <v>46</v>
       </c>
-      <c r="C108" t="s">
+      <c r="C109" t="s">
         <v>94</v>
       </c>
-      <c r="E108" s="5">
+      <c r="E109" s="5">
         <v>63673</v>
       </c>
-      <c r="F108" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G108" s="2">
+      <c r="F109" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G109" s="2">
         <v>5</v>
       </c>
-      <c r="K108" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="109" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
+      <c r="H109" s="2">
+        <v>2</v>
+      </c>
+      <c r="I109" s="2">
+        <v>3</v>
+      </c>
+      <c r="J109" t="s">
+        <v>242</v>
+      </c>
+      <c r="K109" t="s">
+        <v>307</v>
+      </c>
+      <c r="L109" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A110" s="6">
         <v>107</v>
       </c>
-      <c r="B109" t="s">
+      <c r="B110" t="s">
         <v>219</v>
       </c>
-      <c r="C109" t="s">
+      <c r="C110" t="s">
         <v>225</v>
       </c>
-      <c r="E109" s="5">
+      <c r="E110" s="5">
         <v>63649</v>
       </c>
-      <c r="F109" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G109" s="2">
+      <c r="F110" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G110" s="2">
         <v>6</v>
       </c>
-      <c r="K109" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="110" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A110" s="6">
+      <c r="H110" s="2">
+        <v>1</v>
+      </c>
+      <c r="I110" s="2">
+        <v>5</v>
+      </c>
+      <c r="J110" t="s">
+        <v>239</v>
+      </c>
+      <c r="K110" t="s">
+        <v>274</v>
+      </c>
+      <c r="L110" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A111" s="6">
         <v>108</v>
       </c>
-      <c r="B110" t="s">
+      <c r="B111" t="s">
         <v>148</v>
       </c>
-      <c r="C110" t="s">
+      <c r="C111" t="s">
         <v>226</v>
       </c>
-      <c r="E110" s="5">
+      <c r="E111" s="5">
         <v>63601</v>
       </c>
-      <c r="F110" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G110" s="2">
-        <v>4</v>
-      </c>
-      <c r="K110" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A111" s="6">
+      <c r="F111" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G111" s="2">
+        <v>4</v>
+      </c>
+      <c r="H111" s="2">
+        <v>2</v>
+      </c>
+      <c r="I111" s="2">
+        <v>2</v>
+      </c>
+      <c r="J111" t="s">
+        <v>242</v>
+      </c>
+      <c r="K111" t="s">
+        <v>260</v>
+      </c>
+      <c r="L111" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A112" s="6">
         <v>109</v>
       </c>
-      <c r="B111" t="s">
+      <c r="B112" t="s">
         <v>220</v>
       </c>
-      <c r="C111" t="s">
+      <c r="C112" t="s">
         <v>227</v>
       </c>
-      <c r="E111" s="5">
+      <c r="E112" s="5">
         <v>63569</v>
       </c>
-      <c r="F111" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G111" s="2">
+      <c r="F112" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G112" s="2">
         <v>3</v>
       </c>
-      <c r="K111" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="112" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A112" s="6">
+      <c r="H112" s="2">
+        <v>2</v>
+      </c>
+      <c r="I112" s="2">
+        <v>1</v>
+      </c>
+      <c r="J112" t="s">
+        <v>242</v>
+      </c>
+      <c r="K112" t="s">
+        <v>261</v>
+      </c>
+      <c r="L112" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A113" s="6">
         <v>110</v>
       </c>
-      <c r="B112" t="s">
+      <c r="B113" t="s">
         <v>221</v>
       </c>
-      <c r="C112" t="s">
+      <c r="C113" t="s">
         <v>228</v>
       </c>
-      <c r="D112" t="s">
+      <c r="D113" t="s">
         <v>229</v>
       </c>
-      <c r="E112" s="5">
+      <c r="E113" s="5">
         <v>63566</v>
       </c>
-      <c r="F112" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="G112" s="2">
-        <v>4</v>
-      </c>
-      <c r="K112" t="s">
-        <v>243</v>
+      <c r="F113" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G113" s="2">
+        <v>4</v>
+      </c>
+      <c r="H113" s="2">
+        <v>2</v>
+      </c>
+      <c r="I113" s="2">
+        <v>2</v>
+      </c>
+      <c r="J113" t="s">
+        <v>242</v>
+      </c>
+      <c r="K113" t="s">
+        <v>295</v>
+      </c>
+      <c r="L113" t="s">
+        <v>245</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <sortState ref="A3:L112">
+    <sortCondition ref="A3"/>
+  </sortState>
+  <mergeCells count="5">
     <mergeCell ref="G1:I1"/>
+    <mergeCell ref="K1:K2"/>
     <mergeCell ref="J1:J2"/>
-    <mergeCell ref="K1:K2"/>
     <mergeCell ref="L1:L2"/>
+    <mergeCell ref="M1:M2"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F3:F112" xr:uid="{07EF2559-F163-4DF0-9719-E94C961CBA22}">
-      <formula1>$F$3:$F$22</formula1>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4:F113">
+      <formula1>$F$4:$F$23</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8C21279B-2782-4A90-9224-829963DB16CF}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>Reasons!$A$2:$A$7</xm:f>
+            <xm:f>Reasons!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K3:K112</xm:sqref>
+          <xm:sqref>J4:J113</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -3892,46 +5568,2904 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4064FE7B-4E36-4A68-B45B-B043CE453D88}">
-  <dimension ref="A1:A7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L110"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="18.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="2.21875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A1" s="6">
+        <v>1</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>231</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5">
+        <v>66897</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G1" s="3">
+        <v>4</v>
+      </c>
+      <c r="H1" s="3"/>
+      <c r="I1" s="3">
+        <v>0</v>
+      </c>
+      <c r="K1" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E2" s="5">
+        <v>65366</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G2" s="2">
+        <v>4</v>
+      </c>
+      <c r="H2" s="2">
+        <f>G2-I2</f>
+        <v>2</v>
+      </c>
+      <c r="I2" s="2">
+        <v>2</v>
+      </c>
+      <c r="J2" t="s">
+        <v>235</v>
+      </c>
+      <c r="K2" t="s">
+        <v>242</v>
+      </c>
+      <c r="L2" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="6">
+        <v>49</v>
+      </c>
+      <c r="B3" t="s">
+        <v>50</v>
+      </c>
+      <c r="C3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D3" t="s">
+        <v>109</v>
+      </c>
+      <c r="E3" s="5">
+        <v>65800</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G3" s="2">
+        <v>3</v>
+      </c>
+      <c r="H3" s="2">
+        <v>2</v>
+      </c>
+      <c r="I3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>242</v>
+      </c>
+      <c r="L3" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="6">
+        <v>44</v>
+      </c>
+      <c r="B4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E4" s="5">
+        <v>65877</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G4" s="2">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2"/>
+      <c r="I4" s="2"/>
+      <c r="K4" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="6">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="5">
+        <v>64618</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G5" s="2">
+        <v>4</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2"/>
+      <c r="K5" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="6">
+        <v>80</v>
+      </c>
+      <c r="B6" t="s">
+        <v>144</v>
+      </c>
+      <c r="C6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E6" s="5">
+        <v>65173</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G6" s="2">
+        <v>5</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2"/>
+      <c r="K6" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="6">
+        <v>23</v>
+      </c>
+      <c r="B7" t="s">
+        <v>25</v>
+      </c>
+      <c r="C7" t="s">
+        <v>73</v>
+      </c>
+      <c r="E7" s="5">
+        <v>66392</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G7" s="2">
+        <v>4</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2"/>
+      <c r="K7" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="6">
+        <v>57</v>
+      </c>
+      <c r="B8" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" t="s">
+        <v>171</v>
+      </c>
+      <c r="E8" s="5">
+        <v>65533</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G8" s="2">
+        <v>5</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2"/>
+      <c r="K8" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="6">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
+        <v>136</v>
+      </c>
+      <c r="C9" t="s">
+        <v>185</v>
+      </c>
+      <c r="E9" s="5">
+        <v>65350</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2"/>
+      <c r="I9" s="2"/>
+      <c r="K9" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="6">
+        <v>38</v>
+      </c>
+      <c r="B10" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" t="s">
+        <v>87</v>
+      </c>
+      <c r="E10" s="5">
+        <v>66029</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2"/>
+      <c r="I10" s="2"/>
+      <c r="K10" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="6">
+        <v>19</v>
+      </c>
+      <c r="B11" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" s="5">
+        <v>66573</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G11" s="2">
+        <v>4</v>
+      </c>
+      <c r="H11" s="2"/>
+      <c r="I11" s="2"/>
+      <c r="K11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="6">
+        <v>96</v>
+      </c>
+      <c r="B12" t="s">
+        <v>160</v>
+      </c>
+      <c r="C12" t="s">
+        <v>209</v>
+      </c>
+      <c r="E12" s="5">
+        <v>64166</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G12" s="2">
+        <v>5</v>
+      </c>
+      <c r="H12" s="2"/>
+      <c r="I12" s="2"/>
+      <c r="K12" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="6">
+        <v>68</v>
+      </c>
+      <c r="B13" t="s">
+        <v>133</v>
+      </c>
+      <c r="C13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E13" s="5">
+        <v>65365</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G13" s="2">
+        <v>2</v>
+      </c>
+      <c r="H13" s="2"/>
+      <c r="I13" s="2"/>
+      <c r="K13" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="6">
+        <v>89</v>
+      </c>
+      <c r="B14" t="s">
+        <v>153</v>
+      </c>
+      <c r="C14" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="5">
+        <v>64532</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G14" s="2">
+        <v>4</v>
+      </c>
+      <c r="H14" s="2"/>
+      <c r="I14" s="2"/>
+      <c r="K14" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="6">
+        <v>83</v>
+      </c>
+      <c r="B15" t="s">
+        <v>148</v>
+      </c>
+      <c r="C15" t="s">
+        <v>197</v>
+      </c>
+      <c r="E15" s="5">
+        <v>64935</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G15" s="2">
+        <v>4</v>
+      </c>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="K15" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="6">
+        <v>108</v>
+      </c>
+      <c r="B16" t="s">
+        <v>148</v>
+      </c>
+      <c r="C16" t="s">
+        <v>226</v>
+      </c>
+      <c r="E16" s="5">
+        <v>63601</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G16" s="2">
+        <v>4</v>
+      </c>
+      <c r="H16" s="2"/>
+      <c r="I16" s="2"/>
+      <c r="K16" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A17" s="6">
+        <v>97</v>
+      </c>
+      <c r="B17" t="s">
+        <v>161</v>
+      </c>
+      <c r="C17" t="s">
+        <v>210</v>
+      </c>
+      <c r="E17" s="5">
+        <v>64099</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G17" s="2">
+        <v>5</v>
+      </c>
+      <c r="H17" s="2"/>
+      <c r="I17" s="2"/>
+      <c r="K17" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A18" s="6">
+        <v>109</v>
+      </c>
+      <c r="B18" t="s">
+        <v>220</v>
+      </c>
+      <c r="C18" t="s">
+        <v>227</v>
+      </c>
+      <c r="E18" s="5">
+        <v>63569</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3</v>
+      </c>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="K18" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A19" s="6">
+        <v>91</v>
+      </c>
+      <c r="B19" t="s">
+        <v>155</v>
+      </c>
+      <c r="C19" t="s">
+        <v>204</v>
+      </c>
+      <c r="E19" s="5">
+        <v>64444</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G19" s="2">
+        <v>4</v>
+      </c>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="K19" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="6">
+        <v>31</v>
+      </c>
+      <c r="B20" t="s">
+        <v>32</v>
+      </c>
+      <c r="C20" t="s">
+        <v>80</v>
+      </c>
+      <c r="E20" s="5">
+        <v>66182</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G20" s="2">
+        <v>9</v>
+      </c>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="K20" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" s="6">
+        <v>29</v>
+      </c>
+      <c r="B21" t="s">
+        <v>30</v>
+      </c>
+      <c r="C21" t="s">
+        <v>78</v>
+      </c>
+      <c r="E21" s="5">
+        <v>66188</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G21" s="2">
+        <v>7</v>
+      </c>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="K21" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A22" s="6">
+        <v>73</v>
+      </c>
+      <c r="B22" t="s">
+        <v>138</v>
+      </c>
+      <c r="C22" t="s">
+        <v>187</v>
+      </c>
+      <c r="E22" s="5">
+        <v>65306</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="2">
+        <v>5</v>
+      </c>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="K22" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="6">
+        <v>92</v>
+      </c>
+      <c r="B23" t="s">
+        <v>156</v>
+      </c>
+      <c r="C23" t="s">
+        <v>205</v>
+      </c>
+      <c r="E23" s="5">
+        <v>64424</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G23" s="2">
+        <v>4</v>
+      </c>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="K23" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="6">
+        <v>2</v>
+      </c>
+      <c r="B24" t="s">
+        <v>3</v>
+      </c>
+      <c r="C24" t="s">
+        <v>52</v>
+      </c>
+      <c r="D24" t="s">
+        <v>4</v>
+      </c>
+      <c r="E24" s="5">
+        <v>66890</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G24" s="2">
+        <v>4</v>
+      </c>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="K24" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="6">
+        <v>25</v>
+      </c>
+      <c r="B25" t="s">
+        <v>3</v>
+      </c>
+      <c r="C25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E25" s="5">
+        <v>66242</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G25" s="2">
+        <v>3</v>
+      </c>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="K25" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" s="6">
+        <v>33</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
+        <v>82</v>
+      </c>
+      <c r="E26" s="5">
+        <v>66138</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="2">
+        <v>4</v>
+      </c>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="K26" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" s="6">
+        <v>40</v>
+      </c>
+      <c r="B27" t="s">
+        <v>41</v>
+      </c>
+      <c r="C27" t="s">
+        <v>89</v>
+      </c>
+      <c r="E27" s="5">
+        <v>66021</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G27" s="2">
+        <v>4</v>
+      </c>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="K27" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A28" s="6">
+        <v>6</v>
+      </c>
+      <c r="B28" t="s">
+        <v>8</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="E28" s="5">
+        <v>66762</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G28" s="2">
+        <v>1</v>
+      </c>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="K28" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A29" s="6">
+        <v>46</v>
+      </c>
+      <c r="B29" t="s">
+        <v>47</v>
+      </c>
+      <c r="C29" t="s">
+        <v>95</v>
+      </c>
+      <c r="D29" t="s">
+        <v>112</v>
+      </c>
+      <c r="E29" s="5">
+        <v>65840</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G29" s="2">
+        <v>4</v>
+      </c>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="K29" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="6">
+        <v>100</v>
+      </c>
+      <c r="B30" t="s">
+        <v>164</v>
+      </c>
+      <c r="C30" t="s">
+        <v>213</v>
+      </c>
+      <c r="D30" t="s">
+        <v>214</v>
+      </c>
+      <c r="E30" s="5">
+        <v>63944</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="2">
+        <v>2</v>
+      </c>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="K30" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" s="6">
+        <v>72</v>
+      </c>
+      <c r="B31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C31" t="s">
+        <v>186</v>
+      </c>
+      <c r="E31" s="5">
+        <v>65328</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G31" s="2">
+        <v>5</v>
+      </c>
+      <c r="H31" s="2"/>
+      <c r="I31" s="2"/>
+      <c r="K31" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A32" s="6">
+        <v>11</v>
+      </c>
+      <c r="B32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C32" t="s">
+        <v>61</v>
+      </c>
+      <c r="E32" s="5">
+        <v>66674</v>
+      </c>
+      <c r="F32" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G32" s="2">
+        <v>8</v>
+      </c>
+      <c r="H32" s="2"/>
+      <c r="I32" s="2"/>
+      <c r="K32" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A33" s="6">
+        <v>75</v>
+      </c>
+      <c r="B33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" t="s">
+        <v>189</v>
+      </c>
+      <c r="E33" s="5">
+        <v>65302</v>
+      </c>
+      <c r="F33" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G33" s="2">
+        <v>3</v>
+      </c>
+      <c r="H33" s="2"/>
+      <c r="I33" s="2"/>
+      <c r="K33" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A34" s="6">
+        <v>107</v>
+      </c>
+      <c r="B34" t="s">
+        <v>219</v>
+      </c>
+      <c r="C34" t="s">
+        <v>225</v>
+      </c>
+      <c r="E34" s="5">
+        <v>63649</v>
+      </c>
+      <c r="F34" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="2">
+        <v>6</v>
+      </c>
+      <c r="H34" s="2"/>
+      <c r="I34" s="2"/>
+      <c r="K34" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A35" s="6">
+        <v>16</v>
+      </c>
+      <c r="B35" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" t="s">
+        <v>66</v>
+      </c>
+      <c r="E35" s="5">
+        <v>66594</v>
+      </c>
+      <c r="F35" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G35" s="2">
+        <v>3</v>
+      </c>
+      <c r="H35" s="2"/>
+      <c r="I35" s="2"/>
+      <c r="K35" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="6">
+        <v>22</v>
+      </c>
+      <c r="B36" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" t="s">
+        <v>72</v>
+      </c>
+      <c r="E36" s="5">
+        <v>66408</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G36" s="2">
+        <v>5</v>
+      </c>
+      <c r="H36" s="2"/>
+      <c r="I36" s="2"/>
+      <c r="K36" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A37" s="6">
+        <v>81</v>
+      </c>
+      <c r="B37" t="s">
+        <v>146</v>
+      </c>
+      <c r="C37" t="s">
+        <v>195</v>
+      </c>
+      <c r="E37" s="5">
+        <v>65146</v>
+      </c>
+      <c r="F37" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G37" s="2">
+        <v>5</v>
+      </c>
+      <c r="H37" s="2"/>
+      <c r="I37" s="2"/>
+      <c r="K37" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A38" s="6">
+        <v>35</v>
+      </c>
+      <c r="B38" t="s">
+        <v>36</v>
+      </c>
+      <c r="C38" t="s">
+        <v>84</v>
+      </c>
+      <c r="E38" s="5">
+        <v>66127</v>
+      </c>
+      <c r="F38" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2">
+        <v>4</v>
+      </c>
+      <c r="H38" s="2"/>
+      <c r="I38" s="2"/>
+      <c r="K38" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A39" s="6">
+        <v>98</v>
+      </c>
+      <c r="B39" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" t="s">
+        <v>211</v>
+      </c>
+      <c r="E39" s="5">
+        <v>64032</v>
+      </c>
+      <c r="F39" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G39" s="2">
+        <v>5</v>
+      </c>
+      <c r="H39" s="2"/>
+      <c r="I39" s="2"/>
+      <c r="K39" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A40" s="6">
+        <v>37</v>
+      </c>
+      <c r="B40" t="s">
+        <v>38</v>
+      </c>
+      <c r="C40" t="s">
+        <v>86</v>
+      </c>
+      <c r="E40" s="5">
+        <v>66058</v>
+      </c>
+      <c r="F40" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G40" s="2">
+        <v>4</v>
+      </c>
+      <c r="H40" s="2"/>
+      <c r="I40" s="2"/>
+      <c r="K40" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A41" s="6">
+        <v>104</v>
+      </c>
+      <c r="B41" t="s">
+        <v>38</v>
+      </c>
+      <c r="C41" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="5">
+        <v>63725</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G41" s="2">
+        <v>5</v>
+      </c>
+      <c r="H41" s="2"/>
+      <c r="I41" s="2"/>
+      <c r="K41" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A42" s="6">
+        <v>88</v>
+      </c>
+      <c r="B42" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" t="s">
+        <v>201</v>
+      </c>
+      <c r="E42" s="5">
+        <v>64571</v>
+      </c>
+      <c r="F42" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="2">
+        <v>5</v>
+      </c>
+      <c r="H42" s="2"/>
+      <c r="I42" s="2"/>
+      <c r="K42" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A43" s="6">
+        <v>99</v>
+      </c>
+      <c r="B43" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" t="s">
+        <v>212</v>
+      </c>
+      <c r="E43" s="5">
+        <v>63997</v>
+      </c>
+      <c r="F43" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G43" s="2">
+        <v>4</v>
+      </c>
+      <c r="H43" s="2"/>
+      <c r="I43" s="2"/>
+      <c r="K43" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A44" s="6">
+        <v>15</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44" t="s">
+        <v>65</v>
+      </c>
+      <c r="E44" s="5">
+        <v>66605</v>
+      </c>
+      <c r="F44" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G44" s="2">
+        <v>4</v>
+      </c>
+      <c r="H44" s="2"/>
+      <c r="I44" s="2"/>
+      <c r="K44" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A45" s="6">
+        <v>69</v>
+      </c>
+      <c r="B45" t="s">
+        <v>134</v>
+      </c>
+      <c r="C45" t="s">
+        <v>183</v>
+      </c>
+      <c r="E45" s="5">
+        <v>65356</v>
+      </c>
+      <c r="F45" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G45" s="2">
+        <v>6</v>
+      </c>
+      <c r="H45" s="2"/>
+      <c r="I45" s="2"/>
+      <c r="K45" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A46" s="6">
+        <v>84</v>
+      </c>
+      <c r="B46" t="s">
+        <v>149</v>
+      </c>
+      <c r="C46" t="s">
+        <v>198</v>
+      </c>
+      <c r="E46" s="5">
+        <v>64887</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="2">
+        <v>4</v>
+      </c>
+      <c r="H46" s="2"/>
+      <c r="I46" s="2"/>
+      <c r="K46" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A47" s="6">
+        <v>34</v>
+      </c>
+      <c r="B47" t="s">
+        <v>35</v>
+      </c>
+      <c r="C47" t="s">
+        <v>83</v>
+      </c>
+      <c r="E47" s="5">
+        <v>66132</v>
+      </c>
+      <c r="F47" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G47" s="2">
+        <v>4</v>
+      </c>
+      <c r="H47" s="2"/>
+      <c r="I47" s="2"/>
+      <c r="K47" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A48" s="6">
+        <v>79</v>
+      </c>
+      <c r="B48" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" t="s">
+        <v>193</v>
+      </c>
+      <c r="E48" s="5">
+        <v>65265</v>
+      </c>
+      <c r="F48" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G48" s="2">
+        <v>5</v>
+      </c>
+      <c r="H48" s="2"/>
+      <c r="I48" s="2"/>
+      <c r="K48" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A49" s="6">
+        <v>102</v>
+      </c>
+      <c r="B49" t="s">
+        <v>145</v>
+      </c>
+      <c r="C49" t="s">
+        <v>193</v>
+      </c>
+      <c r="E49" s="5">
+        <v>63834</v>
+      </c>
+      <c r="F49" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G49" s="2">
+        <v>4</v>
+      </c>
+      <c r="H49" s="2"/>
+      <c r="I49" s="2"/>
+      <c r="K49" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A50" s="6">
+        <v>3</v>
+      </c>
+      <c r="B50" t="s">
+        <v>5</v>
+      </c>
+      <c r="C50" t="s">
+        <v>53</v>
+      </c>
+      <c r="E50" s="5">
+        <v>66876</v>
+      </c>
+      <c r="F50" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="2">
+        <v>5</v>
+      </c>
+      <c r="H50" s="2"/>
+      <c r="I50" s="2"/>
+      <c r="K50" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A51" s="6">
+        <v>36</v>
+      </c>
+      <c r="B51" t="s">
+        <v>37</v>
+      </c>
+      <c r="C51" t="s">
+        <v>85</v>
+      </c>
+      <c r="E51" s="5">
+        <v>66121</v>
+      </c>
+      <c r="F51" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G51" s="2">
+        <v>4</v>
+      </c>
+      <c r="H51" s="2"/>
+      <c r="I51" s="2"/>
+      <c r="K51" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A52" s="6">
+        <v>78</v>
+      </c>
+      <c r="B52" t="s">
+        <v>143</v>
+      </c>
+      <c r="C52" t="s">
+        <v>192</v>
+      </c>
+      <c r="E52" s="5">
+        <v>65287</v>
+      </c>
+      <c r="F52" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G52" s="2">
+        <v>4</v>
+      </c>
+      <c r="H52" s="2"/>
+      <c r="I52" s="2"/>
+      <c r="K52" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A53" s="6">
+        <v>66</v>
+      </c>
+      <c r="B53" t="s">
+        <v>131</v>
+      </c>
+      <c r="C53" t="s">
+        <v>180</v>
+      </c>
+      <c r="E53" s="5">
+        <v>65369</v>
+      </c>
+      <c r="F53" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G53" s="2">
+        <v>4</v>
+      </c>
+      <c r="H53" s="2"/>
+      <c r="I53" s="2"/>
+      <c r="K53" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A54" s="6">
+        <v>105</v>
+      </c>
+      <c r="B54" t="s">
+        <v>218</v>
+      </c>
+      <c r="C54" t="s">
+        <v>224</v>
+      </c>
+      <c r="E54" s="5">
+        <v>63683</v>
+      </c>
+      <c r="F54" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G54" s="2">
+        <v>3</v>
+      </c>
+      <c r="H54" s="2"/>
+      <c r="I54" s="2"/>
+      <c r="K54" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A55" s="6">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
+        <v>7</v>
+      </c>
+      <c r="C55" t="s">
+        <v>55</v>
+      </c>
+      <c r="E55" s="5">
+        <v>66809</v>
+      </c>
+      <c r="F55" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G55" s="2">
+        <v>4</v>
+      </c>
+      <c r="H55" s="2"/>
+      <c r="I55" s="2"/>
+      <c r="K55" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A56" s="6">
+        <v>56</v>
+      </c>
+      <c r="B56" t="s">
+        <v>121</v>
+      </c>
+      <c r="C56" t="s">
+        <v>170</v>
+      </c>
+      <c r="E56" s="5">
+        <v>65582</v>
+      </c>
+      <c r="F56" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G56" s="2">
+        <v>3</v>
+      </c>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="K56" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A57" s="6">
+        <v>61</v>
+      </c>
+      <c r="B57" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" t="s">
+        <v>175</v>
+      </c>
+      <c r="E57" s="5">
+        <v>65479</v>
+      </c>
+      <c r="F57" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G57" s="2">
+        <v>4</v>
+      </c>
+      <c r="H57" s="2"/>
+      <c r="I57" s="2"/>
+      <c r="K57" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A58" s="6">
+        <v>110</v>
+      </c>
+      <c r="B58" t="s">
+        <v>221</v>
+      </c>
+      <c r="C58" t="s">
+        <v>228</v>
+      </c>
+      <c r="D58" t="s">
+        <v>229</v>
+      </c>
+      <c r="E58" s="5">
+        <v>63566</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G58" s="2">
+        <v>4</v>
+      </c>
+      <c r="H58" s="2"/>
+      <c r="I58" s="2"/>
+      <c r="K58" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A59" s="6">
+        <v>60</v>
+      </c>
+      <c r="B59" t="s">
+        <v>125</v>
+      </c>
+      <c r="C59" t="s">
+        <v>174</v>
+      </c>
+      <c r="E59" s="5">
+        <v>65490</v>
+      </c>
+      <c r="F59" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G59" s="2">
+        <v>4</v>
+      </c>
+      <c r="H59" s="2"/>
+      <c r="I59" s="2"/>
+      <c r="K59" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A60" s="6">
+        <v>30</v>
+      </c>
+      <c r="B60" t="s">
+        <v>31</v>
+      </c>
+      <c r="C60" t="s">
+        <v>79</v>
+      </c>
+      <c r="E60" s="5">
+        <v>66183</v>
+      </c>
+      <c r="F60" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G60" s="2">
+        <v>1</v>
+      </c>
+      <c r="H60" s="2"/>
+      <c r="I60" s="2"/>
+      <c r="K60" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A61" s="6">
+        <v>101</v>
+      </c>
+      <c r="B61" t="s">
+        <v>216</v>
+      </c>
+      <c r="C61" t="s">
+        <v>222</v>
+      </c>
+      <c r="D61" t="s">
+        <v>230</v>
+      </c>
+      <c r="E61" s="5">
+        <v>63928</v>
+      </c>
+      <c r="F61" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G61" s="2">
+        <v>4</v>
+      </c>
+      <c r="H61" s="2"/>
+      <c r="I61" s="2"/>
+      <c r="K61" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A62" s="6">
+        <v>62</v>
+      </c>
+      <c r="B62" t="s">
+        <v>127</v>
+      </c>
+      <c r="C62" t="s">
+        <v>176</v>
+      </c>
+      <c r="E62" s="5">
+        <v>65478</v>
+      </c>
+      <c r="F62" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G62" s="2">
+        <v>4</v>
+      </c>
+      <c r="H62" s="2"/>
+      <c r="I62" s="2"/>
+      <c r="K62" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A63" s="6">
+        <v>58</v>
+      </c>
+      <c r="B63" t="s">
+        <v>123</v>
+      </c>
+      <c r="C63" t="s">
+        <v>172</v>
+      </c>
+      <c r="E63" s="5">
+        <v>65527</v>
+      </c>
+      <c r="F63" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G63" s="2">
+        <v>5</v>
+      </c>
+      <c r="H63" s="2"/>
+      <c r="I63" s="2"/>
+      <c r="K63" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A64" s="6">
+        <v>47</v>
+      </c>
+      <c r="B64" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" t="s">
+        <v>96</v>
+      </c>
+      <c r="D64" t="s">
+        <v>111</v>
+      </c>
+      <c r="E64" s="5">
+        <v>65826</v>
+      </c>
+      <c r="F64" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G64" s="2">
+        <v>3</v>
+      </c>
+      <c r="H64" s="2"/>
+      <c r="I64" s="2"/>
+      <c r="K64" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A65" s="6">
+        <v>77</v>
+      </c>
+      <c r="B65" t="s">
+        <v>142</v>
+      </c>
+      <c r="C65" t="s">
+        <v>191</v>
+      </c>
+      <c r="E65" s="5">
+        <v>65290</v>
+      </c>
+      <c r="F65" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G65" s="2">
+        <v>4</v>
+      </c>
+      <c r="H65" s="2"/>
+      <c r="I65" s="2"/>
+      <c r="K65" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A66" s="6">
+        <v>64</v>
+      </c>
+      <c r="B66" t="s">
+        <v>129</v>
+      </c>
+      <c r="C66" t="s">
+        <v>178</v>
+      </c>
+      <c r="E66" s="5">
+        <v>65447</v>
+      </c>
+      <c r="F66" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G66" s="2">
+        <v>5</v>
+      </c>
+      <c r="H66" s="2"/>
+      <c r="I66" s="2"/>
+      <c r="K66" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A67" s="6">
+        <v>87</v>
+      </c>
+      <c r="B67" t="s">
+        <v>151</v>
+      </c>
+      <c r="C67" t="s">
+        <v>200</v>
+      </c>
+      <c r="E67" s="5">
+        <v>64618</v>
+      </c>
+      <c r="F67" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G67" s="2">
+        <v>1</v>
+      </c>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="K67" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A68" s="6">
+        <v>39</v>
+      </c>
+      <c r="B68" t="s">
+        <v>40</v>
+      </c>
+      <c r="C68" t="s">
+        <v>88</v>
+      </c>
+      <c r="E68" s="5">
+        <v>66029</v>
+      </c>
+      <c r="F68" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G68" s="2">
+        <v>2</v>
+      </c>
+      <c r="H68" s="2"/>
+      <c r="I68" s="2"/>
+      <c r="K68" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A69" s="6">
+        <v>41</v>
+      </c>
+      <c r="B69" t="s">
+        <v>42</v>
+      </c>
+      <c r="C69" t="s">
+        <v>90</v>
+      </c>
+      <c r="E69" s="5">
+        <v>65997</v>
+      </c>
+      <c r="F69" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G69" s="2">
+        <v>3</v>
+      </c>
+      <c r="H69" s="2"/>
+      <c r="I69" s="2"/>
+      <c r="K69" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A70" s="6">
+        <v>9</v>
+      </c>
+      <c r="B70" t="s">
+        <v>11</v>
+      </c>
+      <c r="C70" t="s">
+        <v>59</v>
+      </c>
+      <c r="E70" s="5">
+        <v>66689</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G70" s="2">
+        <v>4</v>
+      </c>
+      <c r="H70" s="2"/>
+      <c r="I70" s="2"/>
+      <c r="K70" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A71" s="6">
+        <v>90</v>
+      </c>
+      <c r="B71" t="s">
+        <v>154</v>
+      </c>
+      <c r="C71" t="s">
+        <v>203</v>
+      </c>
+      <c r="E71" s="5">
+        <v>64446</v>
+      </c>
+      <c r="F71" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G71" s="2">
+        <v>4</v>
+      </c>
+      <c r="H71" s="2"/>
+      <c r="I71" s="2"/>
+      <c r="K71" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A72" s="6">
+        <v>103</v>
+      </c>
+      <c r="B72" t="s">
+        <v>217</v>
+      </c>
+      <c r="C72" t="s">
+        <v>223</v>
+      </c>
+      <c r="E72" s="5">
+        <v>63817</v>
+      </c>
+      <c r="F72" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G72" s="2">
+        <v>3</v>
+      </c>
+      <c r="H72" s="2"/>
+      <c r="I72" s="2"/>
+      <c r="K72" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A73" s="6">
+        <v>10</v>
+      </c>
+      <c r="B73" t="s">
+        <v>12</v>
+      </c>
+      <c r="C73" t="s">
+        <v>60</v>
+      </c>
+      <c r="E73" s="5">
+        <v>66687</v>
+      </c>
+      <c r="F73" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G73" s="2">
+        <v>4</v>
+      </c>
+      <c r="H73" s="2"/>
+      <c r="I73" s="2"/>
+      <c r="K73" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A74" s="6">
+        <v>28</v>
+      </c>
+      <c r="B74" t="s">
+        <v>29</v>
+      </c>
+      <c r="C74" t="s">
+        <v>77</v>
+      </c>
+      <c r="E74" s="5">
+        <v>66195</v>
+      </c>
+      <c r="F74" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G74" s="2">
+        <v>1</v>
+      </c>
+      <c r="H74" s="2"/>
+      <c r="I74" s="2"/>
+      <c r="K74" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A75" s="6">
+        <v>51</v>
+      </c>
+      <c r="B75" t="s">
+        <v>116</v>
+      </c>
+      <c r="C75" t="s">
+        <v>165</v>
+      </c>
+      <c r="D75" t="s">
+        <v>215</v>
+      </c>
+      <c r="E75" s="5">
+        <v>65736</v>
+      </c>
+      <c r="F75" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G75" s="2">
+        <v>3</v>
+      </c>
+      <c r="H75" s="2"/>
+      <c r="I75" s="2"/>
+      <c r="K75" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A76" s="6">
+        <v>95</v>
+      </c>
+      <c r="B76" t="s">
+        <v>159</v>
+      </c>
+      <c r="C76" t="s">
+        <v>208</v>
+      </c>
+      <c r="E76" s="5">
+        <v>64167</v>
+      </c>
+      <c r="F76" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G76" s="2">
+        <v>2</v>
+      </c>
+      <c r="H76" s="2"/>
+      <c r="I76" s="2"/>
+      <c r="K76" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A77" s="6">
+        <v>45</v>
+      </c>
+      <c r="B77" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" t="s">
+        <v>94</v>
+      </c>
+      <c r="D77" t="s">
+        <v>113</v>
+      </c>
+      <c r="E77" s="5">
+        <v>65858</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G77" s="2">
+        <v>5</v>
+      </c>
+      <c r="H77" s="2"/>
+      <c r="I77" s="2"/>
+      <c r="K77" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A78" s="6">
+        <v>106</v>
+      </c>
+      <c r="B78" t="s">
+        <v>46</v>
+      </c>
+      <c r="C78" t="s">
+        <v>94</v>
+      </c>
+      <c r="E78" s="5">
+        <v>63673</v>
+      </c>
+      <c r="F78" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G78" s="2">
+        <v>5</v>
+      </c>
+      <c r="H78" s="2"/>
+      <c r="I78" s="2"/>
+      <c r="K78" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A79" s="6">
+        <v>52</v>
+      </c>
+      <c r="B79" t="s">
+        <v>117</v>
+      </c>
+      <c r="C79" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E79" s="5">
+        <v>65695</v>
+      </c>
+      <c r="F79" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G79" s="2">
+        <v>4</v>
+      </c>
+      <c r="H79" s="2"/>
+      <c r="I79" s="2"/>
+      <c r="K79" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A80" s="6">
+        <v>53</v>
+      </c>
+      <c r="B80" t="s">
+        <v>118</v>
+      </c>
+      <c r="C80" t="s">
+        <v>167</v>
+      </c>
+      <c r="E80" s="5">
+        <v>65644</v>
+      </c>
+      <c r="F80" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G80" s="2">
+        <v>3</v>
+      </c>
+      <c r="H80" s="2"/>
+      <c r="I80" s="2"/>
+      <c r="K80" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A81" s="6">
+        <v>63</v>
+      </c>
+      <c r="B81" t="s">
+        <v>128</v>
+      </c>
+      <c r="C81" t="s">
+        <v>177</v>
+      </c>
+      <c r="E81" s="5">
+        <v>65466</v>
+      </c>
+      <c r="F81" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G81" s="2">
+        <v>4</v>
+      </c>
+      <c r="H81" s="2"/>
+      <c r="I81" s="2"/>
+      <c r="K81" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A82" s="6">
+        <v>14</v>
+      </c>
+      <c r="B82" t="s">
+        <v>16</v>
+      </c>
+      <c r="C82" t="s">
+        <v>64</v>
+      </c>
+      <c r="E82" s="5">
+        <v>66605</v>
+      </c>
+      <c r="F82" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G82" s="2">
+        <v>3</v>
+      </c>
+      <c r="H82" s="2"/>
+      <c r="I82" s="2"/>
+      <c r="K82" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A83" s="6">
+        <v>7</v>
+      </c>
+      <c r="B83" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" t="s">
+        <v>57</v>
+      </c>
+      <c r="E83" s="5">
+        <v>66760</v>
+      </c>
+      <c r="F83" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G83" s="2">
+        <v>1</v>
+      </c>
+      <c r="H83" s="2"/>
+      <c r="I83" s="2"/>
+      <c r="K83" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A84" s="6">
+        <v>43</v>
+      </c>
+      <c r="B84" t="s">
+        <v>44</v>
+      </c>
+      <c r="C84" t="s">
+        <v>92</v>
+      </c>
+      <c r="D84" t="s">
+        <v>115</v>
+      </c>
+      <c r="E84" s="5">
+        <v>65949</v>
+      </c>
+      <c r="F84" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G84" s="2">
+        <v>4</v>
+      </c>
+      <c r="H84" s="2"/>
+      <c r="I84" s="2"/>
+      <c r="K84" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A85" s="6">
+        <v>27</v>
+      </c>
+      <c r="B85" t="s">
+        <v>28</v>
+      </c>
+      <c r="C85" t="s">
+        <v>76</v>
+      </c>
+      <c r="E85" s="5">
+        <v>66231</v>
+      </c>
+      <c r="F85" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G85" s="2">
+        <v>1</v>
+      </c>
+      <c r="H85" s="2"/>
+      <c r="I85" s="2"/>
+      <c r="K85" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A86" s="6">
+        <v>82</v>
+      </c>
+      <c r="B86" t="s">
+        <v>147</v>
+      </c>
+      <c r="C86" t="s">
+        <v>196</v>
+      </c>
+      <c r="E86" s="5">
+        <v>64977</v>
+      </c>
+      <c r="F86" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G86" s="2">
+        <v>2</v>
+      </c>
+      <c r="H86" s="2"/>
+      <c r="I86" s="2"/>
+      <c r="K86" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A87" s="6">
+        <v>59</v>
+      </c>
+      <c r="B87" t="s">
+        <v>124</v>
+      </c>
+      <c r="C87" t="s">
+        <v>173</v>
+      </c>
+      <c r="E87" s="5">
+        <v>65512</v>
+      </c>
+      <c r="F87" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G87" s="2">
+        <v>2</v>
+      </c>
+      <c r="H87" s="2"/>
+      <c r="I87" s="2"/>
+      <c r="K87" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A88" s="6">
+        <v>76</v>
+      </c>
+      <c r="B88" t="s">
+        <v>141</v>
+      </c>
+      <c r="C88" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="E88" s="5">
+        <v>65291</v>
+      </c>
+      <c r="F88" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G88" s="2">
+        <v>5</v>
+      </c>
+      <c r="H88" s="2"/>
+      <c r="I88" s="2"/>
+      <c r="K88" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A89" s="6">
+        <v>48</v>
+      </c>
+      <c r="B89" t="s">
+        <v>49</v>
+      </c>
+      <c r="C89" t="s">
+        <v>97</v>
+      </c>
+      <c r="D89" t="s">
+        <v>110</v>
+      </c>
+      <c r="E89" s="5">
+        <v>65825</v>
+      </c>
+      <c r="F89" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G89" s="2">
+        <v>4</v>
+      </c>
+      <c r="H89" s="2"/>
+      <c r="I89" s="2"/>
+      <c r="K89" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A90" s="6">
+        <v>42</v>
+      </c>
+      <c r="B90" t="s">
+        <v>43</v>
+      </c>
+      <c r="C90" t="s">
+        <v>91</v>
+      </c>
+      <c r="E90" s="5">
+        <v>65972</v>
+      </c>
+      <c r="F90" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G90" s="2">
+        <v>3</v>
+      </c>
+      <c r="H90" s="2"/>
+      <c r="I90" s="2"/>
+      <c r="K90" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A91" s="6">
+        <v>12</v>
+      </c>
+      <c r="B91" t="s">
+        <v>14</v>
+      </c>
+      <c r="C91" t="s">
+        <v>62</v>
+      </c>
+      <c r="E91" s="5">
+        <v>66668</v>
+      </c>
+      <c r="F91" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G91" s="2">
+        <v>1</v>
+      </c>
+      <c r="H91" s="2"/>
+      <c r="I91" s="2"/>
+      <c r="K91" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A92" s="6">
+        <v>65</v>
+      </c>
+      <c r="B92" t="s">
+        <v>130</v>
+      </c>
+      <c r="C92" t="s">
+        <v>179</v>
+      </c>
+      <c r="E92" s="5">
+        <v>65440</v>
+      </c>
+      <c r="F92" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G92" s="2">
+        <v>6</v>
+      </c>
+      <c r="H92" s="2"/>
+      <c r="I92" s="2"/>
+      <c r="K92" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A93" s="6">
+        <v>8</v>
+      </c>
+      <c r="B93" t="s">
+        <v>10</v>
+      </c>
+      <c r="C93" t="s">
+        <v>58</v>
+      </c>
+      <c r="E93" s="5">
+        <v>66711</v>
+      </c>
+      <c r="F93" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G93" s="2">
+        <v>4</v>
+      </c>
+      <c r="H93" s="2"/>
+      <c r="I93" s="2"/>
+      <c r="K93" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A94" s="6">
+        <v>50</v>
+      </c>
+      <c r="B94" t="s">
+        <v>51</v>
+      </c>
+      <c r="C94" t="s">
+        <v>99</v>
+      </c>
+      <c r="D94" t="s">
+        <v>108</v>
+      </c>
+      <c r="E94" s="5">
+        <v>65762</v>
+      </c>
+      <c r="F94" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G94" s="2">
+        <v>2</v>
+      </c>
+      <c r="H94" s="2"/>
+      <c r="I94" s="2"/>
+      <c r="K94" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A95" s="6">
+        <v>94</v>
+      </c>
+      <c r="B95" t="s">
+        <v>158</v>
+      </c>
+      <c r="C95" t="s">
+        <v>207</v>
+      </c>
+      <c r="E95" s="5">
+        <v>64320</v>
+      </c>
+      <c r="F95" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G95" s="2">
+        <v>4</v>
+      </c>
+      <c r="H95" s="2"/>
+      <c r="I95" s="2"/>
+      <c r="K95" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A96" s="6">
+        <v>54</v>
+      </c>
+      <c r="B96" t="s">
+        <v>119</v>
+      </c>
+      <c r="C96" t="s">
+        <v>168</v>
+      </c>
+      <c r="E96" s="5">
+        <v>65631</v>
+      </c>
+      <c r="F96" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G96" s="2">
+        <v>4</v>
+      </c>
+      <c r="H96" s="2"/>
+      <c r="I96" s="2"/>
+      <c r="K96" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A97" s="6">
+        <v>21</v>
+      </c>
+      <c r="B97" t="s">
+        <v>23</v>
+      </c>
+      <c r="C97" t="s">
+        <v>71</v>
+      </c>
+      <c r="E97" s="5">
+        <v>66423</v>
+      </c>
+      <c r="F97" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G97" s="2">
+        <v>5</v>
+      </c>
+      <c r="H97" s="2"/>
+      <c r="I97" s="2"/>
+      <c r="K97" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A98" s="6">
+        <v>85</v>
+      </c>
+      <c r="B98" t="s">
+        <v>150</v>
+      </c>
+      <c r="C98" t="s">
+        <v>199</v>
+      </c>
+      <c r="E98" s="5">
+        <v>64813</v>
+      </c>
+      <c r="F98" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G98" s="2">
+        <v>4</v>
+      </c>
+      <c r="H98" s="2"/>
+      <c r="I98" s="2"/>
+      <c r="K98" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A99" s="6">
+        <v>55</v>
+      </c>
+      <c r="B99" t="s">
+        <v>120</v>
+      </c>
+      <c r="C99" t="s">
+        <v>169</v>
+      </c>
+      <c r="E99" s="5">
+        <v>65631</v>
+      </c>
+      <c r="F99" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G99" s="2">
+        <v>7</v>
+      </c>
+      <c r="H99" s="2"/>
+      <c r="I99" s="2"/>
+      <c r="K99" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A100" s="6">
+        <v>13</v>
+      </c>
+      <c r="B100" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" t="s">
+        <v>63</v>
+      </c>
+      <c r="E100" s="5">
+        <v>66618</v>
+      </c>
+      <c r="F100" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G100" s="2">
+        <v>4</v>
+      </c>
+      <c r="H100" s="2"/>
+      <c r="I100" s="2"/>
+      <c r="K100" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A101" s="6">
+        <v>32</v>
+      </c>
+      <c r="B101" t="s">
+        <v>33</v>
+      </c>
+      <c r="C101" t="s">
+        <v>81</v>
+      </c>
+      <c r="E101" s="5">
+        <v>66169</v>
+      </c>
+      <c r="F101" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G101" s="2">
+        <v>6</v>
+      </c>
+      <c r="H101" s="2"/>
+      <c r="I101" s="2"/>
+      <c r="K101" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A102" s="6">
+        <v>18</v>
+      </c>
+      <c r="B102" t="s">
+        <v>20</v>
+      </c>
+      <c r="C102" t="s">
+        <v>68</v>
+      </c>
+      <c r="E102" s="5">
+        <v>66587</v>
+      </c>
+      <c r="F102" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G102" s="2">
+        <v>4</v>
+      </c>
+      <c r="H102" s="2"/>
+      <c r="I102" s="2"/>
+      <c r="K102" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A103" s="6">
+        <v>70</v>
+      </c>
+      <c r="B103" t="s">
+        <v>135</v>
+      </c>
+      <c r="C103" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="E103" s="5">
+        <v>65356</v>
+      </c>
+      <c r="F103" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G103" s="2">
+        <v>5</v>
+      </c>
+      <c r="H103" s="2"/>
+      <c r="I103" s="2"/>
+      <c r="K103" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A104" s="6">
+        <v>26</v>
+      </c>
+      <c r="B104" t="s">
+        <v>27</v>
+      </c>
+      <c r="C104" t="s">
+        <v>75</v>
+      </c>
+      <c r="E104" s="5">
+        <v>66240</v>
+      </c>
+      <c r="F104" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G104" s="2">
+        <v>5</v>
+      </c>
+      <c r="H104" s="2"/>
+      <c r="I104" s="2"/>
+      <c r="K104" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A105" s="6">
+        <v>4</v>
+      </c>
+      <c r="B105" t="s">
+        <v>6</v>
+      </c>
+      <c r="C105" t="s">
+        <v>54</v>
+      </c>
+      <c r="E105" s="5">
+        <v>66828</v>
+      </c>
+      <c r="F105" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G105" s="2">
+        <v>2</v>
+      </c>
+      <c r="H105" s="2"/>
+      <c r="I105" s="2"/>
+      <c r="K105" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A106" s="6">
+        <v>24</v>
+      </c>
+      <c r="B106" t="s">
+        <v>26</v>
+      </c>
+      <c r="C106" t="s">
+        <v>74</v>
+      </c>
+      <c r="E106" s="5">
+        <v>66262</v>
+      </c>
+      <c r="F106" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G106" s="2">
+        <v>8</v>
+      </c>
+      <c r="H106" s="2"/>
+      <c r="I106" s="2"/>
+      <c r="K106" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A107" s="6">
+        <v>20</v>
+      </c>
+      <c r="B107" t="s">
+        <v>22</v>
+      </c>
+      <c r="C107" t="s">
+        <v>70</v>
+      </c>
+      <c r="E107" s="5">
+        <v>66559</v>
+      </c>
+      <c r="F107" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="G107" s="2">
+        <v>1</v>
+      </c>
+      <c r="H107" s="2"/>
+      <c r="I107" s="2"/>
+      <c r="K107" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A108" s="6">
+        <v>17</v>
+      </c>
+      <c r="B108" t="s">
+        <v>18</v>
+      </c>
+      <c r="C108" t="s">
+        <v>67</v>
+      </c>
+      <c r="E108" s="5">
+        <v>66589</v>
+      </c>
+      <c r="F108" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G108" s="2">
+        <v>6</v>
+      </c>
+      <c r="H108" s="2"/>
+      <c r="I108" s="2"/>
+      <c r="K108" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A109" s="6">
+        <v>74</v>
+      </c>
+      <c r="B109" t="s">
+        <v>139</v>
+      </c>
+      <c r="C109" t="s">
+        <v>188</v>
+      </c>
+      <c r="E109" s="5">
+        <v>65304</v>
+      </c>
+      <c r="F109" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G109" s="2">
+        <v>2</v>
+      </c>
+      <c r="H109" s="2"/>
+      <c r="I109" s="2"/>
+      <c r="K109" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A110" s="6">
+        <v>93</v>
+      </c>
+      <c r="B110" t="s">
+        <v>157</v>
+      </c>
+      <c r="C110" t="s">
+        <v>206</v>
+      </c>
+      <c r="E110" s="5">
+        <v>64395</v>
+      </c>
+      <c r="F110" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="G110" s="2">
+        <v>2</v>
+      </c>
+      <c r="H110" s="2"/>
+      <c r="I110" s="2"/>
+      <c r="K110" t="s">
+        <v>242</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:L110">
+    <sortState ref="A2:L110">
+      <sortCondition ref="B1:B110"/>
+    </sortState>
+  </autoFilter>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F1:F110">
+      <formula1>$F$3:$F$22</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>Reasons!$A$2:$A$7</xm:f>
+          </x14:formula1>
+          <xm:sqref>K1:K110</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="12" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="10" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="13" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>240</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>242</v>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>

--- a/migration/list of immigrants.xlsx
+++ b/migration/list of immigrants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\migration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C5AB4180-C04B-452B-8617-49CB56394CE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F86C36-74A1-43A3-9E96-701E75D4E017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -174,7 +174,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="630">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="711">
   <si>
     <t>Vikash Karki</t>
   </si>
@@ -2086,6 +2086,249 @@
   </si>
   <si>
     <t>;+lha tfdfª</t>
+  </si>
+  <si>
+    <t>k'gd ;]8fO ld&gt;</t>
+  </si>
+  <si>
+    <t>s]bf/ yfkf</t>
+  </si>
+  <si>
+    <t>ljzfn yfkf</t>
+  </si>
+  <si>
+    <t>jiff{ yfkf</t>
+  </si>
+  <si>
+    <t>/f]lhgf yfkf</t>
+  </si>
+  <si>
+    <t>ljjz yfkf</t>
+  </si>
+  <si>
+    <t>ljZjf; yfkf</t>
+  </si>
+  <si>
+    <t>;'lgtf /}nf</t>
+  </si>
+  <si>
+    <t>;Dj[lb yfkf</t>
+  </si>
+  <si>
+    <t>a]|G8]g yfkf</t>
+  </si>
+  <si>
+    <t>k'?iff]Qd v8\sf</t>
+  </si>
+  <si>
+    <t>;'lznf v8\sf</t>
+  </si>
+  <si>
+    <t>k'ikf v8\sf</t>
+  </si>
+  <si>
+    <t>k'is/ v8\sf</t>
+  </si>
+  <si>
+    <t>Rofd' nfn rf}w/L</t>
+  </si>
+  <si>
+    <t>lg/h rf}w/L</t>
+  </si>
+  <si>
+    <t>lgzfGt rf}w/L</t>
+  </si>
+  <si>
+    <t>e'jg rf}w/L</t>
+  </si>
+  <si>
+    <t>l8NnL s'df/L &gt;]i7</t>
+  </si>
+  <si>
+    <t>k|]d axfb'/ &gt;]i7</t>
+  </si>
+  <si>
+    <t>k'gd &gt;]i7</t>
+  </si>
+  <si>
+    <t>k|lbk &gt;]i7</t>
+  </si>
+  <si>
+    <t>o1 axfb'/ j/fn</t>
+  </si>
+  <si>
+    <t>/df &gt;]i7</t>
+  </si>
+  <si>
+    <t>;f]d s'df/ /fO{</t>
+  </si>
+  <si>
+    <t>vf]l/gf /fO{</t>
+  </si>
+  <si>
+    <t>s?0ff /fO{</t>
+  </si>
+  <si>
+    <t>hf]/dtL /fO{</t>
+  </si>
+  <si>
+    <t>/fdnfn l3ld/]</t>
+  </si>
+  <si>
+    <t>led s'df/L b'nfn</t>
+  </si>
+  <si>
+    <t>tf/fgfy b'nfn</t>
+  </si>
+  <si>
+    <t>dLgfb]jL ;'j]bL</t>
+  </si>
+  <si>
+    <t>;'/h b'nfn</t>
+  </si>
+  <si>
+    <t>;'htf b'nfn</t>
+  </si>
+  <si>
+    <t>5]q axfb'/ &gt;]i7</t>
+  </si>
+  <si>
+    <t>;]tL dfof &gt;]i7</t>
+  </si>
+  <si>
+    <t>Vofg axfb'/ &gt;]i7</t>
+  </si>
+  <si>
+    <t>clgz &gt;]i7</t>
+  </si>
+  <si>
+    <t>clgzf &gt;]i7</t>
+  </si>
+  <si>
+    <t>s]zj s'df/ &gt;]i7</t>
+  </si>
+  <si>
+    <t>lutf b]jL &gt;]i7</t>
+  </si>
+  <si>
+    <t>;l/g s'df/ &gt;]i7</t>
+  </si>
+  <si>
+    <t>;lng s'df/ &gt;]i7</t>
+  </si>
+  <si>
+    <t>u+uf/fd 8+uf]n</t>
+  </si>
+  <si>
+    <t>sfnLdfof 8+uf]n</t>
+  </si>
+  <si>
+    <t>g/Wjh yfkf</t>
+  </si>
+  <si>
+    <t>;+lutf yfkf</t>
+  </si>
+  <si>
+    <t>g/dfof yfkf</t>
+  </si>
+  <si>
+    <t>;ld/ yfkf</t>
+  </si>
+  <si>
+    <t>s[i0f k|;fb rf}nfufO{</t>
+  </si>
+  <si>
+    <t>cl:dtf rf}nfufO{</t>
+  </si>
+  <si>
+    <t>cfo'if rf}nfufO{</t>
+  </si>
+  <si>
+    <t>cfo'idf rf}nfufO{</t>
+  </si>
+  <si>
+    <t>/fh]Gb| k|;fb kf]v|]n</t>
+  </si>
+  <si>
+    <t>d08Lsf yfdL</t>
+  </si>
+  <si>
+    <t>/:dL kf]v|]n</t>
+  </si>
+  <si>
+    <t>ef]h s'df/L kf}8]n</t>
+  </si>
+  <si>
+    <t>;GbLk kf}8]n</t>
+  </si>
+  <si>
+    <t>nIdL k|;fb ltjf/L</t>
+  </si>
+  <si>
+    <t>k"0f{ dfof clwsf/L</t>
+  </si>
+  <si>
+    <t>s[i0f k|;fb ltjf/L</t>
+  </si>
+  <si>
+    <t>/Tg s'df/L &gt;]i7</t>
+  </si>
+  <si>
+    <t>/fd nfn &gt;]i7</t>
+  </si>
+  <si>
+    <t>;/:jtL &gt;]i7</t>
+  </si>
+  <si>
+    <t>l/ltdf &gt;]i7</t>
+  </si>
+  <si>
+    <t>cflbTo &gt;]i7</t>
+  </si>
+  <si>
+    <t>hLa k|;fb bfxfn</t>
+  </si>
+  <si>
+    <t>s]z/ s'df/L bfxfn</t>
+  </si>
+  <si>
+    <t>lgzf zdf{</t>
+  </si>
+  <si>
+    <t>kf]if0f s'df/L zdf{</t>
+  </si>
+  <si>
+    <t>g]z' zdf{</t>
+  </si>
+  <si>
+    <t>piff zdf{</t>
+  </si>
+  <si>
+    <t>rGb| axfb'ª a:g]t</t>
+  </si>
+  <si>
+    <t>kz'klt sfsL{</t>
+  </si>
+  <si>
+    <t>r'8fd0fL vgfn</t>
+  </si>
+  <si>
+    <t>;'gfb]jL clwsf/L</t>
+  </si>
+  <si>
+    <t>;'j0f{ vgfn</t>
+  </si>
+  <si>
+    <t>d'/f/L ;'j]bL</t>
+  </si>
+  <si>
+    <t>;'ldqf ;'j]bL</t>
+  </si>
+  <si>
+    <t>laa]s ;'j]bL</t>
+  </si>
+  <si>
+    <t>;[li6 ;'j]bL</t>
   </si>
 </sst>
 </file>
@@ -2235,7 +2478,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2268,6 +2511,9 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2289,10 +2535,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2573,7 +2815,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N326"/>
+  <dimension ref="A1:N394"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="4" bestFit="1" customWidth="1"/>
@@ -2602,7 +2844,7 @@
       <c r="C1" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="21" t="s">
+      <c r="D1" s="14" t="s">
         <v>342</v>
       </c>
       <c r="E1" s="7" t="s">
@@ -2614,21 +2856,21 @@
       <c r="G1" s="8" t="s">
         <v>101</v>
       </c>
-      <c r="H1" s="14" t="s">
+      <c r="H1" s="17" t="s">
         <v>105</v>
       </c>
-      <c r="I1" s="15"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="18" t="s">
+      <c r="I1" s="18"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="21" t="s">
         <v>236</v>
       </c>
-      <c r="L1" s="17" t="s">
+      <c r="L1" s="20" t="s">
         <v>246</v>
       </c>
-      <c r="M1" s="19" t="s">
+      <c r="M1" s="22" t="s">
         <v>243</v>
       </c>
-      <c r="N1" s="20" t="s">
+      <c r="N1" s="23" t="s">
         <v>247</v>
       </c>
     </row>
@@ -2649,10 +2891,10 @@
       <c r="J2" s="8" t="s">
         <v>234</v>
       </c>
-      <c r="K2" s="18"/>
-      <c r="L2" s="17"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="20"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="22"/>
+      <c r="N2" s="23"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="B3" s="4"/>
@@ -2675,7 +2917,7 @@
       <c r="B4" t="s">
         <v>0</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="15" t="s">
         <v>352</v>
       </c>
       <c r="D4" s="5">
@@ -2711,7 +2953,7 @@
     </row>
     <row r="5" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A5" s="6"/>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="15" t="s">
         <v>343</v>
       </c>
       <c r="D5" s="5">
@@ -2724,7 +2966,7 @@
     </row>
     <row r="6" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A6" s="6"/>
-      <c r="C6" s="22" t="s">
+      <c r="C6" s="15" t="s">
         <v>344</v>
       </c>
       <c r="D6" s="5">
@@ -2737,7 +2979,7 @@
     </row>
     <row r="7" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A7" s="6"/>
-      <c r="C7" s="22" t="s">
+      <c r="C7" s="15" t="s">
         <v>345</v>
       </c>
       <c r="D7" s="5">
@@ -2755,7 +2997,7 @@
       <c r="B8" t="s">
         <v>3</v>
       </c>
-      <c r="C8" s="22" t="s">
+      <c r="C8" s="15" t="s">
         <v>353</v>
       </c>
       <c r="D8" s="5">
@@ -2795,7 +3037,7 @@
     </row>
     <row r="9" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A9" s="6"/>
-      <c r="C9" s="22" t="s">
+      <c r="C9" s="15" t="s">
         <v>346</v>
       </c>
       <c r="D9" s="5">
@@ -2808,7 +3050,7 @@
     </row>
     <row r="10" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A10" s="6"/>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="15" t="s">
         <v>348</v>
       </c>
       <c r="D10" s="5">
@@ -2821,7 +3063,7 @@
     </row>
     <row r="11" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A11" s="6"/>
-      <c r="C11" s="22" t="s">
+      <c r="C11" s="15" t="s">
         <v>345</v>
       </c>
       <c r="D11" s="5">
@@ -2839,7 +3081,7 @@
       <c r="B12" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="15" t="s">
         <v>354</v>
       </c>
       <c r="D12" s="5">
@@ -2876,7 +3118,7 @@
     </row>
     <row r="13" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A13" s="6"/>
-      <c r="C13" s="22" t="s">
+      <c r="C13" s="15" t="s">
         <v>347</v>
       </c>
       <c r="D13" s="5">
@@ -2889,7 +3131,7 @@
     </row>
     <row r="14" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A14" s="6"/>
-      <c r="C14" s="22" t="s">
+      <c r="C14" s="15" t="s">
         <v>349</v>
       </c>
       <c r="D14" s="5">
@@ -2902,7 +3144,7 @@
     </row>
     <row r="15" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A15" s="6"/>
-      <c r="C15" s="22" t="s">
+      <c r="C15" s="15" t="s">
         <v>350</v>
       </c>
       <c r="D15" s="5">
@@ -2915,7 +3157,7 @@
     </row>
     <row r="16" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A16" s="6"/>
-      <c r="C16" s="22" t="s">
+      <c r="C16" s="15" t="s">
         <v>351</v>
       </c>
       <c r="D16" s="5">
@@ -2933,7 +3175,7 @@
       <c r="B17" t="s">
         <v>6</v>
       </c>
-      <c r="C17" s="22" t="s">
+      <c r="C17" s="15" t="s">
         <v>355</v>
       </c>
       <c r="D17" s="5">
@@ -2970,7 +3212,7 @@
     </row>
     <row r="18" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A18" s="6"/>
-      <c r="C18" s="22" t="s">
+      <c r="C18" s="15" t="s">
         <v>356</v>
       </c>
       <c r="D18" s="5">
@@ -2988,7 +3230,7 @@
       <c r="B19" t="s">
         <v>7</v>
       </c>
-      <c r="C19" s="22" t="s">
+      <c r="C19" s="15" t="s">
         <v>357</v>
       </c>
       <c r="D19" s="5">
@@ -3025,7 +3267,7 @@
     </row>
     <row r="20" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
-      <c r="C20" s="22" t="s">
+      <c r="C20" s="15" t="s">
         <v>358</v>
       </c>
       <c r="D20" s="5">
@@ -3038,7 +3280,7 @@
     </row>
     <row r="21" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
-      <c r="C21" s="22" t="s">
+      <c r="C21" s="15" t="s">
         <v>359</v>
       </c>
       <c r="D21" s="5">
@@ -3051,7 +3293,7 @@
     </row>
     <row r="22" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
-      <c r="C22" s="22" t="s">
+      <c r="C22" s="15" t="s">
         <v>360</v>
       </c>
       <c r="D22" s="5">
@@ -3069,7 +3311,7 @@
       <c r="B23" t="s">
         <v>8</v>
       </c>
-      <c r="C23" s="22" t="s">
+      <c r="C23" s="15" t="s">
         <v>361</v>
       </c>
       <c r="D23" s="5">
@@ -3108,7 +3350,7 @@
       <c r="B24" t="s">
         <v>9</v>
       </c>
-      <c r="C24" s="22" t="s">
+      <c r="C24" s="15" t="s">
         <v>362</v>
       </c>
       <c r="D24" s="5">
@@ -3147,7 +3389,7 @@
       <c r="B25" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="22" t="s">
+      <c r="C25" s="15" t="s">
         <v>363</v>
       </c>
       <c r="D25" s="5">
@@ -3184,7 +3426,7 @@
     </row>
     <row r="26" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
-      <c r="C26" s="22" t="s">
+      <c r="C26" s="15" t="s">
         <v>364</v>
       </c>
       <c r="D26" s="5">
@@ -3197,7 +3439,7 @@
     </row>
     <row r="27" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
-      <c r="C27" s="22" t="s">
+      <c r="C27" s="15" t="s">
         <v>365</v>
       </c>
       <c r="D27" s="5">
@@ -3210,7 +3452,7 @@
     </row>
     <row r="28" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
-      <c r="C28" s="22" t="s">
+      <c r="C28" s="15" t="s">
         <v>366</v>
       </c>
       <c r="D28" s="5">
@@ -3228,7 +3470,7 @@
       <c r="B29" t="s">
         <v>11</v>
       </c>
-      <c r="C29" s="22" t="s">
+      <c r="C29" s="15" t="s">
         <v>367</v>
       </c>
       <c r="D29" s="5">
@@ -3265,7 +3507,7 @@
     </row>
     <row r="30" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
-      <c r="C30" s="22" t="s">
+      <c r="C30" s="15" t="s">
         <v>368</v>
       </c>
       <c r="D30" s="5">
@@ -3278,7 +3520,7 @@
     </row>
     <row r="31" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
-      <c r="C31" s="22" t="s">
+      <c r="C31" s="15" t="s">
         <v>369</v>
       </c>
       <c r="D31" s="5">
@@ -3291,7 +3533,7 @@
     </row>
     <row r="32" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
-      <c r="C32" s="22" t="s">
+      <c r="C32" s="15" t="s">
         <v>370</v>
       </c>
       <c r="D32" s="5">
@@ -3309,7 +3551,7 @@
       <c r="B33" t="s">
         <v>12</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="15" t="s">
         <v>371</v>
       </c>
       <c r="D33" s="5"/>
@@ -3337,7 +3579,7 @@
       <c r="B34" t="s">
         <v>13</v>
       </c>
-      <c r="C34" s="22" t="s">
+      <c r="C34" s="15" t="s">
         <v>372</v>
       </c>
       <c r="D34" s="5">
@@ -3374,7 +3616,7 @@
     </row>
     <row r="35" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A35" s="6"/>
-      <c r="C35" s="22" t="s">
+      <c r="C35" s="15" t="s">
         <v>373</v>
       </c>
       <c r="D35" s="5">
@@ -3387,7 +3629,7 @@
     </row>
     <row r="36" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A36" s="6"/>
-      <c r="C36" s="22" t="s">
+      <c r="C36" s="15" t="s">
         <v>374</v>
       </c>
       <c r="D36" s="5">
@@ -3400,7 +3642,7 @@
     </row>
     <row r="37" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A37" s="6"/>
-      <c r="C37" s="22" t="s">
+      <c r="C37" s="15" t="s">
         <v>375</v>
       </c>
       <c r="D37" s="5">
@@ -3413,7 +3655,7 @@
     </row>
     <row r="38" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A38" s="6"/>
-      <c r="C38" s="22" t="s">
+      <c r="C38" s="15" t="s">
         <v>376</v>
       </c>
       <c r="D38" s="5">
@@ -3426,7 +3668,7 @@
     </row>
     <row r="39" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A39" s="6"/>
-      <c r="C39" s="22" t="s">
+      <c r="C39" s="15" t="s">
         <v>377</v>
       </c>
       <c r="D39" s="5">
@@ -3439,7 +3681,7 @@
     </row>
     <row r="40" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A40" s="6"/>
-      <c r="C40" s="22" t="s">
+      <c r="C40" s="15" t="s">
         <v>378</v>
       </c>
       <c r="D40" s="5">
@@ -3452,7 +3694,7 @@
     </row>
     <row r="41" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A41" s="6"/>
-      <c r="C41" s="22" t="s">
+      <c r="C41" s="15" t="s">
         <v>379</v>
       </c>
       <c r="D41" s="5">
@@ -3470,7 +3712,7 @@
       <c r="B42" t="s">
         <v>14</v>
       </c>
-      <c r="C42" s="22" t="s">
+      <c r="C42" s="15" t="s">
         <v>380</v>
       </c>
       <c r="D42" s="5">
@@ -3509,7 +3751,7 @@
       <c r="B43" t="s">
         <v>15</v>
       </c>
-      <c r="C43" s="22" t="s">
+      <c r="C43" s="15" t="s">
         <v>381</v>
       </c>
       <c r="D43" s="5">
@@ -3542,7 +3784,7 @@
     </row>
     <row r="44" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A44" s="6"/>
-      <c r="C44" s="22" t="s">
+      <c r="C44" s="15" t="s">
         <v>382</v>
       </c>
       <c r="D44" s="5">
@@ -3552,7 +3794,7 @@
     </row>
     <row r="45" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A45" s="6"/>
-      <c r="C45" s="22" t="s">
+      <c r="C45" s="15" t="s">
         <v>383</v>
       </c>
       <c r="D45" s="5">
@@ -3562,7 +3804,7 @@
     </row>
     <row r="46" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A46" s="6"/>
-      <c r="C46" s="22" t="s">
+      <c r="C46" s="15" t="s">
         <v>384</v>
       </c>
       <c r="D46" s="5">
@@ -3577,7 +3819,7 @@
       <c r="B47" t="s">
         <v>16</v>
       </c>
-      <c r="C47" s="22" t="s">
+      <c r="C47" s="15" t="s">
         <v>385</v>
       </c>
       <c r="D47" s="5">
@@ -3610,7 +3852,7 @@
     </row>
     <row r="48" spans="1:14" ht="18" x14ac:dyDescent="0.25">
       <c r="A48" s="6"/>
-      <c r="C48" s="22" t="s">
+      <c r="C48" s="15" t="s">
         <v>386</v>
       </c>
       <c r="D48" s="5">
@@ -3620,7 +3862,7 @@
     </row>
     <row r="49" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A49" s="6"/>
-      <c r="C49" s="23" t="s">
+      <c r="C49" s="16" t="s">
         <v>387</v>
       </c>
       <c r="D49" s="5">
@@ -3635,7 +3877,7 @@
       <c r="B50" t="s">
         <v>17</v>
       </c>
-      <c r="C50" s="23" t="s">
+      <c r="C50" s="16" t="s">
         <v>388</v>
       </c>
       <c r="D50" s="5">
@@ -3668,7 +3910,7 @@
     </row>
     <row r="51" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A51" s="6"/>
-      <c r="C51" s="23" t="s">
+      <c r="C51" s="16" t="s">
         <v>389</v>
       </c>
       <c r="D51" s="5">
@@ -3678,7 +3920,7 @@
     </row>
     <row r="52" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A52" s="6"/>
-      <c r="C52" s="23" t="s">
+      <c r="C52" s="16" t="s">
         <v>390</v>
       </c>
       <c r="D52" s="5">
@@ -3688,7 +3930,7 @@
     </row>
     <row r="53" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A53" s="6"/>
-      <c r="C53" s="23" t="s">
+      <c r="C53" s="16" t="s">
         <v>391</v>
       </c>
       <c r="D53" s="5">
@@ -3703,7 +3945,7 @@
       <c r="B54" t="s">
         <v>19</v>
       </c>
-      <c r="C54" s="23" t="s">
+      <c r="C54" s="16" t="s">
         <v>392</v>
       </c>
       <c r="D54" s="5">
@@ -3736,7 +3978,7 @@
     </row>
     <row r="55" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A55" s="6"/>
-      <c r="C55" s="23" t="s">
+      <c r="C55" s="16" t="s">
         <v>393</v>
       </c>
       <c r="D55" s="5">
@@ -3746,7 +3988,7 @@
     </row>
     <row r="56" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A56" s="6"/>
-      <c r="C56" s="23" t="s">
+      <c r="C56" s="16" t="s">
         <v>394</v>
       </c>
       <c r="D56" s="5">
@@ -3761,7 +4003,7 @@
       <c r="B57" t="s">
         <v>18</v>
       </c>
-      <c r="C57" s="23" t="s">
+      <c r="C57" s="16" t="s">
         <v>395</v>
       </c>
       <c r="D57" s="5">
@@ -3794,7 +4036,7 @@
     </row>
     <row r="58" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A58" s="6"/>
-      <c r="C58" s="23" t="s">
+      <c r="C58" s="16" t="s">
         <v>396</v>
       </c>
       <c r="D58" s="5">
@@ -3804,7 +4046,7 @@
     </row>
     <row r="59" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A59" s="6"/>
-      <c r="C59" s="23" t="s">
+      <c r="C59" s="16" t="s">
         <v>397</v>
       </c>
       <c r="D59" s="5">
@@ -3814,7 +4056,7 @@
     </row>
     <row r="60" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A60" s="6"/>
-      <c r="C60" s="23" t="s">
+      <c r="C60" s="16" t="s">
         <v>398</v>
       </c>
       <c r="D60" s="5">
@@ -3824,7 +4066,7 @@
     </row>
     <row r="61" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A61" s="6"/>
-      <c r="C61" s="23" t="s">
+      <c r="C61" s="16" t="s">
         <v>399</v>
       </c>
       <c r="D61" s="5">
@@ -3834,7 +4076,7 @@
     </row>
     <row r="62" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A62" s="6"/>
-      <c r="C62" s="23" t="s">
+      <c r="C62" s="16" t="s">
         <v>400</v>
       </c>
       <c r="D62" s="5">
@@ -3849,7 +4091,7 @@
       <c r="B63" t="s">
         <v>20</v>
       </c>
-      <c r="C63" s="23" t="s">
+      <c r="C63" s="16" t="s">
         <v>401</v>
       </c>
       <c r="D63" s="5">
@@ -3882,7 +4124,7 @@
     </row>
     <row r="64" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A64" s="6"/>
-      <c r="C64" s="23" t="s">
+      <c r="C64" s="16" t="s">
         <v>402</v>
       </c>
       <c r="D64" s="5">
@@ -3892,7 +4134,7 @@
     </row>
     <row r="65" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A65" s="6"/>
-      <c r="C65" s="23" t="s">
+      <c r="C65" s="16" t="s">
         <v>403</v>
       </c>
       <c r="D65" s="5">
@@ -3902,7 +4144,7 @@
     </row>
     <row r="66" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A66" s="6"/>
-      <c r="C66" s="23" t="s">
+      <c r="C66" s="16" t="s">
         <v>404</v>
       </c>
       <c r="D66" s="5">
@@ -3917,7 +4159,7 @@
       <c r="B67" t="s">
         <v>21</v>
       </c>
-      <c r="C67" s="23" t="s">
+      <c r="C67" s="16" t="s">
         <v>405</v>
       </c>
       <c r="D67" s="5">
@@ -3950,7 +4192,7 @@
     </row>
     <row r="68" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A68" s="6"/>
-      <c r="C68" s="23" t="s">
+      <c r="C68" s="16" t="s">
         <v>406</v>
       </c>
       <c r="D68" s="5">
@@ -3960,7 +4202,7 @@
     </row>
     <row r="69" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A69" s="6"/>
-      <c r="C69" s="23" t="s">
+      <c r="C69" s="16" t="s">
         <v>407</v>
       </c>
       <c r="D69" s="5">
@@ -3970,7 +4212,7 @@
     </row>
     <row r="70" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A70" s="6"/>
-      <c r="C70" s="23" t="s">
+      <c r="C70" s="16" t="s">
         <v>408</v>
       </c>
       <c r="D70" s="5">
@@ -3985,7 +4227,7 @@
       <c r="B71" t="s">
         <v>22</v>
       </c>
-      <c r="C71" s="23" t="s">
+      <c r="C71" s="16" t="s">
         <v>409</v>
       </c>
       <c r="D71" s="5">
@@ -4020,7 +4262,7 @@
       <c r="B72" t="s">
         <v>23</v>
       </c>
-      <c r="C72" s="23" t="s">
+      <c r="C72" s="16" t="s">
         <v>410</v>
       </c>
       <c r="D72" s="5">
@@ -4053,7 +4295,7 @@
     </row>
     <row r="73" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A73" s="6"/>
-      <c r="C73" s="23" t="s">
+      <c r="C73" s="16" t="s">
         <v>411</v>
       </c>
       <c r="D73" s="5">
@@ -4063,7 +4305,7 @@
     </row>
     <row r="74" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A74" s="6"/>
-      <c r="C74" s="23" t="s">
+      <c r="C74" s="16" t="s">
         <v>412</v>
       </c>
       <c r="D74" s="5">
@@ -4073,7 +4315,7 @@
     </row>
     <row r="75" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A75" s="6"/>
-      <c r="C75" s="23" t="s">
+      <c r="C75" s="16" t="s">
         <v>413</v>
       </c>
       <c r="D75" s="5">
@@ -4083,7 +4325,7 @@
     </row>
     <row r="76" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A76" s="6"/>
-      <c r="C76" s="23" t="s">
+      <c r="C76" s="16" t="s">
         <v>414</v>
       </c>
       <c r="D76" s="5">
@@ -4098,7 +4340,7 @@
       <c r="B77" t="s">
         <v>24</v>
       </c>
-      <c r="C77" s="23" t="s">
+      <c r="C77" s="16" t="s">
         <v>415</v>
       </c>
       <c r="D77" s="5">
@@ -4131,7 +4373,7 @@
     </row>
     <row r="78" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A78" s="6"/>
-      <c r="C78" s="23" t="s">
+      <c r="C78" s="16" t="s">
         <v>416</v>
       </c>
       <c r="D78" s="5">
@@ -4141,7 +4383,7 @@
     </row>
     <row r="79" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A79" s="6"/>
-      <c r="C79" s="23" t="s">
+      <c r="C79" s="16" t="s">
         <v>417</v>
       </c>
       <c r="D79" s="5">
@@ -4151,7 +4393,7 @@
     </row>
     <row r="80" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A80" s="6"/>
-      <c r="C80" s="23" t="s">
+      <c r="C80" s="16" t="s">
         <v>418</v>
       </c>
       <c r="D80" s="5">
@@ -4161,7 +4403,7 @@
     </row>
     <row r="81" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A81" s="6"/>
-      <c r="C81" s="23" t="s">
+      <c r="C81" s="16" t="s">
         <v>419</v>
       </c>
       <c r="D81" s="5">
@@ -4176,7 +4418,7 @@
       <c r="B82" t="s">
         <v>25</v>
       </c>
-      <c r="C82" s="23" t="s">
+      <c r="C82" s="16" t="s">
         <v>420</v>
       </c>
       <c r="D82" s="5">
@@ -4209,7 +4451,7 @@
     </row>
     <row r="83" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A83" s="6"/>
-      <c r="C83" s="23" t="s">
+      <c r="C83" s="16" t="s">
         <v>421</v>
       </c>
       <c r="D83" s="5">
@@ -4219,7 +4461,7 @@
     </row>
     <row r="84" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A84" s="6"/>
-      <c r="C84" s="23" t="s">
+      <c r="C84" s="16" t="s">
         <v>422</v>
       </c>
       <c r="D84" s="5">
@@ -4229,7 +4471,7 @@
     </row>
     <row r="85" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A85" s="6"/>
-      <c r="C85" s="23" t="s">
+      <c r="C85" s="16" t="s">
         <v>423</v>
       </c>
       <c r="D85" s="5">
@@ -4244,7 +4486,7 @@
       <c r="B86" t="s">
         <v>26</v>
       </c>
-      <c r="C86" s="23" t="s">
+      <c r="C86" s="16" t="s">
         <v>424</v>
       </c>
       <c r="D86" s="5">
@@ -4277,7 +4519,7 @@
     </row>
     <row r="87" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A87" s="6"/>
-      <c r="C87" s="23" t="s">
+      <c r="C87" s="16" t="s">
         <v>425</v>
       </c>
       <c r="D87" s="5">
@@ -4287,7 +4529,7 @@
     </row>
     <row r="88" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A88" s="6"/>
-      <c r="C88" s="23" t="s">
+      <c r="C88" s="16" t="s">
         <v>426</v>
       </c>
       <c r="D88" s="5">
@@ -4297,7 +4539,7 @@
     </row>
     <row r="89" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A89" s="6"/>
-      <c r="C89" s="23" t="s">
+      <c r="C89" s="16" t="s">
         <v>427</v>
       </c>
       <c r="D89" s="5">
@@ -4307,7 +4549,7 @@
     </row>
     <row r="90" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A90" s="6"/>
-      <c r="C90" s="23" t="s">
+      <c r="C90" s="16" t="s">
         <v>428</v>
       </c>
       <c r="D90" s="5">
@@ -4317,7 +4559,7 @@
     </row>
     <row r="91" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A91" s="6"/>
-      <c r="C91" s="23" t="s">
+      <c r="C91" s="16" t="s">
         <v>429</v>
       </c>
       <c r="D91" s="5">
@@ -4327,7 +4569,7 @@
     </row>
     <row r="92" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A92" s="6"/>
-      <c r="C92" s="23" t="s">
+      <c r="C92" s="16" t="s">
         <v>430</v>
       </c>
       <c r="D92" s="5">
@@ -4337,7 +4579,7 @@
     </row>
     <row r="93" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A93" s="6"/>
-      <c r="C93" s="23" t="s">
+      <c r="C93" s="16" t="s">
         <v>431</v>
       </c>
       <c r="D93" s="5">
@@ -4352,7 +4594,7 @@
       <c r="B94" t="s">
         <v>3</v>
       </c>
-      <c r="C94" s="22" t="s">
+      <c r="C94" s="15" t="s">
         <v>353</v>
       </c>
       <c r="D94" s="5">
@@ -4383,30 +4625,28 @@
         <v>332</v>
       </c>
     </row>
-    <row r="95" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A95" s="6"/>
-      <c r="C95" s="22" t="s">
+      <c r="C95" s="15" t="s">
         <v>348</v>
       </c>
       <c r="D95" s="5">
         <v>60709</v>
       </c>
       <c r="F95" s="5"/>
-      <c r="G95" s="2"/>
       <c r="H95" s="3"/>
       <c r="I95" s="3"/>
       <c r="J95" s="3"/>
     </row>
-    <row r="96" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A96" s="6"/>
-      <c r="C96" s="22" t="s">
+      <c r="C96" s="15" t="s">
         <v>345</v>
       </c>
       <c r="D96" s="5">
         <v>61616</v>
       </c>
       <c r="F96" s="5"/>
-      <c r="G96" s="2"/>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
@@ -4485,7 +4725,7 @@
       <c r="B99" t="s">
         <v>29</v>
       </c>
-      <c r="C99" s="22" t="s">
+      <c r="C99" s="15" t="s">
         <v>432</v>
       </c>
       <c r="D99" s="5">
@@ -4520,7 +4760,7 @@
       <c r="B100" t="s">
         <v>30</v>
       </c>
-      <c r="C100" s="22" t="s">
+      <c r="C100" s="15" t="s">
         <v>433</v>
       </c>
       <c r="D100" s="5">
@@ -4551,89 +4791,65 @@
         <v>245</v>
       </c>
     </row>
-    <row r="101" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
-      <c r="C101" s="22" t="s">
+      <c r="C101" s="15" t="s">
         <v>434</v>
       </c>
       <c r="D101" s="5">
         <v>56012</v>
       </c>
       <c r="F101" s="5"/>
-      <c r="G101" s="2"/>
-      <c r="H101" s="2"/>
-      <c r="I101" s="2"/>
-      <c r="J101" s="2"/>
-    </row>
-    <row r="102" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="102" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A102" s="6"/>
-      <c r="C102" s="22" t="s">
+      <c r="C102" s="15" t="s">
         <v>435</v>
       </c>
       <c r="D102" s="5">
         <v>65710</v>
       </c>
       <c r="F102" s="5"/>
-      <c r="G102" s="2"/>
-      <c r="H102" s="2"/>
-      <c r="I102" s="2"/>
-      <c r="J102" s="2"/>
-    </row>
-    <row r="103" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="103" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A103" s="6"/>
-      <c r="C103" s="22" t="s">
+      <c r="C103" s="15" t="s">
         <v>436</v>
       </c>
       <c r="D103" s="5">
         <v>53794</v>
       </c>
       <c r="F103" s="5"/>
-      <c r="G103" s="2"/>
-      <c r="H103" s="2"/>
-      <c r="I103" s="2"/>
-      <c r="J103" s="2"/>
-    </row>
-    <row r="104" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="104" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A104" s="6"/>
-      <c r="C104" s="22" t="s">
+      <c r="C104" s="15" t="s">
         <v>437</v>
       </c>
       <c r="D104" s="5">
         <v>64340</v>
       </c>
       <c r="F104" s="5"/>
-      <c r="G104" s="2"/>
-      <c r="H104" s="2"/>
-      <c r="I104" s="2"/>
-      <c r="J104" s="2"/>
-    </row>
-    <row r="105" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="105" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
-      <c r="C105" s="22" t="s">
+      <c r="C105" s="15" t="s">
         <v>438</v>
       </c>
       <c r="D105" s="5">
         <v>33209</v>
       </c>
       <c r="F105" s="5"/>
-      <c r="G105" s="2"/>
-      <c r="H105" s="2"/>
-      <c r="I105" s="2"/>
-      <c r="J105" s="2"/>
-    </row>
-    <row r="106" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="106" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
-      <c r="C106" s="22" t="s">
+      <c r="C106" s="15" t="s">
         <v>439</v>
       </c>
       <c r="D106" s="5">
         <v>45332</v>
       </c>
       <c r="F106" s="5"/>
-      <c r="G106" s="2"/>
-      <c r="H106" s="2"/>
-      <c r="I106" s="2"/>
-      <c r="J106" s="2"/>
     </row>
     <row r="107" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A107" s="6">
@@ -4709,7 +4925,7 @@
       <c r="B109" t="s">
         <v>33</v>
       </c>
-      <c r="C109" s="22" t="s">
+      <c r="C109" s="15" t="s">
         <v>440</v>
       </c>
       <c r="D109" s="5">
@@ -4740,75 +4956,55 @@
         <v>328</v>
       </c>
     </row>
-    <row r="110" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
-      <c r="C110" s="22" t="s">
+      <c r="C110" s="15" t="s">
         <v>441</v>
       </c>
       <c r="D110" s="5">
         <v>45148</v>
       </c>
       <c r="F110" s="5"/>
-      <c r="G110" s="2"/>
-      <c r="H110" s="2"/>
-      <c r="I110" s="2"/>
-      <c r="J110" s="2"/>
-    </row>
-    <row r="111" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="111" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A111" s="6"/>
-      <c r="C111" s="22" t="s">
+      <c r="C111" s="15" t="s">
         <v>442</v>
       </c>
       <c r="D111" s="5">
         <v>46509</v>
       </c>
       <c r="F111" s="5"/>
-      <c r="G111" s="2"/>
-      <c r="H111" s="2"/>
-      <c r="I111" s="2"/>
-      <c r="J111" s="2"/>
-    </row>
-    <row r="112" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="112" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A112" s="6"/>
-      <c r="C112" s="22" t="s">
+      <c r="C112" s="15" t="s">
         <v>443</v>
       </c>
       <c r="D112" s="5">
         <v>55011</v>
       </c>
       <c r="F112" s="5"/>
-      <c r="G112" s="2"/>
-      <c r="H112" s="2"/>
-      <c r="I112" s="2"/>
-      <c r="J112" s="2"/>
-    </row>
-    <row r="113" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="113" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
-      <c r="C113" s="22" t="s">
+      <c r="C113" s="15" t="s">
         <v>444</v>
       </c>
       <c r="D113" s="5">
         <v>63210</v>
       </c>
       <c r="F113" s="5"/>
-      <c r="G113" s="2"/>
-      <c r="H113" s="2"/>
-      <c r="I113" s="2"/>
-      <c r="J113" s="2"/>
-    </row>
-    <row r="114" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="114" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
-      <c r="C114" s="22" t="s">
+      <c r="C114" s="15" t="s">
         <v>445</v>
       </c>
       <c r="D114" s="5">
         <v>65635</v>
       </c>
       <c r="F114" s="5"/>
-      <c r="G114" s="2"/>
-      <c r="H114" s="2"/>
-      <c r="I114" s="2"/>
-      <c r="J114" s="2"/>
     </row>
     <row r="115" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A115" s="6">
@@ -4852,7 +5048,7 @@
       <c r="B116" t="s">
         <v>35</v>
       </c>
-      <c r="C116" s="22" t="s">
+      <c r="C116" s="15" t="s">
         <v>446</v>
       </c>
       <c r="D116" s="5">
@@ -4883,47 +5079,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="117" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
-      <c r="C117" s="22" t="s">
+      <c r="C117" s="15" t="s">
         <v>447</v>
       </c>
       <c r="D117" s="5">
         <v>52292</v>
       </c>
       <c r="F117" s="5"/>
-      <c r="G117" s="2"/>
-      <c r="H117" s="2"/>
-      <c r="I117" s="2"/>
-      <c r="J117" s="2"/>
-    </row>
-    <row r="118" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="118" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
-      <c r="C118" s="22" t="s">
+      <c r="C118" s="15" t="s">
         <v>448</v>
       </c>
       <c r="D118" s="5">
         <v>60272</v>
       </c>
       <c r="F118" s="5"/>
-      <c r="G118" s="2"/>
-      <c r="H118" s="2"/>
-      <c r="I118" s="2"/>
-      <c r="J118" s="2"/>
-    </row>
-    <row r="119" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="119" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
-      <c r="C119" s="22" t="s">
+      <c r="C119" s="15" t="s">
         <v>449</v>
       </c>
       <c r="D119" s="5">
         <v>61765</v>
       </c>
       <c r="F119" s="5"/>
-      <c r="G119" s="2"/>
-      <c r="H119" s="2"/>
-      <c r="I119" s="2"/>
-      <c r="J119" s="2"/>
     </row>
     <row r="120" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A120" s="6">
@@ -4932,7 +5116,7 @@
       <c r="B120" t="s">
         <v>36</v>
       </c>
-      <c r="C120" s="22" t="s">
+      <c r="C120" s="15" t="s">
         <v>450</v>
       </c>
       <c r="D120" s="5">
@@ -4963,47 +5147,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="121" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A121" s="6"/>
-      <c r="C121" s="22" t="s">
+      <c r="C121" s="15" t="s">
         <v>451</v>
       </c>
       <c r="D121" s="5">
         <v>53171</v>
       </c>
       <c r="F121" s="5"/>
-      <c r="G121" s="2"/>
-      <c r="H121" s="2"/>
-      <c r="I121" s="2"/>
-      <c r="J121" s="2"/>
-    </row>
-    <row r="122" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="122" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
-      <c r="C122" s="22" t="s">
+      <c r="C122" s="15" t="s">
         <v>452</v>
       </c>
       <c r="D122" s="5">
         <v>62769</v>
       </c>
       <c r="F122" s="5"/>
-      <c r="G122" s="2"/>
-      <c r="H122" s="2"/>
-      <c r="I122" s="2"/>
-      <c r="J122" s="2"/>
-    </row>
-    <row r="123" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="123" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
-      <c r="C123" s="22" t="s">
+      <c r="C123" s="15" t="s">
         <v>453</v>
       </c>
       <c r="D123" s="5">
         <v>64563</v>
       </c>
       <c r="F123" s="5"/>
-      <c r="G123" s="2"/>
-      <c r="H123" s="2"/>
-      <c r="I123" s="2"/>
-      <c r="J123" s="2"/>
     </row>
     <row r="124" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A124" s="6">
@@ -5012,7 +5184,7 @@
       <c r="B124" t="s">
         <v>37</v>
       </c>
-      <c r="C124" s="22" t="s">
+      <c r="C124" s="15" t="s">
         <v>454</v>
       </c>
       <c r="D124" s="5">
@@ -5043,47 +5215,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="125" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
-      <c r="C125" s="22" t="s">
+      <c r="C125" s="15" t="s">
         <v>455</v>
       </c>
       <c r="D125" s="5">
         <v>59986</v>
       </c>
       <c r="F125" s="5"/>
-      <c r="G125" s="2"/>
-      <c r="H125" s="2"/>
-      <c r="I125" s="2"/>
-      <c r="J125" s="2"/>
-    </row>
-    <row r="126" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="126" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
-      <c r="C126" s="22" t="s">
+      <c r="C126" s="15" t="s">
         <v>456</v>
       </c>
       <c r="D126" s="5">
         <v>52324</v>
       </c>
       <c r="F126" s="5"/>
-      <c r="G126" s="2"/>
-      <c r="H126" s="2"/>
-      <c r="I126" s="2"/>
-      <c r="J126" s="2"/>
-    </row>
-    <row r="127" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="127" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A127" s="6"/>
-      <c r="C127" s="22" t="s">
+      <c r="C127" s="15" t="s">
         <v>457</v>
       </c>
       <c r="D127" s="5">
         <v>58903</v>
       </c>
       <c r="F127" s="5"/>
-      <c r="G127" s="2"/>
-      <c r="H127" s="2"/>
-      <c r="I127" s="2"/>
-      <c r="J127" s="2"/>
     </row>
     <row r="128" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A128" s="6">
@@ -5092,7 +5252,7 @@
       <c r="B128" t="s">
         <v>38</v>
       </c>
-      <c r="C128" s="22" t="s">
+      <c r="C128" s="15" t="s">
         <v>458</v>
       </c>
       <c r="D128" s="5">
@@ -5123,47 +5283,35 @@
         <v>280</v>
       </c>
     </row>
-    <row r="129" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
-      <c r="C129" s="22" t="s">
+      <c r="C129" s="15" t="s">
         <v>459</v>
       </c>
       <c r="D129" s="5">
         <v>32797</v>
       </c>
       <c r="F129" s="5"/>
-      <c r="G129" s="2"/>
-      <c r="H129" s="2"/>
-      <c r="I129" s="2"/>
-      <c r="J129" s="2"/>
-    </row>
-    <row r="130" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
-      <c r="C130" s="22" t="s">
+      <c r="C130" s="15" t="s">
         <v>460</v>
       </c>
       <c r="D130" s="5">
         <v>44749</v>
       </c>
       <c r="F130" s="5"/>
-      <c r="G130" s="2"/>
-      <c r="H130" s="2"/>
-      <c r="I130" s="2"/>
-      <c r="J130" s="2"/>
-    </row>
-    <row r="131" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A131" s="6"/>
-      <c r="C131" s="22" t="s">
+      <c r="C131" s="15" t="s">
         <v>461</v>
       </c>
       <c r="D131" s="5">
         <v>54759</v>
       </c>
       <c r="F131" s="5"/>
-      <c r="G131" s="2"/>
-      <c r="H131" s="2"/>
-      <c r="I131" s="2"/>
-      <c r="J131" s="2"/>
     </row>
     <row r="132" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A132" s="6">
@@ -5172,7 +5320,7 @@
       <c r="B132" t="s">
         <v>39</v>
       </c>
-      <c r="C132" s="22" t="s">
+      <c r="C132" s="15" t="s">
         <v>462</v>
       </c>
       <c r="D132" s="5">
@@ -5203,33 +5351,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="133" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
-      <c r="C133" s="22" t="s">
+      <c r="C133" s="15" t="s">
         <v>463</v>
       </c>
       <c r="D133" s="5">
         <v>51641</v>
       </c>
       <c r="F133" s="5"/>
-      <c r="G133" s="2"/>
-      <c r="H133" s="2"/>
-      <c r="I133" s="2"/>
-      <c r="J133" s="2"/>
-    </row>
-    <row r="134" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="134" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
-      <c r="C134" s="22" t="s">
+      <c r="C134" s="15" t="s">
         <v>464</v>
       </c>
       <c r="D134" s="5">
         <v>63145</v>
       </c>
       <c r="F134" s="5"/>
-      <c r="G134" s="2"/>
-      <c r="H134" s="2"/>
-      <c r="I134" s="2"/>
-      <c r="J134" s="2"/>
     </row>
     <row r="135" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
@@ -5238,7 +5378,7 @@
       <c r="B135" t="s">
         <v>40</v>
       </c>
-      <c r="C135" s="22" t="s">
+      <c r="C135" s="15" t="s">
         <v>465</v>
       </c>
       <c r="D135" s="5">
@@ -5266,19 +5406,15 @@
         <v>245</v>
       </c>
     </row>
-    <row r="136" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
-      <c r="C136" s="22" t="s">
+      <c r="C136" s="15" t="s">
         <v>466</v>
       </c>
       <c r="D136" s="5">
         <v>59699</v>
       </c>
       <c r="F136" s="5"/>
-      <c r="G136" s="2"/>
-      <c r="H136" s="2"/>
-      <c r="I136" s="2"/>
-      <c r="J136" s="2"/>
     </row>
     <row r="137" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A137" s="6">
@@ -5287,7 +5423,7 @@
       <c r="B137" t="s">
         <v>41</v>
       </c>
-      <c r="C137" s="22" t="s">
+      <c r="C137" s="15" t="s">
         <v>467</v>
       </c>
       <c r="D137" s="5">
@@ -5318,47 +5454,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="138" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
-      <c r="C138" s="22" t="s">
+      <c r="C138" s="15" t="s">
         <v>468</v>
       </c>
       <c r="D138" s="5">
         <v>45407</v>
       </c>
       <c r="F138" s="5"/>
-      <c r="G138" s="2"/>
-      <c r="H138" s="2"/>
-      <c r="I138" s="2"/>
-      <c r="J138" s="2"/>
-    </row>
-    <row r="139" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="139" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A139" s="6"/>
-      <c r="C139" s="22" t="s">
+      <c r="C139" s="15" t="s">
         <v>469</v>
       </c>
       <c r="D139" s="5">
         <v>51487</v>
       </c>
       <c r="F139" s="5"/>
-      <c r="G139" s="2"/>
-      <c r="H139" s="2"/>
-      <c r="I139" s="2"/>
-      <c r="J139" s="2"/>
-    </row>
-    <row r="140" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="140" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
-      <c r="C140" s="22" t="s">
+      <c r="C140" s="15" t="s">
         <v>470</v>
       </c>
       <c r="D140" s="5">
         <v>51569</v>
       </c>
       <c r="F140" s="5"/>
-      <c r="G140" s="2"/>
-      <c r="H140" s="2"/>
-      <c r="I140" s="2"/>
-      <c r="J140" s="2"/>
     </row>
     <row r="141" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A141" s="6">
@@ -5367,7 +5491,7 @@
       <c r="B141" t="s">
         <v>42</v>
       </c>
-      <c r="C141" s="23" t="s">
+      <c r="C141" s="16" t="s">
         <v>471</v>
       </c>
       <c r="D141" s="5">
@@ -5398,33 +5522,25 @@
         <v>257</v>
       </c>
     </row>
-    <row r="142" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
-      <c r="C142" s="23" t="s">
+      <c r="C142" s="16" t="s">
         <v>472</v>
       </c>
       <c r="D142" s="5">
         <v>56860</v>
       </c>
       <c r="F142" s="5"/>
-      <c r="G142" s="2"/>
-      <c r="H142" s="2"/>
-      <c r="I142" s="2"/>
-      <c r="J142" s="2"/>
-    </row>
-    <row r="143" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="143" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A143" s="6"/>
-      <c r="C143" s="23" t="s">
+      <c r="C143" s="16" t="s">
         <v>473</v>
       </c>
       <c r="D143" s="5">
         <v>64508</v>
       </c>
       <c r="F143" s="5"/>
-      <c r="G143" s="2"/>
-      <c r="H143" s="2"/>
-      <c r="I143" s="2"/>
-      <c r="J143" s="2"/>
     </row>
     <row r="144" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A144" s="6">
@@ -5433,7 +5549,7 @@
       <c r="B144" t="s">
         <v>43</v>
       </c>
-      <c r="C144" s="23" t="s">
+      <c r="C144" s="16" t="s">
         <v>474</v>
       </c>
       <c r="D144" s="5">
@@ -5464,33 +5580,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="145" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
-      <c r="C145" s="23" t="s">
+      <c r="C145" s="16" t="s">
         <v>475</v>
       </c>
       <c r="D145" s="5">
         <v>44854</v>
       </c>
       <c r="F145" s="5"/>
-      <c r="G145" s="2"/>
-      <c r="H145" s="2"/>
-      <c r="I145" s="2"/>
-      <c r="J145" s="2"/>
-    </row>
-    <row r="146" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="146" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
-      <c r="C146" s="23" t="s">
+      <c r="C146" s="16" t="s">
         <v>476</v>
       </c>
       <c r="D146" s="5">
         <v>53405</v>
       </c>
       <c r="F146" s="5"/>
-      <c r="G146" s="2"/>
-      <c r="H146" s="2"/>
-      <c r="I146" s="2"/>
-      <c r="J146" s="2"/>
     </row>
     <row r="147" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
@@ -5499,7 +5607,7 @@
       <c r="B147" t="s">
         <v>44</v>
       </c>
-      <c r="C147" s="23" t="s">
+      <c r="C147" s="16" t="s">
         <v>477</v>
       </c>
       <c r="D147" s="5">
@@ -5533,47 +5641,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="148" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
-      <c r="C148" s="23" t="s">
+      <c r="C148" s="16" t="s">
         <v>478</v>
       </c>
       <c r="D148" s="5">
         <v>53965</v>
       </c>
       <c r="F148" s="5"/>
-      <c r="G148" s="2"/>
-      <c r="H148" s="2"/>
-      <c r="I148" s="2"/>
-      <c r="J148" s="2"/>
-    </row>
-    <row r="149" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="149" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
-      <c r="C149" s="23" t="s">
+      <c r="C149" s="16" t="s">
         <v>479</v>
       </c>
       <c r="D149" s="5">
         <v>61535</v>
       </c>
       <c r="F149" s="5"/>
-      <c r="G149" s="2"/>
-      <c r="H149" s="2"/>
-      <c r="I149" s="2"/>
-      <c r="J149" s="2"/>
-    </row>
-    <row r="150" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A150" s="6"/>
-      <c r="C150" s="23" t="s">
+      <c r="C150" s="16" t="s">
         <v>480</v>
       </c>
       <c r="D150" s="5">
         <v>63156</v>
       </c>
       <c r="F150" s="5"/>
-      <c r="G150" s="2"/>
-      <c r="H150" s="2"/>
-      <c r="I150" s="2"/>
-      <c r="J150" s="2"/>
     </row>
     <row r="151" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A151" s="6">
@@ -5658,7 +5754,7 @@
       <c r="B153" t="s">
         <v>47</v>
       </c>
-      <c r="C153" s="22" t="s">
+      <c r="C153" s="15" t="s">
         <v>481</v>
       </c>
       <c r="D153" s="5">
@@ -5692,47 +5788,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="154" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
-      <c r="C154" s="22" t="s">
+      <c r="C154" s="15" t="s">
         <v>482</v>
       </c>
       <c r="D154" s="5">
         <v>59613</v>
       </c>
       <c r="F154" s="5"/>
-      <c r="G154" s="2"/>
-      <c r="H154" s="2"/>
-      <c r="I154" s="2"/>
-      <c r="J154" s="2"/>
-    </row>
-    <row r="155" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="155" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
-      <c r="C155" s="22" t="s">
+      <c r="C155" s="15" t="s">
         <v>483</v>
       </c>
       <c r="D155" s="5">
         <v>48314</v>
       </c>
       <c r="F155" s="5"/>
-      <c r="G155" s="2"/>
-      <c r="H155" s="2"/>
-      <c r="I155" s="2"/>
-      <c r="J155" s="2"/>
-    </row>
-    <row r="156" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="156" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A156" s="6"/>
-      <c r="C156" s="22" t="s">
+      <c r="C156" s="15" t="s">
         <v>484</v>
       </c>
       <c r="D156" s="5">
         <v>59102</v>
       </c>
       <c r="F156" s="5"/>
-      <c r="G156" s="2"/>
-      <c r="H156" s="2"/>
-      <c r="I156" s="2"/>
-      <c r="J156" s="2"/>
     </row>
     <row r="157" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A157" s="6">
@@ -5741,7 +5825,7 @@
       <c r="B157" t="s">
         <v>48</v>
       </c>
-      <c r="C157" s="22" t="s">
+      <c r="C157" s="15" t="s">
         <v>485</v>
       </c>
       <c r="D157" s="5">
@@ -5775,33 +5859,25 @@
         <v>298</v>
       </c>
     </row>
-    <row r="158" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
-      <c r="C158" s="22" t="s">
+      <c r="C158" s="15" t="s">
         <v>486</v>
       </c>
       <c r="D158" s="5">
         <v>50325</v>
       </c>
       <c r="F158" s="5"/>
-      <c r="G158" s="2"/>
-      <c r="H158" s="2"/>
-      <c r="I158" s="2"/>
-      <c r="J158" s="2"/>
-    </row>
-    <row r="159" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="159" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A159" s="6"/>
-      <c r="C159" s="22" t="s">
+      <c r="C159" s="15" t="s">
         <v>487</v>
       </c>
       <c r="D159" s="5">
         <v>59030</v>
       </c>
       <c r="F159" s="5"/>
-      <c r="G159" s="2"/>
-      <c r="H159" s="2"/>
-      <c r="I159" s="2"/>
-      <c r="J159" s="2"/>
     </row>
     <row r="160" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A160" s="6">
@@ -5810,7 +5886,7 @@
       <c r="B160" t="s">
         <v>49</v>
       </c>
-      <c r="C160" s="22" t="s">
+      <c r="C160" s="15" t="s">
         <v>488</v>
       </c>
       <c r="D160" s="5">
@@ -5844,47 +5920,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="161" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
-      <c r="C161" s="22" t="s">
+      <c r="C161" s="15" t="s">
         <v>489</v>
       </c>
       <c r="D161" s="5">
         <v>47832</v>
       </c>
       <c r="F161" s="5"/>
-      <c r="G161" s="2"/>
-      <c r="H161" s="2"/>
-      <c r="I161" s="2"/>
-      <c r="J161" s="2"/>
-    </row>
-    <row r="162" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="162" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A162" s="6"/>
-      <c r="C162" s="22" t="s">
+      <c r="C162" s="15" t="s">
         <v>490</v>
       </c>
       <c r="D162" s="5">
         <v>56831</v>
       </c>
       <c r="F162" s="5"/>
-      <c r="G162" s="2"/>
-      <c r="H162" s="2"/>
-      <c r="I162" s="2"/>
-      <c r="J162" s="2"/>
-    </row>
-    <row r="163" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="163" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
-      <c r="C163" s="22" t="s">
+      <c r="C163" s="15" t="s">
         <v>491</v>
       </c>
       <c r="D163" s="5">
         <v>58358</v>
       </c>
       <c r="F163" s="5"/>
-      <c r="G163" s="2"/>
-      <c r="H163" s="2"/>
-      <c r="I163" s="2"/>
-      <c r="J163" s="2"/>
     </row>
     <row r="164" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A164" s="6">
@@ -5893,7 +5957,7 @@
       <c r="B164" t="s">
         <v>50</v>
       </c>
-      <c r="C164" s="22" t="s">
+      <c r="C164" s="15" t="s">
         <v>492</v>
       </c>
       <c r="D164" s="5">
@@ -5927,33 +5991,25 @@
         <v>244</v>
       </c>
     </row>
-    <row r="165" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
-      <c r="C165" s="22" t="s">
+      <c r="C165" s="15" t="s">
         <v>493</v>
       </c>
       <c r="D165" s="5">
         <v>53030</v>
       </c>
       <c r="F165" s="5"/>
-      <c r="G165" s="2"/>
-      <c r="H165" s="2"/>
-      <c r="I165" s="2"/>
-      <c r="J165" s="2"/>
-    </row>
-    <row r="166" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="166" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A166" s="6"/>
-      <c r="C166" s="22" t="s">
+      <c r="C166" s="15" t="s">
         <v>494</v>
       </c>
       <c r="D166" s="5">
         <v>55329</v>
       </c>
       <c r="F166" s="5"/>
-      <c r="G166" s="2"/>
-      <c r="H166" s="2"/>
-      <c r="I166" s="2"/>
-      <c r="J166" s="2"/>
     </row>
     <row r="167" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A167" s="6">
@@ -5962,7 +6018,7 @@
       <c r="B167" t="s">
         <v>51</v>
       </c>
-      <c r="C167" s="22" t="s">
+      <c r="C167" s="15" t="s">
         <v>495</v>
       </c>
       <c r="D167" s="5">
@@ -5996,19 +6052,15 @@
         <v>245</v>
       </c>
     </row>
-    <row r="168" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
-      <c r="C168" s="22" t="s">
+      <c r="C168" s="15" t="s">
         <v>496</v>
       </c>
       <c r="D168" s="5">
         <v>42870</v>
       </c>
       <c r="F168" s="5"/>
-      <c r="G168" s="2"/>
-      <c r="H168" s="2"/>
-      <c r="I168" s="2"/>
-      <c r="J168" s="2"/>
     </row>
     <row r="169" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A169" s="6">
@@ -6017,7 +6069,7 @@
       <c r="B169" t="s">
         <v>116</v>
       </c>
-      <c r="C169" s="22" t="s">
+      <c r="C169" s="15" t="s">
         <v>497</v>
       </c>
       <c r="D169" s="5">
@@ -6051,33 +6103,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="170" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A170" s="6"/>
-      <c r="C170" s="22" t="s">
+      <c r="C170" s="15" t="s">
         <v>498</v>
       </c>
       <c r="D170" s="5">
         <v>48156</v>
       </c>
       <c r="F170" s="5"/>
-      <c r="G170" s="2"/>
-      <c r="H170" s="2"/>
-      <c r="I170" s="2"/>
-      <c r="J170" s="2"/>
-    </row>
-    <row r="171" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="171" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
-      <c r="C171" s="22" t="s">
+      <c r="C171" s="15" t="s">
         <v>499</v>
       </c>
       <c r="D171" s="5">
         <v>55796</v>
       </c>
       <c r="F171" s="5"/>
-      <c r="G171" s="2"/>
-      <c r="H171" s="2"/>
-      <c r="I171" s="2"/>
-      <c r="J171" s="2"/>
     </row>
     <row r="172" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A172" s="6">
@@ -6086,7 +6130,7 @@
       <c r="B172" t="s">
         <v>117</v>
       </c>
-      <c r="C172" s="22" t="s">
+      <c r="C172" s="15" t="s">
         <v>500</v>
       </c>
       <c r="D172" s="5">
@@ -6117,47 +6161,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="173" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
-      <c r="C173" s="22" t="s">
+      <c r="C173" s="15" t="s">
         <v>501</v>
       </c>
       <c r="D173" s="5">
         <v>49344</v>
       </c>
       <c r="F173" s="5"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="2"/>
-      <c r="I173" s="2"/>
-      <c r="J173" s="2"/>
-    </row>
-    <row r="174" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="174" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
-      <c r="C174" s="22" t="s">
+      <c r="C174" s="15" t="s">
         <v>502</v>
       </c>
       <c r="D174" s="5">
         <v>59373</v>
       </c>
       <c r="F174" s="5"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="2"/>
-      <c r="I174" s="2"/>
-      <c r="J174" s="2"/>
-    </row>
-    <row r="175" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="175" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A175" s="6"/>
-      <c r="C175" s="22" t="s">
+      <c r="C175" s="15" t="s">
         <v>503</v>
       </c>
       <c r="D175" s="5">
         <v>63170</v>
       </c>
       <c r="F175" s="5"/>
-      <c r="G175" s="2"/>
-      <c r="H175" s="2"/>
-      <c r="I175" s="2"/>
-      <c r="J175" s="2"/>
     </row>
     <row r="176" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A176" s="6">
@@ -6166,7 +6198,7 @@
       <c r="B176" t="s">
         <v>118</v>
       </c>
-      <c r="C176" s="22" t="s">
+      <c r="C176" s="15" t="s">
         <v>504</v>
       </c>
       <c r="D176" s="5">
@@ -6197,33 +6229,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="177" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
-      <c r="C177" s="22" t="s">
+      <c r="C177" s="15" t="s">
         <v>505</v>
       </c>
       <c r="D177" s="5">
         <v>47618</v>
       </c>
       <c r="F177" s="5"/>
-      <c r="G177" s="2"/>
-      <c r="H177" s="2"/>
-      <c r="I177" s="2"/>
-      <c r="J177" s="2"/>
-    </row>
-    <row r="178" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="178" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
-      <c r="C178" s="22" t="s">
+      <c r="C178" s="15" t="s">
         <v>506</v>
       </c>
       <c r="D178" s="5">
         <v>57826</v>
       </c>
       <c r="F178" s="5"/>
-      <c r="G178" s="2"/>
-      <c r="H178" s="2"/>
-      <c r="I178" s="2"/>
-      <c r="J178" s="2"/>
     </row>
     <row r="179" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
@@ -6232,7 +6256,7 @@
       <c r="B179" t="s">
         <v>119</v>
       </c>
-      <c r="C179" s="22" t="s">
+      <c r="C179" s="15" t="s">
         <v>507</v>
       </c>
       <c r="D179" s="5">
@@ -6263,47 +6287,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="180" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
-      <c r="C180" s="22" t="s">
+      <c r="C180" s="15" t="s">
         <v>508</v>
       </c>
       <c r="D180" s="5">
         <v>58359</v>
       </c>
       <c r="F180" s="5"/>
-      <c r="G180" s="2"/>
-      <c r="H180" s="2"/>
-      <c r="I180" s="2"/>
-      <c r="J180" s="2"/>
-    </row>
-    <row r="181" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="181" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
-      <c r="C181" s="22" t="s">
+      <c r="C181" s="15" t="s">
         <v>509</v>
       </c>
       <c r="D181" s="5">
         <v>60169</v>
       </c>
       <c r="F181" s="5"/>
-      <c r="G181" s="2"/>
-      <c r="H181" s="2"/>
-      <c r="I181" s="2"/>
-      <c r="J181" s="2"/>
-    </row>
-    <row r="182" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="182" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A182" s="6"/>
-      <c r="C182" s="22" t="s">
+      <c r="C182" s="15" t="s">
         <v>510</v>
       </c>
       <c r="D182" s="5">
         <v>50276</v>
       </c>
       <c r="F182" s="5"/>
-      <c r="G182" s="2"/>
-      <c r="H182" s="2"/>
-      <c r="I182" s="2"/>
-      <c r="J182" s="2"/>
     </row>
     <row r="183" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A183" s="6">
@@ -6312,7 +6324,7 @@
       <c r="B183" t="s">
         <v>120</v>
       </c>
-      <c r="C183" s="22" t="s">
+      <c r="C183" s="15" t="s">
         <v>511</v>
       </c>
       <c r="D183" s="5">
@@ -6343,89 +6355,65 @@
         <v>245</v>
       </c>
     </row>
-    <row r="184" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
-      <c r="C184" s="22" t="s">
+      <c r="C184" s="15" t="s">
         <v>512</v>
       </c>
       <c r="D184" s="5">
         <v>39118</v>
       </c>
       <c r="F184" s="5"/>
-      <c r="G184" s="2"/>
-      <c r="H184" s="2"/>
-      <c r="I184" s="2"/>
-      <c r="J184" s="2"/>
-    </row>
-    <row r="185" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="185" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
-      <c r="C185" s="22" t="s">
+      <c r="C185" s="15" t="s">
         <v>513</v>
       </c>
       <c r="D185" s="5">
         <v>40281</v>
       </c>
       <c r="F185" s="5"/>
-      <c r="G185" s="2"/>
-      <c r="H185" s="2"/>
-      <c r="I185" s="2"/>
-      <c r="J185" s="2"/>
-    </row>
-    <row r="186" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="186" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A186" s="6"/>
-      <c r="C186" s="22" t="s">
+      <c r="C186" s="15" t="s">
         <v>514</v>
       </c>
       <c r="D186" s="5">
         <v>51337</v>
       </c>
       <c r="F186" s="5"/>
-      <c r="G186" s="2"/>
-      <c r="H186" s="2"/>
-      <c r="I186" s="2"/>
-      <c r="J186" s="2"/>
-    </row>
-    <row r="187" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="187" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
-      <c r="C187" s="22" t="s">
+      <c r="C187" s="15" t="s">
         <v>515</v>
       </c>
       <c r="D187" s="5">
         <v>48440</v>
       </c>
       <c r="F187" s="5"/>
-      <c r="G187" s="2"/>
-      <c r="H187" s="2"/>
-      <c r="I187" s="2"/>
-      <c r="J187" s="2"/>
-    </row>
-    <row r="188" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="188" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
-      <c r="C188" s="22" t="s">
+      <c r="C188" s="15" t="s">
         <v>516</v>
       </c>
       <c r="D188" s="5">
         <v>61351</v>
       </c>
       <c r="F188" s="5"/>
-      <c r="G188" s="2"/>
-      <c r="H188" s="2"/>
-      <c r="I188" s="2"/>
-      <c r="J188" s="2"/>
-    </row>
-    <row r="189" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="189" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A189" s="6"/>
-      <c r="C189" s="22" t="s">
+      <c r="C189" s="15" t="s">
         <v>517</v>
       </c>
       <c r="D189" s="5">
         <v>65006</v>
       </c>
       <c r="F189" s="5"/>
-      <c r="G189" s="2"/>
-      <c r="H189" s="2"/>
-      <c r="I189" s="2"/>
-      <c r="J189" s="2"/>
     </row>
     <row r="190" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A190" s="6">
@@ -6434,7 +6422,7 @@
       <c r="B190" t="s">
         <v>121</v>
       </c>
-      <c r="C190" s="22" t="s">
+      <c r="C190" s="15" t="s">
         <v>518</v>
       </c>
       <c r="D190" s="5">
@@ -6465,33 +6453,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="191" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A191" s="6"/>
-      <c r="C191" s="22" t="s">
+      <c r="C191" s="15" t="s">
         <v>519</v>
       </c>
       <c r="D191" s="5">
         <v>59240</v>
       </c>
       <c r="F191" s="5"/>
-      <c r="G191" s="2"/>
-      <c r="H191" s="2"/>
-      <c r="I191" s="2"/>
-      <c r="J191" s="2"/>
-    </row>
-    <row r="192" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="192" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
-      <c r="C192" s="22" t="s">
+      <c r="C192" s="15" t="s">
         <v>520</v>
       </c>
       <c r="D192" s="5">
         <v>60958</v>
       </c>
       <c r="F192" s="5"/>
-      <c r="G192" s="2"/>
-      <c r="H192" s="2"/>
-      <c r="I192" s="2"/>
-      <c r="J192" s="2"/>
     </row>
     <row r="193" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A193" s="6">
@@ -6500,7 +6480,7 @@
       <c r="B193" t="s">
         <v>122</v>
       </c>
-      <c r="C193" s="22" t="s">
+      <c r="C193" s="15" t="s">
         <v>521</v>
       </c>
       <c r="D193" s="5">
@@ -6531,61 +6511,45 @@
         <v>245</v>
       </c>
     </row>
-    <row r="194" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A194" s="6"/>
-      <c r="C194" s="22" t="s">
+      <c r="C194" s="15" t="s">
         <v>522</v>
       </c>
       <c r="D194" s="5">
         <v>47603</v>
       </c>
       <c r="F194" s="5"/>
-      <c r="G194" s="2"/>
-      <c r="H194" s="2"/>
-      <c r="I194" s="2"/>
-      <c r="J194" s="2"/>
-    </row>
-    <row r="195" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="195" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
-      <c r="C195" s="22" t="s">
+      <c r="C195" s="15" t="s">
         <v>523</v>
       </c>
       <c r="D195" s="5">
         <v>47500</v>
       </c>
       <c r="F195" s="5"/>
-      <c r="G195" s="2"/>
-      <c r="H195" s="2"/>
-      <c r="I195" s="2"/>
-      <c r="J195" s="2"/>
-    </row>
-    <row r="196" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="196" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
-      <c r="C196" s="22" t="s">
+      <c r="C196" s="15" t="s">
         <v>524</v>
       </c>
       <c r="D196" s="5">
         <v>55460</v>
       </c>
       <c r="F196" s="5"/>
-      <c r="G196" s="2"/>
-      <c r="H196" s="2"/>
-      <c r="I196" s="2"/>
-      <c r="J196" s="2"/>
-    </row>
-    <row r="197" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="197" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
-      <c r="C197" s="22" t="s">
+      <c r="C197" s="15" t="s">
         <v>525</v>
       </c>
       <c r="D197" s="5">
         <v>56300</v>
       </c>
       <c r="F197" s="5"/>
-      <c r="G197" s="2"/>
-      <c r="H197" s="2"/>
-      <c r="I197" s="2"/>
-      <c r="J197" s="2"/>
     </row>
     <row r="198" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
@@ -6594,7 +6558,7 @@
       <c r="B198" t="s">
         <v>123</v>
       </c>
-      <c r="C198" s="22" t="s">
+      <c r="C198" s="15" t="s">
         <v>526</v>
       </c>
       <c r="D198" s="5">
@@ -6625,61 +6589,45 @@
         <v>245</v>
       </c>
     </row>
-    <row r="199" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
-      <c r="C199" s="22" t="s">
+      <c r="C199" s="15" t="s">
         <v>527</v>
       </c>
       <c r="D199" s="5">
         <v>53865</v>
       </c>
       <c r="F199" s="5"/>
-      <c r="G199" s="2"/>
-      <c r="H199" s="2"/>
-      <c r="I199" s="2"/>
-      <c r="J199" s="2"/>
-    </row>
-    <row r="200" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="200" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
-      <c r="C200" s="22" t="s">
+      <c r="C200" s="15" t="s">
         <v>528</v>
       </c>
       <c r="D200" s="5">
         <v>55787</v>
       </c>
       <c r="F200" s="5"/>
-      <c r="G200" s="2"/>
-      <c r="H200" s="2"/>
-      <c r="I200" s="2"/>
-      <c r="J200" s="2"/>
-    </row>
-    <row r="201" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="201" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
-      <c r="C201" s="22" t="s">
+      <c r="C201" s="15" t="s">
         <v>529</v>
       </c>
       <c r="D201" s="5">
         <v>59241</v>
       </c>
       <c r="F201" s="5"/>
-      <c r="G201" s="2"/>
-      <c r="H201" s="2"/>
-      <c r="I201" s="2"/>
-      <c r="J201" s="2"/>
-    </row>
-    <row r="202" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="202" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
-      <c r="C202" s="22" t="s">
+      <c r="C202" s="15" t="s">
         <v>530</v>
       </c>
       <c r="D202" s="5">
         <v>64502</v>
       </c>
       <c r="F202" s="5"/>
-      <c r="G202" s="2"/>
-      <c r="H202" s="2"/>
-      <c r="I202" s="2"/>
-      <c r="J202" s="2"/>
     </row>
     <row r="203" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A203" s="6">
@@ -6688,7 +6636,7 @@
       <c r="B203" t="s">
         <v>124</v>
       </c>
-      <c r="C203" s="22" t="s">
+      <c r="C203" s="15" t="s">
         <v>531</v>
       </c>
       <c r="D203" s="5">
@@ -6719,19 +6667,15 @@
         <v>271</v>
       </c>
     </row>
-    <row r="204" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
-      <c r="C204" s="22" t="s">
+      <c r="C204" s="15" t="s">
         <v>532</v>
       </c>
       <c r="D204" s="5">
         <v>44325</v>
       </c>
       <c r="F204" s="5"/>
-      <c r="G204" s="2"/>
-      <c r="H204" s="2"/>
-      <c r="I204" s="2"/>
-      <c r="J204" s="2"/>
     </row>
     <row r="205" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
@@ -6740,7 +6684,7 @@
       <c r="B205" t="s">
         <v>125</v>
       </c>
-      <c r="C205" s="22" t="s">
+      <c r="C205" s="15" t="s">
         <v>533</v>
       </c>
       <c r="D205" s="5">
@@ -6771,47 +6715,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="206" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
-      <c r="C206" s="22" t="s">
+      <c r="C206" s="15" t="s">
         <v>534</v>
       </c>
       <c r="D206" s="5">
         <v>50326</v>
       </c>
       <c r="F206" s="5"/>
-      <c r="G206" s="2"/>
-      <c r="H206" s="2"/>
-      <c r="I206" s="2"/>
-      <c r="J206" s="2"/>
-    </row>
-    <row r="207" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="207" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
-      <c r="C207" s="22" t="s">
+      <c r="C207" s="15" t="s">
         <v>535</v>
       </c>
       <c r="D207" s="5">
         <v>54515</v>
       </c>
       <c r="F207" s="5"/>
-      <c r="G207" s="2"/>
-      <c r="H207" s="2"/>
-      <c r="I207" s="2"/>
-      <c r="J207" s="2"/>
-    </row>
-    <row r="208" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="208" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
-      <c r="C208" s="22" t="s">
+      <c r="C208" s="15" t="s">
         <v>536</v>
       </c>
       <c r="D208" s="5">
         <v>55041</v>
       </c>
       <c r="F208" s="5"/>
-      <c r="G208" s="2"/>
-      <c r="H208" s="2"/>
-      <c r="I208" s="2"/>
-      <c r="J208" s="2"/>
     </row>
     <row r="209" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A209" s="6">
@@ -6820,7 +6752,7 @@
       <c r="B209" t="s">
         <v>126</v>
       </c>
-      <c r="C209" s="22" t="s">
+      <c r="C209" s="15" t="s">
         <v>537</v>
       </c>
       <c r="D209" s="5">
@@ -6851,47 +6783,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="210" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
-      <c r="C210" s="22" t="s">
+      <c r="C210" s="15" t="s">
         <v>538</v>
       </c>
       <c r="D210" s="5">
         <v>58632</v>
       </c>
       <c r="F210" s="5"/>
-      <c r="G210" s="2"/>
-      <c r="H210" s="2"/>
-      <c r="I210" s="2"/>
-      <c r="J210" s="2"/>
-    </row>
-    <row r="211" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="211" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
-      <c r="C211" s="22" t="s">
+      <c r="C211" s="15" t="s">
         <v>539</v>
       </c>
       <c r="D211" s="5">
         <v>59438</v>
       </c>
       <c r="F211" s="5"/>
-      <c r="G211" s="2"/>
-      <c r="H211" s="2"/>
-      <c r="I211" s="2"/>
-      <c r="J211" s="2"/>
-    </row>
-    <row r="212" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
-      <c r="C212" s="22" t="s">
+      <c r="C212" s="15" t="s">
         <v>540</v>
       </c>
       <c r="D212" s="5">
         <v>49841</v>
       </c>
       <c r="F212" s="5"/>
-      <c r="G212" s="2"/>
-      <c r="H212" s="2"/>
-      <c r="I212" s="2"/>
-      <c r="J212" s="2"/>
     </row>
     <row r="213" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A213" s="6">
@@ -6900,7 +6820,7 @@
       <c r="B213" t="s">
         <v>127</v>
       </c>
-      <c r="C213" s="22" t="s">
+      <c r="C213" s="15" t="s">
         <v>541</v>
       </c>
       <c r="D213" s="5">
@@ -6931,47 +6851,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="214" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
-      <c r="C214" s="22" t="s">
+      <c r="C214" s="15" t="s">
         <v>542</v>
       </c>
       <c r="D214" s="5">
         <v>49368</v>
       </c>
       <c r="F214" s="5"/>
-      <c r="G214" s="2"/>
-      <c r="H214" s="2"/>
-      <c r="I214" s="2"/>
-      <c r="J214" s="2"/>
-    </row>
-    <row r="215" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="215" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
-      <c r="C215" s="22" t="s">
+      <c r="C215" s="15" t="s">
         <v>543</v>
       </c>
       <c r="D215" s="5">
         <v>56873</v>
       </c>
       <c r="F215" s="5"/>
-      <c r="G215" s="2"/>
-      <c r="H215" s="2"/>
-      <c r="I215" s="2"/>
-      <c r="J215" s="2"/>
-    </row>
-    <row r="216" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="216" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
-      <c r="C216" s="22" t="s">
+      <c r="C216" s="15" t="s">
         <v>544</v>
       </c>
       <c r="D216" s="5">
         <v>59205</v>
       </c>
       <c r="F216" s="5"/>
-      <c r="G216" s="2"/>
-      <c r="H216" s="2"/>
-      <c r="I216" s="2"/>
-      <c r="J216" s="2"/>
     </row>
     <row r="217" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A217" s="6">
@@ -6980,7 +6888,7 @@
       <c r="B217" t="s">
         <v>128</v>
       </c>
-      <c r="C217" s="22" t="s">
+      <c r="C217" s="15" t="s">
         <v>545</v>
       </c>
       <c r="D217" s="5">
@@ -7011,47 +6919,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="218" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
-      <c r="C218" s="22" t="s">
+      <c r="C218" s="15" t="s">
         <v>546</v>
       </c>
       <c r="D218" s="5">
         <v>51362</v>
       </c>
       <c r="F218" s="5"/>
-      <c r="G218" s="2"/>
-      <c r="H218" s="2"/>
-      <c r="I218" s="2"/>
-      <c r="J218" s="2"/>
-    </row>
-    <row r="219" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="219" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
-      <c r="C219" s="22" t="s">
+      <c r="C219" s="15" t="s">
         <v>547</v>
       </c>
       <c r="D219" s="5">
         <v>58953</v>
       </c>
       <c r="F219" s="5"/>
-      <c r="G219" s="2"/>
-      <c r="H219" s="2"/>
-      <c r="I219" s="2"/>
-      <c r="J219" s="2"/>
-    </row>
-    <row r="220" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="220" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
-      <c r="C220" s="22" t="s">
+      <c r="C220" s="15" t="s">
         <v>548</v>
       </c>
       <c r="D220" s="5">
         <v>59995</v>
       </c>
       <c r="F220" s="5"/>
-      <c r="G220" s="2"/>
-      <c r="H220" s="2"/>
-      <c r="I220" s="2"/>
-      <c r="J220" s="2"/>
     </row>
     <row r="221" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A221" s="6">
@@ -7060,7 +6956,7 @@
       <c r="B221" t="s">
         <v>129</v>
       </c>
-      <c r="C221" s="22" t="s">
+      <c r="C221" s="15" t="s">
         <v>549</v>
       </c>
       <c r="D221" s="5">
@@ -7091,61 +6987,45 @@
         <v>245</v>
       </c>
     </row>
-    <row r="222" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
-      <c r="C222" s="22" t="s">
+      <c r="C222" s="15" t="s">
         <v>550</v>
       </c>
       <c r="D222" s="5">
         <v>47480</v>
       </c>
       <c r="F222" s="5"/>
-      <c r="G222" s="2"/>
-      <c r="H222" s="2"/>
-      <c r="I222" s="2"/>
-      <c r="J222" s="2"/>
-    </row>
-    <row r="223" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="223" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
-      <c r="C223" s="22" t="s">
+      <c r="C223" s="15" t="s">
         <v>551</v>
       </c>
       <c r="D223" s="5">
         <v>54180</v>
       </c>
       <c r="F223" s="5"/>
-      <c r="G223" s="2"/>
-      <c r="H223" s="2"/>
-      <c r="I223" s="2"/>
-      <c r="J223" s="2"/>
-    </row>
-    <row r="224" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="224" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
-      <c r="C224" s="22" t="s">
+      <c r="C224" s="15" t="s">
         <v>552</v>
       </c>
       <c r="D224" s="5">
         <v>56406</v>
       </c>
       <c r="F224" s="5"/>
-      <c r="G224" s="2"/>
-      <c r="H224" s="2"/>
-      <c r="I224" s="2"/>
-      <c r="J224" s="2"/>
-    </row>
-    <row r="225" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="225" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
-      <c r="C225" s="22" t="s">
+      <c r="C225" s="15" t="s">
         <v>553</v>
       </c>
       <c r="D225" s="5">
         <v>54378</v>
       </c>
       <c r="F225" s="5"/>
-      <c r="G225" s="2"/>
-      <c r="H225" s="2"/>
-      <c r="I225" s="2"/>
-      <c r="J225" s="2"/>
     </row>
     <row r="226" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A226" s="6">
@@ -7154,7 +7034,7 @@
       <c r="B226" t="s">
         <v>130</v>
       </c>
-      <c r="C226" s="22" t="s">
+      <c r="C226" s="15" t="s">
         <v>554</v>
       </c>
       <c r="D226" s="5">
@@ -7185,75 +7065,55 @@
         <v>245</v>
       </c>
     </row>
-    <row r="227" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
-      <c r="C227" s="22" t="s">
+      <c r="C227" s="15" t="s">
         <v>555</v>
       </c>
       <c r="D227" s="5">
         <v>50889</v>
       </c>
       <c r="F227" s="5"/>
-      <c r="G227" s="2"/>
-      <c r="H227" s="2"/>
-      <c r="I227" s="2"/>
-      <c r="J227" s="2"/>
-    </row>
-    <row r="228" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="228" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
-      <c r="C228" s="22" t="s">
+      <c r="C228" s="15" t="s">
         <v>556</v>
       </c>
       <c r="D228" s="5">
         <v>55229</v>
       </c>
       <c r="F228" s="5"/>
-      <c r="G228" s="2"/>
-      <c r="H228" s="2"/>
-      <c r="I228" s="2"/>
-      <c r="J228" s="2"/>
-    </row>
-    <row r="229" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="229" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
-      <c r="C229" s="22" t="s">
+      <c r="C229" s="15" t="s">
         <v>557</v>
       </c>
       <c r="D229" s="5">
         <v>54680</v>
       </c>
       <c r="F229" s="5"/>
-      <c r="G229" s="2"/>
-      <c r="H229" s="2"/>
-      <c r="I229" s="2"/>
-      <c r="J229" s="2"/>
-    </row>
-    <row r="230" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="230" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
-      <c r="C230" s="22" t="s">
+      <c r="C230" s="15" t="s">
         <v>558</v>
       </c>
       <c r="D230" s="5">
         <v>62901</v>
       </c>
       <c r="F230" s="5"/>
-      <c r="G230" s="2"/>
-      <c r="H230" s="2"/>
-      <c r="I230" s="2"/>
-      <c r="J230" s="2"/>
-    </row>
-    <row r="231" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="231" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
-      <c r="C231" s="22" t="s">
+      <c r="C231" s="15" t="s">
         <v>559</v>
       </c>
       <c r="D231" s="5">
         <v>64512</v>
       </c>
       <c r="F231" s="5"/>
-      <c r="G231" s="2"/>
-      <c r="H231" s="2"/>
-      <c r="I231" s="2"/>
-      <c r="J231" s="2"/>
     </row>
     <row r="232" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A232" s="6">
@@ -7262,7 +7122,7 @@
       <c r="B232" t="s">
         <v>131</v>
       </c>
-      <c r="C232" s="22" t="s">
+      <c r="C232" s="15" t="s">
         <v>560</v>
       </c>
       <c r="D232" s="5">
@@ -7293,33 +7153,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="233" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
-      <c r="C233" s="22" t="s">
+      <c r="C233" s="15" t="s">
         <v>561</v>
       </c>
       <c r="D233" s="5">
         <v>46448</v>
       </c>
       <c r="F233" s="5"/>
-      <c r="G233" s="2"/>
-      <c r="H233" s="2"/>
-      <c r="I233" s="2"/>
-      <c r="J233" s="2"/>
-    </row>
-    <row r="234" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="234" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
-      <c r="C234" s="22" t="s">
+      <c r="C234" s="15" t="s">
         <v>562</v>
       </c>
       <c r="D234" s="5">
         <v>53878</v>
       </c>
       <c r="F234" s="5"/>
-      <c r="G234" s="2"/>
-      <c r="H234" s="2"/>
-      <c r="I234" s="2"/>
-      <c r="J234" s="2"/>
     </row>
     <row r="235" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
@@ -7328,7 +7180,7 @@
       <c r="B235" t="s">
         <v>132</v>
       </c>
-      <c r="C235" s="22" t="s">
+      <c r="C235" s="15" t="s">
         <v>563</v>
       </c>
       <c r="D235" s="5">
@@ -7360,47 +7212,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="236" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
-      <c r="C236" s="22" t="s">
+      <c r="C236" s="15" t="s">
         <v>564</v>
       </c>
       <c r="D236" s="5">
         <v>48519</v>
       </c>
       <c r="F236" s="5"/>
-      <c r="G236" s="2"/>
-      <c r="H236" s="2"/>
-      <c r="I236" s="2"/>
-      <c r="J236" s="2"/>
-    </row>
-    <row r="237" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="237" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
-      <c r="C237" s="22" t="s">
+      <c r="C237" s="15" t="s">
         <v>565</v>
       </c>
       <c r="D237" s="5">
         <v>55917</v>
       </c>
       <c r="F237" s="5"/>
-      <c r="G237" s="2"/>
-      <c r="H237" s="2"/>
-      <c r="I237" s="2"/>
-      <c r="J237" s="2"/>
-    </row>
-    <row r="238" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="238" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
-      <c r="C238" s="22" t="s">
+      <c r="C238" s="15" t="s">
         <v>566</v>
       </c>
       <c r="D238" s="5">
         <v>61012</v>
       </c>
       <c r="F238" s="5"/>
-      <c r="G238" s="2"/>
-      <c r="H238" s="2"/>
-      <c r="I238" s="2"/>
-      <c r="J238" s="2"/>
     </row>
     <row r="239" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
@@ -7409,7 +7249,7 @@
       <c r="B239" t="s">
         <v>133</v>
       </c>
-      <c r="C239" s="22" t="s">
+      <c r="C239" s="15" t="s">
         <v>567</v>
       </c>
       <c r="D239" s="5">
@@ -7444,7 +7284,7 @@
       <c r="B240" t="s">
         <v>134</v>
       </c>
-      <c r="C240" s="22" t="s">
+      <c r="C240" s="15" t="s">
         <v>568</v>
       </c>
       <c r="D240" s="5">
@@ -7475,61 +7315,45 @@
         <v>245</v>
       </c>
     </row>
-    <row r="241" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
-      <c r="C241" s="22" t="s">
+      <c r="C241" s="15" t="s">
         <v>569</v>
       </c>
       <c r="D241" s="5">
         <v>51817</v>
       </c>
       <c r="F241" s="5"/>
-      <c r="G241" s="2"/>
-      <c r="H241" s="2"/>
-      <c r="I241" s="2"/>
-      <c r="J241" s="2"/>
-    </row>
-    <row r="242" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="242" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
-      <c r="C242" s="22" t="s">
+      <c r="C242" s="15" t="s">
         <v>570</v>
       </c>
       <c r="D242" s="5">
         <v>59254</v>
       </c>
       <c r="F242" s="5"/>
-      <c r="G242" s="2"/>
-      <c r="H242" s="2"/>
-      <c r="I242" s="2"/>
-      <c r="J242" s="2"/>
-    </row>
-    <row r="243" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="243" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
-      <c r="C243" s="22" t="s">
+      <c r="C243" s="15" t="s">
         <v>571</v>
       </c>
       <c r="D243" s="5">
         <v>61726</v>
       </c>
       <c r="F243" s="5"/>
-      <c r="G243" s="2"/>
-      <c r="H243" s="2"/>
-      <c r="I243" s="2"/>
-      <c r="J243" s="2"/>
-    </row>
-    <row r="244" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="244" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
-      <c r="C244" s="22" t="s">
+      <c r="C244" s="15" t="s">
         <v>572</v>
       </c>
       <c r="D244" s="5">
         <v>62333</v>
       </c>
       <c r="F244" s="5"/>
-      <c r="G244" s="2"/>
-      <c r="H244" s="2"/>
-      <c r="I244" s="2"/>
-      <c r="J244" s="2"/>
     </row>
     <row r="245" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A245" s="6">
@@ -7538,7 +7362,7 @@
       <c r="B245" t="s">
         <v>135</v>
       </c>
-      <c r="C245" s="22" t="s">
+      <c r="C245" s="15" t="s">
         <v>573</v>
       </c>
       <c r="D245" s="5">
@@ -7569,47 +7393,35 @@
         <v>318</v>
       </c>
     </row>
-    <row r="246" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
-      <c r="C246" s="22" t="s">
+      <c r="C246" s="15" t="s">
         <v>574</v>
       </c>
       <c r="D246" s="5">
         <v>48916</v>
       </c>
       <c r="F246" s="5"/>
-      <c r="G246" s="2"/>
-      <c r="H246" s="2"/>
-      <c r="I246" s="2"/>
-      <c r="J246" s="2"/>
-    </row>
-    <row r="247" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="247" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
-      <c r="C247" s="22" t="s">
+      <c r="C247" s="15" t="s">
         <v>575</v>
       </c>
       <c r="D247" s="5">
         <v>58981</v>
       </c>
       <c r="F247" s="5"/>
-      <c r="G247" s="2"/>
-      <c r="H247" s="2"/>
-      <c r="I247" s="2"/>
-      <c r="J247" s="2"/>
-    </row>
-    <row r="248" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="248" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
-      <c r="C248" s="22" t="s">
+      <c r="C248" s="15" t="s">
         <v>576</v>
       </c>
       <c r="D248" s="5">
         <v>59339</v>
       </c>
       <c r="F248" s="5"/>
-      <c r="G248" s="2"/>
-      <c r="H248" s="2"/>
-      <c r="I248" s="2"/>
-      <c r="J248" s="2"/>
     </row>
     <row r="249" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A249" s="6">
@@ -7618,7 +7430,7 @@
       <c r="B249" t="s">
         <v>136</v>
       </c>
-      <c r="C249" s="22" t="s">
+      <c r="C249" s="15" t="s">
         <v>577</v>
       </c>
       <c r="D249" s="5">
@@ -7649,19 +7461,15 @@
         <v>245</v>
       </c>
     </row>
-    <row r="250" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
-      <c r="C250" s="22" t="s">
+      <c r="C250" s="15" t="s">
         <v>578</v>
       </c>
       <c r="D250" s="5">
         <v>46430</v>
       </c>
       <c r="F250" s="5"/>
-      <c r="G250" s="2"/>
-      <c r="H250" s="2"/>
-      <c r="I250" s="2"/>
-      <c r="J250" s="2"/>
     </row>
     <row r="251" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A251" s="6">
@@ -7670,7 +7478,7 @@
       <c r="B251" t="s">
         <v>137</v>
       </c>
-      <c r="C251" s="22" t="s">
+      <c r="C251" s="15" t="s">
         <v>579</v>
       </c>
       <c r="D251" s="5">
@@ -7701,47 +7509,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="252" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
-      <c r="C252" s="22" t="s">
+      <c r="C252" s="15" t="s">
         <v>580</v>
       </c>
       <c r="D252" s="5">
         <v>51269</v>
       </c>
       <c r="F252" s="5"/>
-      <c r="G252" s="2"/>
-      <c r="H252" s="2"/>
-      <c r="I252" s="2"/>
-      <c r="J252" s="2"/>
-    </row>
-    <row r="253" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="253" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
-      <c r="C253" s="22" t="s">
+      <c r="C253" s="15" t="s">
         <v>581</v>
       </c>
       <c r="D253" s="5">
         <v>61751</v>
       </c>
       <c r="F253" s="5"/>
-      <c r="G253" s="2"/>
-      <c r="H253" s="2"/>
-      <c r="I253" s="2"/>
-      <c r="J253" s="2"/>
-    </row>
-    <row r="254" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="254" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
-      <c r="C254" s="22" t="s">
+      <c r="C254" s="15" t="s">
         <v>582</v>
       </c>
       <c r="D254" s="5">
         <v>63908</v>
       </c>
       <c r="F254" s="5"/>
-      <c r="G254" s="2"/>
-      <c r="H254" s="2"/>
-      <c r="I254" s="2"/>
-      <c r="J254" s="2"/>
     </row>
     <row r="255" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A255" s="6">
@@ -7750,7 +7546,7 @@
       <c r="B255" t="s">
         <v>138</v>
       </c>
-      <c r="C255" s="22" t="s">
+      <c r="C255" s="15" t="s">
         <v>583</v>
       </c>
       <c r="D255" s="5">
@@ -7781,47 +7577,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="256" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
-      <c r="C256" s="22" t="s">
+      <c r="C256" s="15" t="s">
         <v>584</v>
       </c>
       <c r="D256" s="5">
         <v>51111</v>
       </c>
       <c r="F256" s="5"/>
-      <c r="G256" s="2"/>
-      <c r="H256" s="2"/>
-      <c r="I256" s="2"/>
-      <c r="J256" s="2"/>
-    </row>
-    <row r="257" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="257" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
-      <c r="C257" s="22" t="s">
+      <c r="C257" s="15" t="s">
         <v>585</v>
       </c>
       <c r="D257" s="5">
         <v>60808</v>
       </c>
       <c r="F257" s="5"/>
-      <c r="G257" s="2"/>
-      <c r="H257" s="2"/>
-      <c r="I257" s="2"/>
-      <c r="J257" s="2"/>
-    </row>
-    <row r="258" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="258" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
-      <c r="C258" s="22" t="s">
+      <c r="C258" s="15" t="s">
         <v>586</v>
       </c>
       <c r="D258" s="5">
         <v>62507</v>
       </c>
       <c r="F258" s="5"/>
-      <c r="G258" s="2"/>
-      <c r="H258" s="2"/>
-      <c r="I258" s="2"/>
-      <c r="J258" s="2"/>
     </row>
     <row r="259" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A259" s="6">
@@ -7830,7 +7614,7 @@
       <c r="B259" t="s">
         <v>139</v>
       </c>
-      <c r="C259" s="22" t="s">
+      <c r="C259" s="15" t="s">
         <v>587</v>
       </c>
       <c r="D259" s="5">
@@ -7865,7 +7649,7 @@
       <c r="B260" t="s">
         <v>140</v>
       </c>
-      <c r="C260" s="22" t="s">
+      <c r="C260" s="15" t="s">
         <v>588</v>
       </c>
       <c r="D260" s="5">
@@ -7896,33 +7680,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="261" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
-      <c r="C261" s="22" t="s">
+      <c r="C261" s="15" t="s">
         <v>589</v>
       </c>
       <c r="D261" s="5">
         <v>57055</v>
       </c>
       <c r="F261" s="5"/>
-      <c r="G261" s="2"/>
-      <c r="H261" s="2"/>
-      <c r="I261" s="2"/>
-      <c r="J261" s="2"/>
-    </row>
-    <row r="262" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="262" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
-      <c r="C262" s="22" t="s">
+      <c r="C262" s="15" t="s">
         <v>590</v>
       </c>
       <c r="D262" s="5">
         <v>54482</v>
       </c>
       <c r="F262" s="5"/>
-      <c r="G262" s="2"/>
-      <c r="H262" s="2"/>
-      <c r="I262" s="2"/>
-      <c r="J262" s="2"/>
     </row>
     <row r="263" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A263" s="6">
@@ -7931,7 +7707,7 @@
       <c r="B263" t="s">
         <v>141</v>
       </c>
-      <c r="C263" s="22" t="s">
+      <c r="C263" s="15" t="s">
         <v>591</v>
       </c>
       <c r="D263" s="5">
@@ -7962,47 +7738,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="264" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
-      <c r="C264" s="22" t="s">
+      <c r="C264" s="15" t="s">
         <v>592</v>
       </c>
       <c r="D264" s="5">
         <v>51503</v>
       </c>
       <c r="F264" s="5"/>
-      <c r="G264" s="2"/>
-      <c r="H264" s="2"/>
-      <c r="I264" s="2"/>
-      <c r="J264" s="2"/>
-    </row>
-    <row r="265" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="265" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
-      <c r="C265" s="22" t="s">
+      <c r="C265" s="15" t="s">
         <v>593</v>
       </c>
       <c r="D265" s="5">
         <v>56017</v>
       </c>
       <c r="F265" s="5"/>
-      <c r="G265" s="2"/>
-      <c r="H265" s="2"/>
-      <c r="I265" s="2"/>
-      <c r="J265" s="2"/>
-    </row>
-    <row r="266" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="266" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
-      <c r="C266" s="22" t="s">
+      <c r="C266" s="15" t="s">
         <v>594</v>
       </c>
       <c r="D266" s="5">
         <v>58629</v>
       </c>
       <c r="F266" s="5"/>
-      <c r="G266" s="2"/>
-      <c r="H266" s="2"/>
-      <c r="I266" s="2"/>
-      <c r="J266" s="2"/>
     </row>
     <row r="267" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
@@ -8011,7 +7775,7 @@
       <c r="B267" t="s">
         <v>142</v>
       </c>
-      <c r="C267" s="22" t="s">
+      <c r="C267" s="15" t="s">
         <v>595</v>
       </c>
       <c r="D267" s="5">
@@ -8042,33 +7806,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="268" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
-      <c r="C268" s="22" t="s">
+      <c r="C268" s="15" t="s">
         <v>486</v>
       </c>
       <c r="D268" s="5">
         <v>50325</v>
       </c>
       <c r="F268" s="5"/>
-      <c r="G268" s="2"/>
-      <c r="H268" s="2"/>
-      <c r="I268" s="2"/>
-      <c r="J268" s="2"/>
-    </row>
-    <row r="269" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="269" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
-      <c r="C269" s="22" t="s">
+      <c r="C269" s="15" t="s">
         <v>596</v>
       </c>
       <c r="D269" s="5">
         <v>48072</v>
       </c>
       <c r="F269" s="5"/>
-      <c r="G269" s="2"/>
-      <c r="H269" s="2"/>
-      <c r="I269" s="2"/>
-      <c r="J269" s="2"/>
     </row>
     <row r="270" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A270" s="6">
@@ -8077,7 +7833,7 @@
       <c r="B270" t="s">
         <v>143</v>
       </c>
-      <c r="C270" s="22" t="s">
+      <c r="C270" s="15" t="s">
         <v>597</v>
       </c>
       <c r="D270" s="5">
@@ -8108,33 +7864,25 @@
         <v>245</v>
       </c>
     </row>
-    <row r="271" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
-      <c r="C271" s="22" t="s">
+      <c r="C271" s="15" t="s">
         <v>598</v>
       </c>
       <c r="D271" s="5">
         <v>50505</v>
       </c>
       <c r="F271" s="5"/>
-      <c r="G271" s="2"/>
-      <c r="H271" s="2"/>
-      <c r="I271" s="2"/>
-      <c r="J271" s="2"/>
-    </row>
-    <row r="272" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="272" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
-      <c r="C272" s="22" t="s">
+      <c r="C272" s="15" t="s">
         <v>599</v>
       </c>
       <c r="D272" s="5">
         <v>58169</v>
       </c>
       <c r="F272" s="5"/>
-      <c r="G272" s="2"/>
-      <c r="H272" s="2"/>
-      <c r="I272" s="2"/>
-      <c r="J272" s="2"/>
     </row>
     <row r="273" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
@@ -8143,7 +7891,7 @@
       <c r="B273" t="s">
         <v>145</v>
       </c>
-      <c r="C273" s="22" t="s">
+      <c r="C273" s="15" t="s">
         <v>600</v>
       </c>
       <c r="D273" s="5">
@@ -8174,47 +7922,35 @@
         <v>289</v>
       </c>
     </row>
-    <row r="274" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
-      <c r="C274" s="22" t="s">
+      <c r="C274" s="15" t="s">
         <v>601</v>
       </c>
       <c r="D274" s="5">
         <v>52692</v>
       </c>
       <c r="F274" s="5"/>
-      <c r="G274" s="2"/>
-      <c r="H274" s="2"/>
-      <c r="I274" s="2"/>
-      <c r="J274" s="2"/>
-    </row>
-    <row r="275" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="275" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
-      <c r="C275" s="22" t="s">
+      <c r="C275" s="15" t="s">
         <v>602</v>
       </c>
       <c r="D275" s="5">
         <v>61493</v>
       </c>
       <c r="F275" s="5"/>
-      <c r="G275" s="2"/>
-      <c r="H275" s="2"/>
-      <c r="I275" s="2"/>
-      <c r="J275" s="2"/>
-    </row>
-    <row r="276" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="276" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
-      <c r="C276" s="22" t="s">
+      <c r="C276" s="15" t="s">
         <v>603</v>
       </c>
       <c r="D276" s="5">
         <v>63209</v>
       </c>
       <c r="F276" s="5"/>
-      <c r="G276" s="2"/>
-      <c r="H276" s="2"/>
-      <c r="I276" s="2"/>
-      <c r="J276" s="2"/>
     </row>
     <row r="277" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
@@ -8223,7 +7959,7 @@
       <c r="B277" t="s">
         <v>144</v>
       </c>
-      <c r="C277" s="22" t="s">
+      <c r="C277" s="15" t="s">
         <v>604</v>
       </c>
       <c r="D277" s="5">
@@ -8254,47 +7990,35 @@
         <v>252</v>
       </c>
     </row>
-    <row r="278" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
-      <c r="C278" s="22" t="s">
+      <c r="C278" s="15" t="s">
         <v>605</v>
       </c>
       <c r="D278" s="5">
         <v>55130</v>
       </c>
       <c r="F278" s="5"/>
-      <c r="G278" s="2"/>
-      <c r="H278" s="2"/>
-      <c r="I278" s="2"/>
-      <c r="J278" s="2"/>
-    </row>
-    <row r="279" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="279" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
-      <c r="C279" s="22" t="s">
+      <c r="C279" s="15" t="s">
         <v>606</v>
       </c>
       <c r="D279" s="5">
         <v>55878</v>
       </c>
       <c r="F279" s="5"/>
-      <c r="G279" s="2"/>
-      <c r="H279" s="2"/>
-      <c r="I279" s="2"/>
-      <c r="J279" s="2"/>
-    </row>
-    <row r="280" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="280" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
-      <c r="C280" s="22" t="s">
+      <c r="C280" s="15" t="s">
         <v>607</v>
       </c>
       <c r="D280" s="5">
         <v>60148</v>
       </c>
       <c r="F280" s="5"/>
-      <c r="G280" s="2"/>
-      <c r="H280" s="2"/>
-      <c r="I280" s="2"/>
-      <c r="J280" s="2"/>
     </row>
     <row r="281" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
@@ -8303,7 +8027,7 @@
       <c r="B281" t="s">
         <v>146</v>
       </c>
-      <c r="C281" s="22" t="s">
+      <c r="C281" s="15" t="s">
         <v>608</v>
       </c>
       <c r="D281" s="5">
@@ -8334,47 +8058,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="282" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
-      <c r="C282" s="22" t="s">
+      <c r="C282" s="15" t="s">
         <v>609</v>
       </c>
       <c r="D282" s="5">
         <v>53998</v>
       </c>
       <c r="F282" s="5"/>
-      <c r="G282" s="2"/>
-      <c r="H282" s="2"/>
-      <c r="I282" s="2"/>
-      <c r="J282" s="2"/>
-    </row>
-    <row r="283" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="283" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
-      <c r="C283" s="22" t="s">
+      <c r="C283" s="15" t="s">
         <v>610</v>
       </c>
       <c r="D283" s="5">
         <v>62663</v>
       </c>
       <c r="F283" s="5"/>
-      <c r="G283" s="2"/>
-      <c r="H283" s="2"/>
-      <c r="I283" s="2"/>
-      <c r="J283" s="2"/>
-    </row>
-    <row r="284" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="284" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
-      <c r="C284" s="22" t="s">
+      <c r="C284" s="15" t="s">
         <v>611</v>
       </c>
       <c r="D284" s="5">
         <v>64448</v>
       </c>
       <c r="F284" s="5"/>
-      <c r="G284" s="2"/>
-      <c r="H284" s="2"/>
-      <c r="I284" s="2"/>
-      <c r="J284" s="2"/>
     </row>
     <row r="285" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
@@ -8383,7 +8095,7 @@
       <c r="B285" t="s">
         <v>147</v>
       </c>
-      <c r="C285" s="22" t="s">
+      <c r="C285" s="15" t="s">
         <v>612</v>
       </c>
       <c r="D285" s="5">
@@ -8414,19 +8126,15 @@
         <v>245</v>
       </c>
     </row>
-    <row r="286" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
-      <c r="C286" s="22" t="s">
+      <c r="C286" s="15" t="s">
         <v>613</v>
       </c>
       <c r="D286" s="5">
         <v>62722</v>
       </c>
       <c r="F286" s="5"/>
-      <c r="G286" s="2"/>
-      <c r="H286" s="2"/>
-      <c r="I286" s="2"/>
-      <c r="J286" s="2"/>
     </row>
     <row r="287" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A287" s="6">
@@ -8435,7 +8143,7 @@
       <c r="B287" t="s">
         <v>148</v>
       </c>
-      <c r="C287" s="22" t="s">
+      <c r="C287" s="15" t="s">
         <v>614</v>
       </c>
       <c r="D287" s="5">
@@ -8466,47 +8174,35 @@
         <v>260</v>
       </c>
     </row>
-    <row r="288" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
-      <c r="C288" s="22" t="s">
+      <c r="C288" s="15" t="s">
         <v>615</v>
       </c>
       <c r="D288" s="5">
         <v>51353</v>
       </c>
       <c r="F288" s="5"/>
-      <c r="G288" s="2"/>
-      <c r="H288" s="2"/>
-      <c r="I288" s="2"/>
-      <c r="J288" s="2"/>
-    </row>
-    <row r="289" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="289" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
-      <c r="C289" s="22" t="s">
+      <c r="C289" s="15" t="s">
         <v>616</v>
       </c>
       <c r="D289" s="5">
         <v>59571</v>
       </c>
       <c r="F289" s="5"/>
-      <c r="G289" s="2"/>
-      <c r="H289" s="2"/>
-      <c r="I289" s="2"/>
-      <c r="J289" s="2"/>
-    </row>
-    <row r="290" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="290" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
-      <c r="C290" s="22" t="s">
+      <c r="C290" s="15" t="s">
         <v>617</v>
       </c>
       <c r="D290" s="5">
         <v>60017</v>
       </c>
       <c r="F290" s="5"/>
-      <c r="G290" s="2"/>
-      <c r="H290" s="2"/>
-      <c r="I290" s="2"/>
-      <c r="J290" s="2"/>
     </row>
     <row r="291" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A291" s="6">
@@ -8515,7 +8211,7 @@
       <c r="B291" t="s">
         <v>149</v>
       </c>
-      <c r="C291" s="22" t="s">
+      <c r="C291" s="15" t="s">
         <v>618</v>
       </c>
       <c r="D291" s="5">
@@ -8546,47 +8242,35 @@
         <v>245</v>
       </c>
     </row>
-    <row r="292" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
-      <c r="C292" s="22" t="s">
+      <c r="C292" s="15" t="s">
         <v>619</v>
       </c>
       <c r="D292" s="5">
         <v>50936</v>
       </c>
       <c r="F292" s="5"/>
-      <c r="G292" s="2"/>
-      <c r="H292" s="2"/>
-      <c r="I292" s="2"/>
-      <c r="J292" s="2"/>
-    </row>
-    <row r="293" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="293" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
-      <c r="C293" s="22" t="s">
+      <c r="C293" s="15" t="s">
         <v>620</v>
       </c>
       <c r="D293" s="5">
         <v>58649</v>
       </c>
       <c r="F293" s="5"/>
-      <c r="G293" s="2"/>
-      <c r="H293" s="2"/>
-      <c r="I293" s="2"/>
-      <c r="J293" s="2"/>
-    </row>
-    <row r="294" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="294" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
-      <c r="C294" s="22" t="s">
+      <c r="C294" s="15" t="s">
         <v>621</v>
       </c>
       <c r="D294" s="5">
         <v>59533</v>
       </c>
       <c r="F294" s="5"/>
-      <c r="G294" s="2"/>
-      <c r="H294" s="2"/>
-      <c r="I294" s="2"/>
-      <c r="J294" s="2"/>
     </row>
     <row r="295" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
@@ -8595,7 +8279,7 @@
       <c r="B295" t="s">
         <v>150</v>
       </c>
-      <c r="C295" s="22" t="s">
+      <c r="C295" s="15" t="s">
         <v>622</v>
       </c>
       <c r="D295" s="5">
@@ -8626,47 +8310,35 @@
         <v>294</v>
       </c>
     </row>
-    <row r="296" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
-      <c r="C296" s="22" t="s">
+      <c r="C296" s="15" t="s">
         <v>623</v>
       </c>
       <c r="D296" s="5">
         <v>53348</v>
       </c>
       <c r="F296" s="5"/>
-      <c r="G296" s="2"/>
-      <c r="H296" s="2"/>
-      <c r="I296" s="2"/>
-      <c r="J296" s="2"/>
-    </row>
-    <row r="297" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="297" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
-      <c r="C297" s="22" t="s">
+      <c r="C297" s="15" t="s">
         <v>624</v>
       </c>
       <c r="D297" s="5">
         <v>60717</v>
       </c>
       <c r="F297" s="5"/>
-      <c r="G297" s="2"/>
-      <c r="H297" s="2"/>
-      <c r="I297" s="2"/>
-      <c r="J297" s="2"/>
-    </row>
-    <row r="298" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="298" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
-      <c r="C298" s="22" t="s">
+      <c r="C298" s="15" t="s">
         <v>625</v>
       </c>
       <c r="D298" s="5">
         <v>61629</v>
       </c>
       <c r="F298" s="5"/>
-      <c r="G298" s="2"/>
-      <c r="H298" s="2"/>
-      <c r="I298" s="2"/>
-      <c r="J298" s="2"/>
     </row>
     <row r="299" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
@@ -8675,7 +8347,7 @@
       <c r="B299" t="s">
         <v>45</v>
       </c>
-      <c r="C299" s="22" t="s">
+      <c r="C299" s="15" t="s">
         <v>626</v>
       </c>
       <c r="D299" s="5">
@@ -8706,57 +8378,48 @@
         <v>245</v>
       </c>
     </row>
-    <row r="300" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
-      <c r="C300" s="22" t="s">
+      <c r="C300" s="15" t="s">
         <v>627</v>
       </c>
       <c r="D300" s="5">
         <v>45350</v>
       </c>
       <c r="F300" s="5"/>
-      <c r="G300" s="2"/>
-      <c r="H300" s="2"/>
-      <c r="I300" s="2"/>
-      <c r="J300" s="2"/>
-    </row>
-    <row r="301" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="301" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
-      <c r="C301" s="22" t="s">
+      <c r="C301" s="15" t="s">
         <v>628</v>
       </c>
       <c r="D301" s="5">
         <v>54849</v>
       </c>
       <c r="F301" s="5"/>
-      <c r="G301" s="2"/>
-      <c r="H301" s="2"/>
-      <c r="I301" s="2"/>
-      <c r="J301" s="2"/>
-    </row>
-    <row r="302" spans="1:13" s="24" customFormat="1" ht="18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="302" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
-      <c r="C302" s="22" t="s">
+      <c r="C302" s="15" t="s">
         <v>629</v>
       </c>
       <c r="D302" s="5">
         <v>55649</v>
       </c>
       <c r="F302" s="5"/>
-      <c r="G302" s="2"/>
-      <c r="H302" s="2"/>
-      <c r="I302" s="2"/>
-      <c r="J302" s="2"/>
-    </row>
-    <row r="303" spans="1:13" x14ac:dyDescent="0.25">
+    </row>
+    <row r="303" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
         <v>87</v>
       </c>
       <c r="B303" t="s">
         <v>151</v>
       </c>
-      <c r="C303" t="s">
-        <v>200</v>
+      <c r="C303" s="15" t="s">
+        <v>630</v>
+      </c>
+      <c r="D303" s="5">
+        <v>50638</v>
       </c>
       <c r="F303" s="5">
         <v>64618</v>
@@ -8780,15 +8443,18 @@
         <v>245</v>
       </c>
     </row>
-    <row r="304" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A304" s="6">
         <v>88</v>
       </c>
       <c r="B304" t="s">
         <v>152</v>
       </c>
-      <c r="C304" t="s">
-        <v>201</v>
+      <c r="C304" s="15" t="s">
+        <v>631</v>
+      </c>
+      <c r="D304" s="5">
+        <v>45741</v>
       </c>
       <c r="F304" s="5">
         <v>64571</v>
@@ -8815,444 +8481,197 @@
         <v>245</v>
       </c>
     </row>
-    <row r="305" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A305" s="6">
+    <row r="305" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A305" s="6"/>
+      <c r="C305" s="15" t="s">
+        <v>632</v>
+      </c>
+      <c r="D305" s="5">
+        <v>55622</v>
+      </c>
+      <c r="F305" s="5"/>
+    </row>
+    <row r="306" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A306" s="6"/>
+      <c r="C306" s="15" t="s">
+        <v>633</v>
+      </c>
+      <c r="D306" s="5">
+        <v>56503</v>
+      </c>
+      <c r="F306" s="5"/>
+    </row>
+    <row r="307" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A307" s="6"/>
+      <c r="C307" s="15" t="s">
+        <v>634</v>
+      </c>
+      <c r="D307" s="5">
+        <v>47613</v>
+      </c>
+      <c r="F307" s="5"/>
+    </row>
+    <row r="308" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A308" s="6"/>
+      <c r="C308" s="15" t="s">
+        <v>635</v>
+      </c>
+      <c r="D308" s="5">
+        <v>58328</v>
+      </c>
+      <c r="F308" s="5"/>
+    </row>
+    <row r="309" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A309" s="6">
         <v>89</v>
       </c>
-      <c r="B305" t="s">
+      <c r="B309" t="s">
         <v>153</v>
       </c>
-      <c r="C305" t="s">
-        <v>202</v>
-      </c>
-      <c r="F305" s="5">
+      <c r="C309" s="15" t="s">
+        <v>636</v>
+      </c>
+      <c r="D309" s="5">
+        <v>46510</v>
+      </c>
+      <c r="F309" s="5">
         <v>64532</v>
       </c>
-      <c r="G305" s="2" t="s">
+      <c r="G309" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="H305" s="2">
+      <c r="H309" s="2">
         <v>4</v>
       </c>
-      <c r="I305" s="2">
-        <v>2</v>
-      </c>
-      <c r="J305" s="2">
-        <v>2</v>
-      </c>
-      <c r="K305" t="s">
-        <v>242</v>
-      </c>
-      <c r="L305" t="s">
+      <c r="I309" s="2">
+        <v>2</v>
+      </c>
+      <c r="J309" s="2">
+        <v>2</v>
+      </c>
+      <c r="K309" t="s">
+        <v>242</v>
+      </c>
+      <c r="L309" t="s">
         <v>245</v>
       </c>
-      <c r="M305" t="s">
+      <c r="M309" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="306" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A306" s="6">
+    <row r="310" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A310" s="6"/>
+      <c r="C310" s="15" t="s">
+        <v>637</v>
+      </c>
+      <c r="D310" s="5">
+        <v>52829</v>
+      </c>
+      <c r="F310" s="5"/>
+    </row>
+    <row r="311" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A311" s="6"/>
+      <c r="C311" s="15" t="s">
+        <v>638</v>
+      </c>
+      <c r="D311" s="5">
+        <v>61785</v>
+      </c>
+      <c r="F311" s="5"/>
+    </row>
+    <row r="312" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A312" s="6"/>
+      <c r="C312" s="15" t="s">
+        <v>639</v>
+      </c>
+      <c r="D312" s="5">
+        <v>64259</v>
+      </c>
+      <c r="F312" s="5"/>
+    </row>
+    <row r="313" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A313" s="6">
         <v>90</v>
       </c>
-      <c r="B306" t="s">
+      <c r="B313" t="s">
         <v>154</v>
       </c>
-      <c r="C306" t="s">
-        <v>203</v>
-      </c>
-      <c r="F306" s="5">
+      <c r="C313" s="15" t="s">
+        <v>640</v>
+      </c>
+      <c r="D313" s="5">
+        <v>46659</v>
+      </c>
+      <c r="F313" s="5">
         <v>64446</v>
       </c>
-      <c r="G306" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H306" s="2">
+      <c r="G313" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H313" s="2">
         <v>4</v>
       </c>
-      <c r="I306" s="2">
+      <c r="I313" s="2">
         <v>1</v>
       </c>
-      <c r="J306" s="2">
+      <c r="J313" s="2">
         <v>3</v>
       </c>
-      <c r="K306" t="s">
-        <v>242</v>
-      </c>
-      <c r="L306" t="s">
+      <c r="K313" t="s">
+        <v>242</v>
+      </c>
+      <c r="L313" t="s">
         <v>294</v>
-      </c>
-      <c r="M306" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="307" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A307" s="6">
-        <v>91</v>
-      </c>
-      <c r="B307" t="s">
-        <v>155</v>
-      </c>
-      <c r="C307" t="s">
-        <v>204</v>
-      </c>
-      <c r="F307" s="5">
-        <v>64444</v>
-      </c>
-      <c r="G307" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H307" s="2">
-        <v>4</v>
-      </c>
-      <c r="I307" s="2">
-        <v>3</v>
-      </c>
-      <c r="J307" s="2">
-        <v>1</v>
-      </c>
-      <c r="K307" t="s">
-        <v>242</v>
-      </c>
-      <c r="L307" t="s">
-        <v>262</v>
-      </c>
-      <c r="M307" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="308" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A308" s="6">
-        <v>92</v>
-      </c>
-      <c r="B308" t="s">
-        <v>156</v>
-      </c>
-      <c r="C308" t="s">
-        <v>205</v>
-      </c>
-      <c r="F308" s="5">
-        <v>64424</v>
-      </c>
-      <c r="G308" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H308" s="2">
-        <v>4</v>
-      </c>
-      <c r="I308" s="2">
-        <v>2</v>
-      </c>
-      <c r="J308" s="2">
-        <v>2</v>
-      </c>
-      <c r="K308" t="s">
-        <v>242</v>
-      </c>
-      <c r="L308" t="s">
-        <v>265</v>
-      </c>
-      <c r="M308" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="309" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A309" s="6">
-        <v>93</v>
-      </c>
-      <c r="B309" t="s">
-        <v>157</v>
-      </c>
-      <c r="C309" t="s">
-        <v>206</v>
-      </c>
-      <c r="F309" s="5">
-        <v>64395</v>
-      </c>
-      <c r="G309" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H309" s="2">
-        <v>2</v>
-      </c>
-      <c r="I309" s="2">
-        <v>1</v>
-      </c>
-      <c r="J309" s="2">
-        <v>1</v>
-      </c>
-      <c r="K309" t="s">
-        <v>242</v>
-      </c>
-      <c r="L309" t="s">
-        <v>335</v>
-      </c>
-      <c r="M309" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="310" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A310" s="6">
-        <v>94</v>
-      </c>
-      <c r="B310" t="s">
-        <v>158</v>
-      </c>
-      <c r="C310" t="s">
-        <v>207</v>
-      </c>
-      <c r="F310" s="5">
-        <v>64320</v>
-      </c>
-      <c r="G310" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H310" s="2">
-        <v>4</v>
-      </c>
-      <c r="I310" s="2">
-        <v>1</v>
-      </c>
-      <c r="J310" s="2">
-        <v>3</v>
-      </c>
-      <c r="K310" t="s">
-        <v>241</v>
-      </c>
-      <c r="L310" t="s">
-        <v>323</v>
-      </c>
-      <c r="M310" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="311" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A311" s="6">
-        <v>95</v>
-      </c>
-      <c r="B311" t="s">
-        <v>159</v>
-      </c>
-      <c r="C311" t="s">
-        <v>208</v>
-      </c>
-      <c r="F311" s="5">
-        <v>64167</v>
-      </c>
-      <c r="G311" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H311" s="2">
-        <v>2</v>
-      </c>
-      <c r="I311" s="2">
-        <v>1</v>
-      </c>
-      <c r="J311" s="2">
-        <v>1</v>
-      </c>
-      <c r="K311" t="s">
-        <v>242</v>
-      </c>
-      <c r="L311" t="s">
-        <v>306</v>
-      </c>
-      <c r="M311" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="312" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A312" s="6">
-        <v>96</v>
-      </c>
-      <c r="B312" t="s">
-        <v>160</v>
-      </c>
-      <c r="C312" t="s">
-        <v>209</v>
-      </c>
-      <c r="F312" s="5">
-        <v>64166</v>
-      </c>
-      <c r="G312" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H312" s="2">
-        <v>5</v>
-      </c>
-      <c r="I312" s="2">
-        <v>2</v>
-      </c>
-      <c r="J312" s="2">
-        <v>3</v>
-      </c>
-      <c r="K312" t="s">
-        <v>242</v>
-      </c>
-      <c r="L312" t="s">
-        <v>245</v>
-      </c>
-      <c r="M312" t="s">
-        <v>257</v>
-      </c>
-    </row>
-    <row r="313" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A313" s="6">
-        <v>97</v>
-      </c>
-      <c r="B313" t="s">
-        <v>161</v>
-      </c>
-      <c r="C313" t="s">
-        <v>210</v>
-      </c>
-      <c r="F313" s="5">
-        <v>64099</v>
-      </c>
-      <c r="G313" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H313" s="2">
-        <v>5</v>
-      </c>
-      <c r="I313" s="2">
-        <v>3</v>
-      </c>
-      <c r="J313" s="2">
-        <v>2</v>
-      </c>
-      <c r="K313" t="s">
-        <v>242</v>
-      </c>
-      <c r="L313" t="s">
-        <v>284</v>
       </c>
       <c r="M313" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="314" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A314" s="6">
-        <v>98</v>
-      </c>
-      <c r="B314" t="s">
-        <v>162</v>
-      </c>
-      <c r="C314" t="s">
-        <v>211</v>
-      </c>
-      <c r="F314" s="5">
-        <v>64032</v>
-      </c>
-      <c r="G314" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H314" s="2">
-        <v>5</v>
-      </c>
-      <c r="I314" s="2">
-        <v>3</v>
-      </c>
-      <c r="J314" s="2">
-        <v>2</v>
-      </c>
-      <c r="K314" t="s">
-        <v>242</v>
-      </c>
-      <c r="L314" t="s">
-        <v>245</v>
-      </c>
-      <c r="M314" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="315" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A315" s="6">
-        <v>99</v>
-      </c>
-      <c r="B315" t="s">
-        <v>163</v>
-      </c>
-      <c r="C315" t="s">
-        <v>212</v>
-      </c>
-      <c r="F315" s="5">
-        <v>63997</v>
-      </c>
-      <c r="G315" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H315" s="2">
-        <v>4</v>
-      </c>
-      <c r="I315" s="2">
-        <v>2</v>
-      </c>
-      <c r="J315" s="2">
-        <v>2</v>
-      </c>
-      <c r="K315" t="s">
-        <v>242</v>
-      </c>
-      <c r="L315" t="s">
-        <v>282</v>
-      </c>
-      <c r="M315" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="316" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A316" s="6">
-        <v>100</v>
-      </c>
-      <c r="B316" t="s">
-        <v>164</v>
-      </c>
-      <c r="C316" t="s">
-        <v>213</v>
-      </c>
-      <c r="E316" t="s">
-        <v>214</v>
-      </c>
-      <c r="F316" s="5">
-        <v>63944</v>
-      </c>
-      <c r="G316" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H316" s="2">
-        <v>2</v>
-      </c>
-      <c r="I316" s="2">
-        <v>1</v>
-      </c>
-      <c r="J316" s="2">
-        <v>1</v>
-      </c>
-      <c r="K316" t="s">
-        <v>242</v>
-      </c>
-      <c r="L316" t="s">
-        <v>269</v>
-      </c>
-      <c r="M316" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="317" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A314" s="6"/>
+      <c r="C314" s="15" t="s">
+        <v>641</v>
+      </c>
+      <c r="D314" s="5">
+        <v>48034</v>
+      </c>
+      <c r="F314" s="5"/>
+    </row>
+    <row r="315" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A315" s="6"/>
+      <c r="C315" s="15" t="s">
+        <v>642</v>
+      </c>
+      <c r="D315" s="5">
+        <v>56151</v>
+      </c>
+      <c r="F315" s="5"/>
+    </row>
+    <row r="316" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A316" s="6"/>
+      <c r="C316" s="15" t="s">
+        <v>643</v>
+      </c>
+      <c r="D316" s="5">
+        <v>57208</v>
+      </c>
+      <c r="F316" s="5"/>
+    </row>
+    <row r="317" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A317" s="6">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="B317" t="s">
-        <v>216</v>
-      </c>
-      <c r="C317" t="s">
-        <v>222</v>
-      </c>
-      <c r="E317" t="s">
-        <v>230</v>
+        <v>155</v>
+      </c>
+      <c r="C317" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="D317" s="5">
+        <v>45148</v>
       </c>
       <c r="F317" s="5">
-        <v>63928</v>
+        <v>64444</v>
       </c>
       <c r="G317" s="2" t="s">
         <v>2</v>
@@ -9261,287 +8680,143 @@
         <v>4</v>
       </c>
       <c r="I317" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J317" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K317" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="L317" t="s">
-        <v>297</v>
+        <v>262</v>
       </c>
       <c r="M317" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="318" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A318" s="6">
-        <v>102</v>
-      </c>
-      <c r="B318" t="s">
-        <v>145</v>
-      </c>
-      <c r="C318" t="s">
-        <v>193</v>
-      </c>
-      <c r="F318" s="5">
-        <v>63834</v>
-      </c>
-      <c r="G318" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H318" s="2">
+    <row r="318" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A318" s="6"/>
+      <c r="C318" s="15" t="s">
+        <v>645</v>
+      </c>
+      <c r="D318" s="5">
+        <v>55855</v>
+      </c>
+      <c r="F318" s="5"/>
+    </row>
+    <row r="319" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A319" s="6"/>
+      <c r="C319" s="15" t="s">
+        <v>646</v>
+      </c>
+      <c r="D319" s="5">
+        <v>58650</v>
+      </c>
+      <c r="F319" s="5"/>
+    </row>
+    <row r="320" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A320" s="6"/>
+      <c r="C320" s="15" t="s">
+        <v>647</v>
+      </c>
+      <c r="D320" s="5">
+        <v>48319</v>
+      </c>
+      <c r="F320" s="5"/>
+    </row>
+    <row r="321" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A321" s="6">
+        <v>92</v>
+      </c>
+      <c r="B321" t="s">
+        <v>156</v>
+      </c>
+      <c r="C321" s="15" t="s">
+        <v>648</v>
+      </c>
+      <c r="D321" s="5">
+        <v>49775</v>
+      </c>
+      <c r="F321" s="5">
+        <v>64424</v>
+      </c>
+      <c r="G321" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H321" s="2">
         <v>4</v>
       </c>
-      <c r="I318" s="2">
-        <v>2</v>
-      </c>
-      <c r="J318" s="2">
-        <v>2</v>
-      </c>
-      <c r="K318" t="s">
-        <v>241</v>
-      </c>
-      <c r="L318" t="s">
-        <v>288</v>
-      </c>
-      <c r="M318" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="319" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A319" s="6">
-        <v>103</v>
-      </c>
-      <c r="B319" t="s">
-        <v>217</v>
-      </c>
-      <c r="C319" t="s">
-        <v>223</v>
-      </c>
-      <c r="F319" s="5">
-        <v>63817</v>
-      </c>
-      <c r="G319" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H319" s="2">
-        <v>3</v>
-      </c>
-      <c r="I319" s="2">
-        <v>1</v>
-      </c>
-      <c r="J319" s="2">
-        <v>2</v>
-      </c>
-      <c r="K319" t="s">
-        <v>242</v>
-      </c>
-      <c r="L319" t="s">
-        <v>295</v>
-      </c>
-      <c r="M319" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="320" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A320" s="6">
-        <v>104</v>
-      </c>
-      <c r="B320" t="s">
-        <v>38</v>
-      </c>
-      <c r="C320" t="s">
-        <v>86</v>
-      </c>
-      <c r="F320" s="5">
-        <v>63725</v>
-      </c>
-      <c r="G320" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H320" s="2">
-        <v>5</v>
-      </c>
-      <c r="I320" s="2">
-        <v>3</v>
-      </c>
-      <c r="J320" s="2">
-        <v>2</v>
-      </c>
-      <c r="K320" t="s">
-        <v>239</v>
-      </c>
-      <c r="L320" t="s">
-        <v>279</v>
-      </c>
-      <c r="M320" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="321" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A321" s="6">
-        <v>105</v>
-      </c>
-      <c r="B321" t="s">
-        <v>218</v>
-      </c>
-      <c r="C321" t="s">
-        <v>224</v>
-      </c>
-      <c r="F321" s="5">
-        <v>63683</v>
-      </c>
-      <c r="G321" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H321" s="2">
-        <v>3</v>
-      </c>
       <c r="I321" s="2">
         <v>2</v>
       </c>
       <c r="J321" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K321" t="s">
         <v>242</v>
       </c>
       <c r="L321" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="M321" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="322" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A322" s="6">
-        <v>106</v>
-      </c>
-      <c r="B322" t="s">
-        <v>46</v>
-      </c>
-      <c r="C322" t="s">
-        <v>94</v>
-      </c>
-      <c r="F322" s="5">
-        <v>63673</v>
-      </c>
-      <c r="G322" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H322" s="2">
-        <v>5</v>
-      </c>
-      <c r="I322" s="2">
-        <v>2</v>
-      </c>
-      <c r="J322" s="2">
-        <v>3</v>
-      </c>
-      <c r="K322" t="s">
-        <v>242</v>
-      </c>
-      <c r="L322" t="s">
-        <v>307</v>
-      </c>
-      <c r="M322" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="323" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A323" s="6">
-        <v>107</v>
-      </c>
-      <c r="B323" t="s">
-        <v>219</v>
-      </c>
-      <c r="C323" t="s">
-        <v>225</v>
-      </c>
-      <c r="F323" s="5">
-        <v>63649</v>
-      </c>
-      <c r="G323" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H323" s="2">
-        <v>6</v>
-      </c>
-      <c r="I323" s="2">
+    <row r="322" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A322" s="6"/>
+      <c r="C322" s="15" t="s">
+        <v>649</v>
+      </c>
+      <c r="D322" s="5">
+        <v>44270</v>
+      </c>
+      <c r="F322" s="5"/>
+    </row>
+    <row r="323" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A323" s="6"/>
+      <c r="C323" s="15" t="s">
+        <v>650</v>
+      </c>
+      <c r="D323" s="5">
+        <v>57742</v>
+      </c>
+      <c r="F323" s="5"/>
+    </row>
+    <row r="324" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A324" s="6"/>
+      <c r="C324" s="15" t="s">
+        <v>651</v>
+      </c>
+      <c r="D324" s="5">
+        <v>59421</v>
+      </c>
+      <c r="F324" s="5"/>
+    </row>
+    <row r="325" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A325" s="6">
+        <v>93</v>
+      </c>
+      <c r="B325" t="s">
+        <v>157</v>
+      </c>
+      <c r="C325" s="15" t="s">
+        <v>652</v>
+      </c>
+      <c r="D325" s="5">
+        <v>52455</v>
+      </c>
+      <c r="F325" s="5">
+        <v>64395</v>
+      </c>
+      <c r="G325" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H325" s="2">
+        <v>2</v>
+      </c>
+      <c r="I325" s="2">
         <v>1</v>
-      </c>
-      <c r="J323" s="2">
-        <v>5</v>
-      </c>
-      <c r="K323" t="s">
-        <v>239</v>
-      </c>
-      <c r="L323" t="s">
-        <v>274</v>
-      </c>
-      <c r="M323" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="324" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A324" s="6">
-        <v>108</v>
-      </c>
-      <c r="B324" t="s">
-        <v>148</v>
-      </c>
-      <c r="C324" t="s">
-        <v>226</v>
-      </c>
-      <c r="F324" s="5">
-        <v>63601</v>
-      </c>
-      <c r="G324" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H324" s="2">
-        <v>4</v>
-      </c>
-      <c r="I324" s="2">
-        <v>2</v>
-      </c>
-      <c r="J324" s="2">
-        <v>2</v>
-      </c>
-      <c r="K324" t="s">
-        <v>242</v>
-      </c>
-      <c r="L324" t="s">
-        <v>260</v>
-      </c>
-      <c r="M324" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="325" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A325" s="6">
-        <v>109</v>
-      </c>
-      <c r="B325" t="s">
-        <v>220</v>
-      </c>
-      <c r="C325" t="s">
-        <v>227</v>
-      </c>
-      <c r="F325" s="5">
-        <v>63569</v>
-      </c>
-      <c r="G325" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H325" s="2">
-        <v>3</v>
-      </c>
-      <c r="I325" s="2">
-        <v>2</v>
       </c>
       <c r="J325" s="2">
         <v>1</v>
@@ -9550,52 +8825,1189 @@
         <v>242</v>
       </c>
       <c r="L325" t="s">
-        <v>261</v>
+        <v>335</v>
       </c>
       <c r="M325" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="326" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A326" s="6">
+    <row r="326" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A326" s="6"/>
+      <c r="C326" s="15" t="s">
+        <v>653</v>
+      </c>
+      <c r="D326" s="5">
+        <v>53855</v>
+      </c>
+      <c r="F326" s="5"/>
+    </row>
+    <row r="327" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A327" s="6">
+        <v>94</v>
+      </c>
+      <c r="B327" t="s">
+        <v>158</v>
+      </c>
+      <c r="C327" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="D327" s="5">
+        <v>46350</v>
+      </c>
+      <c r="F327" s="5">
+        <v>64320</v>
+      </c>
+      <c r="G327" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H327" s="2">
+        <v>4</v>
+      </c>
+      <c r="I327" s="2">
+        <v>1</v>
+      </c>
+      <c r="J327" s="2">
+        <v>3</v>
+      </c>
+      <c r="K327" t="s">
+        <v>241</v>
+      </c>
+      <c r="L327" t="s">
+        <v>323</v>
+      </c>
+      <c r="M327" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="328" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A328" s="6"/>
+      <c r="C328" s="15" t="s">
+        <v>655</v>
+      </c>
+      <c r="D328" s="5">
+        <v>56069</v>
+      </c>
+      <c r="F328" s="5"/>
+    </row>
+    <row r="329" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A329" s="6"/>
+      <c r="C329" s="15" t="s">
+        <v>656</v>
+      </c>
+      <c r="D329" s="5">
+        <v>57797</v>
+      </c>
+      <c r="F329" s="5"/>
+    </row>
+    <row r="330" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A330" s="6"/>
+      <c r="C330" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="D330" s="5">
+        <v>45239</v>
+      </c>
+      <c r="F330" s="5"/>
+    </row>
+    <row r="331" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A331" s="6">
+        <v>95</v>
+      </c>
+      <c r="B331" t="s">
+        <v>159</v>
+      </c>
+      <c r="C331" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="D331" s="5">
+        <v>37226</v>
+      </c>
+      <c r="F331" s="5">
+        <v>64167</v>
+      </c>
+      <c r="G331" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H331" s="2">
+        <v>2</v>
+      </c>
+      <c r="I331" s="2">
+        <v>1</v>
+      </c>
+      <c r="J331" s="2">
+        <v>1</v>
+      </c>
+      <c r="K331" t="s">
+        <v>242</v>
+      </c>
+      <c r="L331" t="s">
+        <v>306</v>
+      </c>
+      <c r="M331" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="332" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A332" s="6"/>
+      <c r="C332" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D332" s="5">
+        <v>39052</v>
+      </c>
+      <c r="F332" s="5"/>
+    </row>
+    <row r="333" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A333" s="6">
+        <v>96</v>
+      </c>
+      <c r="B333" t="s">
+        <v>160</v>
+      </c>
+      <c r="C333" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="D333" s="5">
+        <v>48501</v>
+      </c>
+      <c r="F333" s="5">
+        <v>64166</v>
+      </c>
+      <c r="G333" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H333" s="2">
+        <v>5</v>
+      </c>
+      <c r="I333" s="2">
+        <v>2</v>
+      </c>
+      <c r="J333" s="2">
+        <v>3</v>
+      </c>
+      <c r="K333" t="s">
+        <v>242</v>
+      </c>
+      <c r="L333" t="s">
+        <v>245</v>
+      </c>
+      <c r="M333" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="334" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A334" s="6"/>
+      <c r="C334" s="15" t="s">
+        <v>660</v>
+      </c>
+      <c r="D334" s="5">
+        <v>46282</v>
+      </c>
+      <c r="F334" s="5"/>
+    </row>
+    <row r="335" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A335" s="6"/>
+      <c r="C335" s="15" t="s">
+        <v>661</v>
+      </c>
+      <c r="D335" s="5">
+        <v>36910</v>
+      </c>
+      <c r="F335" s="5"/>
+    </row>
+    <row r="336" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A336" s="6"/>
+      <c r="C336" s="15" t="s">
+        <v>662</v>
+      </c>
+      <c r="D336" s="5">
+        <v>56446</v>
+      </c>
+      <c r="F336" s="5"/>
+    </row>
+    <row r="337" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A337" s="6"/>
+      <c r="C337" s="15" t="s">
+        <v>663</v>
+      </c>
+      <c r="D337" s="5">
+        <v>58435</v>
+      </c>
+      <c r="F337" s="5"/>
+    </row>
+    <row r="338" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A338" s="6">
+        <v>97</v>
+      </c>
+      <c r="B338" t="s">
+        <v>161</v>
+      </c>
+      <c r="C338" s="15" t="s">
+        <v>664</v>
+      </c>
+      <c r="D338" s="5">
+        <v>45255</v>
+      </c>
+      <c r="F338" s="5">
+        <v>64099</v>
+      </c>
+      <c r="G338" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H338" s="2">
+        <v>5</v>
+      </c>
+      <c r="I338" s="2">
+        <v>3</v>
+      </c>
+      <c r="J338" s="2">
+        <v>2</v>
+      </c>
+      <c r="K338" t="s">
+        <v>242</v>
+      </c>
+      <c r="L338" t="s">
+        <v>284</v>
+      </c>
+      <c r="M338" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="339" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A339" s="6"/>
+      <c r="C339" s="15" t="s">
+        <v>665</v>
+      </c>
+      <c r="D339" s="5">
+        <v>46947</v>
+      </c>
+      <c r="F339" s="5"/>
+    </row>
+    <row r="340" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A340" s="6"/>
+      <c r="C340" s="15" t="s">
+        <v>666</v>
+      </c>
+      <c r="D340" s="5">
+        <v>55117</v>
+      </c>
+      <c r="F340" s="5"/>
+    </row>
+    <row r="341" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A341" s="6"/>
+      <c r="C341" s="15" t="s">
+        <v>667</v>
+      </c>
+      <c r="D341" s="5">
+        <v>56476</v>
+      </c>
+      <c r="F341" s="5"/>
+    </row>
+    <row r="342" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A342" s="6"/>
+      <c r="C342" s="15" t="s">
+        <v>668</v>
+      </c>
+      <c r="D342" s="5">
+        <v>58438</v>
+      </c>
+      <c r="F342" s="5"/>
+    </row>
+    <row r="343" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A343" s="6">
+        <v>98</v>
+      </c>
+      <c r="B343" t="s">
+        <v>162</v>
+      </c>
+      <c r="C343" s="15" t="s">
+        <v>441</v>
+      </c>
+      <c r="D343" s="5">
+        <v>45148</v>
+      </c>
+      <c r="F343" s="5">
+        <v>64032</v>
+      </c>
+      <c r="G343" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H343" s="2">
+        <v>5</v>
+      </c>
+      <c r="I343" s="2">
+        <v>3</v>
+      </c>
+      <c r="J343" s="2">
+        <v>2</v>
+      </c>
+      <c r="K343" t="s">
+        <v>242</v>
+      </c>
+      <c r="L343" t="s">
+        <v>245</v>
+      </c>
+      <c r="M343" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="344" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A344" s="6"/>
+      <c r="C344" s="15" t="s">
+        <v>442</v>
+      </c>
+      <c r="D344" s="5">
+        <v>46509</v>
+      </c>
+      <c r="F344" s="5"/>
+    </row>
+    <row r="345" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A345" s="6"/>
+      <c r="C345" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="D345" s="5">
+        <v>53896</v>
+      </c>
+      <c r="F345" s="5"/>
+    </row>
+    <row r="346" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A346" s="6"/>
+      <c r="C346" s="15" t="s">
+        <v>443</v>
+      </c>
+      <c r="D346" s="5">
+        <v>55011</v>
+      </c>
+      <c r="F346" s="5"/>
+    </row>
+    <row r="347" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A347" s="6"/>
+      <c r="C347" s="15" t="s">
+        <v>444</v>
+      </c>
+      <c r="D347" s="5">
+        <v>63210</v>
+      </c>
+      <c r="F347" s="5"/>
+    </row>
+    <row r="348" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A348" s="6">
+        <v>99</v>
+      </c>
+      <c r="B348" t="s">
+        <v>163</v>
+      </c>
+      <c r="C348" s="15" t="s">
+        <v>669</v>
+      </c>
+      <c r="D348" s="5">
+        <v>42311</v>
+      </c>
+      <c r="F348" s="5">
+        <v>63997</v>
+      </c>
+      <c r="G348" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H348" s="2">
+        <v>4</v>
+      </c>
+      <c r="I348" s="2">
+        <v>2</v>
+      </c>
+      <c r="J348" s="2">
+        <v>2</v>
+      </c>
+      <c r="K348" t="s">
+        <v>242</v>
+      </c>
+      <c r="L348" t="s">
+        <v>282</v>
+      </c>
+      <c r="M348" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="349" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A349" s="6"/>
+      <c r="C349" s="15" t="s">
+        <v>670</v>
+      </c>
+      <c r="D349" s="5">
+        <v>46696</v>
+      </c>
+      <c r="F349" s="5"/>
+    </row>
+    <row r="350" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A350" s="6"/>
+      <c r="C350" s="15" t="s">
+        <v>671</v>
+      </c>
+      <c r="D350" s="5">
+        <v>54655</v>
+      </c>
+      <c r="F350" s="5"/>
+    </row>
+    <row r="351" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A351" s="6"/>
+      <c r="C351" s="15" t="s">
+        <v>672</v>
+      </c>
+      <c r="D351" s="5">
+        <v>53800</v>
+      </c>
+      <c r="F351" s="5"/>
+    </row>
+    <row r="352" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A352" s="6">
+        <v>100</v>
+      </c>
+      <c r="B352" t="s">
+        <v>164</v>
+      </c>
+      <c r="C352" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="D352" s="5">
+        <v>36222</v>
+      </c>
+      <c r="E352" t="s">
+        <v>214</v>
+      </c>
+      <c r="F352" s="5">
+        <v>63944</v>
+      </c>
+      <c r="G352" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H352" s="2">
+        <v>2</v>
+      </c>
+      <c r="I352" s="2">
+        <v>1</v>
+      </c>
+      <c r="J352" s="2">
+        <v>1</v>
+      </c>
+      <c r="K352" t="s">
+        <v>242</v>
+      </c>
+      <c r="L352" t="s">
+        <v>269</v>
+      </c>
+      <c r="M352" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="353" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A353" s="6"/>
+      <c r="C353" s="15" t="s">
+        <v>674</v>
+      </c>
+      <c r="D353" s="5">
+        <v>12554</v>
+      </c>
+      <c r="F353" s="5"/>
+    </row>
+    <row r="354" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A354" s="6">
+        <v>101</v>
+      </c>
+      <c r="B354" t="s">
+        <v>216</v>
+      </c>
+      <c r="C354" s="15" t="s">
+        <v>675</v>
+      </c>
+      <c r="D354" s="5">
+        <v>49684</v>
+      </c>
+      <c r="E354" t="s">
+        <v>230</v>
+      </c>
+      <c r="F354" s="5">
+        <v>63928</v>
+      </c>
+      <c r="G354" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H354" s="2">
+        <v>4</v>
+      </c>
+      <c r="I354" s="2">
+        <v>2</v>
+      </c>
+      <c r="J354" s="2">
+        <v>2</v>
+      </c>
+      <c r="K354" t="s">
+        <v>237</v>
+      </c>
+      <c r="L354" t="s">
+        <v>297</v>
+      </c>
+      <c r="M354" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="355" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A355" s="6"/>
+      <c r="C355" s="15" t="s">
+        <v>676</v>
+      </c>
+      <c r="D355" s="5">
+        <v>50861</v>
+      </c>
+      <c r="F355" s="5"/>
+    </row>
+    <row r="356" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A356" s="6"/>
+      <c r="C356" s="15" t="s">
+        <v>677</v>
+      </c>
+      <c r="D356" s="5">
+        <v>39461</v>
+      </c>
+      <c r="F356" s="5"/>
+    </row>
+    <row r="357" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A357" s="6"/>
+      <c r="C357" s="15" t="s">
+        <v>678</v>
+      </c>
+      <c r="D357" s="5">
+        <v>58217</v>
+      </c>
+      <c r="F357" s="5"/>
+    </row>
+    <row r="358" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A358" s="6">
+        <v>102</v>
+      </c>
+      <c r="B358" t="s">
+        <v>145</v>
+      </c>
+      <c r="C358" s="15" t="s">
+        <v>679</v>
+      </c>
+      <c r="D358" s="5">
+        <v>52174</v>
+      </c>
+      <c r="F358" s="5">
+        <v>63834</v>
+      </c>
+      <c r="G358" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H358" s="2">
+        <v>4</v>
+      </c>
+      <c r="I358" s="2">
+        <v>2</v>
+      </c>
+      <c r="J358" s="2">
+        <v>2</v>
+      </c>
+      <c r="K358" t="s">
+        <v>241</v>
+      </c>
+      <c r="L358" t="s">
+        <v>288</v>
+      </c>
+      <c r="M358" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="359" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A359" s="6"/>
+      <c r="C359" s="15" t="s">
+        <v>680</v>
+      </c>
+      <c r="D359" s="5">
+        <v>52692</v>
+      </c>
+      <c r="F359" s="5"/>
+    </row>
+    <row r="360" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A360" s="6"/>
+      <c r="C360" s="15" t="s">
+        <v>681</v>
+      </c>
+      <c r="D360" s="5">
+        <v>61493</v>
+      </c>
+      <c r="F360" s="5"/>
+    </row>
+    <row r="361" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A361" s="6"/>
+      <c r="C361" s="15" t="s">
+        <v>682</v>
+      </c>
+      <c r="D361" s="5">
+        <v>63209</v>
+      </c>
+      <c r="F361" s="5"/>
+    </row>
+    <row r="362" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A362" s="6">
+        <v>103</v>
+      </c>
+      <c r="B362" t="s">
+        <v>217</v>
+      </c>
+      <c r="C362" s="15" t="s">
+        <v>683</v>
+      </c>
+      <c r="D362" s="5">
+        <v>49255</v>
+      </c>
+      <c r="F362" s="5">
+        <v>63817</v>
+      </c>
+      <c r="G362" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H362" s="2">
+        <v>3</v>
+      </c>
+      <c r="I362" s="2">
+        <v>1</v>
+      </c>
+      <c r="J362" s="2">
+        <v>2</v>
+      </c>
+      <c r="K362" t="s">
+        <v>242</v>
+      </c>
+      <c r="L362" t="s">
+        <v>295</v>
+      </c>
+      <c r="M362" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="363" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A363" s="6"/>
+      <c r="C363" s="15" t="s">
+        <v>684</v>
+      </c>
+      <c r="D363" s="5">
+        <v>52543</v>
+      </c>
+      <c r="F363" s="5"/>
+    </row>
+    <row r="364" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A364" s="6"/>
+      <c r="C364" s="15" t="s">
+        <v>685</v>
+      </c>
+      <c r="D364" s="5">
+        <v>63360</v>
+      </c>
+      <c r="F364" s="5"/>
+    </row>
+    <row r="365" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A365" s="6">
+        <v>104</v>
+      </c>
+      <c r="B365" t="s">
+        <v>38</v>
+      </c>
+      <c r="C365" s="15" t="s">
+        <v>458</v>
+      </c>
+      <c r="D365" s="5">
+        <v>43935</v>
+      </c>
+      <c r="F365" s="5">
+        <v>63725</v>
+      </c>
+      <c r="G365" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H365" s="2">
+        <v>5</v>
+      </c>
+      <c r="I365" s="2">
+        <v>3</v>
+      </c>
+      <c r="J365" s="2">
+        <v>2</v>
+      </c>
+      <c r="K365" t="s">
+        <v>239</v>
+      </c>
+      <c r="L365" t="s">
+        <v>279</v>
+      </c>
+      <c r="M365" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="366" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A366" s="6"/>
+      <c r="C366" s="15" t="s">
+        <v>459</v>
+      </c>
+      <c r="D366" s="5">
+        <v>32432</v>
+      </c>
+      <c r="F366" s="5"/>
+    </row>
+    <row r="367" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A367" s="6"/>
+      <c r="C367" s="15" t="s">
+        <v>686</v>
+      </c>
+      <c r="D367" s="5">
+        <v>33025</v>
+      </c>
+      <c r="F367" s="5"/>
+    </row>
+    <row r="368" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A368" s="6"/>
+      <c r="C368" s="15" t="s">
+        <v>460</v>
+      </c>
+      <c r="D368" s="5">
+        <v>44749</v>
+      </c>
+      <c r="F368" s="5"/>
+    </row>
+    <row r="369" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A369" s="6"/>
+      <c r="C369" s="15" t="s">
+        <v>687</v>
+      </c>
+      <c r="D369" s="5">
+        <v>54758</v>
+      </c>
+      <c r="F369" s="5"/>
+    </row>
+    <row r="370" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A370" s="6">
+        <v>105</v>
+      </c>
+      <c r="B370" t="s">
+        <v>218</v>
+      </c>
+      <c r="C370" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="D370" s="5">
+        <v>41927</v>
+      </c>
+      <c r="F370" s="5">
+        <v>63683</v>
+      </c>
+      <c r="G370" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H370" s="2">
+        <v>3</v>
+      </c>
+      <c r="I370" s="2">
+        <v>2</v>
+      </c>
+      <c r="J370" s="2">
+        <v>1</v>
+      </c>
+      <c r="K370" t="s">
+        <v>242</v>
+      </c>
+      <c r="L370" t="s">
+        <v>269</v>
+      </c>
+      <c r="M370" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="371" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A371" s="6"/>
+      <c r="C371" s="15" t="s">
+        <v>689</v>
+      </c>
+      <c r="D371" s="5">
+        <v>43620</v>
+      </c>
+      <c r="F371" s="5"/>
+    </row>
+    <row r="372" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A372" s="6"/>
+      <c r="C372" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="D372" s="5">
+        <v>57440</v>
+      </c>
+      <c r="F372" s="5"/>
+    </row>
+    <row r="373" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A373" s="6">
+        <v>106</v>
+      </c>
+      <c r="B373" t="s">
+        <v>46</v>
+      </c>
+      <c r="C373" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="D373" s="5">
+        <v>36554</v>
+      </c>
+      <c r="F373" s="5">
+        <v>63673</v>
+      </c>
+      <c r="G373" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H373" s="2">
+        <v>5</v>
+      </c>
+      <c r="I373" s="2">
+        <v>2</v>
+      </c>
+      <c r="J373" s="2">
+        <v>3</v>
+      </c>
+      <c r="K373" t="s">
+        <v>242</v>
+      </c>
+      <c r="L373" t="s">
+        <v>307</v>
+      </c>
+      <c r="M373" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="374" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A374" s="6"/>
+      <c r="C374" s="15" t="s">
+        <v>692</v>
+      </c>
+      <c r="D374" s="5">
+        <v>50613</v>
+      </c>
+      <c r="F374" s="5"/>
+    </row>
+    <row r="375" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A375" s="6"/>
+      <c r="C375" s="15" t="s">
+        <v>693</v>
+      </c>
+      <c r="D375" s="5">
+        <v>53207</v>
+      </c>
+      <c r="F375" s="5"/>
+    </row>
+    <row r="376" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A376" s="6"/>
+      <c r="C376" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="D376" s="5">
+        <v>59777</v>
+      </c>
+      <c r="F376" s="5"/>
+    </row>
+    <row r="377" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A377" s="6"/>
+      <c r="C377" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="D377" s="5">
+        <v>61147</v>
+      </c>
+      <c r="F377" s="5"/>
+    </row>
+    <row r="378" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A378" s="6">
+        <v>107</v>
+      </c>
+      <c r="B378" t="s">
+        <v>219</v>
+      </c>
+      <c r="C378" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="D378" s="5">
+        <v>38852</v>
+      </c>
+      <c r="F378" s="5">
+        <v>63649</v>
+      </c>
+      <c r="G378" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H378" s="2">
+        <v>6</v>
+      </c>
+      <c r="I378" s="2">
+        <v>1</v>
+      </c>
+      <c r="J378" s="2">
+        <v>5</v>
+      </c>
+      <c r="K378" t="s">
+        <v>239</v>
+      </c>
+      <c r="L378" t="s">
+        <v>274</v>
+      </c>
+      <c r="M378" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="379" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A379" s="6"/>
+      <c r="C379" s="15" t="s">
+        <v>697</v>
+      </c>
+      <c r="D379" s="5">
+        <v>40237</v>
+      </c>
+      <c r="F379" s="5"/>
+    </row>
+    <row r="380" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A380" s="6"/>
+      <c r="C380" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="D380" s="5">
+        <v>52332</v>
+      </c>
+      <c r="F380" s="5"/>
+    </row>
+    <row r="381" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A381" s="6"/>
+      <c r="C381" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="D381" s="5">
+        <v>54879</v>
+      </c>
+      <c r="F381" s="5"/>
+    </row>
+    <row r="382" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A382" s="6"/>
+      <c r="C382" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="D382" s="5">
+        <v>55353</v>
+      </c>
+      <c r="F382" s="5"/>
+    </row>
+    <row r="383" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A383" s="6"/>
+      <c r="C383" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="D383" s="5">
+        <v>48546</v>
+      </c>
+      <c r="F383" s="5"/>
+    </row>
+    <row r="384" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A384" s="6">
+        <v>108</v>
+      </c>
+      <c r="B384" t="s">
+        <v>148</v>
+      </c>
+      <c r="C384" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="D384" s="5">
+        <v>46667</v>
+      </c>
+      <c r="F384" s="5">
+        <v>63601</v>
+      </c>
+      <c r="G384" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H384" s="2">
+        <v>4</v>
+      </c>
+      <c r="I384" s="2">
+        <v>2</v>
+      </c>
+      <c r="J384" s="2">
+        <v>2</v>
+      </c>
+      <c r="K384" t="s">
+        <v>242</v>
+      </c>
+      <c r="L384" t="s">
+        <v>260</v>
+      </c>
+      <c r="M384" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="385" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A385" s="6"/>
+      <c r="C385" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="D385" s="5">
+        <v>51353</v>
+      </c>
+      <c r="F385" s="5"/>
+    </row>
+    <row r="386" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A386" s="6"/>
+      <c r="C386" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="D386" s="5">
+        <v>59571</v>
+      </c>
+      <c r="F386" s="5"/>
+    </row>
+    <row r="387" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A387" s="6"/>
+      <c r="C387" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="D387" s="5">
+        <v>60017</v>
+      </c>
+      <c r="F387" s="5"/>
+    </row>
+    <row r="388" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A388" s="6">
+        <v>109</v>
+      </c>
+      <c r="B388" t="s">
+        <v>220</v>
+      </c>
+      <c r="C388" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="D388" s="5">
+        <v>48043</v>
+      </c>
+      <c r="F388" s="5">
+        <v>63569</v>
+      </c>
+      <c r="G388" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H388" s="2">
+        <v>3</v>
+      </c>
+      <c r="I388" s="2">
+        <v>2</v>
+      </c>
+      <c r="J388" s="2">
+        <v>1</v>
+      </c>
+      <c r="K388" t="s">
+        <v>242</v>
+      </c>
+      <c r="L388" t="s">
+        <v>261</v>
+      </c>
+      <c r="M388" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="389" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A389" s="6"/>
+      <c r="C389" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="D389" s="5">
+        <v>48590</v>
+      </c>
+      <c r="F389" s="5"/>
+    </row>
+    <row r="390" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A390" s="6"/>
+      <c r="C390" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="D390" s="5">
+        <v>58901</v>
+      </c>
+      <c r="F390" s="5"/>
+    </row>
+    <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A391" s="6">
         <v>110</v>
       </c>
-      <c r="B326" t="s">
+      <c r="B391" t="s">
         <v>221</v>
       </c>
-      <c r="C326" t="s">
-        <v>228</v>
-      </c>
-      <c r="E326" t="s">
+      <c r="C391" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="D391" s="5">
+        <v>47140</v>
+      </c>
+      <c r="E391" t="s">
         <v>229</v>
       </c>
-      <c r="F326" s="5">
+      <c r="F391" s="5">
         <v>63566</v>
       </c>
-      <c r="G326" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H326" s="2">
+      <c r="G391" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H391" s="2">
         <v>4</v>
       </c>
-      <c r="I326" s="2">
-        <v>2</v>
-      </c>
-      <c r="J326" s="2">
-        <v>2</v>
-      </c>
-      <c r="K326" t="s">
-        <v>242</v>
-      </c>
-      <c r="L326" t="s">
+      <c r="I391" s="2">
+        <v>2</v>
+      </c>
+      <c r="J391" s="2">
+        <v>2</v>
+      </c>
+      <c r="K391" t="s">
+        <v>242</v>
+      </c>
+      <c r="L391" t="s">
         <v>295</v>
       </c>
-      <c r="M326" t="s">
+      <c r="M391" t="s">
         <v>245</v>
       </c>
     </row>
+    <row r="392" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A392" s="6"/>
+      <c r="C392" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="D392" s="5">
+        <v>49059</v>
+      </c>
+      <c r="F392" s="5"/>
+    </row>
+    <row r="393" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A393" s="6"/>
+      <c r="C393" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="D393" s="5">
+        <v>59058</v>
+      </c>
+      <c r="F393" s="5"/>
+    </row>
+    <row r="394" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A394" s="6"/>
+      <c r="C394" s="15" t="s">
+        <v>710</v>
+      </c>
+      <c r="D394" s="5">
+        <v>62109</v>
+      </c>
+      <c r="F394" s="5"/>
+    </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M325">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M388">
     <sortCondition ref="A3"/>
   </sortState>
   <mergeCells count="5">
@@ -9606,8 +10018,8 @@
     <mergeCell ref="N1:N2"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G326" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G394" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$G$4:$G$71</formula1>
     </dataValidation>
   </dataValidations>
@@ -9616,12 +10028,12 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="1">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
           <x14:formula1>
             <xm:f>Reasons!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K4:K326</xm:sqref>
+          <xm:sqref>K4:K394</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/migration/list of immigrants.xlsx
+++ b/migration/list of immigrants.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\2082_2083\migration\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6F86C36-74A1-43A3-9E96-701E75D4E017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37AD83D6-C760-43CF-BB15-3B7DC0B59177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -69,7 +69,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="D194" authorId="0" shapeId="0" xr:uid="{433EA9C4-DB80-427F-8CAB-54A34D7AD829}">
+    <comment ref="D167" authorId="0" shapeId="0" xr:uid="{2E945AD8-BB38-4F6F-BCA2-5FC06F021BEF}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t>User:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+          </rPr>
+          <t xml:space="preserve">
+2024/2/30=real</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D216" authorId="0" shapeId="0" xr:uid="{433EA9C4-DB80-427F-8CAB-54A34D7AD829}">
       <text>
         <r>
           <rPr>
@@ -94,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D214" authorId="0" shapeId="0" xr:uid="{CFE6DE9B-5288-430B-8024-16AFF14AD381}">
+    <comment ref="D236" authorId="0" shapeId="0" xr:uid="{CFE6DE9B-5288-430B-8024-16AFF14AD381}">
       <text>
         <r>
           <rPr>
@@ -119,7 +141,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D262" authorId="0" shapeId="0" xr:uid="{A3C2DFD5-A185-4CAA-9B8B-CD7CE2737B18}">
+    <comment ref="D284" authorId="0" shapeId="0" xr:uid="{A3C2DFD5-A185-4CAA-9B8B-CD7CE2737B18}">
       <text>
         <r>
           <rPr>
@@ -144,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D300" authorId="0" shapeId="0" xr:uid="{042B8424-88E8-4CAE-9A7E-F982D5BCB770}">
+    <comment ref="D322" authorId="0" shapeId="0" xr:uid="{042B8424-88E8-4CAE-9A7E-F982D5BCB770}">
       <text>
         <r>
           <rPr>
@@ -174,7 +196,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1433" uniqueCount="711">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1455" uniqueCount="736">
   <si>
     <t>Vikash Karki</t>
   </si>
@@ -2330,6 +2352,81 @@
   <si>
     <t>;[li6 ;'j]bL</t>
   </si>
+  <si>
+    <t>6]s axfb'/ du/ jnDkfsL</t>
+  </si>
+  <si>
+    <t>lnnf dfof du/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">;Gtf]if anDkfsL du/ </t>
+  </si>
+  <si>
+    <t>ladnf s'df/L du/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">/]zd anDkfsL du/ </t>
+  </si>
+  <si>
+    <t>;Gtf]sL vqL</t>
+  </si>
+  <si>
+    <t>gfgL/fd v8\sf</t>
+  </si>
+  <si>
+    <t>bNnL ljZjsdf{</t>
+  </si>
+  <si>
+    <t>1fg axfb'/ ljZjsdf{</t>
+  </si>
+  <si>
+    <t>kq'; j/fOnL</t>
+  </si>
+  <si>
+    <t>lagf sfdL</t>
+  </si>
+  <si>
+    <t>o1 axfb'/ ljZjsdf{</t>
+  </si>
+  <si>
+    <t>uf]df ljZjsdf{</t>
+  </si>
+  <si>
+    <t>ld/f j/fOnL</t>
+  </si>
+  <si>
+    <t>Oefg j/fOnL</t>
+  </si>
+  <si>
+    <t>O;fs j/fOnL</t>
+  </si>
+  <si>
+    <t>bf]rL{ z]kf{</t>
+  </si>
+  <si>
+    <t>ldªdf nd' z]kf{</t>
+  </si>
+  <si>
+    <t>k]Daf gf];f{ª z]kf{</t>
+  </si>
+  <si>
+    <t>kf;fª 5f]6Lg z]kf{</t>
+  </si>
+  <si>
+    <t>;+lhj tfdfª</t>
+  </si>
+  <si>
+    <t>led axfb'/ &gt;]i7</t>
+  </si>
+  <si>
+    <t>ladnf &gt;]i7</t>
+  </si>
+  <si>
+    <t>cle &gt;]i7</t>
+  </si>
+  <si>
+    <t>cfef &gt;]i7</t>
+  </si>
 </sst>
 </file>
 
@@ -2339,7 +2436,7 @@
     <numFmt numFmtId="164" formatCode="[$-4000439]0"/>
     <numFmt numFmtId="165" formatCode="[$-4000000]yyyy\-mm\-dd"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2384,6 +2481,17 @@
       <color indexed="81"/>
       <name val="Tahoma"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
     </font>
   </fonts>
   <fills count="2">
@@ -2815,7 +2923,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N394"/>
+  <dimension ref="A1:N416"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.140625" style="4" bestFit="1" customWidth="1"/>
@@ -4651,15 +4759,18 @@
       <c r="I96" s="3"/>
       <c r="J96" s="3"/>
     </row>
-    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A97" s="6">
         <v>26</v>
       </c>
       <c r="B97" t="s">
         <v>27</v>
       </c>
-      <c r="C97" t="s">
-        <v>75</v>
+      <c r="C97" s="15" t="s">
+        <v>711</v>
+      </c>
+      <c r="D97" s="5">
+        <v>44383</v>
       </c>
       <c r="F97" s="5">
         <v>66240</v>
@@ -4686,711 +4797,614 @@
         <v>245</v>
       </c>
     </row>
-    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A98" s="6">
-        <v>27</v>
-      </c>
-      <c r="B98" t="s">
-        <v>28</v>
-      </c>
-      <c r="C98" t="s">
-        <v>76</v>
-      </c>
-      <c r="F98" s="5">
-        <v>66231</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H98" s="2">
-        <v>1</v>
-      </c>
-      <c r="I98" s="2">
-        <v>1</v>
-      </c>
-      <c r="K98" t="s">
-        <v>242</v>
-      </c>
-      <c r="L98" t="s">
-        <v>314</v>
-      </c>
-      <c r="M98" t="s">
-        <v>245</v>
-      </c>
+    <row r="98" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A98" s="6"/>
+      <c r="C98" s="15" t="s">
+        <v>712</v>
+      </c>
+      <c r="D98" s="5">
+        <v>47794</v>
+      </c>
+      <c r="F98" s="5"/>
     </row>
     <row r="99" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A99" s="6">
-        <v>28</v>
-      </c>
-      <c r="B99" t="s">
-        <v>29</v>
-      </c>
+      <c r="A99" s="6"/>
       <c r="C99" s="15" t="s">
-        <v>432</v>
+        <v>713</v>
       </c>
       <c r="D99" s="5">
-        <v>49050</v>
-      </c>
-      <c r="F99" s="5">
-        <v>66195</v>
-      </c>
-      <c r="G99" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H99" s="2">
-        <v>1</v>
-      </c>
-      <c r="I99" s="2">
-        <v>1</v>
-      </c>
-      <c r="K99" t="s">
-        <v>242</v>
-      </c>
-      <c r="L99" t="s">
-        <v>245</v>
-      </c>
-      <c r="M99" t="s">
-        <v>304</v>
-      </c>
+        <v>54584</v>
+      </c>
+      <c r="F99" s="5"/>
     </row>
     <row r="100" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A100" s="6">
-        <v>29</v>
-      </c>
-      <c r="B100" t="s">
-        <v>30</v>
-      </c>
+      <c r="A100" s="6"/>
       <c r="C100" s="15" t="s">
-        <v>433</v>
+        <v>714</v>
       </c>
       <c r="D100" s="5">
-        <v>45491</v>
-      </c>
-      <c r="F100" s="5">
-        <v>66188</v>
-      </c>
-      <c r="G100" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H100" s="2">
-        <v>7</v>
-      </c>
-      <c r="I100" s="2">
-        <v>3</v>
-      </c>
-      <c r="J100" s="2">
-        <v>4</v>
-      </c>
-      <c r="K100" t="s">
-        <v>242</v>
-      </c>
-      <c r="L100" t="s">
-        <v>254</v>
-      </c>
-      <c r="M100" t="s">
-        <v>245</v>
-      </c>
+        <v>55375</v>
+      </c>
+      <c r="F100" s="5"/>
     </row>
     <row r="101" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A101" s="6"/>
       <c r="C101" s="15" t="s">
-        <v>434</v>
+        <v>715</v>
       </c>
       <c r="D101" s="5">
-        <v>56012</v>
+        <v>57188</v>
       </c>
       <c r="F101" s="5"/>
     </row>
     <row r="102" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A102" s="6"/>
+      <c r="A102" s="6">
+        <v>27</v>
+      </c>
+      <c r="B102" t="s">
+        <v>28</v>
+      </c>
       <c r="C102" s="15" t="s">
-        <v>435</v>
+        <v>716</v>
       </c>
       <c r="D102" s="5">
-        <v>65710</v>
-      </c>
-      <c r="F102" s="5"/>
+        <v>42805</v>
+      </c>
+      <c r="F102" s="5">
+        <v>66231</v>
+      </c>
+      <c r="G102" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H102" s="2">
+        <v>1</v>
+      </c>
+      <c r="I102" s="2">
+        <v>1</v>
+      </c>
+      <c r="K102" t="s">
+        <v>242</v>
+      </c>
+      <c r="L102" t="s">
+        <v>314</v>
+      </c>
+      <c r="M102" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="103" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A103" s="6"/>
+      <c r="A103" s="6">
+        <v>28</v>
+      </c>
+      <c r="B103" t="s">
+        <v>29</v>
+      </c>
       <c r="C103" s="15" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D103" s="5">
-        <v>53794</v>
-      </c>
-      <c r="F103" s="5"/>
+        <v>49050</v>
+      </c>
+      <c r="F103" s="5">
+        <v>66195</v>
+      </c>
+      <c r="G103" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H103" s="2">
+        <v>1</v>
+      </c>
+      <c r="I103" s="2">
+        <v>1</v>
+      </c>
+      <c r="K103" t="s">
+        <v>242</v>
+      </c>
+      <c r="L103" t="s">
+        <v>245</v>
+      </c>
+      <c r="M103" t="s">
+        <v>304</v>
+      </c>
     </row>
     <row r="104" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A104" s="6"/>
+      <c r="A104" s="6">
+        <v>29</v>
+      </c>
+      <c r="B104" t="s">
+        <v>30</v>
+      </c>
       <c r="C104" s="15" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="D104" s="5">
-        <v>64340</v>
-      </c>
-      <c r="F104" s="5"/>
+        <v>45491</v>
+      </c>
+      <c r="F104" s="5">
+        <v>66188</v>
+      </c>
+      <c r="G104" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H104" s="2">
+        <v>7</v>
+      </c>
+      <c r="I104" s="2">
+        <v>3</v>
+      </c>
+      <c r="J104" s="2">
+        <v>4</v>
+      </c>
+      <c r="K104" t="s">
+        <v>242</v>
+      </c>
+      <c r="L104" t="s">
+        <v>254</v>
+      </c>
+      <c r="M104" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="105" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A105" s="6"/>
       <c r="C105" s="15" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="D105" s="5">
-        <v>33209</v>
+        <v>56012</v>
       </c>
       <c r="F105" s="5"/>
     </row>
     <row r="106" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A106" s="6"/>
       <c r="C106" s="15" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D106" s="5">
-        <v>45332</v>
+        <v>65710</v>
       </c>
       <c r="F106" s="5"/>
     </row>
-    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A107" s="6">
-        <v>30</v>
-      </c>
-      <c r="B107" t="s">
-        <v>31</v>
-      </c>
-      <c r="C107" t="s">
-        <v>79</v>
-      </c>
-      <c r="F107" s="5">
-        <v>66183</v>
-      </c>
-      <c r="G107" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H107" s="2">
-        <v>1</v>
-      </c>
-      <c r="I107" s="2">
-        <v>1</v>
-      </c>
-      <c r="K107" t="s">
-        <v>242</v>
-      </c>
-      <c r="L107" t="s">
-        <v>245</v>
-      </c>
-      <c r="M107" t="s">
-        <v>269</v>
-      </c>
-    </row>
-    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A108" s="6">
-        <v>31</v>
-      </c>
-      <c r="B108" t="s">
-        <v>32</v>
-      </c>
-      <c r="C108" t="s">
-        <v>80</v>
-      </c>
-      <c r="F108" s="5">
-        <v>66182</v>
-      </c>
-      <c r="G108" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H108" s="2">
-        <v>9</v>
-      </c>
-      <c r="I108" s="2">
-        <v>5</v>
-      </c>
-      <c r="J108" s="2">
-        <v>4</v>
-      </c>
-      <c r="K108" t="s">
-        <v>241</v>
-      </c>
-      <c r="L108" t="s">
-        <v>264</v>
-      </c>
-      <c r="M108" t="s">
-        <v>245</v>
-      </c>
+    <row r="107" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A107" s="6"/>
+      <c r="C107" s="15" t="s">
+        <v>436</v>
+      </c>
+      <c r="D107" s="5">
+        <v>53794</v>
+      </c>
+      <c r="F107" s="5"/>
+    </row>
+    <row r="108" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A108" s="6"/>
+      <c r="C108" s="15" t="s">
+        <v>437</v>
+      </c>
+      <c r="D108" s="5">
+        <v>64340</v>
+      </c>
+      <c r="F108" s="5"/>
     </row>
     <row r="109" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A109" s="6">
-        <v>32</v>
-      </c>
-      <c r="B109" t="s">
-        <v>33</v>
-      </c>
+      <c r="A109" s="6"/>
       <c r="C109" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D109" s="5">
-        <v>53896</v>
-      </c>
-      <c r="F109" s="5">
-        <v>66169</v>
-      </c>
-      <c r="G109" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H109" s="2">
-        <v>6</v>
-      </c>
-      <c r="I109" s="2">
-        <v>3</v>
-      </c>
-      <c r="J109" s="2">
-        <v>3</v>
-      </c>
-      <c r="K109" t="s">
-        <v>242</v>
-      </c>
-      <c r="L109" t="s">
-        <v>245</v>
-      </c>
-      <c r="M109" t="s">
-        <v>328</v>
-      </c>
+        <v>33209</v>
+      </c>
+      <c r="F109" s="5"/>
     </row>
     <row r="110" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A110" s="6"/>
       <c r="C110" s="15" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="D110" s="5">
-        <v>45148</v>
+        <v>45332</v>
       </c>
       <c r="F110" s="5"/>
     </row>
     <row r="111" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A111" s="6"/>
+      <c r="A111" s="6">
+        <v>30</v>
+      </c>
+      <c r="B111" t="s">
+        <v>31</v>
+      </c>
       <c r="C111" s="15" t="s">
-        <v>442</v>
+        <v>717</v>
       </c>
       <c r="D111" s="5">
-        <v>46509</v>
-      </c>
-      <c r="F111" s="5"/>
+        <v>41346</v>
+      </c>
+      <c r="F111" s="5">
+        <v>66183</v>
+      </c>
+      <c r="G111" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H111" s="2">
+        <v>1</v>
+      </c>
+      <c r="I111" s="2">
+        <v>1</v>
+      </c>
+      <c r="K111" t="s">
+        <v>242</v>
+      </c>
+      <c r="L111" t="s">
+        <v>245</v>
+      </c>
+      <c r="M111" t="s">
+        <v>269</v>
+      </c>
     </row>
     <row r="112" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A112" s="6"/>
+      <c r="A112" s="6">
+        <v>31</v>
+      </c>
+      <c r="B112" t="s">
+        <v>32</v>
+      </c>
       <c r="C112" s="15" t="s">
-        <v>443</v>
+        <v>718</v>
       </c>
       <c r="D112" s="5">
-        <v>55011</v>
-      </c>
-      <c r="F112" s="5"/>
+        <v>46818</v>
+      </c>
+      <c r="F112" s="5">
+        <v>66182</v>
+      </c>
+      <c r="G112" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H112" s="2">
+        <v>9</v>
+      </c>
+      <c r="I112" s="2">
+        <v>5</v>
+      </c>
+      <c r="J112" s="2">
+        <v>4</v>
+      </c>
+      <c r="K112" t="s">
+        <v>241</v>
+      </c>
+      <c r="L112" t="s">
+        <v>264</v>
+      </c>
+      <c r="M112" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="113" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A113" s="6"/>
       <c r="C113" s="15" t="s">
-        <v>444</v>
+        <v>719</v>
       </c>
       <c r="D113" s="5">
-        <v>63210</v>
+        <v>46300</v>
       </c>
       <c r="F113" s="5"/>
     </row>
     <row r="114" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A114" s="6"/>
       <c r="C114" s="15" t="s">
-        <v>445</v>
+        <v>720</v>
       </c>
       <c r="D114" s="5">
-        <v>65635</v>
+        <v>54739</v>
       </c>
       <c r="F114" s="5"/>
     </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A115" s="6">
-        <v>33</v>
-      </c>
-      <c r="B115" t="s">
-        <v>34</v>
-      </c>
-      <c r="C115" t="s">
-        <v>82</v>
-      </c>
-      <c r="F115" s="5">
-        <v>66138</v>
-      </c>
-      <c r="G115" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H115" s="2">
-        <v>4</v>
-      </c>
-      <c r="I115" s="2">
-        <v>2</v>
-      </c>
-      <c r="J115" s="2">
-        <v>2</v>
-      </c>
-      <c r="K115" t="s">
-        <v>242</v>
-      </c>
-      <c r="L115" t="s">
-        <v>266</v>
-      </c>
-      <c r="M115" t="s">
-        <v>245</v>
-      </c>
+    <row r="115" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A115" s="6"/>
+      <c r="C115" s="15" t="s">
+        <v>721</v>
+      </c>
+      <c r="D115" s="5">
+        <v>56741</v>
+      </c>
+      <c r="F115" s="5"/>
     </row>
     <row r="116" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A116" s="6">
-        <v>34</v>
-      </c>
-      <c r="B116" t="s">
-        <v>35</v>
-      </c>
+      <c r="A116" s="6"/>
       <c r="C116" s="15" t="s">
-        <v>446</v>
+        <v>722</v>
       </c>
       <c r="D116" s="5">
-        <v>51271</v>
-      </c>
-      <c r="F116" s="5">
-        <v>66132</v>
-      </c>
-      <c r="G116" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H116" s="2">
-        <v>4</v>
-      </c>
-      <c r="I116" s="2">
-        <v>2</v>
-      </c>
-      <c r="J116" s="2">
-        <v>2</v>
-      </c>
-      <c r="K116" t="s">
-        <v>242</v>
-      </c>
-      <c r="L116" t="s">
-        <v>287</v>
-      </c>
-      <c r="M116" t="s">
-        <v>245</v>
-      </c>
+        <v>54227</v>
+      </c>
+      <c r="F116" s="5"/>
     </row>
     <row r="117" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A117" s="6"/>
       <c r="C117" s="15" t="s">
-        <v>447</v>
+        <v>723</v>
       </c>
       <c r="D117" s="5">
-        <v>52292</v>
+        <v>56162</v>
       </c>
       <c r="F117" s="5"/>
     </row>
     <row r="118" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A118" s="6"/>
       <c r="C118" s="15" t="s">
-        <v>448</v>
+        <v>724</v>
       </c>
       <c r="D118" s="5">
-        <v>60272</v>
+        <v>58108</v>
       </c>
       <c r="F118" s="5"/>
     </row>
     <row r="119" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A119" s="6"/>
       <c r="C119" s="15" t="s">
-        <v>449</v>
+        <v>725</v>
       </c>
       <c r="D119" s="5">
-        <v>61765</v>
+        <v>65172</v>
       </c>
       <c r="F119" s="5"/>
     </row>
     <row r="120" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A120" s="6">
-        <v>35</v>
-      </c>
-      <c r="B120" t="s">
-        <v>36</v>
-      </c>
+      <c r="A120" s="6"/>
       <c r="C120" s="15" t="s">
-        <v>450</v>
+        <v>726</v>
       </c>
       <c r="D120" s="5">
-        <v>53803</v>
-      </c>
-      <c r="F120" s="5">
-        <v>66127</v>
-      </c>
-      <c r="G120" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H120" s="2">
-        <v>4</v>
-      </c>
-      <c r="I120" s="2">
-        <v>2</v>
-      </c>
-      <c r="J120" s="2">
-        <v>2</v>
-      </c>
-      <c r="K120" t="s">
-        <v>242</v>
-      </c>
-      <c r="L120" t="s">
-        <v>275</v>
-      </c>
-      <c r="M120" t="s">
+        <v>62367</v>
+      </c>
+      <c r="F120" s="5"/>
+    </row>
+    <row r="121" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A121" s="6">
+        <v>32</v>
+      </c>
+      <c r="B121" t="s">
+        <v>33</v>
+      </c>
+      <c r="C121" s="15" t="s">
+        <v>440</v>
+      </c>
+      <c r="D121" s="5">
+        <v>53896</v>
+      </c>
+      <c r="F121" s="5">
+        <v>66169</v>
+      </c>
+      <c r="G121" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H121" s="2">
+        <v>6</v>
+      </c>
+      <c r="I121" s="2">
+        <v>3</v>
+      </c>
+      <c r="J121" s="2">
+        <v>3</v>
+      </c>
+      <c r="K121" t="s">
+        <v>242</v>
+      </c>
+      <c r="L121" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="121" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A121" s="6"/>
-      <c r="C121" s="15" t="s">
-        <v>451</v>
-      </c>
-      <c r="D121" s="5">
-        <v>53171</v>
-      </c>
-      <c r="F121" s="5"/>
+      <c r="M121" t="s">
+        <v>328</v>
+      </c>
     </row>
     <row r="122" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A122" s="6"/>
       <c r="C122" s="15" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="D122" s="5">
-        <v>62769</v>
+        <v>45148</v>
       </c>
       <c r="F122" s="5"/>
     </row>
     <row r="123" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A123" s="6"/>
       <c r="C123" s="15" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="D123" s="5">
-        <v>64563</v>
+        <v>46509</v>
       </c>
       <c r="F123" s="5"/>
     </row>
     <row r="124" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A124" s="6">
-        <v>36</v>
-      </c>
-      <c r="B124" t="s">
-        <v>37</v>
-      </c>
+      <c r="A124" s="6"/>
       <c r="C124" s="15" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="D124" s="5">
-        <v>50409</v>
-      </c>
-      <c r="F124" s="5">
-        <v>66121</v>
-      </c>
-      <c r="G124" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H124" s="2">
-        <v>4</v>
-      </c>
-      <c r="I124" s="2">
-        <v>1</v>
-      </c>
-      <c r="J124" s="2">
-        <v>3</v>
-      </c>
-      <c r="K124" t="s">
-        <v>242</v>
-      </c>
-      <c r="L124" t="s">
-        <v>290</v>
-      </c>
-      <c r="M124" t="s">
-        <v>245</v>
-      </c>
+        <v>55011</v>
+      </c>
+      <c r="F124" s="5"/>
     </row>
     <row r="125" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A125" s="6"/>
       <c r="C125" s="15" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="D125" s="5">
-        <v>59986</v>
+        <v>63210</v>
       </c>
       <c r="F125" s="5"/>
     </row>
     <row r="126" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A126" s="6"/>
       <c r="C126" s="15" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="D126" s="5">
-        <v>52324</v>
+        <v>65635</v>
       </c>
       <c r="F126" s="5"/>
     </row>
     <row r="127" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A127" s="6"/>
+      <c r="A127" s="6">
+        <v>33</v>
+      </c>
+      <c r="B127" t="s">
+        <v>34</v>
+      </c>
       <c r="C127" s="15" t="s">
-        <v>457</v>
+        <v>727</v>
       </c>
       <c r="D127" s="5">
-        <v>58903</v>
-      </c>
-      <c r="F127" s="5"/>
+        <v>46671</v>
+      </c>
+      <c r="F127" s="5">
+        <v>66138</v>
+      </c>
+      <c r="G127" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H127" s="2">
+        <v>4</v>
+      </c>
+      <c r="I127" s="2">
+        <v>2</v>
+      </c>
+      <c r="J127" s="2">
+        <v>2</v>
+      </c>
+      <c r="K127" t="s">
+        <v>242</v>
+      </c>
+      <c r="L127" t="s">
+        <v>266</v>
+      </c>
+      <c r="M127" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="128" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A128" s="6">
-        <v>37</v>
-      </c>
-      <c r="B128" t="s">
-        <v>38</v>
-      </c>
+      <c r="A128" s="6"/>
       <c r="C128" s="15" t="s">
-        <v>458</v>
+        <v>728</v>
       </c>
       <c r="D128" s="5">
-        <v>43904</v>
-      </c>
-      <c r="F128" s="5">
-        <v>66058</v>
-      </c>
-      <c r="G128" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H128" s="2">
-        <v>4</v>
-      </c>
-      <c r="I128" s="2">
-        <v>3</v>
-      </c>
-      <c r="J128" s="2">
-        <v>1</v>
-      </c>
-      <c r="K128" t="s">
-        <v>242</v>
-      </c>
-      <c r="L128" t="s">
-        <v>245</v>
-      </c>
-      <c r="M128" t="s">
-        <v>280</v>
-      </c>
+        <v>48140</v>
+      </c>
+      <c r="F128" s="5"/>
     </row>
     <row r="129" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A129" s="6"/>
       <c r="C129" s="15" t="s">
-        <v>459</v>
+        <v>729</v>
       </c>
       <c r="D129" s="5">
-        <v>32797</v>
+        <v>57369</v>
       </c>
       <c r="F129" s="5"/>
     </row>
     <row r="130" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A130" s="6"/>
       <c r="C130" s="15" t="s">
-        <v>460</v>
+        <v>730</v>
       </c>
       <c r="D130" s="5">
-        <v>44749</v>
+        <v>58760</v>
       </c>
       <c r="F130" s="5"/>
     </row>
     <row r="131" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A131" s="6"/>
+      <c r="A131" s="6">
+        <v>34</v>
+      </c>
+      <c r="B131" t="s">
+        <v>35</v>
+      </c>
       <c r="C131" s="15" t="s">
-        <v>461</v>
+        <v>446</v>
       </c>
       <c r="D131" s="5">
-        <v>54759</v>
-      </c>
-      <c r="F131" s="5"/>
+        <v>51271</v>
+      </c>
+      <c r="F131" s="5">
+        <v>66132</v>
+      </c>
+      <c r="G131" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H131" s="2">
+        <v>4</v>
+      </c>
+      <c r="I131" s="2">
+        <v>2</v>
+      </c>
+      <c r="J131" s="2">
+        <v>2</v>
+      </c>
+      <c r="K131" t="s">
+        <v>242</v>
+      </c>
+      <c r="L131" t="s">
+        <v>287</v>
+      </c>
+      <c r="M131" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="132" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A132" s="6">
-        <v>38</v>
-      </c>
-      <c r="B132" t="s">
-        <v>39</v>
-      </c>
+      <c r="A132" s="6"/>
       <c r="C132" s="15" t="s">
-        <v>462</v>
+        <v>447</v>
       </c>
       <c r="D132" s="5">
-        <v>50966</v>
-      </c>
-      <c r="F132" s="5">
-        <v>66029</v>
-      </c>
-      <c r="G132" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H132" s="2">
-        <v>3</v>
-      </c>
-      <c r="I132" s="2">
-        <v>1</v>
-      </c>
-      <c r="J132" s="2">
-        <v>2</v>
-      </c>
-      <c r="K132" t="s">
-        <v>242</v>
-      </c>
-      <c r="L132" t="s">
-        <v>255</v>
-      </c>
-      <c r="M132" t="s">
-        <v>245</v>
-      </c>
+        <v>52292</v>
+      </c>
+      <c r="F132" s="5"/>
     </row>
     <row r="133" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A133" s="6"/>
       <c r="C133" s="15" t="s">
-        <v>463</v>
+        <v>448</v>
       </c>
       <c r="D133" s="5">
-        <v>51641</v>
+        <v>60272</v>
       </c>
       <c r="F133" s="5"/>
     </row>
     <row r="134" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A134" s="6"/>
       <c r="C134" s="15" t="s">
-        <v>464</v>
+        <v>449</v>
       </c>
       <c r="D134" s="5">
-        <v>63145</v>
+        <v>61765</v>
       </c>
       <c r="F134" s="5"/>
     </row>
     <row r="135" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A135" s="6">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B135" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C135" s="15" t="s">
-        <v>465</v>
+        <v>450</v>
       </c>
       <c r="D135" s="5">
-        <v>58738</v>
+        <v>53803</v>
       </c>
       <c r="F135" s="5">
-        <v>66029</v>
+        <v>66127</v>
       </c>
       <c r="G135" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H135" s="2">
+        <v>4</v>
+      </c>
+      <c r="I135" s="2">
         <v>2</v>
       </c>
       <c r="J135" s="2">
@@ -5400,7 +5414,7 @@
         <v>242</v>
       </c>
       <c r="L135" t="s">
-        <v>302</v>
+        <v>275</v>
       </c>
       <c r="M135" t="s">
         <v>245</v>
@@ -5409,224 +5423,193 @@
     <row r="136" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A136" s="6"/>
       <c r="C136" s="15" t="s">
-        <v>466</v>
+        <v>451</v>
       </c>
       <c r="D136" s="5">
-        <v>59699</v>
+        <v>53171</v>
       </c>
       <c r="F136" s="5"/>
     </row>
     <row r="137" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A137" s="6">
-        <v>40</v>
-      </c>
-      <c r="B137" t="s">
-        <v>41</v>
-      </c>
+      <c r="A137" s="6"/>
       <c r="C137" s="15" t="s">
-        <v>467</v>
+        <v>452</v>
       </c>
       <c r="D137" s="5">
-        <v>39252</v>
-      </c>
-      <c r="F137" s="5">
-        <v>66021</v>
-      </c>
-      <c r="G137" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H137" s="2">
-        <v>4</v>
-      </c>
-      <c r="I137" s="2">
-        <v>2</v>
-      </c>
-      <c r="J137" s="2">
-        <v>2</v>
-      </c>
-      <c r="K137" t="s">
-        <v>242</v>
-      </c>
-      <c r="L137" t="s">
-        <v>267</v>
-      </c>
-      <c r="M137" t="s">
-        <v>245</v>
-      </c>
+        <v>62769</v>
+      </c>
+      <c r="F137" s="5"/>
     </row>
     <row r="138" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A138" s="6"/>
       <c r="C138" s="15" t="s">
-        <v>468</v>
+        <v>453</v>
       </c>
       <c r="D138" s="5">
-        <v>45407</v>
+        <v>64563</v>
       </c>
       <c r="F138" s="5"/>
     </row>
     <row r="139" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A139" s="6"/>
+      <c r="A139" s="6">
+        <v>36</v>
+      </c>
+      <c r="B139" t="s">
+        <v>37</v>
+      </c>
       <c r="C139" s="15" t="s">
-        <v>469</v>
+        <v>454</v>
       </c>
       <c r="D139" s="5">
-        <v>51487</v>
-      </c>
-      <c r="F139" s="5"/>
+        <v>50409</v>
+      </c>
+      <c r="F139" s="5">
+        <v>66121</v>
+      </c>
+      <c r="G139" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H139" s="2">
+        <v>4</v>
+      </c>
+      <c r="I139" s="2">
+        <v>1</v>
+      </c>
+      <c r="J139" s="2">
+        <v>3</v>
+      </c>
+      <c r="K139" t="s">
+        <v>242</v>
+      </c>
+      <c r="L139" t="s">
+        <v>290</v>
+      </c>
+      <c r="M139" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="140" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A140" s="6"/>
       <c r="C140" s="15" t="s">
-        <v>470</v>
+        <v>455</v>
       </c>
       <c r="D140" s="5">
-        <v>51569</v>
+        <v>59986</v>
       </c>
       <c r="F140" s="5"/>
     </row>
     <row r="141" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A141" s="6">
-        <v>41</v>
-      </c>
-      <c r="B141" t="s">
-        <v>42</v>
-      </c>
-      <c r="C141" s="16" t="s">
-        <v>471</v>
+      <c r="A141" s="6"/>
+      <c r="C141" s="15" t="s">
+        <v>456</v>
       </c>
       <c r="D141" s="5">
-        <v>53976</v>
-      </c>
-      <c r="F141" s="5">
-        <v>65997</v>
-      </c>
-      <c r="G141" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H141" s="2">
-        <v>3</v>
-      </c>
-      <c r="I141" s="2">
-        <v>1</v>
-      </c>
-      <c r="J141" s="2">
-        <v>2</v>
-      </c>
-      <c r="K141" t="s">
-        <v>242</v>
-      </c>
-      <c r="L141" t="s">
-        <v>245</v>
-      </c>
-      <c r="M141" t="s">
-        <v>257</v>
-      </c>
+        <v>52324</v>
+      </c>
+      <c r="F141" s="5"/>
     </row>
     <row r="142" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A142" s="6"/>
-      <c r="C142" s="16" t="s">
-        <v>472</v>
+      <c r="C142" s="15" t="s">
+        <v>457</v>
       </c>
       <c r="D142" s="5">
-        <v>56860</v>
+        <v>58903</v>
       </c>
       <c r="F142" s="5"/>
     </row>
     <row r="143" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A143" s="6"/>
-      <c r="C143" s="16" t="s">
-        <v>473</v>
+      <c r="A143" s="6">
+        <v>37</v>
+      </c>
+      <c r="B143" t="s">
+        <v>38</v>
+      </c>
+      <c r="C143" s="15" t="s">
+        <v>458</v>
       </c>
       <c r="D143" s="5">
-        <v>64508</v>
-      </c>
-      <c r="F143" s="5"/>
+        <v>43904</v>
+      </c>
+      <c r="F143" s="5">
+        <v>66058</v>
+      </c>
+      <c r="G143" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H143" s="2">
+        <v>4</v>
+      </c>
+      <c r="I143" s="2">
+        <v>3</v>
+      </c>
+      <c r="J143" s="2">
+        <v>1</v>
+      </c>
+      <c r="K143" t="s">
+        <v>242</v>
+      </c>
+      <c r="L143" t="s">
+        <v>245</v>
+      </c>
+      <c r="M143" t="s">
+        <v>280</v>
+      </c>
     </row>
     <row r="144" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A144" s="6">
-        <v>42</v>
-      </c>
-      <c r="B144" t="s">
-        <v>43</v>
-      </c>
-      <c r="C144" s="16" t="s">
-        <v>474</v>
+      <c r="A144" s="6"/>
+      <c r="C144" s="15" t="s">
+        <v>459</v>
       </c>
       <c r="D144" s="5">
-        <v>46863</v>
-      </c>
-      <c r="F144" s="5">
-        <v>65972</v>
-      </c>
-      <c r="G144" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H144" s="2">
-        <v>3</v>
-      </c>
-      <c r="I144" s="2">
-        <v>2</v>
-      </c>
-      <c r="J144" s="2">
-        <v>1</v>
-      </c>
-      <c r="K144" t="s">
-        <v>242</v>
-      </c>
-      <c r="L144" t="s">
-        <v>322</v>
-      </c>
-      <c r="M144" t="s">
-        <v>245</v>
-      </c>
+        <v>32797</v>
+      </c>
+      <c r="F144" s="5"/>
     </row>
     <row r="145" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A145" s="6"/>
-      <c r="C145" s="16" t="s">
-        <v>475</v>
+      <c r="C145" s="15" t="s">
+        <v>460</v>
       </c>
       <c r="D145" s="5">
-        <v>44854</v>
+        <v>44749</v>
       </c>
       <c r="F145" s="5"/>
     </row>
     <row r="146" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A146" s="6"/>
-      <c r="C146" s="16" t="s">
-        <v>476</v>
+      <c r="C146" s="15" t="s">
+        <v>461</v>
       </c>
       <c r="D146" s="5">
-        <v>53405</v>
+        <v>54759</v>
       </c>
       <c r="F146" s="5"/>
     </row>
     <row r="147" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A147" s="6">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B147" t="s">
-        <v>44</v>
-      </c>
-      <c r="C147" s="16" t="s">
-        <v>477</v>
+        <v>39</v>
+      </c>
+      <c r="C147" s="15" t="s">
+        <v>462</v>
       </c>
       <c r="D147" s="5">
-        <v>47948</v>
-      </c>
-      <c r="E147" t="s">
-        <v>115</v>
+        <v>50966</v>
       </c>
       <c r="F147" s="5">
-        <v>65949</v>
+        <v>66029</v>
       </c>
       <c r="G147" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H147" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I147" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J147" s="2">
         <v>2</v>
@@ -5635,7 +5618,7 @@
         <v>242</v>
       </c>
       <c r="L147" t="s">
-        <v>313</v>
+        <v>255</v>
       </c>
       <c r="M147" t="s">
         <v>245</v>
@@ -5643,636 +5626,574 @@
     </row>
     <row r="148" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A148" s="6"/>
-      <c r="C148" s="16" t="s">
-        <v>478</v>
+      <c r="C148" s="15" t="s">
+        <v>463</v>
       </c>
       <c r="D148" s="5">
-        <v>53965</v>
+        <v>51641</v>
       </c>
       <c r="F148" s="5"/>
     </row>
     <row r="149" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A149" s="6"/>
-      <c r="C149" s="16" t="s">
-        <v>479</v>
+      <c r="C149" s="15" t="s">
+        <v>464</v>
       </c>
       <c r="D149" s="5">
-        <v>61535</v>
+        <v>63145</v>
       </c>
       <c r="F149" s="5"/>
     </row>
     <row r="150" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A150" s="6"/>
-      <c r="C150" s="16" t="s">
-        <v>480</v>
+      <c r="A150" s="6">
+        <v>39</v>
+      </c>
+      <c r="B150" t="s">
+        <v>40</v>
+      </c>
+      <c r="C150" s="15" t="s">
+        <v>465</v>
       </c>
       <c r="D150" s="5">
-        <v>63156</v>
-      </c>
-      <c r="F150" s="5"/>
-    </row>
-    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A151" s="6">
-        <v>44</v>
-      </c>
-      <c r="B151" t="s">
-        <v>45</v>
-      </c>
-      <c r="C151" t="s">
-        <v>93</v>
-      </c>
-      <c r="E151" t="s">
-        <v>114</v>
-      </c>
-      <c r="F151" s="5">
-        <v>65877</v>
-      </c>
-      <c r="G151" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H151" s="2">
+        <v>58738</v>
+      </c>
+      <c r="F150" s="5">
+        <v>66029</v>
+      </c>
+      <c r="G150" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H150" s="2">
+        <v>2</v>
+      </c>
+      <c r="J150" s="2">
+        <v>2</v>
+      </c>
+      <c r="K150" t="s">
+        <v>242</v>
+      </c>
+      <c r="L150" t="s">
+        <v>302</v>
+      </c>
+      <c r="M150" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A151" s="6"/>
+      <c r="C151" s="15" t="s">
+        <v>466</v>
+      </c>
+      <c r="D151" s="5">
+        <v>59699</v>
+      </c>
+      <c r="F151" s="5"/>
+    </row>
+    <row r="152" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A152" s="6">
+        <v>40</v>
+      </c>
+      <c r="B152" t="s">
+        <v>41</v>
+      </c>
+      <c r="C152" s="15" t="s">
+        <v>467</v>
+      </c>
+      <c r="D152" s="5">
+        <v>39252</v>
+      </c>
+      <c r="F152" s="5">
+        <v>66021</v>
+      </c>
+      <c r="G152" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H152" s="2">
         <v>4</v>
       </c>
-      <c r="I151" s="2">
-        <v>3</v>
-      </c>
-      <c r="J151" s="2">
-        <v>1</v>
-      </c>
-      <c r="K151" t="s">
-        <v>242</v>
-      </c>
-      <c r="L151" t="s">
-        <v>249</v>
-      </c>
-      <c r="M151" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A152" s="6">
-        <v>45</v>
-      </c>
-      <c r="B152" t="s">
-        <v>46</v>
-      </c>
-      <c r="C152" t="s">
-        <v>94</v>
-      </c>
-      <c r="E152" t="s">
-        <v>113</v>
-      </c>
-      <c r="F152" s="5">
-        <v>65858</v>
-      </c>
-      <c r="G152" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H152" s="2">
-        <v>5</v>
-      </c>
       <c r="I152" s="2">
         <v>2</v>
       </c>
       <c r="J152" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K152" t="s">
         <v>242</v>
       </c>
       <c r="L152" t="s">
-        <v>308</v>
+        <v>267</v>
       </c>
       <c r="M152" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A153" s="6">
-        <v>46</v>
-      </c>
-      <c r="B153" t="s">
-        <v>47</v>
-      </c>
+      <c r="A153" s="6"/>
       <c r="C153" s="15" t="s">
-        <v>481</v>
+        <v>468</v>
       </c>
       <c r="D153" s="5">
-        <v>49130</v>
-      </c>
-      <c r="E153" t="s">
-        <v>112</v>
-      </c>
-      <c r="F153" s="5">
-        <v>65840</v>
-      </c>
-      <c r="G153" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H153" s="2">
-        <v>4</v>
-      </c>
-      <c r="I153" s="2">
-        <v>3</v>
-      </c>
-      <c r="J153" s="2">
-        <v>1</v>
-      </c>
-      <c r="K153" t="s">
-        <v>242</v>
-      </c>
-      <c r="L153" t="s">
-        <v>268</v>
-      </c>
-      <c r="M153" t="s">
-        <v>245</v>
-      </c>
+        <v>45407</v>
+      </c>
+      <c r="F153" s="5"/>
     </row>
     <row r="154" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A154" s="6"/>
       <c r="C154" s="15" t="s">
-        <v>482</v>
+        <v>469</v>
       </c>
       <c r="D154" s="5">
-        <v>59613</v>
+        <v>51487</v>
       </c>
       <c r="F154" s="5"/>
     </row>
     <row r="155" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A155" s="6"/>
       <c r="C155" s="15" t="s">
-        <v>483</v>
+        <v>470</v>
       </c>
       <c r="D155" s="5">
-        <v>48314</v>
+        <v>51569</v>
       </c>
       <c r="F155" s="5"/>
     </row>
     <row r="156" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A156" s="6"/>
-      <c r="C156" s="15" t="s">
-        <v>484</v>
+      <c r="A156" s="6">
+        <v>41</v>
+      </c>
+      <c r="B156" t="s">
+        <v>42</v>
+      </c>
+      <c r="C156" s="16" t="s">
+        <v>471</v>
       </c>
       <c r="D156" s="5">
-        <v>59102</v>
-      </c>
-      <c r="F156" s="5"/>
+        <v>53976</v>
+      </c>
+      <c r="F156" s="5">
+        <v>65997</v>
+      </c>
+      <c r="G156" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H156" s="2">
+        <v>3</v>
+      </c>
+      <c r="I156" s="2">
+        <v>1</v>
+      </c>
+      <c r="J156" s="2">
+        <v>2</v>
+      </c>
+      <c r="K156" t="s">
+        <v>242</v>
+      </c>
+      <c r="L156" t="s">
+        <v>245</v>
+      </c>
+      <c r="M156" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="157" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A157" s="6">
-        <v>47</v>
-      </c>
-      <c r="B157" t="s">
-        <v>48</v>
-      </c>
-      <c r="C157" s="15" t="s">
-        <v>485</v>
+      <c r="A157" s="6"/>
+      <c r="C157" s="16" t="s">
+        <v>472</v>
       </c>
       <c r="D157" s="5">
-        <v>50721</v>
-      </c>
-      <c r="E157" t="s">
-        <v>111</v>
-      </c>
-      <c r="F157" s="5">
-        <v>65826</v>
-      </c>
-      <c r="G157" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H157" s="2">
-        <v>3</v>
-      </c>
-      <c r="I157" s="2">
-        <v>2</v>
-      </c>
-      <c r="J157" s="2">
-        <v>1</v>
-      </c>
-      <c r="K157" t="s">
-        <v>242</v>
-      </c>
-      <c r="L157" t="s">
-        <v>245</v>
-      </c>
-      <c r="M157" t="s">
-        <v>298</v>
-      </c>
+        <v>56860</v>
+      </c>
+      <c r="F157" s="5"/>
     </row>
     <row r="158" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A158" s="6"/>
-      <c r="C158" s="15" t="s">
-        <v>486</v>
+      <c r="C158" s="16" t="s">
+        <v>473</v>
       </c>
       <c r="D158" s="5">
-        <v>50325</v>
+        <v>64508</v>
       </c>
       <c r="F158" s="5"/>
     </row>
     <row r="159" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A159" s="6"/>
-      <c r="C159" s="15" t="s">
-        <v>487</v>
+      <c r="A159" s="6">
+        <v>42</v>
+      </c>
+      <c r="B159" t="s">
+        <v>43</v>
+      </c>
+      <c r="C159" s="16" t="s">
+        <v>474</v>
       </c>
       <c r="D159" s="5">
-        <v>59030</v>
-      </c>
-      <c r="F159" s="5"/>
+        <v>46863</v>
+      </c>
+      <c r="F159" s="5">
+        <v>65972</v>
+      </c>
+      <c r="G159" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H159" s="2">
+        <v>3</v>
+      </c>
+      <c r="I159" s="2">
+        <v>2</v>
+      </c>
+      <c r="J159" s="2">
+        <v>1</v>
+      </c>
+      <c r="K159" t="s">
+        <v>242</v>
+      </c>
+      <c r="L159" t="s">
+        <v>322</v>
+      </c>
+      <c r="M159" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="160" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A160" s="6">
-        <v>48</v>
-      </c>
-      <c r="B160" t="s">
-        <v>49</v>
-      </c>
-      <c r="C160" s="15" t="s">
-        <v>488</v>
+      <c r="A160" s="6"/>
+      <c r="C160" s="16" t="s">
+        <v>475</v>
       </c>
       <c r="D160" s="5">
-        <v>49574</v>
-      </c>
-      <c r="E160" t="s">
-        <v>110</v>
-      </c>
-      <c r="F160" s="5">
-        <v>65825</v>
-      </c>
-      <c r="G160" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H160" s="2">
-        <v>4</v>
-      </c>
-      <c r="I160" s="2">
-        <v>3</v>
-      </c>
-      <c r="J160" s="2">
-        <v>1</v>
-      </c>
-      <c r="K160" t="s">
-        <v>242</v>
-      </c>
-      <c r="L160" t="s">
-        <v>317</v>
-      </c>
-      <c r="M160" t="s">
-        <v>245</v>
-      </c>
+        <v>44854</v>
+      </c>
+      <c r="F160" s="5"/>
     </row>
     <row r="161" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A161" s="6"/>
-      <c r="C161" s="15" t="s">
-        <v>489</v>
+      <c r="C161" s="16" t="s">
+        <v>476</v>
       </c>
       <c r="D161" s="5">
-        <v>47832</v>
+        <v>53405</v>
       </c>
       <c r="F161" s="5"/>
     </row>
     <row r="162" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A162" s="6"/>
-      <c r="C162" s="15" t="s">
-        <v>490</v>
+      <c r="A162" s="6">
+        <v>43</v>
+      </c>
+      <c r="B162" t="s">
+        <v>44</v>
+      </c>
+      <c r="C162" s="16" t="s">
+        <v>477</v>
       </c>
       <c r="D162" s="5">
-        <v>56831</v>
-      </c>
-      <c r="F162" s="5"/>
+        <v>47948</v>
+      </c>
+      <c r="E162" t="s">
+        <v>115</v>
+      </c>
+      <c r="F162" s="5">
+        <v>65949</v>
+      </c>
+      <c r="G162" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H162" s="2">
+        <v>4</v>
+      </c>
+      <c r="I162" s="2">
+        <v>2</v>
+      </c>
+      <c r="J162" s="2">
+        <v>2</v>
+      </c>
+      <c r="K162" t="s">
+        <v>242</v>
+      </c>
+      <c r="L162" t="s">
+        <v>313</v>
+      </c>
+      <c r="M162" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="163" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A163" s="6"/>
-      <c r="C163" s="15" t="s">
-        <v>491</v>
+      <c r="C163" s="16" t="s">
+        <v>478</v>
       </c>
       <c r="D163" s="5">
-        <v>58358</v>
+        <v>53965</v>
       </c>
       <c r="F163" s="5"/>
     </row>
     <row r="164" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A164" s="6">
-        <v>49</v>
-      </c>
-      <c r="B164" t="s">
-        <v>50</v>
-      </c>
-      <c r="C164" s="15" t="s">
-        <v>492</v>
+      <c r="A164" s="6"/>
+      <c r="C164" s="16" t="s">
+        <v>479</v>
       </c>
       <c r="D164" s="5">
-        <v>53186</v>
-      </c>
-      <c r="E164" t="s">
-        <v>109</v>
-      </c>
-      <c r="F164" s="5">
-        <v>65800</v>
-      </c>
-      <c r="G164" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H164" s="2">
-        <v>3</v>
-      </c>
-      <c r="I164" s="2">
-        <v>2</v>
-      </c>
-      <c r="J164" s="2">
-        <v>1</v>
-      </c>
-      <c r="K164" t="s">
-        <v>242</v>
-      </c>
-      <c r="L164" t="s">
-        <v>245</v>
-      </c>
-      <c r="M164" t="s">
-        <v>244</v>
-      </c>
+        <v>61535</v>
+      </c>
+      <c r="F164" s="5"/>
     </row>
     <row r="165" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A165" s="6"/>
-      <c r="C165" s="15" t="s">
-        <v>493</v>
+      <c r="C165" s="16" t="s">
+        <v>480</v>
       </c>
       <c r="D165" s="5">
-        <v>53030</v>
+        <v>63156</v>
       </c>
       <c r="F165" s="5"/>
     </row>
     <row r="166" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A166" s="6"/>
-      <c r="C166" s="15" t="s">
-        <v>494</v>
+      <c r="A166" s="6">
+        <v>44</v>
+      </c>
+      <c r="B166" t="s">
+        <v>45</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>626</v>
       </c>
       <c r="D166" s="5">
-        <v>55329</v>
-      </c>
-      <c r="F166" s="5"/>
+        <v>47853</v>
+      </c>
+      <c r="E166" t="s">
+        <v>114</v>
+      </c>
+      <c r="F166" s="5">
+        <v>65877</v>
+      </c>
+      <c r="G166" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H166" s="2">
+        <v>4</v>
+      </c>
+      <c r="I166" s="2">
+        <v>3</v>
+      </c>
+      <c r="J166" s="2">
+        <v>1</v>
+      </c>
+      <c r="K166" t="s">
+        <v>242</v>
+      </c>
+      <c r="L166" t="s">
+        <v>249</v>
+      </c>
+      <c r="M166" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="167" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A167" s="6">
-        <v>50</v>
-      </c>
-      <c r="B167" t="s">
-        <v>51</v>
-      </c>
-      <c r="C167" s="15" t="s">
-        <v>495</v>
+      <c r="A167" s="6"/>
+      <c r="C167" s="16" t="s">
+        <v>627</v>
       </c>
       <c r="D167" s="5">
-        <v>41748</v>
-      </c>
-      <c r="E167" t="s">
-        <v>108</v>
-      </c>
-      <c r="F167" s="5">
-        <v>65762</v>
-      </c>
-      <c r="G167" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H167" s="2">
-        <v>2</v>
-      </c>
-      <c r="I167" s="2">
-        <v>1</v>
-      </c>
-      <c r="J167" s="2">
-        <v>1</v>
-      </c>
-      <c r="K167" t="s">
-        <v>242</v>
-      </c>
-      <c r="L167" t="s">
-        <v>321</v>
-      </c>
-      <c r="M167" t="s">
-        <v>245</v>
-      </c>
+        <v>45350</v>
+      </c>
+      <c r="F167" s="5"/>
     </row>
     <row r="168" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A168" s="6"/>
-      <c r="C168" s="15" t="s">
-        <v>496</v>
+      <c r="C168" s="16" t="s">
+        <v>628</v>
       </c>
       <c r="D168" s="5">
-        <v>42870</v>
+        <v>54849</v>
       </c>
       <c r="F168" s="5"/>
     </row>
     <row r="169" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A169" s="6">
-        <v>51</v>
-      </c>
-      <c r="B169" t="s">
-        <v>116</v>
-      </c>
-      <c r="C169" s="15" t="s">
-        <v>497</v>
+      <c r="A169" s="6"/>
+      <c r="C169" s="16" t="s">
+        <v>731</v>
       </c>
       <c r="D169" s="5">
-        <v>45299</v>
-      </c>
-      <c r="E169" t="s">
-        <v>215</v>
-      </c>
-      <c r="F169" s="5">
-        <v>65736</v>
-      </c>
-      <c r="G169" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H169" s="2">
+        <v>55649</v>
+      </c>
+      <c r="F169" s="5"/>
+    </row>
+    <row r="170" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A170" s="6">
+        <v>45</v>
+      </c>
+      <c r="B170" t="s">
+        <v>46</v>
+      </c>
+      <c r="C170" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="D170" s="5">
+        <v>53767</v>
+      </c>
+      <c r="E170" t="s">
+        <v>113</v>
+      </c>
+      <c r="F170" s="5">
+        <v>65858</v>
+      </c>
+      <c r="G170" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H170" s="2">
+        <v>5</v>
+      </c>
+      <c r="I170" s="2">
+        <v>2</v>
+      </c>
+      <c r="J170" s="2">
         <v>3</v>
       </c>
-      <c r="I169" s="2">
-        <v>2</v>
-      </c>
-      <c r="J169" s="2">
-        <v>1</v>
-      </c>
-      <c r="K169" t="s">
-        <v>242</v>
-      </c>
-      <c r="L169" t="s">
-        <v>305</v>
-      </c>
-      <c r="M169" t="s">
+      <c r="K170" t="s">
+        <v>242</v>
+      </c>
+      <c r="L170" t="s">
+        <v>308</v>
+      </c>
+      <c r="M170" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="170" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A170" s="6"/>
-      <c r="C170" s="15" t="s">
-        <v>498</v>
-      </c>
-      <c r="D170" s="5">
-        <v>48156</v>
-      </c>
-      <c r="F170" s="5"/>
     </row>
     <row r="171" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A171" s="6"/>
       <c r="C171" s="15" t="s">
-        <v>499</v>
+        <v>732</v>
       </c>
       <c r="D171" s="5">
-        <v>55796</v>
+        <v>46039</v>
       </c>
       <c r="F171" s="5"/>
     </row>
     <row r="172" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A172" s="6">
-        <v>52</v>
-      </c>
-      <c r="B172" t="s">
-        <v>117</v>
-      </c>
+      <c r="A172" s="6"/>
       <c r="C172" s="15" t="s">
-        <v>500</v>
+        <v>733</v>
       </c>
       <c r="D172" s="5">
-        <v>50544</v>
-      </c>
-      <c r="F172" s="5">
-        <v>65695</v>
-      </c>
-      <c r="G172" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H172" s="2">
-        <v>4</v>
-      </c>
-      <c r="I172" s="2">
-        <v>2</v>
-      </c>
-      <c r="J172" s="2">
-        <v>2</v>
-      </c>
-      <c r="K172" t="s">
-        <v>242</v>
-      </c>
-      <c r="L172" t="s">
-        <v>309</v>
-      </c>
-      <c r="M172" t="s">
-        <v>245</v>
-      </c>
+        <v>54304</v>
+      </c>
+      <c r="F172" s="5"/>
     </row>
     <row r="173" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A173" s="6"/>
       <c r="C173" s="15" t="s">
-        <v>501</v>
+        <v>734</v>
       </c>
       <c r="D173" s="5">
-        <v>49344</v>
+        <v>64129</v>
       </c>
       <c r="F173" s="5"/>
     </row>
     <row r="174" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A174" s="6"/>
       <c r="C174" s="15" t="s">
-        <v>502</v>
+        <v>735</v>
       </c>
       <c r="D174" s="5">
-        <v>59373</v>
+        <v>65575</v>
       </c>
       <c r="F174" s="5"/>
     </row>
     <row r="175" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A175" s="6"/>
+      <c r="A175" s="6">
+        <v>46</v>
+      </c>
+      <c r="B175" t="s">
+        <v>47</v>
+      </c>
       <c r="C175" s="15" t="s">
-        <v>503</v>
+        <v>481</v>
       </c>
       <c r="D175" s="5">
-        <v>63170</v>
-      </c>
-      <c r="F175" s="5"/>
+        <v>49130</v>
+      </c>
+      <c r="E175" t="s">
+        <v>112</v>
+      </c>
+      <c r="F175" s="5">
+        <v>65840</v>
+      </c>
+      <c r="G175" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H175" s="2">
+        <v>4</v>
+      </c>
+      <c r="I175" s="2">
+        <v>3</v>
+      </c>
+      <c r="J175" s="2">
+        <v>1</v>
+      </c>
+      <c r="K175" t="s">
+        <v>242</v>
+      </c>
+      <c r="L175" t="s">
+        <v>268</v>
+      </c>
+      <c r="M175" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="176" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A176" s="6">
-        <v>53</v>
-      </c>
-      <c r="B176" t="s">
-        <v>118</v>
-      </c>
+      <c r="A176" s="6"/>
       <c r="C176" s="15" t="s">
-        <v>504</v>
+        <v>482</v>
       </c>
       <c r="D176" s="5">
-        <v>56159</v>
-      </c>
-      <c r="F176" s="5">
-        <v>65644</v>
-      </c>
-      <c r="G176" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H176" s="2">
-        <v>3</v>
-      </c>
-      <c r="I176" s="2">
-        <v>1</v>
-      </c>
-      <c r="J176" s="2">
-        <v>2</v>
-      </c>
-      <c r="K176" t="s">
-        <v>242</v>
-      </c>
-      <c r="L176" t="s">
-        <v>310</v>
-      </c>
-      <c r="M176" t="s">
-        <v>245</v>
-      </c>
+        <v>59613</v>
+      </c>
+      <c r="F176" s="5"/>
     </row>
     <row r="177" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A177" s="6"/>
       <c r="C177" s="15" t="s">
-        <v>505</v>
+        <v>483</v>
       </c>
       <c r="D177" s="5">
-        <v>47618</v>
+        <v>48314</v>
       </c>
       <c r="F177" s="5"/>
     </row>
     <row r="178" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A178" s="6"/>
       <c r="C178" s="15" t="s">
-        <v>506</v>
+        <v>484</v>
       </c>
       <c r="D178" s="5">
-        <v>57826</v>
+        <v>59102</v>
       </c>
       <c r="F178" s="5"/>
     </row>
     <row r="179" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A179" s="6">
-        <v>54</v>
+        <v>47</v>
       </c>
       <c r="B179" t="s">
-        <v>119</v>
+        <v>48</v>
       </c>
       <c r="C179" s="15" t="s">
-        <v>507</v>
+        <v>485</v>
       </c>
       <c r="D179" s="5">
-        <v>45718</v>
+        <v>50721</v>
+      </c>
+      <c r="E179" t="s">
+        <v>111</v>
       </c>
       <c r="F179" s="5">
-        <v>65631</v>
+        <v>65826</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H179" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I179" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J179" s="2">
         <v>1</v>
@@ -6281,300 +6202,368 @@
         <v>242</v>
       </c>
       <c r="L179" t="s">
-        <v>324</v>
+        <v>245</v>
       </c>
       <c r="M179" t="s">
-        <v>245</v>
+        <v>298</v>
       </c>
     </row>
     <row r="180" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A180" s="6"/>
       <c r="C180" s="15" t="s">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="D180" s="5">
-        <v>58359</v>
+        <v>50325</v>
       </c>
       <c r="F180" s="5"/>
     </row>
     <row r="181" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A181" s="6"/>
       <c r="C181" s="15" t="s">
-        <v>509</v>
+        <v>487</v>
       </c>
       <c r="D181" s="5">
-        <v>60169</v>
+        <v>59030</v>
       </c>
       <c r="F181" s="5"/>
     </row>
     <row r="182" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A182" s="6"/>
+      <c r="A182" s="6">
+        <v>48</v>
+      </c>
+      <c r="B182" t="s">
+        <v>49</v>
+      </c>
       <c r="C182" s="15" t="s">
-        <v>510</v>
+        <v>488</v>
       </c>
       <c r="D182" s="5">
-        <v>50276</v>
-      </c>
-      <c r="F182" s="5"/>
+        <v>49574</v>
+      </c>
+      <c r="E182" t="s">
+        <v>110</v>
+      </c>
+      <c r="F182" s="5">
+        <v>65825</v>
+      </c>
+      <c r="G182" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H182" s="2">
+        <v>4</v>
+      </c>
+      <c r="I182" s="2">
+        <v>3</v>
+      </c>
+      <c r="J182" s="2">
+        <v>1</v>
+      </c>
+      <c r="K182" t="s">
+        <v>242</v>
+      </c>
+      <c r="L182" t="s">
+        <v>317</v>
+      </c>
+      <c r="M182" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="183" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A183" s="6">
-        <v>55</v>
-      </c>
-      <c r="B183" t="s">
-        <v>120</v>
-      </c>
+      <c r="A183" s="6"/>
       <c r="C183" s="15" t="s">
-        <v>511</v>
+        <v>489</v>
       </c>
       <c r="D183" s="5">
-        <v>48058</v>
-      </c>
-      <c r="F183" s="5">
-        <v>65631</v>
-      </c>
-      <c r="G183" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H183" s="2">
-        <v>7</v>
-      </c>
-      <c r="I183" s="2">
-        <v>5</v>
-      </c>
-      <c r="J183" s="2">
-        <v>2</v>
-      </c>
-      <c r="K183" t="s">
-        <v>242</v>
-      </c>
-      <c r="L183" t="s">
-        <v>326</v>
-      </c>
-      <c r="M183" t="s">
-        <v>245</v>
-      </c>
+        <v>47832</v>
+      </c>
+      <c r="F183" s="5"/>
     </row>
     <row r="184" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A184" s="6"/>
       <c r="C184" s="15" t="s">
-        <v>512</v>
+        <v>490</v>
       </c>
       <c r="D184" s="5">
-        <v>39118</v>
+        <v>56831</v>
       </c>
       <c r="F184" s="5"/>
     </row>
     <row r="185" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A185" s="6"/>
       <c r="C185" s="15" t="s">
-        <v>513</v>
+        <v>491</v>
       </c>
       <c r="D185" s="5">
-        <v>40281</v>
+        <v>58358</v>
       </c>
       <c r="F185" s="5"/>
     </row>
     <row r="186" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A186" s="6"/>
+      <c r="A186" s="6">
+        <v>49</v>
+      </c>
+      <c r="B186" t="s">
+        <v>50</v>
+      </c>
       <c r="C186" s="15" t="s">
-        <v>514</v>
+        <v>492</v>
       </c>
       <c r="D186" s="5">
-        <v>51337</v>
-      </c>
-      <c r="F186" s="5"/>
+        <v>53186</v>
+      </c>
+      <c r="E186" t="s">
+        <v>109</v>
+      </c>
+      <c r="F186" s="5">
+        <v>65800</v>
+      </c>
+      <c r="G186" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H186" s="2">
+        <v>3</v>
+      </c>
+      <c r="I186" s="2">
+        <v>2</v>
+      </c>
+      <c r="J186" s="2">
+        <v>1</v>
+      </c>
+      <c r="K186" t="s">
+        <v>242</v>
+      </c>
+      <c r="L186" t="s">
+        <v>245</v>
+      </c>
+      <c r="M186" t="s">
+        <v>244</v>
+      </c>
     </row>
     <row r="187" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A187" s="6"/>
       <c r="C187" s="15" t="s">
-        <v>515</v>
+        <v>493</v>
       </c>
       <c r="D187" s="5">
-        <v>48440</v>
+        <v>53030</v>
       </c>
       <c r="F187" s="5"/>
     </row>
     <row r="188" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A188" s="6"/>
       <c r="C188" s="15" t="s">
-        <v>516</v>
+        <v>494</v>
       </c>
       <c r="D188" s="5">
-        <v>61351</v>
+        <v>55329</v>
       </c>
       <c r="F188" s="5"/>
     </row>
     <row r="189" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A189" s="6"/>
+      <c r="A189" s="6">
+        <v>50</v>
+      </c>
+      <c r="B189" t="s">
+        <v>51</v>
+      </c>
       <c r="C189" s="15" t="s">
-        <v>517</v>
+        <v>495</v>
       </c>
       <c r="D189" s="5">
-        <v>65006</v>
-      </c>
-      <c r="F189" s="5"/>
+        <v>41748</v>
+      </c>
+      <c r="E189" t="s">
+        <v>108</v>
+      </c>
+      <c r="F189" s="5">
+        <v>65762</v>
+      </c>
+      <c r="G189" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H189" s="2">
+        <v>2</v>
+      </c>
+      <c r="I189" s="2">
+        <v>1</v>
+      </c>
+      <c r="J189" s="2">
+        <v>1</v>
+      </c>
+      <c r="K189" t="s">
+        <v>242</v>
+      </c>
+      <c r="L189" t="s">
+        <v>321</v>
+      </c>
+      <c r="M189" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="190" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A190" s="6">
-        <v>56</v>
-      </c>
-      <c r="B190" t="s">
-        <v>121</v>
-      </c>
+      <c r="A190" s="6"/>
       <c r="C190" s="15" t="s">
-        <v>518</v>
+        <v>496</v>
       </c>
       <c r="D190" s="5">
-        <v>51942</v>
-      </c>
-      <c r="F190" s="5">
-        <v>65582</v>
-      </c>
-      <c r="G190" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H190" s="2">
+        <v>42870</v>
+      </c>
+      <c r="F190" s="5"/>
+    </row>
+    <row r="191" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A191" s="6">
+        <v>51</v>
+      </c>
+      <c r="B191" t="s">
+        <v>116</v>
+      </c>
+      <c r="C191" s="15" t="s">
+        <v>497</v>
+      </c>
+      <c r="D191" s="5">
+        <v>45299</v>
+      </c>
+      <c r="E191" t="s">
+        <v>215</v>
+      </c>
+      <c r="F191" s="5">
+        <v>65736</v>
+      </c>
+      <c r="G191" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H191" s="2">
         <v>3</v>
       </c>
-      <c r="I190" s="2">
+      <c r="I191" s="2">
+        <v>2</v>
+      </c>
+      <c r="J191" s="2">
         <v>1</v>
       </c>
-      <c r="J190" s="2">
-        <v>2</v>
-      </c>
-      <c r="K190" t="s">
-        <v>242</v>
-      </c>
-      <c r="L190" t="s">
-        <v>293</v>
-      </c>
-      <c r="M190" t="s">
+      <c r="K191" t="s">
+        <v>242</v>
+      </c>
+      <c r="L191" t="s">
+        <v>305</v>
+      </c>
+      <c r="M191" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="191" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A191" s="6"/>
-      <c r="C191" s="15" t="s">
-        <v>519</v>
-      </c>
-      <c r="D191" s="5">
-        <v>59240</v>
-      </c>
-      <c r="F191" s="5"/>
     </row>
     <row r="192" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A192" s="6"/>
       <c r="C192" s="15" t="s">
-        <v>520</v>
+        <v>498</v>
       </c>
       <c r="D192" s="5">
-        <v>60958</v>
+        <v>48156</v>
       </c>
       <c r="F192" s="5"/>
     </row>
     <row r="193" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A193" s="6">
-        <v>57</v>
-      </c>
-      <c r="B193" t="s">
-        <v>122</v>
-      </c>
+      <c r="A193" s="6"/>
       <c r="C193" s="15" t="s">
-        <v>521</v>
+        <v>499</v>
       </c>
       <c r="D193" s="5">
-        <v>55860</v>
-      </c>
-      <c r="F193" s="5">
-        <v>65533</v>
-      </c>
-      <c r="G193" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H193" s="2">
-        <v>5</v>
-      </c>
-      <c r="I193" s="2">
-        <v>2</v>
-      </c>
-      <c r="J193" s="2">
-        <v>3</v>
-      </c>
-      <c r="K193" t="s">
-        <v>242</v>
-      </c>
-      <c r="L193" t="s">
-        <v>254</v>
-      </c>
-      <c r="M193" t="s">
+        <v>55796</v>
+      </c>
+      <c r="F193" s="5"/>
+    </row>
+    <row r="194" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A194" s="6">
+        <v>52</v>
+      </c>
+      <c r="B194" t="s">
+        <v>117</v>
+      </c>
+      <c r="C194" s="15" t="s">
+        <v>500</v>
+      </c>
+      <c r="D194" s="5">
+        <v>50544</v>
+      </c>
+      <c r="F194" s="5">
+        <v>65695</v>
+      </c>
+      <c r="G194" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H194" s="2">
+        <v>4</v>
+      </c>
+      <c r="I194" s="2">
+        <v>2</v>
+      </c>
+      <c r="J194" s="2">
+        <v>2</v>
+      </c>
+      <c r="K194" t="s">
+        <v>242</v>
+      </c>
+      <c r="L194" t="s">
+        <v>309</v>
+      </c>
+      <c r="M194" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="194" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A194" s="6"/>
-      <c r="C194" s="15" t="s">
-        <v>522</v>
-      </c>
-      <c r="D194" s="5">
-        <v>47603</v>
-      </c>
-      <c r="F194" s="5"/>
     </row>
     <row r="195" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A195" s="6"/>
       <c r="C195" s="15" t="s">
-        <v>523</v>
+        <v>501</v>
       </c>
       <c r="D195" s="5">
-        <v>47500</v>
+        <v>49344</v>
       </c>
       <c r="F195" s="5"/>
     </row>
     <row r="196" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A196" s="6"/>
       <c r="C196" s="15" t="s">
-        <v>524</v>
+        <v>502</v>
       </c>
       <c r="D196" s="5">
-        <v>55460</v>
+        <v>59373</v>
       </c>
       <c r="F196" s="5"/>
     </row>
     <row r="197" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A197" s="6"/>
       <c r="C197" s="15" t="s">
-        <v>525</v>
+        <v>503</v>
       </c>
       <c r="D197" s="5">
-        <v>56300</v>
+        <v>63170</v>
       </c>
       <c r="F197" s="5"/>
     </row>
     <row r="198" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A198" s="6">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="B198" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="C198" s="15" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="D198" s="5">
-        <v>49005</v>
+        <v>56159</v>
       </c>
       <c r="F198" s="5">
-        <v>65527</v>
+        <v>65644</v>
       </c>
       <c r="G198" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H198" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="I198" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J198" s="2">
         <v>2</v>
@@ -6583,7 +6572,7 @@
         <v>242</v>
       </c>
       <c r="L198" t="s">
-        <v>254</v>
+        <v>310</v>
       </c>
       <c r="M198" t="s">
         <v>245</v>
@@ -6592,124 +6581,124 @@
     <row r="199" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="C199" s="15" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="D199" s="5">
-        <v>53865</v>
+        <v>47618</v>
       </c>
       <c r="F199" s="5"/>
     </row>
     <row r="200" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="C200" s="15" t="s">
-        <v>528</v>
+        <v>506</v>
       </c>
       <c r="D200" s="5">
-        <v>55787</v>
+        <v>57826</v>
       </c>
       <c r="F200" s="5"/>
     </row>
     <row r="201" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A201" s="6"/>
+      <c r="A201" s="6">
+        <v>54</v>
+      </c>
+      <c r="B201" t="s">
+        <v>119</v>
+      </c>
       <c r="C201" s="15" t="s">
-        <v>529</v>
+        <v>507</v>
       </c>
       <c r="D201" s="5">
-        <v>59241</v>
-      </c>
-      <c r="F201" s="5"/>
+        <v>45718</v>
+      </c>
+      <c r="F201" s="5">
+        <v>65631</v>
+      </c>
+      <c r="G201" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H201" s="2">
+        <v>4</v>
+      </c>
+      <c r="I201" s="2">
+        <v>3</v>
+      </c>
+      <c r="J201" s="2">
+        <v>1</v>
+      </c>
+      <c r="K201" t="s">
+        <v>242</v>
+      </c>
+      <c r="L201" t="s">
+        <v>324</v>
+      </c>
+      <c r="M201" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="202" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="C202" s="15" t="s">
-        <v>530</v>
+        <v>508</v>
       </c>
       <c r="D202" s="5">
-        <v>64502</v>
+        <v>58359</v>
       </c>
       <c r="F202" s="5"/>
     </row>
     <row r="203" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A203" s="6">
-        <v>59</v>
-      </c>
-      <c r="B203" t="s">
-        <v>124</v>
-      </c>
+      <c r="A203" s="6"/>
       <c r="C203" s="15" t="s">
-        <v>531</v>
+        <v>509</v>
       </c>
       <c r="D203" s="5">
-        <v>41529</v>
-      </c>
-      <c r="F203" s="5">
-        <v>65512</v>
-      </c>
-      <c r="G203" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H203" s="2">
-        <v>2</v>
-      </c>
-      <c r="I203" s="2">
-        <v>1</v>
-      </c>
-      <c r="J203" s="2">
-        <v>1</v>
-      </c>
-      <c r="K203" t="s">
-        <v>242</v>
-      </c>
-      <c r="L203" t="s">
-        <v>245</v>
-      </c>
-      <c r="M203" t="s">
-        <v>271</v>
-      </c>
+        <v>60169</v>
+      </c>
+      <c r="F203" s="5"/>
     </row>
     <row r="204" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="C204" s="15" t="s">
-        <v>532</v>
+        <v>510</v>
       </c>
       <c r="D204" s="5">
-        <v>44325</v>
+        <v>50276</v>
       </c>
       <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A205" s="6">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="B205" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="C205" s="15" t="s">
-        <v>533</v>
+        <v>511</v>
       </c>
       <c r="D205" s="5">
-        <v>43346</v>
+        <v>48058</v>
       </c>
       <c r="F205" s="5">
-        <v>65490</v>
+        <v>65631</v>
       </c>
       <c r="G205" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H205" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="I205" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J205" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K205" t="s">
         <v>242</v>
       </c>
       <c r="L205" t="s">
-        <v>296</v>
+        <v>326</v>
       </c>
       <c r="M205" t="s">
         <v>245</v>
@@ -6718,476 +6707,476 @@
     <row r="206" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="C206" s="15" t="s">
-        <v>534</v>
+        <v>512</v>
       </c>
       <c r="D206" s="5">
-        <v>50326</v>
+        <v>39118</v>
       </c>
       <c r="F206" s="5"/>
     </row>
     <row r="207" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="C207" s="15" t="s">
-        <v>535</v>
+        <v>513</v>
       </c>
       <c r="D207" s="5">
-        <v>54515</v>
+        <v>40281</v>
       </c>
       <c r="F207" s="5"/>
     </row>
     <row r="208" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="C208" s="15" t="s">
-        <v>536</v>
+        <v>514</v>
       </c>
       <c r="D208" s="5">
-        <v>55041</v>
+        <v>51337</v>
       </c>
       <c r="F208" s="5"/>
     </row>
     <row r="209" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A209" s="6">
-        <v>61</v>
-      </c>
-      <c r="B209" t="s">
-        <v>126</v>
-      </c>
+      <c r="A209" s="6"/>
       <c r="C209" s="15" t="s">
-        <v>537</v>
+        <v>515</v>
       </c>
       <c r="D209" s="5">
-        <v>50895</v>
-      </c>
-      <c r="F209" s="5">
-        <v>65479</v>
-      </c>
-      <c r="G209" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H209" s="2">
-        <v>4</v>
-      </c>
-      <c r="I209" s="2">
-        <v>3</v>
-      </c>
-      <c r="J209" s="2">
-        <v>1</v>
-      </c>
-      <c r="K209" t="s">
-        <v>242</v>
-      </c>
-      <c r="L209" t="s">
-        <v>294</v>
-      </c>
-      <c r="M209" t="s">
-        <v>245</v>
-      </c>
+        <v>48440</v>
+      </c>
+      <c r="F209" s="5"/>
     </row>
     <row r="210" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="C210" s="15" t="s">
-        <v>538</v>
+        <v>516</v>
       </c>
       <c r="D210" s="5">
-        <v>58632</v>
+        <v>61351</v>
       </c>
       <c r="F210" s="5"/>
     </row>
     <row r="211" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="C211" s="15" t="s">
-        <v>539</v>
+        <v>517</v>
       </c>
       <c r="D211" s="5">
-        <v>59438</v>
+        <v>65006</v>
       </c>
       <c r="F211" s="5"/>
     </row>
     <row r="212" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A212" s="6"/>
+      <c r="A212" s="6">
+        <v>56</v>
+      </c>
+      <c r="B212" t="s">
+        <v>121</v>
+      </c>
       <c r="C212" s="15" t="s">
-        <v>540</v>
+        <v>518</v>
       </c>
       <c r="D212" s="5">
-        <v>49841</v>
-      </c>
-      <c r="F212" s="5"/>
+        <v>51942</v>
+      </c>
+      <c r="F212" s="5">
+        <v>65582</v>
+      </c>
+      <c r="G212" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H212" s="2">
+        <v>3</v>
+      </c>
+      <c r="I212" s="2">
+        <v>1</v>
+      </c>
+      <c r="J212" s="2">
+        <v>2</v>
+      </c>
+      <c r="K212" t="s">
+        <v>242</v>
+      </c>
+      <c r="L212" t="s">
+        <v>293</v>
+      </c>
+      <c r="M212" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="213" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A213" s="6">
-        <v>62</v>
-      </c>
-      <c r="B213" t="s">
-        <v>127</v>
-      </c>
+      <c r="A213" s="6"/>
       <c r="C213" s="15" t="s">
-        <v>541</v>
+        <v>519</v>
       </c>
       <c r="D213" s="5">
-        <v>50822</v>
-      </c>
-      <c r="F213" s="5">
-        <v>65478</v>
-      </c>
-      <c r="G213" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H213" s="2">
-        <v>4</v>
-      </c>
-      <c r="I213" s="2">
-        <v>3</v>
-      </c>
-      <c r="J213" s="2">
-        <v>1</v>
-      </c>
-      <c r="K213" t="s">
-        <v>242</v>
-      </c>
-      <c r="L213" t="s">
-        <v>294</v>
-      </c>
-      <c r="M213" t="s">
-        <v>245</v>
-      </c>
+        <v>59240</v>
+      </c>
+      <c r="F213" s="5"/>
     </row>
     <row r="214" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="C214" s="15" t="s">
-        <v>542</v>
+        <v>520</v>
       </c>
       <c r="D214" s="5">
-        <v>49368</v>
+        <v>60958</v>
       </c>
       <c r="F214" s="5"/>
     </row>
     <row r="215" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A215" s="6"/>
+      <c r="A215" s="6">
+        <v>57</v>
+      </c>
+      <c r="B215" t="s">
+        <v>122</v>
+      </c>
       <c r="C215" s="15" t="s">
-        <v>543</v>
+        <v>521</v>
       </c>
       <c r="D215" s="5">
-        <v>56873</v>
-      </c>
-      <c r="F215" s="5"/>
+        <v>55860</v>
+      </c>
+      <c r="F215" s="5">
+        <v>65533</v>
+      </c>
+      <c r="G215" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H215" s="2">
+        <v>5</v>
+      </c>
+      <c r="I215" s="2">
+        <v>2</v>
+      </c>
+      <c r="J215" s="2">
+        <v>3</v>
+      </c>
+      <c r="K215" t="s">
+        <v>242</v>
+      </c>
+      <c r="L215" t="s">
+        <v>254</v>
+      </c>
+      <c r="M215" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="216" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="C216" s="15" t="s">
-        <v>544</v>
+        <v>522</v>
       </c>
       <c r="D216" s="5">
-        <v>59205</v>
+        <v>47603</v>
       </c>
       <c r="F216" s="5"/>
     </row>
     <row r="217" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A217" s="6">
-        <v>63</v>
-      </c>
-      <c r="B217" t="s">
-        <v>128</v>
-      </c>
+      <c r="A217" s="6"/>
       <c r="C217" s="15" t="s">
-        <v>545</v>
+        <v>523</v>
       </c>
       <c r="D217" s="5">
-        <v>45975</v>
-      </c>
-      <c r="F217" s="5">
-        <v>65466</v>
-      </c>
-      <c r="G217" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H217" s="2">
-        <v>4</v>
-      </c>
-      <c r="I217" s="2">
-        <v>1</v>
-      </c>
-      <c r="J217" s="2">
-        <v>3</v>
-      </c>
-      <c r="K217" t="s">
-        <v>242</v>
-      </c>
-      <c r="L217" t="s">
-        <v>311</v>
-      </c>
-      <c r="M217" t="s">
-        <v>245</v>
-      </c>
+        <v>47500</v>
+      </c>
+      <c r="F217" s="5"/>
     </row>
     <row r="218" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="C218" s="15" t="s">
-        <v>546</v>
+        <v>524</v>
       </c>
       <c r="D218" s="5">
-        <v>51362</v>
+        <v>55460</v>
       </c>
       <c r="F218" s="5"/>
     </row>
     <row r="219" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="C219" s="15" t="s">
-        <v>547</v>
+        <v>525</v>
       </c>
       <c r="D219" s="5">
-        <v>58953</v>
+        <v>56300</v>
       </c>
       <c r="F219" s="5"/>
     </row>
     <row r="220" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A220" s="6"/>
+      <c r="A220" s="6">
+        <v>58</v>
+      </c>
+      <c r="B220" t="s">
+        <v>123</v>
+      </c>
       <c r="C220" s="15" t="s">
-        <v>548</v>
+        <v>526</v>
       </c>
       <c r="D220" s="5">
-        <v>59995</v>
-      </c>
-      <c r="F220" s="5"/>
+        <v>49005</v>
+      </c>
+      <c r="F220" s="5">
+        <v>65527</v>
+      </c>
+      <c r="G220" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H220" s="2">
+        <v>5</v>
+      </c>
+      <c r="I220" s="2">
+        <v>3</v>
+      </c>
+      <c r="J220" s="2">
+        <v>2</v>
+      </c>
+      <c r="K220" t="s">
+        <v>242</v>
+      </c>
+      <c r="L220" t="s">
+        <v>254</v>
+      </c>
+      <c r="M220" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="221" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A221" s="6">
-        <v>64</v>
-      </c>
-      <c r="B221" t="s">
-        <v>129</v>
-      </c>
+      <c r="A221" s="6"/>
       <c r="C221" s="15" t="s">
-        <v>549</v>
+        <v>527</v>
       </c>
       <c r="D221" s="5">
-        <v>44171</v>
-      </c>
-      <c r="F221" s="5">
-        <v>65447</v>
-      </c>
-      <c r="G221" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H221" s="2">
-        <v>5</v>
-      </c>
-      <c r="I221" s="2">
-        <v>3</v>
-      </c>
-      <c r="J221" s="2">
-        <v>2</v>
-      </c>
-      <c r="K221" t="s">
-        <v>239</v>
-      </c>
-      <c r="L221" t="s">
-        <v>300</v>
-      </c>
-      <c r="M221" t="s">
-        <v>245</v>
-      </c>
+        <v>53865</v>
+      </c>
+      <c r="F221" s="5"/>
     </row>
     <row r="222" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="C222" s="15" t="s">
-        <v>550</v>
+        <v>528</v>
       </c>
       <c r="D222" s="5">
-        <v>47480</v>
+        <v>55787</v>
       </c>
       <c r="F222" s="5"/>
     </row>
     <row r="223" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="C223" s="15" t="s">
-        <v>551</v>
+        <v>529</v>
       </c>
       <c r="D223" s="5">
-        <v>54180</v>
+        <v>59241</v>
       </c>
       <c r="F223" s="5"/>
     </row>
     <row r="224" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="C224" s="15" t="s">
-        <v>552</v>
+        <v>530</v>
       </c>
       <c r="D224" s="5">
-        <v>56406</v>
+        <v>64502</v>
       </c>
       <c r="F224" s="5"/>
     </row>
     <row r="225" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A225" s="6"/>
+      <c r="A225" s="6">
+        <v>59</v>
+      </c>
+      <c r="B225" t="s">
+        <v>124</v>
+      </c>
       <c r="C225" s="15" t="s">
-        <v>553</v>
+        <v>531</v>
       </c>
       <c r="D225" s="5">
-        <v>54378</v>
-      </c>
-      <c r="F225" s="5"/>
+        <v>41529</v>
+      </c>
+      <c r="F225" s="5">
+        <v>65512</v>
+      </c>
+      <c r="G225" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H225" s="2">
+        <v>2</v>
+      </c>
+      <c r="I225" s="2">
+        <v>1</v>
+      </c>
+      <c r="J225" s="2">
+        <v>1</v>
+      </c>
+      <c r="K225" t="s">
+        <v>242</v>
+      </c>
+      <c r="L225" t="s">
+        <v>245</v>
+      </c>
+      <c r="M225" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="226" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A226" s="6">
-        <v>65</v>
-      </c>
-      <c r="B226" t="s">
-        <v>130</v>
-      </c>
+      <c r="A226" s="6"/>
       <c r="C226" s="15" t="s">
-        <v>554</v>
+        <v>532</v>
       </c>
       <c r="D226" s="5">
-        <v>49531</v>
-      </c>
-      <c r="F226" s="5">
-        <v>65440</v>
-      </c>
-      <c r="G226" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H226" s="2">
-        <v>6</v>
-      </c>
-      <c r="I226" s="2">
-        <v>2</v>
-      </c>
-      <c r="J226" s="2">
+        <v>44325</v>
+      </c>
+      <c r="F226" s="5"/>
+    </row>
+    <row r="227" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A227" s="6">
+        <v>60</v>
+      </c>
+      <c r="B227" t="s">
+        <v>125</v>
+      </c>
+      <c r="C227" s="15" t="s">
+        <v>533</v>
+      </c>
+      <c r="D227" s="5">
+        <v>43346</v>
+      </c>
+      <c r="F227" s="5">
+        <v>65490</v>
+      </c>
+      <c r="G227" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H227" s="2">
         <v>4</v>
       </c>
-      <c r="K226" t="s">
-        <v>242</v>
-      </c>
-      <c r="L226" t="s">
-        <v>252</v>
-      </c>
-      <c r="M226" t="s">
+      <c r="I227" s="2">
+        <v>3</v>
+      </c>
+      <c r="J227" s="2">
+        <v>1</v>
+      </c>
+      <c r="K227" t="s">
+        <v>242</v>
+      </c>
+      <c r="L227" t="s">
+        <v>296</v>
+      </c>
+      <c r="M227" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="227" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A227" s="6"/>
-      <c r="C227" s="15" t="s">
-        <v>555</v>
-      </c>
-      <c r="D227" s="5">
-        <v>50889</v>
-      </c>
-      <c r="F227" s="5"/>
     </row>
     <row r="228" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="C228" s="15" t="s">
-        <v>556</v>
+        <v>534</v>
       </c>
       <c r="D228" s="5">
-        <v>55229</v>
+        <v>50326</v>
       </c>
       <c r="F228" s="5"/>
     </row>
     <row r="229" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="C229" s="15" t="s">
-        <v>557</v>
+        <v>535</v>
       </c>
       <c r="D229" s="5">
-        <v>54680</v>
+        <v>54515</v>
       </c>
       <c r="F229" s="5"/>
     </row>
     <row r="230" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="C230" s="15" t="s">
-        <v>558</v>
+        <v>536</v>
       </c>
       <c r="D230" s="5">
-        <v>62901</v>
+        <v>55041</v>
       </c>
       <c r="F230" s="5"/>
     </row>
     <row r="231" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A231" s="6"/>
+      <c r="A231" s="6">
+        <v>61</v>
+      </c>
+      <c r="B231" t="s">
+        <v>126</v>
+      </c>
       <c r="C231" s="15" t="s">
-        <v>559</v>
+        <v>537</v>
       </c>
       <c r="D231" s="5">
-        <v>64512</v>
-      </c>
-      <c r="F231" s="5"/>
+        <v>50895</v>
+      </c>
+      <c r="F231" s="5">
+        <v>65479</v>
+      </c>
+      <c r="G231" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H231" s="2">
+        <v>4</v>
+      </c>
+      <c r="I231" s="2">
+        <v>3</v>
+      </c>
+      <c r="J231" s="2">
+        <v>1</v>
+      </c>
+      <c r="K231" t="s">
+        <v>242</v>
+      </c>
+      <c r="L231" t="s">
+        <v>294</v>
+      </c>
+      <c r="M231" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="232" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A232" s="6">
-        <v>66</v>
-      </c>
-      <c r="B232" t="s">
-        <v>131</v>
-      </c>
+      <c r="A232" s="6"/>
       <c r="C232" s="15" t="s">
-        <v>560</v>
+        <v>538</v>
       </c>
       <c r="D232" s="5">
-        <v>44591</v>
-      </c>
-      <c r="F232" s="5">
-        <v>65369</v>
-      </c>
-      <c r="G232" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H232" s="2">
-        <v>4</v>
-      </c>
-      <c r="I232" s="2">
-        <v>2</v>
-      </c>
-      <c r="J232" s="2">
-        <v>1</v>
-      </c>
-      <c r="K232" t="s">
-        <v>242</v>
-      </c>
-      <c r="L232" t="s">
-        <v>292</v>
-      </c>
-      <c r="M232" t="s">
-        <v>245</v>
-      </c>
+        <v>58632</v>
+      </c>
+      <c r="F232" s="5"/>
     </row>
     <row r="233" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="C233" s="15" t="s">
-        <v>561</v>
+        <v>539</v>
       </c>
       <c r="D233" s="5">
-        <v>46448</v>
+        <v>59438</v>
       </c>
       <c r="F233" s="5"/>
     </row>
     <row r="234" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="C234" s="15" t="s">
-        <v>562</v>
+        <v>540</v>
       </c>
       <c r="D234" s="5">
-        <v>53878</v>
+        <v>49841</v>
       </c>
       <c r="F234" s="5"/>
     </row>
     <row r="235" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A235" s="6">
-        <v>67</v>
+        <v>62</v>
       </c>
       <c r="B235" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="C235" s="15" t="s">
-        <v>563</v>
+        <v>541</v>
       </c>
       <c r="D235" s="5">
-        <v>52725</v>
+        <v>50822</v>
       </c>
       <c r="F235" s="5">
-        <v>65366</v>
+        <v>65478</v>
       </c>
       <c r="G235" s="2" t="s">
         <v>2</v>
@@ -7196,17 +7185,16 @@
         <v>4</v>
       </c>
       <c r="I235" s="2">
-        <f>H235-J235</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J235" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K235" t="s">
         <v>242</v>
       </c>
       <c r="L235" t="s">
-        <v>235</v>
+        <v>294</v>
       </c>
       <c r="M235" t="s">
         <v>245</v>
@@ -7215,583 +7203,531 @@
     <row r="236" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="C236" s="15" t="s">
-        <v>564</v>
+        <v>542</v>
       </c>
       <c r="D236" s="5">
-        <v>48519</v>
+        <v>49368</v>
       </c>
       <c r="F236" s="5"/>
     </row>
     <row r="237" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="C237" s="15" t="s">
-        <v>565</v>
+        <v>543</v>
       </c>
       <c r="D237" s="5">
-        <v>55917</v>
+        <v>56873</v>
       </c>
       <c r="F237" s="5"/>
     </row>
     <row r="238" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="C238" s="15" t="s">
-        <v>566</v>
+        <v>544</v>
       </c>
       <c r="D238" s="5">
-        <v>61012</v>
+        <v>59205</v>
       </c>
       <c r="F238" s="5"/>
     </row>
     <row r="239" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A239" s="6">
-        <v>68</v>
+        <v>63</v>
       </c>
       <c r="B239" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C239" s="15" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="D239" s="5">
-        <v>39810</v>
+        <v>45975</v>
       </c>
       <c r="F239" s="5">
-        <v>65365</v>
+        <v>65466</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H239" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I239" s="2">
         <v>1</v>
       </c>
+      <c r="J239" s="2">
+        <v>3</v>
+      </c>
       <c r="K239" t="s">
         <v>242</v>
       </c>
       <c r="L239" t="s">
+        <v>311</v>
+      </c>
+      <c r="M239" t="s">
         <v>245</v>
       </c>
-      <c r="M239" t="s">
-        <v>258</v>
-      </c>
     </row>
     <row r="240" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A240" s="6">
-        <v>69</v>
-      </c>
-      <c r="B240" t="s">
-        <v>134</v>
-      </c>
+      <c r="A240" s="6"/>
       <c r="C240" s="15" t="s">
-        <v>568</v>
+        <v>546</v>
       </c>
       <c r="D240" s="5">
-        <v>51115</v>
-      </c>
-      <c r="F240" s="5">
-        <v>65356</v>
-      </c>
-      <c r="G240" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H240" s="2">
-        <v>6</v>
-      </c>
-      <c r="I240" s="2">
-        <v>2</v>
-      </c>
-      <c r="J240" s="2">
-        <v>3</v>
-      </c>
-      <c r="K240" t="s">
-        <v>242</v>
-      </c>
-      <c r="L240" t="s">
-        <v>283</v>
-      </c>
-      <c r="M240" t="s">
-        <v>245</v>
-      </c>
+        <v>51362</v>
+      </c>
+      <c r="F240" s="5"/>
     </row>
     <row r="241" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="C241" s="15" t="s">
-        <v>569</v>
+        <v>547</v>
       </c>
       <c r="D241" s="5">
-        <v>51817</v>
+        <v>58953</v>
       </c>
       <c r="F241" s="5"/>
     </row>
     <row r="242" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="C242" s="15" t="s">
-        <v>570</v>
+        <v>548</v>
       </c>
       <c r="D242" s="5">
-        <v>59254</v>
+        <v>59995</v>
       </c>
       <c r="F242" s="5"/>
     </row>
     <row r="243" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A243" s="6"/>
+      <c r="A243" s="6">
+        <v>64</v>
+      </c>
+      <c r="B243" t="s">
+        <v>129</v>
+      </c>
       <c r="C243" s="15" t="s">
-        <v>571</v>
+        <v>549</v>
       </c>
       <c r="D243" s="5">
-        <v>61726</v>
-      </c>
-      <c r="F243" s="5"/>
+        <v>44171</v>
+      </c>
+      <c r="F243" s="5">
+        <v>65447</v>
+      </c>
+      <c r="G243" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H243" s="2">
+        <v>5</v>
+      </c>
+      <c r="I243" s="2">
+        <v>3</v>
+      </c>
+      <c r="J243" s="2">
+        <v>2</v>
+      </c>
+      <c r="K243" t="s">
+        <v>239</v>
+      </c>
+      <c r="L243" t="s">
+        <v>300</v>
+      </c>
+      <c r="M243" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="244" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="C244" s="15" t="s">
-        <v>572</v>
+        <v>550</v>
       </c>
       <c r="D244" s="5">
-        <v>62333</v>
+        <v>47480</v>
       </c>
       <c r="F244" s="5"/>
     </row>
     <row r="245" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A245" s="6">
-        <v>70</v>
-      </c>
-      <c r="B245" t="s">
-        <v>135</v>
-      </c>
+      <c r="A245" s="6"/>
       <c r="C245" s="15" t="s">
-        <v>573</v>
+        <v>551</v>
       </c>
       <c r="D245" s="5">
-        <v>51636</v>
-      </c>
-      <c r="F245" s="5">
-        <v>65356</v>
-      </c>
-      <c r="G245" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H245" s="2">
-        <v>5</v>
-      </c>
-      <c r="I245" s="2">
-        <v>3</v>
-      </c>
-      <c r="J245" s="2">
-        <v>1</v>
-      </c>
-      <c r="K245" t="s">
-        <v>242</v>
-      </c>
-      <c r="L245" t="s">
-        <v>245</v>
-      </c>
-      <c r="M245" t="s">
-        <v>318</v>
-      </c>
+        <v>54180</v>
+      </c>
+      <c r="F245" s="5"/>
     </row>
     <row r="246" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="C246" s="15" t="s">
-        <v>574</v>
+        <v>552</v>
       </c>
       <c r="D246" s="5">
-        <v>48916</v>
+        <v>56406</v>
       </c>
       <c r="F246" s="5"/>
     </row>
     <row r="247" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="C247" s="15" t="s">
-        <v>575</v>
+        <v>553</v>
       </c>
       <c r="D247" s="5">
-        <v>58981</v>
+        <v>54378</v>
       </c>
       <c r="F247" s="5"/>
     </row>
     <row r="248" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A248" s="6"/>
+      <c r="A248" s="6">
+        <v>65</v>
+      </c>
+      <c r="B248" t="s">
+        <v>130</v>
+      </c>
       <c r="C248" s="15" t="s">
-        <v>576</v>
+        <v>554</v>
       </c>
       <c r="D248" s="5">
-        <v>59339</v>
-      </c>
-      <c r="F248" s="5"/>
+        <v>49531</v>
+      </c>
+      <c r="F248" s="5">
+        <v>65440</v>
+      </c>
+      <c r="G248" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H248" s="2">
+        <v>6</v>
+      </c>
+      <c r="I248" s="2">
+        <v>2</v>
+      </c>
+      <c r="J248" s="2">
+        <v>4</v>
+      </c>
+      <c r="K248" t="s">
+        <v>242</v>
+      </c>
+      <c r="L248" t="s">
+        <v>252</v>
+      </c>
+      <c r="M248" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="249" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A249" s="6">
-        <v>71</v>
-      </c>
-      <c r="B249" t="s">
-        <v>136</v>
-      </c>
+      <c r="A249" s="6"/>
       <c r="C249" s="15" t="s">
-        <v>577</v>
+        <v>555</v>
       </c>
       <c r="D249" s="5">
-        <v>44021</v>
-      </c>
-      <c r="F249" s="5">
-        <v>65350</v>
-      </c>
-      <c r="G249" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H249" s="2">
-        <v>2</v>
-      </c>
-      <c r="I249" s="2">
-        <v>1</v>
-      </c>
-      <c r="J249" s="2">
-        <v>1</v>
-      </c>
-      <c r="K249" t="s">
-        <v>242</v>
-      </c>
-      <c r="L249" t="s">
-        <v>254</v>
-      </c>
-      <c r="M249" t="s">
-        <v>245</v>
-      </c>
+        <v>50889</v>
+      </c>
+      <c r="F249" s="5"/>
     </row>
     <row r="250" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="C250" s="15" t="s">
-        <v>578</v>
+        <v>556</v>
       </c>
       <c r="D250" s="5">
-        <v>46430</v>
+        <v>55229</v>
       </c>
       <c r="F250" s="5"/>
     </row>
     <row r="251" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A251" s="6">
-        <v>72</v>
-      </c>
-      <c r="B251" t="s">
-        <v>137</v>
-      </c>
+      <c r="A251" s="6"/>
       <c r="C251" s="15" t="s">
-        <v>579</v>
+        <v>557</v>
       </c>
       <c r="D251" s="5">
-        <v>49884</v>
-      </c>
-      <c r="F251" s="5">
-        <v>65328</v>
-      </c>
-      <c r="G251" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H251" s="2">
-        <v>5</v>
-      </c>
-      <c r="I251" s="2">
-        <v>3</v>
-      </c>
-      <c r="J251" s="2">
-        <v>1</v>
-      </c>
-      <c r="K251" t="s">
-        <v>242</v>
-      </c>
-      <c r="L251" t="s">
-        <v>270</v>
-      </c>
-      <c r="M251" t="s">
-        <v>245</v>
-      </c>
+        <v>54680</v>
+      </c>
+      <c r="F251" s="5"/>
     </row>
     <row r="252" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="C252" s="15" t="s">
-        <v>580</v>
+        <v>558</v>
       </c>
       <c r="D252" s="5">
-        <v>51269</v>
+        <v>62901</v>
       </c>
       <c r="F252" s="5"/>
     </row>
     <row r="253" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="C253" s="15" t="s">
-        <v>581</v>
+        <v>559</v>
       </c>
       <c r="D253" s="5">
-        <v>61751</v>
+        <v>64512</v>
       </c>
       <c r="F253" s="5"/>
     </row>
     <row r="254" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A254" s="6"/>
+      <c r="A254" s="6">
+        <v>66</v>
+      </c>
+      <c r="B254" t="s">
+        <v>131</v>
+      </c>
       <c r="C254" s="15" t="s">
-        <v>582</v>
+        <v>560</v>
       </c>
       <c r="D254" s="5">
-        <v>63908</v>
-      </c>
-      <c r="F254" s="5"/>
+        <v>44591</v>
+      </c>
+      <c r="F254" s="5">
+        <v>65369</v>
+      </c>
+      <c r="G254" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H254" s="2">
+        <v>4</v>
+      </c>
+      <c r="I254" s="2">
+        <v>2</v>
+      </c>
+      <c r="J254" s="2">
+        <v>1</v>
+      </c>
+      <c r="K254" t="s">
+        <v>242</v>
+      </c>
+      <c r="L254" t="s">
+        <v>292</v>
+      </c>
+      <c r="M254" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="255" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A255" s="6">
-        <v>73</v>
-      </c>
-      <c r="B255" t="s">
-        <v>138</v>
-      </c>
+      <c r="A255" s="6"/>
       <c r="C255" s="15" t="s">
-        <v>583</v>
+        <v>561</v>
       </c>
       <c r="D255" s="5">
-        <v>54382</v>
-      </c>
-      <c r="F255" s="5">
-        <v>65306</v>
-      </c>
-      <c r="G255" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H255" s="2">
-        <v>5</v>
-      </c>
-      <c r="I255" s="2">
-        <v>2</v>
-      </c>
-      <c r="J255" s="2">
-        <v>2</v>
-      </c>
-      <c r="K255" t="s">
-        <v>242</v>
-      </c>
-      <c r="L255" t="s">
-        <v>263</v>
-      </c>
-      <c r="M255" t="s">
-        <v>245</v>
-      </c>
+        <v>46448</v>
+      </c>
+      <c r="F255" s="5"/>
     </row>
     <row r="256" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="C256" s="15" t="s">
-        <v>584</v>
+        <v>562</v>
       </c>
       <c r="D256" s="5">
-        <v>51111</v>
+        <v>53878</v>
       </c>
       <c r="F256" s="5"/>
     </row>
     <row r="257" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A257" s="6"/>
+      <c r="A257" s="6">
+        <v>67</v>
+      </c>
+      <c r="B257" t="s">
+        <v>132</v>
+      </c>
       <c r="C257" s="15" t="s">
-        <v>585</v>
+        <v>563</v>
       </c>
       <c r="D257" s="5">
-        <v>60808</v>
-      </c>
-      <c r="F257" s="5"/>
+        <v>52725</v>
+      </c>
+      <c r="F257" s="5">
+        <v>65366</v>
+      </c>
+      <c r="G257" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H257" s="2">
+        <v>4</v>
+      </c>
+      <c r="I257" s="2">
+        <f>H257-J257</f>
+        <v>2</v>
+      </c>
+      <c r="J257" s="2">
+        <v>2</v>
+      </c>
+      <c r="K257" t="s">
+        <v>242</v>
+      </c>
+      <c r="L257" t="s">
+        <v>235</v>
+      </c>
+      <c r="M257" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="258" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="C258" s="15" t="s">
-        <v>586</v>
+        <v>564</v>
       </c>
       <c r="D258" s="5">
-        <v>62507</v>
+        <v>48519</v>
       </c>
       <c r="F258" s="5"/>
     </row>
     <row r="259" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A259" s="6">
-        <v>74</v>
-      </c>
-      <c r="B259" t="s">
-        <v>139</v>
-      </c>
+      <c r="A259" s="6"/>
       <c r="C259" s="15" t="s">
-        <v>587</v>
+        <v>565</v>
       </c>
       <c r="D259" s="5">
-        <v>43801</v>
-      </c>
-      <c r="F259" s="5">
-        <v>65304</v>
-      </c>
-      <c r="G259" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H259" s="2">
-        <v>2</v>
-      </c>
-      <c r="I259" s="2">
+        <v>55917</v>
+      </c>
+      <c r="F259" s="5"/>
+    </row>
+    <row r="260" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A260" s="6"/>
+      <c r="C260" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="D260" s="5">
+        <v>61012</v>
+      </c>
+      <c r="F260" s="5"/>
+    </row>
+    <row r="261" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A261" s="6">
+        <v>68</v>
+      </c>
+      <c r="B261" t="s">
+        <v>133</v>
+      </c>
+      <c r="C261" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="D261" s="5">
+        <v>39810</v>
+      </c>
+      <c r="F261" s="5">
+        <v>65365</v>
+      </c>
+      <c r="G261" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="H261" s="2">
+        <v>2</v>
+      </c>
+      <c r="I261" s="2">
         <v>1</v>
       </c>
-      <c r="K259" t="s">
-        <v>242</v>
-      </c>
-      <c r="L259" t="s">
-        <v>334</v>
-      </c>
-      <c r="M259" t="s">
+      <c r="K261" t="s">
+        <v>242</v>
+      </c>
+      <c r="L261" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="260" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A260" s="6">
-        <v>75</v>
-      </c>
-      <c r="B260" t="s">
-        <v>140</v>
-      </c>
-      <c r="C260" s="15" t="s">
-        <v>588</v>
-      </c>
-      <c r="D260" s="5">
-        <v>53503</v>
-      </c>
-      <c r="F260" s="5">
-        <v>65302</v>
-      </c>
-      <c r="G260" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H260" s="2">
+      <c r="M261" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="262" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A262" s="6">
+        <v>69</v>
+      </c>
+      <c r="B262" t="s">
+        <v>134</v>
+      </c>
+      <c r="C262" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="D262" s="5">
+        <v>51115</v>
+      </c>
+      <c r="F262" s="5">
+        <v>65356</v>
+      </c>
+      <c r="G262" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H262" s="2">
+        <v>6</v>
+      </c>
+      <c r="I262" s="2">
+        <v>2</v>
+      </c>
+      <c r="J262" s="2">
         <v>3</v>
       </c>
-      <c r="I260" s="2">
-        <v>2</v>
-      </c>
-      <c r="J260" s="2">
-        <v>1</v>
-      </c>
-      <c r="K260" t="s">
-        <v>241</v>
-      </c>
-      <c r="L260" t="s">
-        <v>273</v>
-      </c>
-      <c r="M260" t="s">
+      <c r="K262" t="s">
+        <v>242</v>
+      </c>
+      <c r="L262" t="s">
+        <v>283</v>
+      </c>
+      <c r="M262" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="261" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A261" s="6"/>
-      <c r="C261" s="15" t="s">
-        <v>589</v>
-      </c>
-      <c r="D261" s="5">
-        <v>57055</v>
-      </c>
-      <c r="F261" s="5"/>
-    </row>
-    <row r="262" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A262" s="6"/>
-      <c r="C262" s="15" t="s">
-        <v>590</v>
-      </c>
-      <c r="D262" s="5">
-        <v>54482</v>
-      </c>
-      <c r="F262" s="5"/>
-    </row>
     <row r="263" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A263" s="6">
-        <v>76</v>
-      </c>
-      <c r="B263" t="s">
-        <v>141</v>
-      </c>
+      <c r="A263" s="6"/>
       <c r="C263" s="15" t="s">
-        <v>591</v>
+        <v>569</v>
       </c>
       <c r="D263" s="5">
-        <v>47070</v>
-      </c>
-      <c r="F263" s="5">
-        <v>65291</v>
-      </c>
-      <c r="G263" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H263" s="2">
-        <v>5</v>
-      </c>
-      <c r="I263" s="2">
-        <v>1</v>
-      </c>
-      <c r="J263" s="2">
-        <v>3</v>
-      </c>
-      <c r="K263" t="s">
-        <v>242</v>
-      </c>
-      <c r="L263" t="s">
-        <v>316</v>
-      </c>
-      <c r="M263" t="s">
-        <v>245</v>
-      </c>
+        <v>51817</v>
+      </c>
+      <c r="F263" s="5"/>
     </row>
     <row r="264" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="C264" s="15" t="s">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="D264" s="5">
-        <v>51503</v>
+        <v>59254</v>
       </c>
       <c r="F264" s="5"/>
     </row>
     <row r="265" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="C265" s="15" t="s">
-        <v>593</v>
+        <v>571</v>
       </c>
       <c r="D265" s="5">
-        <v>56017</v>
+        <v>61726</v>
       </c>
       <c r="F265" s="5"/>
     </row>
     <row r="266" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="C266" s="15" t="s">
-        <v>594</v>
+        <v>572</v>
       </c>
       <c r="D266" s="5">
-        <v>58629</v>
+        <v>62333</v>
       </c>
       <c r="F266" s="5"/>
     </row>
     <row r="267" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A267" s="6">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="B267" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="C267" s="15" t="s">
-        <v>595</v>
+        <v>573</v>
       </c>
       <c r="D267" s="5">
-        <v>50721</v>
+        <v>51636</v>
       </c>
       <c r="F267" s="5">
-        <v>65290</v>
+        <v>65356</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H267" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I267" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J267" s="2">
         <v>1</v>
@@ -7800,179 +7736,179 @@
         <v>242</v>
       </c>
       <c r="L267" t="s">
-        <v>299</v>
+        <v>245</v>
       </c>
       <c r="M267" t="s">
-        <v>245</v>
+        <v>318</v>
       </c>
     </row>
     <row r="268" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="C268" s="15" t="s">
-        <v>486</v>
+        <v>574</v>
       </c>
       <c r="D268" s="5">
-        <v>50325</v>
+        <v>48916</v>
       </c>
       <c r="F268" s="5"/>
     </row>
     <row r="269" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="C269" s="15" t="s">
-        <v>596</v>
+        <v>575</v>
       </c>
       <c r="D269" s="5">
-        <v>48072</v>
+        <v>58981</v>
       </c>
       <c r="F269" s="5"/>
     </row>
     <row r="270" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A270" s="6">
-        <v>78</v>
-      </c>
-      <c r="B270" t="s">
-        <v>143</v>
-      </c>
+      <c r="A270" s="6"/>
       <c r="C270" s="15" t="s">
-        <v>597</v>
+        <v>576</v>
       </c>
       <c r="D270" s="5">
-        <v>48223</v>
-      </c>
-      <c r="F270" s="5">
-        <v>65287</v>
-      </c>
-      <c r="G270" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H270" s="2">
-        <v>4</v>
-      </c>
-      <c r="I270" s="2">
-        <v>2</v>
-      </c>
-      <c r="J270" s="2">
+        <v>59339</v>
+      </c>
+      <c r="F270" s="5"/>
+    </row>
+    <row r="271" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A271" s="6">
+        <v>71</v>
+      </c>
+      <c r="B271" t="s">
+        <v>136</v>
+      </c>
+      <c r="C271" s="15" t="s">
+        <v>577</v>
+      </c>
+      <c r="D271" s="5">
+        <v>44021</v>
+      </c>
+      <c r="F271" s="5">
+        <v>65350</v>
+      </c>
+      <c r="G271" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H271" s="2">
+        <v>2</v>
+      </c>
+      <c r="I271" s="2">
         <v>1</v>
       </c>
-      <c r="K270" t="s">
-        <v>242</v>
-      </c>
-      <c r="L270" t="s">
-        <v>291</v>
-      </c>
-      <c r="M270" t="s">
+      <c r="J271" s="2">
+        <v>1</v>
+      </c>
+      <c r="K271" t="s">
+        <v>242</v>
+      </c>
+      <c r="L271" t="s">
+        <v>254</v>
+      </c>
+      <c r="M271" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="271" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A271" s="6"/>
-      <c r="C271" s="15" t="s">
-        <v>598</v>
-      </c>
-      <c r="D271" s="5">
-        <v>50505</v>
-      </c>
-      <c r="F271" s="5"/>
     </row>
     <row r="272" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="C272" s="15" t="s">
-        <v>599</v>
+        <v>578</v>
       </c>
       <c r="D272" s="5">
-        <v>58169</v>
+        <v>46430</v>
       </c>
       <c r="F272" s="5"/>
     </row>
     <row r="273" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A273" s="6">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="B273" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
       <c r="C273" s="15" t="s">
-        <v>600</v>
+        <v>579</v>
       </c>
       <c r="D273" s="5">
-        <v>52174</v>
+        <v>49884</v>
       </c>
       <c r="F273" s="5">
-        <v>65265</v>
+        <v>65328</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H273" s="2">
         <v>5</v>
       </c>
       <c r="I273" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J273" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K273" t="s">
         <v>242</v>
       </c>
       <c r="L273" t="s">
+        <v>270</v>
+      </c>
+      <c r="M273" t="s">
         <v>245</v>
-      </c>
-      <c r="M273" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="274" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="C274" s="15" t="s">
-        <v>601</v>
+        <v>580</v>
       </c>
       <c r="D274" s="5">
-        <v>52692</v>
+        <v>51269</v>
       </c>
       <c r="F274" s="5"/>
     </row>
     <row r="275" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="C275" s="15" t="s">
-        <v>602</v>
+        <v>581</v>
       </c>
       <c r="D275" s="5">
-        <v>61493</v>
+        <v>61751</v>
       </c>
       <c r="F275" s="5"/>
     </row>
     <row r="276" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="C276" s="15" t="s">
-        <v>603</v>
+        <v>582</v>
       </c>
       <c r="D276" s="5">
-        <v>63209</v>
+        <v>63908</v>
       </c>
       <c r="F276" s="5"/>
     </row>
     <row r="277" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A277" s="6">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B277" t="s">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="C277" s="15" t="s">
-        <v>604</v>
+        <v>583</v>
       </c>
       <c r="D277" s="5">
-        <v>47464</v>
+        <v>54382</v>
       </c>
       <c r="F277" s="5">
-        <v>65173</v>
+        <v>65306</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H277" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I277" s="2">
         <v>2</v>
@@ -7981,146 +7917,171 @@
         <v>2</v>
       </c>
       <c r="K277" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L277" t="s">
+        <v>263</v>
+      </c>
+      <c r="M277" t="s">
         <v>245</v>
-      </c>
-      <c r="M277" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="278" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="C278" s="15" t="s">
-        <v>605</v>
+        <v>584</v>
       </c>
       <c r="D278" s="5">
-        <v>55130</v>
+        <v>51111</v>
       </c>
       <c r="F278" s="5"/>
     </row>
     <row r="279" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="C279" s="15" t="s">
-        <v>606</v>
+        <v>585</v>
       </c>
       <c r="D279" s="5">
-        <v>55878</v>
+        <v>60808</v>
       </c>
       <c r="F279" s="5"/>
     </row>
     <row r="280" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="C280" s="15" t="s">
-        <v>607</v>
+        <v>586</v>
       </c>
       <c r="D280" s="5">
-        <v>60148</v>
+        <v>62507</v>
       </c>
       <c r="F280" s="5"/>
     </row>
     <row r="281" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A281" s="6">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="B281" t="s">
-        <v>146</v>
+        <v>139</v>
       </c>
       <c r="C281" s="15" t="s">
-        <v>608</v>
+        <v>587</v>
       </c>
       <c r="D281" s="5">
-        <v>53287</v>
+        <v>43801</v>
       </c>
       <c r="F281" s="5">
-        <v>65146</v>
+        <v>65304</v>
       </c>
       <c r="G281" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H281" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="I281" s="2">
-        <v>2</v>
-      </c>
-      <c r="J281" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K281" t="s">
         <v>242</v>
       </c>
       <c r="L281" t="s">
-        <v>277</v>
+        <v>334</v>
       </c>
       <c r="M281" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="282" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A282" s="6"/>
+      <c r="A282" s="6">
+        <v>75</v>
+      </c>
+      <c r="B282" t="s">
+        <v>140</v>
+      </c>
       <c r="C282" s="15" t="s">
-        <v>609</v>
+        <v>588</v>
       </c>
       <c r="D282" s="5">
-        <v>53998</v>
-      </c>
-      <c r="F282" s="5"/>
+        <v>53503</v>
+      </c>
+      <c r="F282" s="5">
+        <v>65302</v>
+      </c>
+      <c r="G282" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H282" s="2">
+        <v>3</v>
+      </c>
+      <c r="I282" s="2">
+        <v>2</v>
+      </c>
+      <c r="J282" s="2">
+        <v>1</v>
+      </c>
+      <c r="K282" t="s">
+        <v>241</v>
+      </c>
+      <c r="L282" t="s">
+        <v>273</v>
+      </c>
+      <c r="M282" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="283" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="C283" s="15" t="s">
-        <v>610</v>
+        <v>589</v>
       </c>
       <c r="D283" s="5">
-        <v>62663</v>
+        <v>57055</v>
       </c>
       <c r="F283" s="5"/>
     </row>
     <row r="284" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="C284" s="15" t="s">
-        <v>611</v>
+        <v>590</v>
       </c>
       <c r="D284" s="5">
-        <v>64448</v>
+        <v>54482</v>
       </c>
       <c r="F284" s="5"/>
     </row>
     <row r="285" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A285" s="6">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="B285" t="s">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="C285" s="15" t="s">
-        <v>612</v>
+        <v>591</v>
       </c>
       <c r="D285" s="5">
-        <v>53163</v>
+        <v>47070</v>
       </c>
       <c r="F285" s="5">
-        <v>64977</v>
+        <v>65291</v>
       </c>
       <c r="G285" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H285" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="I285" s="2">
         <v>1</v>
       </c>
       <c r="J285" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K285" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="L285" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M285" t="s">
         <v>245</v>
@@ -8129,170 +8090,170 @@
     <row r="286" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="C286" s="15" t="s">
-        <v>613</v>
+        <v>592</v>
       </c>
       <c r="D286" s="5">
-        <v>62722</v>
+        <v>51503</v>
       </c>
       <c r="F286" s="5"/>
     </row>
     <row r="287" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A287" s="6">
-        <v>83</v>
-      </c>
-      <c r="B287" t="s">
-        <v>148</v>
-      </c>
+      <c r="A287" s="6"/>
       <c r="C287" s="15" t="s">
-        <v>614</v>
+        <v>593</v>
       </c>
       <c r="D287" s="5">
-        <v>46667</v>
-      </c>
-      <c r="F287" s="5">
-        <v>64935</v>
-      </c>
-      <c r="G287" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H287" s="2">
-        <v>4</v>
-      </c>
-      <c r="I287" s="2">
-        <v>2</v>
-      </c>
-      <c r="J287" s="2">
-        <v>2</v>
-      </c>
-      <c r="K287" t="s">
-        <v>242</v>
-      </c>
-      <c r="L287" t="s">
-        <v>245</v>
-      </c>
-      <c r="M287" t="s">
-        <v>260</v>
-      </c>
+        <v>56017</v>
+      </c>
+      <c r="F287" s="5"/>
     </row>
     <row r="288" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="C288" s="15" t="s">
-        <v>615</v>
+        <v>594</v>
       </c>
       <c r="D288" s="5">
-        <v>51353</v>
+        <v>58629</v>
       </c>
       <c r="F288" s="5"/>
     </row>
     <row r="289" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A289" s="6"/>
+      <c r="A289" s="6">
+        <v>77</v>
+      </c>
+      <c r="B289" t="s">
+        <v>142</v>
+      </c>
       <c r="C289" s="15" t="s">
-        <v>616</v>
+        <v>595</v>
       </c>
       <c r="D289" s="5">
-        <v>59571</v>
-      </c>
-      <c r="F289" s="5"/>
+        <v>50721</v>
+      </c>
+      <c r="F289" s="5">
+        <v>65290</v>
+      </c>
+      <c r="G289" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H289" s="2">
+        <v>4</v>
+      </c>
+      <c r="I289" s="2">
+        <v>2</v>
+      </c>
+      <c r="J289" s="2">
+        <v>1</v>
+      </c>
+      <c r="K289" t="s">
+        <v>242</v>
+      </c>
+      <c r="L289" t="s">
+        <v>299</v>
+      </c>
+      <c r="M289" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="290" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="C290" s="15" t="s">
-        <v>617</v>
+        <v>486</v>
       </c>
       <c r="D290" s="5">
-        <v>60017</v>
+        <v>50325</v>
       </c>
       <c r="F290" s="5"/>
     </row>
     <row r="291" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A291" s="6">
-        <v>84</v>
-      </c>
-      <c r="B291" t="s">
-        <v>149</v>
-      </c>
+      <c r="A291" s="6"/>
       <c r="C291" s="15" t="s">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="D291" s="5">
-        <v>50045</v>
-      </c>
-      <c r="F291" s="5">
-        <v>64887</v>
-      </c>
-      <c r="G291" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H291" s="2">
+        <v>48072</v>
+      </c>
+      <c r="F291" s="5"/>
+    </row>
+    <row r="292" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A292" s="6">
+        <v>78</v>
+      </c>
+      <c r="B292" t="s">
+        <v>143</v>
+      </c>
+      <c r="C292" s="15" t="s">
+        <v>597</v>
+      </c>
+      <c r="D292" s="5">
+        <v>48223</v>
+      </c>
+      <c r="F292" s="5">
+        <v>65287</v>
+      </c>
+      <c r="G292" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H292" s="2">
         <v>4</v>
       </c>
-      <c r="I291" s="2">
-        <v>2</v>
-      </c>
-      <c r="J291" s="2">
-        <v>2</v>
-      </c>
-      <c r="K291" t="s">
-        <v>242</v>
-      </c>
-      <c r="L291" t="s">
-        <v>286</v>
-      </c>
-      <c r="M291" t="s">
+      <c r="I292" s="2">
+        <v>2</v>
+      </c>
+      <c r="J292" s="2">
+        <v>1</v>
+      </c>
+      <c r="K292" t="s">
+        <v>242</v>
+      </c>
+      <c r="L292" t="s">
+        <v>291</v>
+      </c>
+      <c r="M292" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="292" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A292" s="6"/>
-      <c r="C292" s="15" t="s">
-        <v>619</v>
-      </c>
-      <c r="D292" s="5">
-        <v>50936</v>
-      </c>
-      <c r="F292" s="5"/>
     </row>
     <row r="293" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="C293" s="15" t="s">
-        <v>620</v>
+        <v>598</v>
       </c>
       <c r="D293" s="5">
-        <v>58649</v>
+        <v>50505</v>
       </c>
       <c r="F293" s="5"/>
     </row>
     <row r="294" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="C294" s="15" t="s">
-        <v>621</v>
+        <v>599</v>
       </c>
       <c r="D294" s="5">
-        <v>59533</v>
+        <v>58169</v>
       </c>
       <c r="F294" s="5"/>
     </row>
     <row r="295" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A295" s="6">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="B295" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
       <c r="C295" s="15" t="s">
-        <v>622</v>
+        <v>600</v>
       </c>
       <c r="D295" s="5">
-        <v>51945</v>
+        <v>52174</v>
       </c>
       <c r="F295" s="5">
-        <v>64813</v>
+        <v>65265</v>
       </c>
       <c r="G295" s="2" t="s">
         <v>100</v>
       </c>
       <c r="H295" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="I295" s="2">
         <v>2</v>
@@ -8307,235 +8268,238 @@
         <v>245</v>
       </c>
       <c r="M295" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
     </row>
     <row r="296" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="C296" s="15" t="s">
-        <v>623</v>
+        <v>601</v>
       </c>
       <c r="D296" s="5">
-        <v>53348</v>
+        <v>52692</v>
       </c>
       <c r="F296" s="5"/>
     </row>
     <row r="297" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="C297" s="15" t="s">
-        <v>624</v>
+        <v>602</v>
       </c>
       <c r="D297" s="5">
-        <v>60717</v>
+        <v>61493</v>
       </c>
       <c r="F297" s="5"/>
     </row>
     <row r="298" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="C298" s="15" t="s">
-        <v>625</v>
+        <v>603</v>
       </c>
       <c r="D298" s="5">
-        <v>61629</v>
+        <v>63209</v>
       </c>
       <c r="F298" s="5"/>
     </row>
     <row r="299" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A299" s="6">
-        <v>86</v>
+        <v>80</v>
       </c>
       <c r="B299" t="s">
-        <v>45</v>
+        <v>144</v>
       </c>
       <c r="C299" s="15" t="s">
-        <v>626</v>
+        <v>604</v>
       </c>
       <c r="D299" s="5">
-        <v>47853</v>
+        <v>47464</v>
       </c>
       <c r="F299" s="5">
-        <v>64618</v>
+        <v>65173</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H299" s="2">
         <v>4</v>
       </c>
       <c r="I299" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J299" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K299" t="s">
         <v>241</v>
       </c>
       <c r="L299" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="M299" t="s">
-        <v>245</v>
+        <v>252</v>
       </c>
     </row>
     <row r="300" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="C300" s="15" t="s">
-        <v>627</v>
+        <v>605</v>
       </c>
       <c r="D300" s="5">
-        <v>45350</v>
+        <v>55130</v>
       </c>
       <c r="F300" s="5"/>
     </row>
     <row r="301" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="C301" s="15" t="s">
-        <v>628</v>
+        <v>606</v>
       </c>
       <c r="D301" s="5">
-        <v>54849</v>
+        <v>55878</v>
       </c>
       <c r="F301" s="5"/>
     </row>
     <row r="302" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="C302" s="15" t="s">
-        <v>629</v>
+        <v>607</v>
       </c>
       <c r="D302" s="5">
-        <v>55649</v>
+        <v>60148</v>
       </c>
       <c r="F302" s="5"/>
     </row>
     <row r="303" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A303" s="6">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="B303" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
       <c r="C303" s="15" t="s">
-        <v>630</v>
+        <v>608</v>
       </c>
       <c r="D303" s="5">
-        <v>50638</v>
+        <v>53287</v>
       </c>
       <c r="F303" s="5">
-        <v>64618</v>
+        <v>65146</v>
       </c>
       <c r="G303" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H303" s="2">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="I303" s="2">
+        <v>2</v>
       </c>
       <c r="J303" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K303" t="s">
         <v>242</v>
       </c>
       <c r="L303" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="M303" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="304" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A304" s="6">
-        <v>88</v>
-      </c>
-      <c r="B304" t="s">
-        <v>152</v>
-      </c>
+      <c r="A304" s="6"/>
       <c r="C304" s="15" t="s">
-        <v>631</v>
+        <v>609</v>
       </c>
       <c r="D304" s="5">
-        <v>45741</v>
-      </c>
-      <c r="F304" s="5">
-        <v>64571</v>
-      </c>
-      <c r="G304" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H304" s="2">
-        <v>5</v>
-      </c>
-      <c r="I304" s="2">
-        <v>3</v>
-      </c>
-      <c r="J304" s="2">
-        <v>2</v>
-      </c>
-      <c r="K304" t="s">
-        <v>242</v>
-      </c>
-      <c r="L304" t="s">
-        <v>281</v>
-      </c>
-      <c r="M304" t="s">
-        <v>245</v>
-      </c>
+        <v>53998</v>
+      </c>
+      <c r="F304" s="5"/>
     </row>
     <row r="305" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="C305" s="15" t="s">
-        <v>632</v>
+        <v>610</v>
       </c>
       <c r="D305" s="5">
-        <v>55622</v>
+        <v>62663</v>
       </c>
       <c r="F305" s="5"/>
     </row>
     <row r="306" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="C306" s="15" t="s">
-        <v>633</v>
+        <v>611</v>
       </c>
       <c r="D306" s="5">
-        <v>56503</v>
+        <v>64448</v>
       </c>
       <c r="F306" s="5"/>
     </row>
     <row r="307" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A307" s="6"/>
+      <c r="A307" s="6">
+        <v>82</v>
+      </c>
+      <c r="B307" t="s">
+        <v>147</v>
+      </c>
       <c r="C307" s="15" t="s">
-        <v>634</v>
+        <v>612</v>
       </c>
       <c r="D307" s="5">
-        <v>47613</v>
-      </c>
-      <c r="F307" s="5"/>
+        <v>53163</v>
+      </c>
+      <c r="F307" s="5">
+        <v>64977</v>
+      </c>
+      <c r="G307" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H307" s="2">
+        <v>2</v>
+      </c>
+      <c r="I307" s="2">
+        <v>1</v>
+      </c>
+      <c r="J307" s="2">
+        <v>1</v>
+      </c>
+      <c r="K307" t="s">
+        <v>240</v>
+      </c>
+      <c r="L307" t="s">
+        <v>315</v>
+      </c>
+      <c r="M307" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="308" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="C308" s="15" t="s">
-        <v>635</v>
+        <v>613</v>
       </c>
       <c r="D308" s="5">
-        <v>58328</v>
+        <v>62722</v>
       </c>
       <c r="F308" s="5"/>
     </row>
     <row r="309" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A309" s="6">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="B309" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="C309" s="15" t="s">
-        <v>636</v>
+        <v>614</v>
       </c>
       <c r="D309" s="5">
-        <v>46510</v>
+        <v>46667</v>
       </c>
       <c r="F309" s="5">
-        <v>64532</v>
+        <v>64935</v>
       </c>
       <c r="G309" s="2" t="s">
         <v>100</v>
@@ -8556,54 +8520,54 @@
         <v>245</v>
       </c>
       <c r="M309" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="310" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="C310" s="15" t="s">
-        <v>637</v>
+        <v>615</v>
       </c>
       <c r="D310" s="5">
-        <v>52829</v>
+        <v>51353</v>
       </c>
       <c r="F310" s="5"/>
     </row>
     <row r="311" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="C311" s="15" t="s">
-        <v>638</v>
+        <v>616</v>
       </c>
       <c r="D311" s="5">
-        <v>61785</v>
+        <v>59571</v>
       </c>
       <c r="F311" s="5"/>
     </row>
     <row r="312" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="C312" s="15" t="s">
-        <v>639</v>
+        <v>617</v>
       </c>
       <c r="D312" s="5">
-        <v>64259</v>
+        <v>60017</v>
       </c>
       <c r="F312" s="5"/>
     </row>
     <row r="313" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A313" s="6">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="B313" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
       <c r="C313" s="15" t="s">
-        <v>640</v>
+        <v>618</v>
       </c>
       <c r="D313" s="5">
-        <v>46659</v>
+        <v>50045</v>
       </c>
       <c r="F313" s="5">
-        <v>64446</v>
+        <v>64887</v>
       </c>
       <c r="G313" s="2" t="s">
         <v>2</v>
@@ -8612,16 +8576,16 @@
         <v>4</v>
       </c>
       <c r="I313" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J313" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K313" t="s">
         <v>242</v>
       </c>
       <c r="L313" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="M313" t="s">
         <v>245</v>
@@ -8630,116 +8594,116 @@
     <row r="314" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="C314" s="15" t="s">
-        <v>641</v>
+        <v>619</v>
       </c>
       <c r="D314" s="5">
-        <v>48034</v>
+        <v>50936</v>
       </c>
       <c r="F314" s="5"/>
     </row>
     <row r="315" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="C315" s="15" t="s">
-        <v>642</v>
+        <v>620</v>
       </c>
       <c r="D315" s="5">
-        <v>56151</v>
+        <v>58649</v>
       </c>
       <c r="F315" s="5"/>
     </row>
     <row r="316" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="C316" s="15" t="s">
-        <v>643</v>
+        <v>621</v>
       </c>
       <c r="D316" s="5">
-        <v>57208</v>
+        <v>59533</v>
       </c>
       <c r="F316" s="5"/>
     </row>
     <row r="317" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A317" s="6">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="B317" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
       <c r="C317" s="15" t="s">
-        <v>644</v>
+        <v>622</v>
       </c>
       <c r="D317" s="5">
-        <v>45148</v>
+        <v>51945</v>
       </c>
       <c r="F317" s="5">
-        <v>64444</v>
+        <v>64813</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H317" s="2">
         <v>4</v>
       </c>
       <c r="I317" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J317" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K317" t="s">
         <v>242</v>
       </c>
       <c r="L317" t="s">
-        <v>262</v>
+        <v>245</v>
       </c>
       <c r="M317" t="s">
-        <v>245</v>
+        <v>294</v>
       </c>
     </row>
     <row r="318" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="C318" s="15" t="s">
-        <v>645</v>
+        <v>623</v>
       </c>
       <c r="D318" s="5">
-        <v>55855</v>
+        <v>53348</v>
       </c>
       <c r="F318" s="5"/>
     </row>
     <row r="319" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="C319" s="15" t="s">
-        <v>646</v>
+        <v>624</v>
       </c>
       <c r="D319" s="5">
-        <v>58650</v>
+        <v>60717</v>
       </c>
       <c r="F319" s="5"/>
     </row>
     <row r="320" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="C320" s="15" t="s">
-        <v>647</v>
+        <v>625</v>
       </c>
       <c r="D320" s="5">
-        <v>48319</v>
+        <v>61629</v>
       </c>
       <c r="F320" s="5"/>
     </row>
     <row r="321" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A321" s="6">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="B321" t="s">
-        <v>156</v>
+        <v>45</v>
       </c>
       <c r="C321" s="15" t="s">
-        <v>648</v>
+        <v>626</v>
       </c>
       <c r="D321" s="5">
-        <v>49775</v>
+        <v>47853</v>
       </c>
       <c r="F321" s="5">
-        <v>64424</v>
+        <v>64618</v>
       </c>
       <c r="G321" s="2" t="s">
         <v>2</v>
@@ -8748,16 +8712,16 @@
         <v>4</v>
       </c>
       <c r="I321" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J321" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K321" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L321" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="M321" t="s">
         <v>245</v>
@@ -8766,56 +8730,53 @@
     <row r="322" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="C322" s="15" t="s">
-        <v>649</v>
+        <v>627</v>
       </c>
       <c r="D322" s="5">
-        <v>44270</v>
+        <v>45350</v>
       </c>
       <c r="F322" s="5"/>
     </row>
     <row r="323" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="C323" s="15" t="s">
-        <v>650</v>
+        <v>628</v>
       </c>
       <c r="D323" s="5">
-        <v>57742</v>
+        <v>54849</v>
       </c>
       <c r="F323" s="5"/>
     </row>
     <row r="324" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="C324" s="15" t="s">
-        <v>651</v>
+        <v>629</v>
       </c>
       <c r="D324" s="5">
-        <v>59421</v>
+        <v>55649</v>
       </c>
       <c r="F324" s="5"/>
     </row>
     <row r="325" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A325" s="6">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="B325" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C325" s="15" t="s">
-        <v>652</v>
+        <v>630</v>
       </c>
       <c r="D325" s="5">
-        <v>52455</v>
+        <v>50638</v>
       </c>
       <c r="F325" s="5">
-        <v>64395</v>
+        <v>64618</v>
       </c>
       <c r="G325" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H325" s="2">
-        <v>2</v>
-      </c>
-      <c r="I325" s="2">
         <v>1</v>
       </c>
       <c r="J325" s="2">
@@ -8825,318 +8786,318 @@
         <v>242</v>
       </c>
       <c r="L325" t="s">
-        <v>335</v>
+        <v>301</v>
       </c>
       <c r="M325" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="326" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A326" s="6"/>
+      <c r="A326" s="6">
+        <v>88</v>
+      </c>
+      <c r="B326" t="s">
+        <v>152</v>
+      </c>
       <c r="C326" s="15" t="s">
-        <v>653</v>
+        <v>631</v>
       </c>
       <c r="D326" s="5">
-        <v>53855</v>
-      </c>
-      <c r="F326" s="5"/>
+        <v>45741</v>
+      </c>
+      <c r="F326" s="5">
+        <v>64571</v>
+      </c>
+      <c r="G326" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H326" s="2">
+        <v>5</v>
+      </c>
+      <c r="I326" s="2">
+        <v>3</v>
+      </c>
+      <c r="J326" s="2">
+        <v>2</v>
+      </c>
+      <c r="K326" t="s">
+        <v>242</v>
+      </c>
+      <c r="L326" t="s">
+        <v>281</v>
+      </c>
+      <c r="M326" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="327" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A327" s="6">
-        <v>94</v>
-      </c>
-      <c r="B327" t="s">
-        <v>158</v>
-      </c>
+      <c r="A327" s="6"/>
       <c r="C327" s="15" t="s">
-        <v>654</v>
+        <v>632</v>
       </c>
       <c r="D327" s="5">
-        <v>46350</v>
-      </c>
-      <c r="F327" s="5">
-        <v>64320</v>
-      </c>
-      <c r="G327" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H327" s="2">
-        <v>4</v>
-      </c>
-      <c r="I327" s="2">
-        <v>1</v>
-      </c>
-      <c r="J327" s="2">
-        <v>3</v>
-      </c>
-      <c r="K327" t="s">
-        <v>241</v>
-      </c>
-      <c r="L327" t="s">
-        <v>323</v>
-      </c>
-      <c r="M327" t="s">
-        <v>245</v>
-      </c>
+        <v>55622</v>
+      </c>
+      <c r="F327" s="5"/>
     </row>
     <row r="328" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="C328" s="15" t="s">
-        <v>655</v>
+        <v>633</v>
       </c>
       <c r="D328" s="5">
-        <v>56069</v>
+        <v>56503</v>
       </c>
       <c r="F328" s="5"/>
     </row>
     <row r="329" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="C329" s="15" t="s">
-        <v>656</v>
+        <v>634</v>
       </c>
       <c r="D329" s="5">
-        <v>57797</v>
+        <v>47613</v>
       </c>
       <c r="F329" s="5"/>
     </row>
     <row r="330" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="C330" s="15" t="s">
-        <v>657</v>
+        <v>635</v>
       </c>
       <c r="D330" s="5">
-        <v>45239</v>
+        <v>58328</v>
       </c>
       <c r="F330" s="5"/>
     </row>
     <row r="331" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A331" s="6">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="B331" t="s">
-        <v>159</v>
+        <v>153</v>
       </c>
       <c r="C331" s="15" t="s">
-        <v>658</v>
+        <v>636</v>
       </c>
       <c r="D331" s="5">
-        <v>37226</v>
+        <v>46510</v>
       </c>
       <c r="F331" s="5">
-        <v>64167</v>
+        <v>64532</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H331" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="I331" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J331" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K331" t="s">
         <v>242</v>
       </c>
       <c r="L331" t="s">
-        <v>306</v>
+        <v>245</v>
       </c>
       <c r="M331" t="s">
-        <v>245</v>
+        <v>259</v>
       </c>
     </row>
     <row r="332" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="C332" s="15" t="s">
-        <v>409</v>
+        <v>637</v>
       </c>
       <c r="D332" s="5">
-        <v>39052</v>
+        <v>52829</v>
       </c>
       <c r="F332" s="5"/>
     </row>
     <row r="333" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A333" s="6">
-        <v>96</v>
-      </c>
-      <c r="B333" t="s">
-        <v>160</v>
-      </c>
+      <c r="A333" s="6"/>
       <c r="C333" s="15" t="s">
-        <v>659</v>
+        <v>638</v>
       </c>
       <c r="D333" s="5">
-        <v>48501</v>
-      </c>
-      <c r="F333" s="5">
-        <v>64166</v>
-      </c>
-      <c r="G333" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="H333" s="2">
-        <v>5</v>
-      </c>
-      <c r="I333" s="2">
-        <v>2</v>
-      </c>
-      <c r="J333" s="2">
-        <v>3</v>
-      </c>
-      <c r="K333" t="s">
-        <v>242</v>
-      </c>
-      <c r="L333" t="s">
-        <v>245</v>
-      </c>
-      <c r="M333" t="s">
-        <v>257</v>
-      </c>
+        <v>61785</v>
+      </c>
+      <c r="F333" s="5"/>
     </row>
     <row r="334" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="C334" s="15" t="s">
-        <v>660</v>
+        <v>639</v>
       </c>
       <c r="D334" s="5">
-        <v>46282</v>
+        <v>64259</v>
       </c>
       <c r="F334" s="5"/>
     </row>
     <row r="335" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A335" s="6"/>
+      <c r="A335" s="6">
+        <v>90</v>
+      </c>
+      <c r="B335" t="s">
+        <v>154</v>
+      </c>
       <c r="C335" s="15" t="s">
-        <v>661</v>
+        <v>640</v>
       </c>
       <c r="D335" s="5">
-        <v>36910</v>
-      </c>
-      <c r="F335" s="5"/>
+        <v>46659</v>
+      </c>
+      <c r="F335" s="5">
+        <v>64446</v>
+      </c>
+      <c r="G335" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H335" s="2">
+        <v>4</v>
+      </c>
+      <c r="I335" s="2">
+        <v>1</v>
+      </c>
+      <c r="J335" s="2">
+        <v>3</v>
+      </c>
+      <c r="K335" t="s">
+        <v>242</v>
+      </c>
+      <c r="L335" t="s">
+        <v>294</v>
+      </c>
+      <c r="M335" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="336" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="C336" s="15" t="s">
-        <v>662</v>
+        <v>641</v>
       </c>
       <c r="D336" s="5">
-        <v>56446</v>
+        <v>48034</v>
       </c>
       <c r="F336" s="5"/>
     </row>
     <row r="337" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="C337" s="15" t="s">
-        <v>663</v>
+        <v>642</v>
       </c>
       <c r="D337" s="5">
-        <v>58435</v>
+        <v>56151</v>
       </c>
       <c r="F337" s="5"/>
     </row>
     <row r="338" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A338" s="6">
-        <v>97</v>
-      </c>
-      <c r="B338" t="s">
-        <v>161</v>
-      </c>
+      <c r="A338" s="6"/>
       <c r="C338" s="15" t="s">
-        <v>664</v>
+        <v>643</v>
       </c>
       <c r="D338" s="5">
-        <v>45255</v>
-      </c>
-      <c r="F338" s="5">
-        <v>64099</v>
-      </c>
-      <c r="G338" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H338" s="2">
-        <v>5</v>
-      </c>
-      <c r="I338" s="2">
+        <v>57208</v>
+      </c>
+      <c r="F338" s="5"/>
+    </row>
+    <row r="339" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A339" s="6">
+        <v>91</v>
+      </c>
+      <c r="B339" t="s">
+        <v>155</v>
+      </c>
+      <c r="C339" s="15" t="s">
+        <v>644</v>
+      </c>
+      <c r="D339" s="5">
+        <v>45148</v>
+      </c>
+      <c r="F339" s="5">
+        <v>64444</v>
+      </c>
+      <c r="G339" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H339" s="2">
+        <v>4</v>
+      </c>
+      <c r="I339" s="2">
         <v>3</v>
       </c>
-      <c r="J338" s="2">
-        <v>2</v>
-      </c>
-      <c r="K338" t="s">
-        <v>242</v>
-      </c>
-      <c r="L338" t="s">
-        <v>284</v>
-      </c>
-      <c r="M338" t="s">
+      <c r="J339" s="2">
+        <v>1</v>
+      </c>
+      <c r="K339" t="s">
+        <v>242</v>
+      </c>
+      <c r="L339" t="s">
+        <v>262</v>
+      </c>
+      <c r="M339" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="339" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A339" s="6"/>
-      <c r="C339" s="15" t="s">
-        <v>665</v>
-      </c>
-      <c r="D339" s="5">
-        <v>46947</v>
-      </c>
-      <c r="F339" s="5"/>
     </row>
     <row r="340" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="C340" s="15" t="s">
-        <v>666</v>
+        <v>645</v>
       </c>
       <c r="D340" s="5">
-        <v>55117</v>
+        <v>55855</v>
       </c>
       <c r="F340" s="5"/>
     </row>
     <row r="341" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="C341" s="15" t="s">
-        <v>667</v>
+        <v>646</v>
       </c>
       <c r="D341" s="5">
-        <v>56476</v>
+        <v>58650</v>
       </c>
       <c r="F341" s="5"/>
     </row>
     <row r="342" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="C342" s="15" t="s">
-        <v>668</v>
+        <v>647</v>
       </c>
       <c r="D342" s="5">
-        <v>58438</v>
+        <v>48319</v>
       </c>
       <c r="F342" s="5"/>
     </row>
     <row r="343" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A343" s="6">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="B343" t="s">
-        <v>162</v>
+        <v>156</v>
       </c>
       <c r="C343" s="15" t="s">
-        <v>441</v>
+        <v>648</v>
       </c>
       <c r="D343" s="5">
-        <v>45148</v>
+        <v>49775</v>
       </c>
       <c r="F343" s="5">
-        <v>64032</v>
+        <v>64424</v>
       </c>
       <c r="G343" s="2" t="s">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="H343" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="I343" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J343" s="2">
         <v>2</v>
@@ -9145,386 +9106,380 @@
         <v>242</v>
       </c>
       <c r="L343" t="s">
+        <v>265</v>
+      </c>
+      <c r="M343" t="s">
         <v>245</v>
-      </c>
-      <c r="M343" t="s">
-        <v>278</v>
       </c>
     </row>
     <row r="344" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="C344" s="15" t="s">
-        <v>442</v>
+        <v>649</v>
       </c>
       <c r="D344" s="5">
-        <v>46509</v>
+        <v>44270</v>
       </c>
       <c r="F344" s="5"/>
     </row>
     <row r="345" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="C345" s="15" t="s">
-        <v>440</v>
+        <v>650</v>
       </c>
       <c r="D345" s="5">
-        <v>53896</v>
+        <v>57742</v>
       </c>
       <c r="F345" s="5"/>
     </row>
     <row r="346" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="C346" s="15" t="s">
-        <v>443</v>
+        <v>651</v>
       </c>
       <c r="D346" s="5">
-        <v>55011</v>
+        <v>59421</v>
       </c>
       <c r="F346" s="5"/>
     </row>
     <row r="347" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A347" s="6"/>
+      <c r="A347" s="6">
+        <v>93</v>
+      </c>
+      <c r="B347" t="s">
+        <v>157</v>
+      </c>
       <c r="C347" s="15" t="s">
-        <v>444</v>
+        <v>652</v>
       </c>
       <c r="D347" s="5">
-        <v>63210</v>
-      </c>
-      <c r="F347" s="5"/>
+        <v>52455</v>
+      </c>
+      <c r="F347" s="5">
+        <v>64395</v>
+      </c>
+      <c r="G347" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H347" s="2">
+        <v>2</v>
+      </c>
+      <c r="I347" s="2">
+        <v>1</v>
+      </c>
+      <c r="J347" s="2">
+        <v>1</v>
+      </c>
+      <c r="K347" t="s">
+        <v>242</v>
+      </c>
+      <c r="L347" t="s">
+        <v>335</v>
+      </c>
+      <c r="M347" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="348" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A348" s="6">
-        <v>99</v>
-      </c>
-      <c r="B348" t="s">
-        <v>163</v>
-      </c>
+      <c r="A348" s="6"/>
       <c r="C348" s="15" t="s">
-        <v>669</v>
+        <v>653</v>
       </c>
       <c r="D348" s="5">
-        <v>42311</v>
-      </c>
-      <c r="F348" s="5">
-        <v>63997</v>
-      </c>
-      <c r="G348" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H348" s="2">
+        <v>53855</v>
+      </c>
+      <c r="F348" s="5"/>
+    </row>
+    <row r="349" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A349" s="6">
+        <v>94</v>
+      </c>
+      <c r="B349" t="s">
+        <v>158</v>
+      </c>
+      <c r="C349" s="15" t="s">
+        <v>654</v>
+      </c>
+      <c r="D349" s="5">
+        <v>46350</v>
+      </c>
+      <c r="F349" s="5">
+        <v>64320</v>
+      </c>
+      <c r="G349" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H349" s="2">
         <v>4</v>
       </c>
-      <c r="I348" s="2">
-        <v>2</v>
-      </c>
-      <c r="J348" s="2">
-        <v>2</v>
-      </c>
-      <c r="K348" t="s">
-        <v>242</v>
-      </c>
-      <c r="L348" t="s">
-        <v>282</v>
-      </c>
-      <c r="M348" t="s">
+      <c r="I349" s="2">
+        <v>1</v>
+      </c>
+      <c r="J349" s="2">
+        <v>3</v>
+      </c>
+      <c r="K349" t="s">
+        <v>241</v>
+      </c>
+      <c r="L349" t="s">
+        <v>323</v>
+      </c>
+      <c r="M349" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="349" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A349" s="6"/>
-      <c r="C349" s="15" t="s">
-        <v>670</v>
-      </c>
-      <c r="D349" s="5">
-        <v>46696</v>
-      </c>
-      <c r="F349" s="5"/>
     </row>
     <row r="350" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="C350" s="15" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="D350" s="5">
-        <v>54655</v>
+        <v>56069</v>
       </c>
       <c r="F350" s="5"/>
     </row>
     <row r="351" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="C351" s="15" t="s">
-        <v>672</v>
+        <v>656</v>
       </c>
       <c r="D351" s="5">
-        <v>53800</v>
+        <v>57797</v>
       </c>
       <c r="F351" s="5"/>
     </row>
     <row r="352" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A352" s="6">
+      <c r="A352" s="6"/>
+      <c r="C352" s="15" t="s">
+        <v>657</v>
+      </c>
+      <c r="D352" s="5">
+        <v>45239</v>
+      </c>
+      <c r="F352" s="5"/>
+    </row>
+    <row r="353" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A353" s="6">
+        <v>95</v>
+      </c>
+      <c r="B353" t="s">
+        <v>159</v>
+      </c>
+      <c r="C353" s="15" t="s">
+        <v>658</v>
+      </c>
+      <c r="D353" s="5">
+        <v>37226</v>
+      </c>
+      <c r="F353" s="5">
+        <v>64167</v>
+      </c>
+      <c r="G353" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H353" s="2">
+        <v>2</v>
+      </c>
+      <c r="I353" s="2">
+        <v>1</v>
+      </c>
+      <c r="J353" s="2">
+        <v>1</v>
+      </c>
+      <c r="K353" t="s">
+        <v>242</v>
+      </c>
+      <c r="L353" t="s">
+        <v>306</v>
+      </c>
+      <c r="M353" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="354" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A354" s="6"/>
+      <c r="C354" s="15" t="s">
+        <v>409</v>
+      </c>
+      <c r="D354" s="5">
+        <v>39052</v>
+      </c>
+      <c r="F354" s="5"/>
+    </row>
+    <row r="355" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A355" s="6">
+        <v>96</v>
+      </c>
+      <c r="B355" t="s">
+        <v>160</v>
+      </c>
+      <c r="C355" s="15" t="s">
+        <v>659</v>
+      </c>
+      <c r="D355" s="5">
+        <v>48501</v>
+      </c>
+      <c r="F355" s="5">
+        <v>64166</v>
+      </c>
+      <c r="G355" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="B352" t="s">
-        <v>164</v>
-      </c>
-      <c r="C352" s="15" t="s">
-        <v>673</v>
-      </c>
-      <c r="D352" s="5">
-        <v>36222</v>
-      </c>
-      <c r="E352" t="s">
-        <v>214</v>
-      </c>
-      <c r="F352" s="5">
-        <v>63944</v>
-      </c>
-      <c r="G352" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H352" s="2">
-        <v>2</v>
-      </c>
-      <c r="I352" s="2">
-        <v>1</v>
-      </c>
-      <c r="J352" s="2">
-        <v>1</v>
-      </c>
-      <c r="K352" t="s">
-        <v>242</v>
-      </c>
-      <c r="L352" t="s">
-        <v>269</v>
-      </c>
-      <c r="M352" t="s">
+      <c r="H355" s="2">
+        <v>5</v>
+      </c>
+      <c r="I355" s="2">
+        <v>2</v>
+      </c>
+      <c r="J355" s="2">
+        <v>3</v>
+      </c>
+      <c r="K355" t="s">
+        <v>242</v>
+      </c>
+      <c r="L355" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="353" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A353" s="6"/>
-      <c r="C353" s="15" t="s">
-        <v>674</v>
-      </c>
-      <c r="D353" s="5">
-        <v>12554</v>
-      </c>
-      <c r="F353" s="5"/>
-    </row>
-    <row r="354" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A354" s="6">
-        <v>101</v>
-      </c>
-      <c r="B354" t="s">
-        <v>216</v>
-      </c>
-      <c r="C354" s="15" t="s">
-        <v>675</v>
-      </c>
-      <c r="D354" s="5">
-        <v>49684</v>
-      </c>
-      <c r="E354" t="s">
-        <v>230</v>
-      </c>
-      <c r="F354" s="5">
-        <v>63928</v>
-      </c>
-      <c r="G354" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H354" s="2">
-        <v>4</v>
-      </c>
-      <c r="I354" s="2">
-        <v>2</v>
-      </c>
-      <c r="J354" s="2">
-        <v>2</v>
-      </c>
-      <c r="K354" t="s">
-        <v>237</v>
-      </c>
-      <c r="L354" t="s">
-        <v>297</v>
-      </c>
-      <c r="M354" t="s">
-        <v>245</v>
-      </c>
-    </row>
-    <row r="355" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A355" s="6"/>
-      <c r="C355" s="15" t="s">
-        <v>676</v>
-      </c>
-      <c r="D355" s="5">
-        <v>50861</v>
-      </c>
-      <c r="F355" s="5"/>
+      <c r="M355" t="s">
+        <v>257</v>
+      </c>
     </row>
     <row r="356" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="C356" s="15" t="s">
-        <v>677</v>
+        <v>660</v>
       </c>
       <c r="D356" s="5">
-        <v>39461</v>
+        <v>46282</v>
       </c>
       <c r="F356" s="5"/>
     </row>
     <row r="357" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="C357" s="15" t="s">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="D357" s="5">
-        <v>58217</v>
+        <v>36910</v>
       </c>
       <c r="F357" s="5"/>
     </row>
     <row r="358" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A358" s="6">
-        <v>102</v>
-      </c>
-      <c r="B358" t="s">
-        <v>145</v>
-      </c>
+      <c r="A358" s="6"/>
       <c r="C358" s="15" t="s">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="D358" s="5">
-        <v>52174</v>
-      </c>
-      <c r="F358" s="5">
-        <v>63834</v>
-      </c>
-      <c r="G358" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H358" s="2">
-        <v>4</v>
-      </c>
-      <c r="I358" s="2">
-        <v>2</v>
-      </c>
-      <c r="J358" s="2">
-        <v>2</v>
-      </c>
-      <c r="K358" t="s">
-        <v>241</v>
-      </c>
-      <c r="L358" t="s">
-        <v>288</v>
-      </c>
-      <c r="M358" t="s">
-        <v>245</v>
-      </c>
+        <v>56446</v>
+      </c>
+      <c r="F358" s="5"/>
     </row>
     <row r="359" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="C359" s="15" t="s">
-        <v>680</v>
+        <v>663</v>
       </c>
       <c r="D359" s="5">
-        <v>52692</v>
+        <v>58435</v>
       </c>
       <c r="F359" s="5"/>
     </row>
     <row r="360" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A360" s="6"/>
+      <c r="A360" s="6">
+        <v>97</v>
+      </c>
+      <c r="B360" t="s">
+        <v>161</v>
+      </c>
       <c r="C360" s="15" t="s">
-        <v>681</v>
+        <v>664</v>
       </c>
       <c r="D360" s="5">
-        <v>61493</v>
-      </c>
-      <c r="F360" s="5"/>
+        <v>45255</v>
+      </c>
+      <c r="F360" s="5">
+        <v>64099</v>
+      </c>
+      <c r="G360" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H360" s="2">
+        <v>5</v>
+      </c>
+      <c r="I360" s="2">
+        <v>3</v>
+      </c>
+      <c r="J360" s="2">
+        <v>2</v>
+      </c>
+      <c r="K360" t="s">
+        <v>242</v>
+      </c>
+      <c r="L360" t="s">
+        <v>284</v>
+      </c>
+      <c r="M360" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="361" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="C361" s="15" t="s">
-        <v>682</v>
+        <v>665</v>
       </c>
       <c r="D361" s="5">
-        <v>63209</v>
+        <v>46947</v>
       </c>
       <c r="F361" s="5"/>
     </row>
     <row r="362" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A362" s="6">
-        <v>103</v>
-      </c>
-      <c r="B362" t="s">
-        <v>217</v>
-      </c>
+      <c r="A362" s="6"/>
       <c r="C362" s="15" t="s">
-        <v>683</v>
+        <v>666</v>
       </c>
       <c r="D362" s="5">
-        <v>49255</v>
-      </c>
-      <c r="F362" s="5">
-        <v>63817</v>
-      </c>
-      <c r="G362" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H362" s="2">
-        <v>3</v>
-      </c>
-      <c r="I362" s="2">
-        <v>1</v>
-      </c>
-      <c r="J362" s="2">
-        <v>2</v>
-      </c>
-      <c r="K362" t="s">
-        <v>242</v>
-      </c>
-      <c r="L362" t="s">
-        <v>295</v>
-      </c>
-      <c r="M362" t="s">
-        <v>245</v>
-      </c>
+        <v>55117</v>
+      </c>
+      <c r="F362" s="5"/>
     </row>
     <row r="363" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="C363" s="15" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="D363" s="5">
-        <v>52543</v>
+        <v>56476</v>
       </c>
       <c r="F363" s="5"/>
     </row>
     <row r="364" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="C364" s="15" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="D364" s="5">
-        <v>63360</v>
+        <v>58438</v>
       </c>
       <c r="F364" s="5"/>
     </row>
     <row r="365" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A365" s="6">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="B365" t="s">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="C365" s="15" t="s">
-        <v>458</v>
+        <v>441</v>
       </c>
       <c r="D365" s="5">
-        <v>43935</v>
+        <v>45148</v>
       </c>
       <c r="F365" s="5">
-        <v>63725</v>
+        <v>64032</v>
       </c>
       <c r="G365" s="2" t="s">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="H365" s="2">
         <v>5</v>
@@ -9536,88 +9491,88 @@
         <v>2</v>
       </c>
       <c r="K365" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="L365" t="s">
-        <v>279</v>
+        <v>245</v>
       </c>
       <c r="M365" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
     </row>
     <row r="366" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="C366" s="15" t="s">
-        <v>459</v>
+        <v>442</v>
       </c>
       <c r="D366" s="5">
-        <v>32432</v>
+        <v>46509</v>
       </c>
       <c r="F366" s="5"/>
     </row>
     <row r="367" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="C367" s="15" t="s">
-        <v>686</v>
+        <v>440</v>
       </c>
       <c r="D367" s="5">
-        <v>33025</v>
+        <v>53896</v>
       </c>
       <c r="F367" s="5"/>
     </row>
     <row r="368" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="C368" s="15" t="s">
-        <v>460</v>
+        <v>443</v>
       </c>
       <c r="D368" s="5">
-        <v>44749</v>
+        <v>55011</v>
       </c>
       <c r="F368" s="5"/>
     </row>
     <row r="369" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="C369" s="15" t="s">
-        <v>687</v>
+        <v>444</v>
       </c>
       <c r="D369" s="5">
-        <v>54758</v>
+        <v>63210</v>
       </c>
       <c r="F369" s="5"/>
     </row>
     <row r="370" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A370" s="6">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="B370" t="s">
-        <v>218</v>
+        <v>163</v>
       </c>
       <c r="C370" s="15" t="s">
-        <v>688</v>
+        <v>669</v>
       </c>
       <c r="D370" s="5">
-        <v>41927</v>
+        <v>42311</v>
       </c>
       <c r="F370" s="5">
-        <v>63683</v>
+        <v>63997</v>
       </c>
       <c r="G370" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H370" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="I370" s="2">
         <v>2</v>
       </c>
       <c r="J370" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K370" t="s">
         <v>242</v>
       </c>
       <c r="L370" t="s">
-        <v>269</v>
+        <v>282</v>
       </c>
       <c r="M370" t="s">
         <v>245</v>
@@ -9626,213 +9581,247 @@
     <row r="371" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="C371" s="15" t="s">
-        <v>689</v>
+        <v>670</v>
       </c>
       <c r="D371" s="5">
-        <v>43620</v>
+        <v>46696</v>
       </c>
       <c r="F371" s="5"/>
     </row>
     <row r="372" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="C372" s="15" t="s">
-        <v>690</v>
+        <v>671</v>
       </c>
       <c r="D372" s="5">
-        <v>57440</v>
+        <v>54655</v>
       </c>
       <c r="F372" s="5"/>
     </row>
     <row r="373" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A373" s="6">
-        <v>106</v>
-      </c>
-      <c r="B373" t="s">
-        <v>46</v>
-      </c>
+      <c r="A373" s="6"/>
       <c r="C373" s="15" t="s">
-        <v>691</v>
+        <v>672</v>
       </c>
       <c r="D373" s="5">
-        <v>36554</v>
-      </c>
-      <c r="F373" s="5">
-        <v>63673</v>
-      </c>
-      <c r="G373" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H373" s="2">
-        <v>5</v>
-      </c>
-      <c r="I373" s="2">
-        <v>2</v>
-      </c>
-      <c r="J373" s="2">
-        <v>3</v>
-      </c>
-      <c r="K373" t="s">
-        <v>242</v>
-      </c>
-      <c r="L373" t="s">
-        <v>307</v>
-      </c>
-      <c r="M373" t="s">
+        <v>53800</v>
+      </c>
+      <c r="F373" s="5"/>
+    </row>
+    <row r="374" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A374" s="6">
+        <v>100</v>
+      </c>
+      <c r="B374" t="s">
+        <v>164</v>
+      </c>
+      <c r="C374" s="15" t="s">
+        <v>673</v>
+      </c>
+      <c r="D374" s="5">
+        <v>36222</v>
+      </c>
+      <c r="E374" t="s">
+        <v>214</v>
+      </c>
+      <c r="F374" s="5">
+        <v>63944</v>
+      </c>
+      <c r="G374" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H374" s="2">
+        <v>2</v>
+      </c>
+      <c r="I374" s="2">
+        <v>1</v>
+      </c>
+      <c r="J374" s="2">
+        <v>1</v>
+      </c>
+      <c r="K374" t="s">
+        <v>242</v>
+      </c>
+      <c r="L374" t="s">
+        <v>269</v>
+      </c>
+      <c r="M374" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="374" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A374" s="6"/>
-      <c r="C374" s="15" t="s">
-        <v>692</v>
-      </c>
-      <c r="D374" s="5">
-        <v>50613</v>
-      </c>
-      <c r="F374" s="5"/>
     </row>
     <row r="375" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="C375" s="15" t="s">
-        <v>693</v>
+        <v>674</v>
       </c>
       <c r="D375" s="5">
-        <v>53207</v>
+        <v>12554</v>
       </c>
       <c r="F375" s="5"/>
     </row>
     <row r="376" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A376" s="6"/>
+      <c r="A376" s="6">
+        <v>101</v>
+      </c>
+      <c r="B376" t="s">
+        <v>216</v>
+      </c>
       <c r="C376" s="15" t="s">
-        <v>694</v>
+        <v>675</v>
       </c>
       <c r="D376" s="5">
-        <v>59777</v>
-      </c>
-      <c r="F376" s="5"/>
+        <v>49684</v>
+      </c>
+      <c r="E376" t="s">
+        <v>230</v>
+      </c>
+      <c r="F376" s="5">
+        <v>63928</v>
+      </c>
+      <c r="G376" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H376" s="2">
+        <v>4</v>
+      </c>
+      <c r="I376" s="2">
+        <v>2</v>
+      </c>
+      <c r="J376" s="2">
+        <v>2</v>
+      </c>
+      <c r="K376" t="s">
+        <v>237</v>
+      </c>
+      <c r="L376" t="s">
+        <v>297</v>
+      </c>
+      <c r="M376" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="377" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="C377" s="15" t="s">
-        <v>695</v>
+        <v>676</v>
       </c>
       <c r="D377" s="5">
-        <v>61147</v>
+        <v>50861</v>
       </c>
       <c r="F377" s="5"/>
     </row>
     <row r="378" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A378" s="6">
-        <v>107</v>
-      </c>
-      <c r="B378" t="s">
-        <v>219</v>
-      </c>
+      <c r="A378" s="6"/>
       <c r="C378" s="15" t="s">
-        <v>696</v>
+        <v>677</v>
       </c>
       <c r="D378" s="5">
-        <v>38852</v>
-      </c>
-      <c r="F378" s="5">
-        <v>63649</v>
-      </c>
-      <c r="G378" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H378" s="2">
-        <v>6</v>
-      </c>
-      <c r="I378" s="2">
-        <v>1</v>
-      </c>
-      <c r="J378" s="2">
-        <v>5</v>
-      </c>
-      <c r="K378" t="s">
-        <v>239</v>
-      </c>
-      <c r="L378" t="s">
-        <v>274</v>
-      </c>
-      <c r="M378" t="s">
-        <v>245</v>
-      </c>
+        <v>39461</v>
+      </c>
+      <c r="F378" s="5"/>
     </row>
     <row r="379" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="C379" s="15" t="s">
-        <v>697</v>
+        <v>678</v>
       </c>
       <c r="D379" s="5">
-        <v>40237</v>
+        <v>58217</v>
       </c>
       <c r="F379" s="5"/>
     </row>
     <row r="380" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A380" s="6"/>
+      <c r="A380" s="6">
+        <v>102</v>
+      </c>
+      <c r="B380" t="s">
+        <v>145</v>
+      </c>
       <c r="C380" s="15" t="s">
-        <v>698</v>
+        <v>679</v>
       </c>
       <c r="D380" s="5">
-        <v>52332</v>
-      </c>
-      <c r="F380" s="5"/>
+        <v>52174</v>
+      </c>
+      <c r="F380" s="5">
+        <v>63834</v>
+      </c>
+      <c r="G380" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H380" s="2">
+        <v>4</v>
+      </c>
+      <c r="I380" s="2">
+        <v>2</v>
+      </c>
+      <c r="J380" s="2">
+        <v>2</v>
+      </c>
+      <c r="K380" t="s">
+        <v>241</v>
+      </c>
+      <c r="L380" t="s">
+        <v>288</v>
+      </c>
+      <c r="M380" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="381" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="C381" s="15" t="s">
-        <v>699</v>
+        <v>680</v>
       </c>
       <c r="D381" s="5">
-        <v>54879</v>
+        <v>52692</v>
       </c>
       <c r="F381" s="5"/>
     </row>
     <row r="382" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="C382" s="15" t="s">
-        <v>700</v>
+        <v>681</v>
       </c>
       <c r="D382" s="5">
-        <v>55353</v>
+        <v>61493</v>
       </c>
       <c r="F382" s="5"/>
     </row>
     <row r="383" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="C383" s="15" t="s">
-        <v>701</v>
+        <v>682</v>
       </c>
       <c r="D383" s="5">
-        <v>48546</v>
+        <v>63209</v>
       </c>
       <c r="F383" s="5"/>
     </row>
     <row r="384" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A384" s="6">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="B384" t="s">
-        <v>148</v>
+        <v>217</v>
       </c>
       <c r="C384" s="15" t="s">
-        <v>702</v>
+        <v>683</v>
       </c>
       <c r="D384" s="5">
-        <v>46667</v>
+        <v>49255</v>
       </c>
       <c r="F384" s="5">
-        <v>63601</v>
+        <v>63817</v>
       </c>
       <c r="G384" s="2" t="s">
         <v>2</v>
       </c>
       <c r="H384" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I384" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J384" s="2">
         <v>2</v>
@@ -9841,7 +9830,7 @@
         <v>242</v>
       </c>
       <c r="L384" t="s">
-        <v>260</v>
+        <v>295</v>
       </c>
       <c r="M384" t="s">
         <v>245</v>
@@ -9850,164 +9839,524 @@
     <row r="385" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="C385" s="15" t="s">
-        <v>703</v>
+        <v>684</v>
       </c>
       <c r="D385" s="5">
-        <v>51353</v>
+        <v>52543</v>
       </c>
       <c r="F385" s="5"/>
     </row>
     <row r="386" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="C386" s="15" t="s">
-        <v>616</v>
+        <v>685</v>
       </c>
       <c r="D386" s="5">
-        <v>59571</v>
+        <v>63360</v>
       </c>
       <c r="F386" s="5"/>
     </row>
     <row r="387" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A387" s="6"/>
+      <c r="A387" s="6">
+        <v>104</v>
+      </c>
+      <c r="B387" t="s">
+        <v>38</v>
+      </c>
       <c r="C387" s="15" t="s">
-        <v>617</v>
+        <v>458</v>
       </c>
       <c r="D387" s="5">
-        <v>60017</v>
-      </c>
-      <c r="F387" s="5"/>
+        <v>43935</v>
+      </c>
+      <c r="F387" s="5">
+        <v>63725</v>
+      </c>
+      <c r="G387" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H387" s="2">
+        <v>5</v>
+      </c>
+      <c r="I387" s="2">
+        <v>3</v>
+      </c>
+      <c r="J387" s="2">
+        <v>2</v>
+      </c>
+      <c r="K387" t="s">
+        <v>239</v>
+      </c>
+      <c r="L387" t="s">
+        <v>279</v>
+      </c>
+      <c r="M387" t="s">
+        <v>245</v>
+      </c>
     </row>
     <row r="388" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A388" s="6">
-        <v>109</v>
-      </c>
-      <c r="B388" t="s">
-        <v>220</v>
-      </c>
+      <c r="A388" s="6"/>
       <c r="C388" s="15" t="s">
-        <v>704</v>
+        <v>459</v>
       </c>
       <c r="D388" s="5">
-        <v>48043</v>
-      </c>
-      <c r="F388" s="5">
-        <v>63569</v>
-      </c>
-      <c r="G388" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H388" s="2">
-        <v>3</v>
-      </c>
-      <c r="I388" s="2">
-        <v>2</v>
-      </c>
-      <c r="J388" s="2">
-        <v>1</v>
-      </c>
-      <c r="K388" t="s">
-        <v>242</v>
-      </c>
-      <c r="L388" t="s">
-        <v>261</v>
-      </c>
-      <c r="M388" t="s">
-        <v>245</v>
-      </c>
+        <v>32432</v>
+      </c>
+      <c r="F388" s="5"/>
     </row>
     <row r="389" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="C389" s="15" t="s">
-        <v>705</v>
+        <v>686</v>
       </c>
       <c r="D389" s="5">
-        <v>48590</v>
+        <v>33025</v>
       </c>
       <c r="F389" s="5"/>
     </row>
     <row r="390" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="C390" s="15" t="s">
-        <v>706</v>
+        <v>460</v>
       </c>
       <c r="D390" s="5">
-        <v>58901</v>
+        <v>44749</v>
       </c>
       <c r="F390" s="5"/>
     </row>
     <row r="391" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A391" s="6">
-        <v>110</v>
-      </c>
-      <c r="B391" t="s">
-        <v>221</v>
-      </c>
+      <c r="A391" s="6"/>
       <c r="C391" s="15" t="s">
-        <v>707</v>
+        <v>687</v>
       </c>
       <c r="D391" s="5">
-        <v>47140</v>
-      </c>
-      <c r="E391" t="s">
-        <v>229</v>
-      </c>
-      <c r="F391" s="5">
-        <v>63566</v>
-      </c>
-      <c r="G391" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="H391" s="2">
-        <v>4</v>
-      </c>
-      <c r="I391" s="2">
-        <v>2</v>
-      </c>
-      <c r="J391" s="2">
-        <v>2</v>
-      </c>
-      <c r="K391" t="s">
-        <v>242</v>
-      </c>
-      <c r="L391" t="s">
-        <v>295</v>
-      </c>
-      <c r="M391" t="s">
+        <v>54758</v>
+      </c>
+      <c r="F391" s="5"/>
+    </row>
+    <row r="392" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A392" s="6">
+        <v>105</v>
+      </c>
+      <c r="B392" t="s">
+        <v>218</v>
+      </c>
+      <c r="C392" s="15" t="s">
+        <v>688</v>
+      </c>
+      <c r="D392" s="5">
+        <v>41927</v>
+      </c>
+      <c r="F392" s="5">
+        <v>63683</v>
+      </c>
+      <c r="G392" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H392" s="2">
+        <v>3</v>
+      </c>
+      <c r="I392" s="2">
+        <v>2</v>
+      </c>
+      <c r="J392" s="2">
+        <v>1</v>
+      </c>
+      <c r="K392" t="s">
+        <v>242</v>
+      </c>
+      <c r="L392" t="s">
+        <v>269</v>
+      </c>
+      <c r="M392" t="s">
         <v>245</v>
       </c>
-    </row>
-    <row r="392" spans="1:13" ht="18" x14ac:dyDescent="0.25">
-      <c r="A392" s="6"/>
-      <c r="C392" s="15" t="s">
-        <v>708</v>
-      </c>
-      <c r="D392" s="5">
-        <v>49059</v>
-      </c>
-      <c r="F392" s="5"/>
     </row>
     <row r="393" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="C393" s="15" t="s">
-        <v>709</v>
+        <v>689</v>
       </c>
       <c r="D393" s="5">
-        <v>59058</v>
+        <v>43620</v>
       </c>
       <c r="F393" s="5"/>
     </row>
     <row r="394" spans="1:13" ht="18" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="C394" s="15" t="s">
+        <v>690</v>
+      </c>
+      <c r="D394" s="5">
+        <v>57440</v>
+      </c>
+      <c r="F394" s="5"/>
+    </row>
+    <row r="395" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A395" s="6">
+        <v>106</v>
+      </c>
+      <c r="B395" t="s">
+        <v>46</v>
+      </c>
+      <c r="C395" s="15" t="s">
+        <v>691</v>
+      </c>
+      <c r="D395" s="5">
+        <v>36554</v>
+      </c>
+      <c r="F395" s="5">
+        <v>63673</v>
+      </c>
+      <c r="G395" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H395" s="2">
+        <v>5</v>
+      </c>
+      <c r="I395" s="2">
+        <v>2</v>
+      </c>
+      <c r="J395" s="2">
+        <v>3</v>
+      </c>
+      <c r="K395" t="s">
+        <v>242</v>
+      </c>
+      <c r="L395" t="s">
+        <v>307</v>
+      </c>
+      <c r="M395" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="396" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A396" s="6"/>
+      <c r="C396" s="15" t="s">
+        <v>692</v>
+      </c>
+      <c r="D396" s="5">
+        <v>50613</v>
+      </c>
+      <c r="F396" s="5"/>
+    </row>
+    <row r="397" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A397" s="6"/>
+      <c r="C397" s="15" t="s">
+        <v>693</v>
+      </c>
+      <c r="D397" s="5">
+        <v>53207</v>
+      </c>
+      <c r="F397" s="5"/>
+    </row>
+    <row r="398" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A398" s="6"/>
+      <c r="C398" s="15" t="s">
+        <v>694</v>
+      </c>
+      <c r="D398" s="5">
+        <v>59777</v>
+      </c>
+      <c r="F398" s="5"/>
+    </row>
+    <row r="399" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A399" s="6"/>
+      <c r="C399" s="15" t="s">
+        <v>695</v>
+      </c>
+      <c r="D399" s="5">
+        <v>61147</v>
+      </c>
+      <c r="F399" s="5"/>
+    </row>
+    <row r="400" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A400" s="6">
+        <v>107</v>
+      </c>
+      <c r="B400" t="s">
+        <v>219</v>
+      </c>
+      <c r="C400" s="15" t="s">
+        <v>696</v>
+      </c>
+      <c r="D400" s="5">
+        <v>38852</v>
+      </c>
+      <c r="F400" s="5">
+        <v>63649</v>
+      </c>
+      <c r="G400" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H400" s="2">
+        <v>6</v>
+      </c>
+      <c r="I400" s="2">
+        <v>1</v>
+      </c>
+      <c r="J400" s="2">
+        <v>5</v>
+      </c>
+      <c r="K400" t="s">
+        <v>239</v>
+      </c>
+      <c r="L400" t="s">
+        <v>274</v>
+      </c>
+      <c r="M400" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="401" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A401" s="6"/>
+      <c r="C401" s="15" t="s">
+        <v>697</v>
+      </c>
+      <c r="D401" s="5">
+        <v>40237</v>
+      </c>
+      <c r="F401" s="5"/>
+    </row>
+    <row r="402" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A402" s="6"/>
+      <c r="C402" s="15" t="s">
+        <v>698</v>
+      </c>
+      <c r="D402" s="5">
+        <v>52332</v>
+      </c>
+      <c r="F402" s="5"/>
+    </row>
+    <row r="403" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A403" s="6"/>
+      <c r="C403" s="15" t="s">
+        <v>699</v>
+      </c>
+      <c r="D403" s="5">
+        <v>54879</v>
+      </c>
+      <c r="F403" s="5"/>
+    </row>
+    <row r="404" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A404" s="6"/>
+      <c r="C404" s="15" t="s">
+        <v>700</v>
+      </c>
+      <c r="D404" s="5">
+        <v>55353</v>
+      </c>
+      <c r="F404" s="5"/>
+    </row>
+    <row r="405" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A405" s="6"/>
+      <c r="C405" s="15" t="s">
+        <v>701</v>
+      </c>
+      <c r="D405" s="5">
+        <v>48546</v>
+      </c>
+      <c r="F405" s="5"/>
+    </row>
+    <row r="406" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A406" s="6">
+        <v>108</v>
+      </c>
+      <c r="B406" t="s">
+        <v>148</v>
+      </c>
+      <c r="C406" s="15" t="s">
+        <v>702</v>
+      </c>
+      <c r="D406" s="5">
+        <v>46667</v>
+      </c>
+      <c r="F406" s="5">
+        <v>63601</v>
+      </c>
+      <c r="G406" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H406" s="2">
+        <v>4</v>
+      </c>
+      <c r="I406" s="2">
+        <v>2</v>
+      </c>
+      <c r="J406" s="2">
+        <v>2</v>
+      </c>
+      <c r="K406" t="s">
+        <v>242</v>
+      </c>
+      <c r="L406" t="s">
+        <v>260</v>
+      </c>
+      <c r="M406" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="407" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A407" s="6"/>
+      <c r="C407" s="15" t="s">
+        <v>703</v>
+      </c>
+      <c r="D407" s="5">
+        <v>51353</v>
+      </c>
+      <c r="F407" s="5"/>
+    </row>
+    <row r="408" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A408" s="6"/>
+      <c r="C408" s="15" t="s">
+        <v>616</v>
+      </c>
+      <c r="D408" s="5">
+        <v>59571</v>
+      </c>
+      <c r="F408" s="5"/>
+    </row>
+    <row r="409" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A409" s="6"/>
+      <c r="C409" s="15" t="s">
+        <v>617</v>
+      </c>
+      <c r="D409" s="5">
+        <v>60017</v>
+      </c>
+      <c r="F409" s="5"/>
+    </row>
+    <row r="410" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A410" s="6">
+        <v>109</v>
+      </c>
+      <c r="B410" t="s">
+        <v>220</v>
+      </c>
+      <c r="C410" s="15" t="s">
+        <v>704</v>
+      </c>
+      <c r="D410" s="5">
+        <v>48043</v>
+      </c>
+      <c r="F410" s="5">
+        <v>63569</v>
+      </c>
+      <c r="G410" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H410" s="2">
+        <v>3</v>
+      </c>
+      <c r="I410" s="2">
+        <v>2</v>
+      </c>
+      <c r="J410" s="2">
+        <v>1</v>
+      </c>
+      <c r="K410" t="s">
+        <v>242</v>
+      </c>
+      <c r="L410" t="s">
+        <v>261</v>
+      </c>
+      <c r="M410" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="411" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A411" s="6"/>
+      <c r="C411" s="15" t="s">
+        <v>705</v>
+      </c>
+      <c r="D411" s="5">
+        <v>48590</v>
+      </c>
+      <c r="F411" s="5"/>
+    </row>
+    <row r="412" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A412" s="6"/>
+      <c r="C412" s="15" t="s">
+        <v>706</v>
+      </c>
+      <c r="D412" s="5">
+        <v>58901</v>
+      </c>
+      <c r="F412" s="5"/>
+    </row>
+    <row r="413" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A413" s="6">
+        <v>110</v>
+      </c>
+      <c r="B413" t="s">
+        <v>221</v>
+      </c>
+      <c r="C413" s="15" t="s">
+        <v>707</v>
+      </c>
+      <c r="D413" s="5">
+        <v>47140</v>
+      </c>
+      <c r="E413" t="s">
+        <v>229</v>
+      </c>
+      <c r="F413" s="5">
+        <v>63566</v>
+      </c>
+      <c r="G413" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="H413" s="2">
+        <v>4</v>
+      </c>
+      <c r="I413" s="2">
+        <v>2</v>
+      </c>
+      <c r="J413" s="2">
+        <v>2</v>
+      </c>
+      <c r="K413" t="s">
+        <v>242</v>
+      </c>
+      <c r="L413" t="s">
+        <v>295</v>
+      </c>
+      <c r="M413" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="414" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A414" s="6"/>
+      <c r="C414" s="15" t="s">
+        <v>708</v>
+      </c>
+      <c r="D414" s="5">
+        <v>49059</v>
+      </c>
+      <c r="F414" s="5"/>
+    </row>
+    <row r="415" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A415" s="6"/>
+      <c r="C415" s="15" t="s">
+        <v>709</v>
+      </c>
+      <c r="D415" s="5">
+        <v>59058</v>
+      </c>
+      <c r="F415" s="5"/>
+    </row>
+    <row r="416" spans="1:13" ht="18" x14ac:dyDescent="0.25">
+      <c r="A416" s="6"/>
+      <c r="C416" s="15" t="s">
         <v>710</v>
       </c>
-      <c r="D394" s="5">
+      <c r="D416" s="5">
         <v>62109</v>
       </c>
-      <c r="F394" s="5"/>
+      <c r="F416" s="5"/>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M388">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A3:M410">
     <sortCondition ref="A3"/>
   </sortState>
   <mergeCells count="5">
@@ -10019,7 +10368,7 @@
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G394" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G4:G416" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>$G$4:$G$71</formula1>
     </dataValidation>
   </dataValidations>
@@ -10033,7 +10382,7 @@
           <x14:formula1>
             <xm:f>Reasons!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K4:K394</xm:sqref>
+          <xm:sqref>K4:K416</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
